--- a/data/pink_sheet.xlsx
+++ b/data/pink_sheet.xlsx
@@ -17,13 +17,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +50,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,3741 +423,3741 @@
   <dimension ref="A1:QW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
-    <col width="25" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="25" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="25" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="25" customWidth="1" min="22" max="22"/>
-    <col width="25" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="25" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="25" customWidth="1" min="27" max="27"/>
-    <col width="25" customWidth="1" min="28" max="28"/>
-    <col width="25" customWidth="1" min="29" max="29"/>
-    <col width="25" customWidth="1" min="30" max="30"/>
-    <col width="25" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
-    <col width="25" customWidth="1" min="33" max="33"/>
-    <col width="25" customWidth="1" min="34" max="34"/>
-    <col width="19" customWidth="1" min="35" max="35"/>
-    <col width="25" customWidth="1" min="36" max="36"/>
-    <col width="25" customWidth="1" min="37" max="37"/>
-    <col width="25" customWidth="1" min="38" max="38"/>
-    <col width="25" customWidth="1" min="39" max="39"/>
-    <col width="25" customWidth="1" min="40" max="40"/>
-    <col width="25" customWidth="1" min="41" max="41"/>
-    <col width="25" customWidth="1" min="42" max="42"/>
-    <col width="25" customWidth="1" min="43" max="43"/>
-    <col width="25" customWidth="1" min="44" max="44"/>
-    <col width="25" customWidth="1" min="45" max="45"/>
-    <col width="25" customWidth="1" min="46" max="46"/>
-    <col width="25" customWidth="1" min="47" max="47"/>
-    <col width="25" customWidth="1" min="48" max="48"/>
-    <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="25" customWidth="1" min="50" max="50"/>
-    <col width="25" customWidth="1" min="51" max="51"/>
-    <col width="25" customWidth="1" min="52" max="52"/>
-    <col width="25" customWidth="1" min="53" max="53"/>
-    <col width="25" customWidth="1" min="54" max="54"/>
-    <col width="25" customWidth="1" min="55" max="55"/>
-    <col width="25" customWidth="1" min="56" max="56"/>
-    <col width="25" customWidth="1" min="57" max="57"/>
-    <col width="25" customWidth="1" min="58" max="58"/>
-    <col width="25" customWidth="1" min="59" max="59"/>
-    <col width="25" customWidth="1" min="60" max="60"/>
-    <col width="25" customWidth="1" min="61" max="61"/>
-    <col width="25" customWidth="1" min="62" max="62"/>
-    <col width="25" customWidth="1" min="63" max="63"/>
-    <col width="25" customWidth="1" min="64" max="64"/>
-    <col width="25" customWidth="1" min="65" max="65"/>
-    <col width="25" customWidth="1" min="66" max="66"/>
-    <col width="25" customWidth="1" min="67" max="67"/>
-    <col width="25" customWidth="1" min="68" max="68"/>
-    <col width="25" customWidth="1" min="69" max="69"/>
-    <col width="25" customWidth="1" min="70" max="70"/>
-    <col width="25" customWidth="1" min="71" max="71"/>
-    <col width="25" customWidth="1" min="72" max="72"/>
-    <col width="25" customWidth="1" min="73" max="73"/>
-    <col width="25" customWidth="1" min="74" max="74"/>
-    <col width="25" customWidth="1" min="75" max="75"/>
-    <col width="25" customWidth="1" min="76" max="76"/>
-    <col width="25" customWidth="1" min="77" max="77"/>
-    <col width="25" customWidth="1" min="78" max="78"/>
-    <col width="25" customWidth="1" min="79" max="79"/>
-    <col width="25" customWidth="1" min="80" max="80"/>
-    <col width="25" customWidth="1" min="81" max="81"/>
-    <col width="25" customWidth="1" min="82" max="82"/>
-    <col width="25" customWidth="1" min="83" max="83"/>
-    <col width="25" customWidth="1" min="84" max="84"/>
-    <col width="25" customWidth="1" min="85" max="85"/>
-    <col width="25" customWidth="1" min="86" max="86"/>
-    <col width="25" customWidth="1" min="87" max="87"/>
-    <col width="25" customWidth="1" min="88" max="88"/>
-    <col width="25" customWidth="1" min="89" max="89"/>
-    <col width="25" customWidth="1" min="90" max="90"/>
-    <col width="25" customWidth="1" min="91" max="91"/>
-    <col width="25" customWidth="1" min="92" max="92"/>
-    <col width="25" customWidth="1" min="93" max="93"/>
-    <col width="25" customWidth="1" min="94" max="94"/>
-    <col width="25" customWidth="1" min="95" max="95"/>
-    <col width="25" customWidth="1" min="96" max="96"/>
-    <col width="25" customWidth="1" min="97" max="97"/>
-    <col width="25" customWidth="1" min="98" max="98"/>
-    <col width="25" customWidth="1" min="99" max="99"/>
-    <col width="25" customWidth="1" min="100" max="100"/>
-    <col width="25" customWidth="1" min="101" max="101"/>
-    <col width="25" customWidth="1" min="102" max="102"/>
-    <col width="25" customWidth="1" min="103" max="103"/>
-    <col width="25" customWidth="1" min="104" max="104"/>
-    <col width="25" customWidth="1" min="105" max="105"/>
-    <col width="25" customWidth="1" min="106" max="106"/>
-    <col width="25" customWidth="1" min="107" max="107"/>
-    <col width="25" customWidth="1" min="108" max="108"/>
-    <col width="25" customWidth="1" min="109" max="109"/>
-    <col width="25" customWidth="1" min="110" max="110"/>
-    <col width="25" customWidth="1" min="111" max="111"/>
-    <col width="25" customWidth="1" min="112" max="112"/>
-    <col width="25" customWidth="1" min="113" max="113"/>
-    <col width="25" customWidth="1" min="114" max="114"/>
-    <col width="25" customWidth="1" min="115" max="115"/>
-    <col width="25" customWidth="1" min="116" max="116"/>
-    <col width="25" customWidth="1" min="117" max="117"/>
-    <col width="25" customWidth="1" min="118" max="118"/>
-    <col width="25" customWidth="1" min="119" max="119"/>
-    <col width="25" customWidth="1" min="120" max="120"/>
-    <col width="25" customWidth="1" min="121" max="121"/>
-    <col width="25" customWidth="1" min="122" max="122"/>
-    <col width="25" customWidth="1" min="123" max="123"/>
-    <col width="25" customWidth="1" min="124" max="124"/>
-    <col width="25" customWidth="1" min="125" max="125"/>
-    <col width="25" customWidth="1" min="126" max="126"/>
-    <col width="25" customWidth="1" min="127" max="127"/>
-    <col width="25" customWidth="1" min="128" max="128"/>
-    <col width="25" customWidth="1" min="129" max="129"/>
-    <col width="25" customWidth="1" min="130" max="130"/>
-    <col width="25" customWidth="1" min="131" max="131"/>
-    <col width="25" customWidth="1" min="132" max="132"/>
-    <col width="25" customWidth="1" min="133" max="133"/>
-    <col width="25" customWidth="1" min="134" max="134"/>
-    <col width="25" customWidth="1" min="135" max="135"/>
-    <col width="25" customWidth="1" min="136" max="136"/>
-    <col width="25" customWidth="1" min="137" max="137"/>
-    <col width="25" customWidth="1" min="138" max="138"/>
-    <col width="25" customWidth="1" min="139" max="139"/>
-    <col width="25" customWidth="1" min="140" max="140"/>
-    <col width="25" customWidth="1" min="141" max="141"/>
-    <col width="25" customWidth="1" min="142" max="142"/>
-    <col width="25" customWidth="1" min="143" max="143"/>
-    <col width="25" customWidth="1" min="144" max="144"/>
-    <col width="25" customWidth="1" min="145" max="145"/>
-    <col width="25" customWidth="1" min="146" max="146"/>
-    <col width="25" customWidth="1" min="147" max="147"/>
-    <col width="25" customWidth="1" min="148" max="148"/>
-    <col width="25" customWidth="1" min="149" max="149"/>
-    <col width="25" customWidth="1" min="150" max="150"/>
-    <col width="25" customWidth="1" min="151" max="151"/>
-    <col width="25" customWidth="1" min="152" max="152"/>
-    <col width="25" customWidth="1" min="153" max="153"/>
-    <col width="25" customWidth="1" min="154" max="154"/>
-    <col width="25" customWidth="1" min="155" max="155"/>
-    <col width="25" customWidth="1" min="156" max="156"/>
-    <col width="25" customWidth="1" min="157" max="157"/>
-    <col width="25" customWidth="1" min="158" max="158"/>
-    <col width="25" customWidth="1" min="159" max="159"/>
-    <col width="25" customWidth="1" min="160" max="160"/>
-    <col width="25" customWidth="1" min="161" max="161"/>
-    <col width="25" customWidth="1" min="162" max="162"/>
-    <col width="25" customWidth="1" min="163" max="163"/>
-    <col width="25" customWidth="1" min="164" max="164"/>
-    <col width="25" customWidth="1" min="165" max="165"/>
-    <col width="25" customWidth="1" min="166" max="166"/>
-    <col width="25" customWidth="1" min="167" max="167"/>
-    <col width="25" customWidth="1" min="168" max="168"/>
-    <col width="25" customWidth="1" min="169" max="169"/>
-    <col width="25" customWidth="1" min="170" max="170"/>
-    <col width="25" customWidth="1" min="171" max="171"/>
-    <col width="25" customWidth="1" min="172" max="172"/>
-    <col width="25" customWidth="1" min="173" max="173"/>
-    <col width="25" customWidth="1" min="174" max="174"/>
-    <col width="25" customWidth="1" min="175" max="175"/>
-    <col width="25" customWidth="1" min="176" max="176"/>
-    <col width="25" customWidth="1" min="177" max="177"/>
-    <col width="25" customWidth="1" min="178" max="178"/>
-    <col width="25" customWidth="1" min="179" max="179"/>
-    <col width="25" customWidth="1" min="180" max="180"/>
-    <col width="25" customWidth="1" min="181" max="181"/>
-    <col width="25" customWidth="1" min="182" max="182"/>
-    <col width="25" customWidth="1" min="183" max="183"/>
-    <col width="25" customWidth="1" min="184" max="184"/>
-    <col width="25" customWidth="1" min="185" max="185"/>
-    <col width="25" customWidth="1" min="186" max="186"/>
-    <col width="25" customWidth="1" min="187" max="187"/>
-    <col width="25" customWidth="1" min="188" max="188"/>
-    <col width="25" customWidth="1" min="189" max="189"/>
-    <col width="25" customWidth="1" min="190" max="190"/>
-    <col width="25" customWidth="1" min="191" max="191"/>
-    <col width="25" customWidth="1" min="192" max="192"/>
-    <col width="25" customWidth="1" min="193" max="193"/>
-    <col width="25" customWidth="1" min="194" max="194"/>
-    <col width="25" customWidth="1" min="195" max="195"/>
-    <col width="25" customWidth="1" min="196" max="196"/>
-    <col width="25" customWidth="1" min="197" max="197"/>
-    <col width="25" customWidth="1" min="198" max="198"/>
-    <col width="25" customWidth="1" min="199" max="199"/>
-    <col width="25" customWidth="1" min="200" max="200"/>
-    <col width="25" customWidth="1" min="201" max="201"/>
-    <col width="25" customWidth="1" min="202" max="202"/>
-    <col width="25" customWidth="1" min="203" max="203"/>
-    <col width="25" customWidth="1" min="204" max="204"/>
-    <col width="25" customWidth="1" min="205" max="205"/>
-    <col width="25" customWidth="1" min="206" max="206"/>
-    <col width="25" customWidth="1" min="207" max="207"/>
-    <col width="25" customWidth="1" min="208" max="208"/>
-    <col width="25" customWidth="1" min="209" max="209"/>
-    <col width="25" customWidth="1" min="210" max="210"/>
-    <col width="25" customWidth="1" min="211" max="211"/>
-    <col width="25" customWidth="1" min="212" max="212"/>
-    <col width="25" customWidth="1" min="213" max="213"/>
-    <col width="25" customWidth="1" min="214" max="214"/>
-    <col width="25" customWidth="1" min="215" max="215"/>
-    <col width="25" customWidth="1" min="216" max="216"/>
-    <col width="25" customWidth="1" min="217" max="217"/>
-    <col width="25" customWidth="1" min="218" max="218"/>
-    <col width="25" customWidth="1" min="219" max="219"/>
-    <col width="25" customWidth="1" min="220" max="220"/>
-    <col width="25" customWidth="1" min="221" max="221"/>
-    <col width="25" customWidth="1" min="222" max="222"/>
-    <col width="25" customWidth="1" min="223" max="223"/>
-    <col width="25" customWidth="1" min="224" max="224"/>
-    <col width="25" customWidth="1" min="225" max="225"/>
-    <col width="25" customWidth="1" min="226" max="226"/>
-    <col width="25" customWidth="1" min="227" max="227"/>
-    <col width="25" customWidth="1" min="228" max="228"/>
-    <col width="25" customWidth="1" min="229" max="229"/>
-    <col width="25" customWidth="1" min="230" max="230"/>
-    <col width="25" customWidth="1" min="231" max="231"/>
-    <col width="25" customWidth="1" min="232" max="232"/>
-    <col width="25" customWidth="1" min="233" max="233"/>
-    <col width="25" customWidth="1" min="234" max="234"/>
-    <col width="25" customWidth="1" min="235" max="235"/>
-    <col width="25" customWidth="1" min="236" max="236"/>
-    <col width="25" customWidth="1" min="237" max="237"/>
-    <col width="25" customWidth="1" min="238" max="238"/>
-    <col width="25" customWidth="1" min="239" max="239"/>
-    <col width="25" customWidth="1" min="240" max="240"/>
-    <col width="25" customWidth="1" min="241" max="241"/>
-    <col width="25" customWidth="1" min="242" max="242"/>
-    <col width="25" customWidth="1" min="243" max="243"/>
-    <col width="25" customWidth="1" min="244" max="244"/>
-    <col width="25" customWidth="1" min="245" max="245"/>
-    <col width="25" customWidth="1" min="246" max="246"/>
-    <col width="25" customWidth="1" min="247" max="247"/>
-    <col width="25" customWidth="1" min="248" max="248"/>
-    <col width="25" customWidth="1" min="249" max="249"/>
-    <col width="25" customWidth="1" min="250" max="250"/>
-    <col width="25" customWidth="1" min="251" max="251"/>
-    <col width="25" customWidth="1" min="252" max="252"/>
-    <col width="25" customWidth="1" min="253" max="253"/>
-    <col width="25" customWidth="1" min="254" max="254"/>
-    <col width="25" customWidth="1" min="255" max="255"/>
-    <col width="25" customWidth="1" min="256" max="256"/>
-    <col width="25" customWidth="1" min="257" max="257"/>
-    <col width="25" customWidth="1" min="258" max="258"/>
-    <col width="25" customWidth="1" min="259" max="259"/>
-    <col width="25" customWidth="1" min="260" max="260"/>
-    <col width="25" customWidth="1" min="261" max="261"/>
-    <col width="25" customWidth="1" min="262" max="262"/>
-    <col width="25" customWidth="1" min="263" max="263"/>
-    <col width="25" customWidth="1" min="264" max="264"/>
-    <col width="25" customWidth="1" min="265" max="265"/>
-    <col width="25" customWidth="1" min="266" max="266"/>
-    <col width="25" customWidth="1" min="267" max="267"/>
-    <col width="25" customWidth="1" min="268" max="268"/>
-    <col width="25" customWidth="1" min="269" max="269"/>
-    <col width="25" customWidth="1" min="270" max="270"/>
-    <col width="25" customWidth="1" min="271" max="271"/>
-    <col width="25" customWidth="1" min="272" max="272"/>
-    <col width="25" customWidth="1" min="273" max="273"/>
-    <col width="25" customWidth="1" min="274" max="274"/>
-    <col width="25" customWidth="1" min="275" max="275"/>
-    <col width="25" customWidth="1" min="276" max="276"/>
-    <col width="25" customWidth="1" min="277" max="277"/>
-    <col width="25" customWidth="1" min="278" max="278"/>
-    <col width="25" customWidth="1" min="279" max="279"/>
-    <col width="25" customWidth="1" min="280" max="280"/>
-    <col width="24" customWidth="1" min="281" max="281"/>
-    <col width="25" customWidth="1" min="282" max="282"/>
-    <col width="25" customWidth="1" min="283" max="283"/>
-    <col width="25" customWidth="1" min="284" max="284"/>
-    <col width="25" customWidth="1" min="285" max="285"/>
-    <col width="25" customWidth="1" min="286" max="286"/>
-    <col width="25" customWidth="1" min="287" max="287"/>
-    <col width="25" customWidth="1" min="288" max="288"/>
-    <col width="25" customWidth="1" min="289" max="289"/>
-    <col width="25" customWidth="1" min="290" max="290"/>
-    <col width="25" customWidth="1" min="291" max="291"/>
-    <col width="25" customWidth="1" min="292" max="292"/>
-    <col width="25" customWidth="1" min="293" max="293"/>
-    <col width="25" customWidth="1" min="294" max="294"/>
-    <col width="25" customWidth="1" min="295" max="295"/>
-    <col width="25" customWidth="1" min="296" max="296"/>
-    <col width="25" customWidth="1" min="297" max="297"/>
-    <col width="25" customWidth="1" min="298" max="298"/>
-    <col width="25" customWidth="1" min="299" max="299"/>
-    <col width="25" customWidth="1" min="300" max="300"/>
-    <col width="25" customWidth="1" min="301" max="301"/>
-    <col width="25" customWidth="1" min="302" max="302"/>
-    <col width="25" customWidth="1" min="303" max="303"/>
-    <col width="25" customWidth="1" min="304" max="304"/>
-    <col width="25" customWidth="1" min="305" max="305"/>
-    <col width="25" customWidth="1" min="306" max="306"/>
-    <col width="25" customWidth="1" min="307" max="307"/>
-    <col width="25" customWidth="1" min="308" max="308"/>
-    <col width="25" customWidth="1" min="309" max="309"/>
-    <col width="25" customWidth="1" min="310" max="310"/>
-    <col width="25" customWidth="1" min="311" max="311"/>
-    <col width="25" customWidth="1" min="312" max="312"/>
-    <col width="24" customWidth="1" min="313" max="313"/>
-    <col width="25" customWidth="1" min="314" max="314"/>
-    <col width="25" customWidth="1" min="315" max="315"/>
-    <col width="25" customWidth="1" min="316" max="316"/>
-    <col width="25" customWidth="1" min="317" max="317"/>
-    <col width="25" customWidth="1" min="318" max="318"/>
-    <col width="25" customWidth="1" min="319" max="319"/>
-    <col width="24" customWidth="1" min="320" max="320"/>
-    <col width="25" customWidth="1" min="321" max="321"/>
-    <col width="25" customWidth="1" min="322" max="322"/>
-    <col width="25" customWidth="1" min="323" max="323"/>
-    <col width="25" customWidth="1" min="324" max="324"/>
-    <col width="25" customWidth="1" min="325" max="325"/>
-    <col width="25" customWidth="1" min="326" max="326"/>
-    <col width="25" customWidth="1" min="327" max="327"/>
-    <col width="25" customWidth="1" min="328" max="328"/>
-    <col width="25" customWidth="1" min="329" max="329"/>
-    <col width="25" customWidth="1" min="330" max="330"/>
-    <col width="25" customWidth="1" min="331" max="331"/>
-    <col width="25" customWidth="1" min="332" max="332"/>
-    <col width="25" customWidth="1" min="333" max="333"/>
-    <col width="25" customWidth="1" min="334" max="334"/>
-    <col width="25" customWidth="1" min="335" max="335"/>
-    <col width="25" customWidth="1" min="336" max="336"/>
-    <col width="25" customWidth="1" min="337" max="337"/>
-    <col width="25" customWidth="1" min="338" max="338"/>
-    <col width="25" customWidth="1" min="339" max="339"/>
-    <col width="25" customWidth="1" min="340" max="340"/>
-    <col width="25" customWidth="1" min="341" max="341"/>
-    <col width="25" customWidth="1" min="342" max="342"/>
-    <col width="25" customWidth="1" min="343" max="343"/>
-    <col width="25" customWidth="1" min="344" max="344"/>
-    <col width="25" customWidth="1" min="345" max="345"/>
-    <col width="25" customWidth="1" min="346" max="346"/>
-    <col width="25" customWidth="1" min="347" max="347"/>
-    <col width="25" customWidth="1" min="348" max="348"/>
-    <col width="25" customWidth="1" min="349" max="349"/>
-    <col width="25" customWidth="1" min="350" max="350"/>
-    <col width="25" customWidth="1" min="351" max="351"/>
-    <col width="25" customWidth="1" min="352" max="352"/>
-    <col width="25" customWidth="1" min="353" max="353"/>
-    <col width="25" customWidth="1" min="354" max="354"/>
-    <col width="25" customWidth="1" min="355" max="355"/>
-    <col width="25" customWidth="1" min="356" max="356"/>
-    <col width="25" customWidth="1" min="357" max="357"/>
-    <col width="25" customWidth="1" min="358" max="358"/>
-    <col width="25" customWidth="1" min="359" max="359"/>
-    <col width="25" customWidth="1" min="360" max="360"/>
-    <col width="25" customWidth="1" min="361" max="361"/>
-    <col width="25" customWidth="1" min="362" max="362"/>
-    <col width="25" customWidth="1" min="363" max="363"/>
-    <col width="25" customWidth="1" min="364" max="364"/>
-    <col width="25" customWidth="1" min="365" max="365"/>
-    <col width="25" customWidth="1" min="366" max="366"/>
-    <col width="25" customWidth="1" min="367" max="367"/>
-    <col width="25" customWidth="1" min="368" max="368"/>
-    <col width="25" customWidth="1" min="369" max="369"/>
-    <col width="25" customWidth="1" min="370" max="370"/>
-    <col width="25" customWidth="1" min="371" max="371"/>
-    <col width="25" customWidth="1" min="372" max="372"/>
-    <col width="25" customWidth="1" min="373" max="373"/>
-    <col width="25" customWidth="1" min="374" max="374"/>
-    <col width="25" customWidth="1" min="375" max="375"/>
-    <col width="25" customWidth="1" min="376" max="376"/>
-    <col width="25" customWidth="1" min="377" max="377"/>
-    <col width="25" customWidth="1" min="378" max="378"/>
-    <col width="25" customWidth="1" min="379" max="379"/>
-    <col width="25" customWidth="1" min="380" max="380"/>
-    <col width="25" customWidth="1" min="381" max="381"/>
-    <col width="25" customWidth="1" min="382" max="382"/>
-    <col width="25" customWidth="1" min="383" max="383"/>
-    <col width="25" customWidth="1" min="384" max="384"/>
-    <col width="25" customWidth="1" min="385" max="385"/>
-    <col width="25" customWidth="1" min="386" max="386"/>
-    <col width="25" customWidth="1" min="387" max="387"/>
-    <col width="25" customWidth="1" min="388" max="388"/>
-    <col width="25" customWidth="1" min="389" max="389"/>
-    <col width="25" customWidth="1" min="390" max="390"/>
-    <col width="25" customWidth="1" min="391" max="391"/>
-    <col width="25" customWidth="1" min="392" max="392"/>
-    <col width="25" customWidth="1" min="393" max="393"/>
-    <col width="25" customWidth="1" min="394" max="394"/>
-    <col width="25" customWidth="1" min="395" max="395"/>
-    <col width="25" customWidth="1" min="396" max="396"/>
-    <col width="25" customWidth="1" min="397" max="397"/>
-    <col width="25" customWidth="1" min="398" max="398"/>
-    <col width="25" customWidth="1" min="399" max="399"/>
-    <col width="25" customWidth="1" min="400" max="400"/>
-    <col width="25" customWidth="1" min="401" max="401"/>
-    <col width="25" customWidth="1" min="402" max="402"/>
-    <col width="25" customWidth="1" min="403" max="403"/>
-    <col width="25" customWidth="1" min="404" max="404"/>
-    <col width="25" customWidth="1" min="405" max="405"/>
-    <col width="25" customWidth="1" min="406" max="406"/>
-    <col width="25" customWidth="1" min="407" max="407"/>
-    <col width="25" customWidth="1" min="408" max="408"/>
-    <col width="25" customWidth="1" min="409" max="409"/>
-    <col width="25" customWidth="1" min="410" max="410"/>
-    <col width="25" customWidth="1" min="411" max="411"/>
-    <col width="25" customWidth="1" min="412" max="412"/>
-    <col width="23" customWidth="1" min="413" max="413"/>
-    <col width="25" customWidth="1" min="414" max="414"/>
-    <col width="25" customWidth="1" min="415" max="415"/>
-    <col width="25" customWidth="1" min="416" max="416"/>
-    <col width="25" customWidth="1" min="417" max="417"/>
-    <col width="25" customWidth="1" min="418" max="418"/>
-    <col width="25" customWidth="1" min="419" max="419"/>
-    <col width="25" customWidth="1" min="420" max="420"/>
-    <col width="25" customWidth="1" min="421" max="421"/>
-    <col width="22" customWidth="1" min="422" max="422"/>
-    <col width="25" customWidth="1" min="423" max="423"/>
-    <col width="25" customWidth="1" min="424" max="424"/>
-    <col width="25" customWidth="1" min="425" max="425"/>
-    <col width="25" customWidth="1" min="426" max="426"/>
-    <col width="25" customWidth="1" min="427" max="427"/>
-    <col width="25" customWidth="1" min="428" max="428"/>
-    <col width="25" customWidth="1" min="429" max="429"/>
-    <col width="25" customWidth="1" min="430" max="430"/>
-    <col width="25" customWidth="1" min="431" max="431"/>
-    <col width="25" customWidth="1" min="432" max="432"/>
-    <col width="25" customWidth="1" min="433" max="433"/>
-    <col width="25" customWidth="1" min="434" max="434"/>
-    <col width="25" customWidth="1" min="435" max="435"/>
-    <col width="25" customWidth="1" min="436" max="436"/>
-    <col width="25" customWidth="1" min="437" max="437"/>
-    <col width="23" customWidth="1" min="438" max="438"/>
-    <col width="25" customWidth="1" min="439" max="439"/>
-    <col width="25" customWidth="1" min="440" max="440"/>
-    <col width="25" customWidth="1" min="441" max="441"/>
-    <col width="25" customWidth="1" min="442" max="442"/>
-    <col width="25" customWidth="1" min="443" max="443"/>
-    <col width="25" customWidth="1" min="444" max="444"/>
-    <col width="25" customWidth="1" min="445" max="445"/>
-    <col width="25" customWidth="1" min="446" max="446"/>
-    <col width="25" customWidth="1" min="447" max="447"/>
-    <col width="25" customWidth="1" min="448" max="448"/>
-    <col width="25" customWidth="1" min="449" max="449"/>
-    <col width="25" customWidth="1" min="450" max="450"/>
-    <col width="25" customWidth="1" min="451" max="451"/>
-    <col width="25" customWidth="1" min="452" max="452"/>
-    <col width="25" customWidth="1" min="453" max="453"/>
-    <col width="25" customWidth="1" min="454" max="454"/>
-    <col width="25" customWidth="1" min="455" max="455"/>
-    <col width="25" customWidth="1" min="456" max="456"/>
-    <col width="25" customWidth="1" min="457" max="457"/>
-    <col width="25" customWidth="1" min="458" max="458"/>
-    <col width="25" customWidth="1" min="459" max="459"/>
-    <col width="25" customWidth="1" min="460" max="460"/>
-    <col width="25" customWidth="1" min="461" max="461"/>
-    <col width="25" customWidth="1" min="462" max="462"/>
-    <col width="25" customWidth="1" min="463" max="463"/>
-    <col width="15" customWidth="1" min="464" max="464"/>
-    <col width="25" customWidth="1" min="465" max="465"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="10" customWidth="1" min="53" max="53"/>
+    <col width="10" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="10" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="10" customWidth="1" min="60" max="60"/>
+    <col width="10" customWidth="1" min="61" max="61"/>
+    <col width="10" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="10" customWidth="1" min="64" max="64"/>
+    <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="10" customWidth="1" min="66" max="66"/>
+    <col width="10" customWidth="1" min="67" max="67"/>
+    <col width="10" customWidth="1" min="68" max="68"/>
+    <col width="10" customWidth="1" min="69" max="69"/>
+    <col width="10" customWidth="1" min="70" max="70"/>
+    <col width="10" customWidth="1" min="71" max="71"/>
+    <col width="10" customWidth="1" min="72" max="72"/>
+    <col width="10" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
+    <col width="10" customWidth="1" min="75" max="75"/>
+    <col width="10" customWidth="1" min="76" max="76"/>
+    <col width="10" customWidth="1" min="77" max="77"/>
+    <col width="10" customWidth="1" min="78" max="78"/>
+    <col width="10" customWidth="1" min="79" max="79"/>
+    <col width="10" customWidth="1" min="80" max="80"/>
+    <col width="10" customWidth="1" min="81" max="81"/>
+    <col width="10" customWidth="1" min="82" max="82"/>
+    <col width="10" customWidth="1" min="83" max="83"/>
+    <col width="10" customWidth="1" min="84" max="84"/>
+    <col width="10" customWidth="1" min="85" max="85"/>
+    <col width="10" customWidth="1" min="86" max="86"/>
+    <col width="10" customWidth="1" min="87" max="87"/>
+    <col width="10" customWidth="1" min="88" max="88"/>
+    <col width="10" customWidth="1" min="89" max="89"/>
+    <col width="10" customWidth="1" min="90" max="90"/>
+    <col width="10" customWidth="1" min="91" max="91"/>
+    <col width="10" customWidth="1" min="92" max="92"/>
+    <col width="10" customWidth="1" min="93" max="93"/>
+    <col width="10" customWidth="1" min="94" max="94"/>
+    <col width="10" customWidth="1" min="95" max="95"/>
+    <col width="10" customWidth="1" min="96" max="96"/>
+    <col width="10" customWidth="1" min="97" max="97"/>
+    <col width="10" customWidth="1" min="98" max="98"/>
+    <col width="10" customWidth="1" min="99" max="99"/>
+    <col width="10" customWidth="1" min="100" max="100"/>
+    <col width="10" customWidth="1" min="101" max="101"/>
+    <col width="10" customWidth="1" min="102" max="102"/>
+    <col width="10" customWidth="1" min="103" max="103"/>
+    <col width="10" customWidth="1" min="104" max="104"/>
+    <col width="10" customWidth="1" min="105" max="105"/>
+    <col width="10" customWidth="1" min="106" max="106"/>
+    <col width="10" customWidth="1" min="107" max="107"/>
+    <col width="10" customWidth="1" min="108" max="108"/>
+    <col width="10" customWidth="1" min="109" max="109"/>
+    <col width="10" customWidth="1" min="110" max="110"/>
+    <col width="10" customWidth="1" min="111" max="111"/>
+    <col width="10" customWidth="1" min="112" max="112"/>
+    <col width="10" customWidth="1" min="113" max="113"/>
+    <col width="10" customWidth="1" min="114" max="114"/>
+    <col width="10" customWidth="1" min="115" max="115"/>
+    <col width="10" customWidth="1" min="116" max="116"/>
+    <col width="10" customWidth="1" min="117" max="117"/>
+    <col width="10" customWidth="1" min="118" max="118"/>
+    <col width="10" customWidth="1" min="119" max="119"/>
+    <col width="10" customWidth="1" min="120" max="120"/>
+    <col width="10" customWidth="1" min="121" max="121"/>
+    <col width="10" customWidth="1" min="122" max="122"/>
+    <col width="10" customWidth="1" min="123" max="123"/>
+    <col width="10" customWidth="1" min="124" max="124"/>
+    <col width="10" customWidth="1" min="125" max="125"/>
+    <col width="10" customWidth="1" min="126" max="126"/>
+    <col width="10" customWidth="1" min="127" max="127"/>
+    <col width="10" customWidth="1" min="128" max="128"/>
+    <col width="10" customWidth="1" min="129" max="129"/>
+    <col width="10" customWidth="1" min="130" max="130"/>
+    <col width="10" customWidth="1" min="131" max="131"/>
+    <col width="10" customWidth="1" min="132" max="132"/>
+    <col width="10" customWidth="1" min="133" max="133"/>
+    <col width="10" customWidth="1" min="134" max="134"/>
+    <col width="10" customWidth="1" min="135" max="135"/>
+    <col width="10" customWidth="1" min="136" max="136"/>
+    <col width="10" customWidth="1" min="137" max="137"/>
+    <col width="10" customWidth="1" min="138" max="138"/>
+    <col width="10" customWidth="1" min="139" max="139"/>
+    <col width="10" customWidth="1" min="140" max="140"/>
+    <col width="10" customWidth="1" min="141" max="141"/>
+    <col width="10" customWidth="1" min="142" max="142"/>
+    <col width="10" customWidth="1" min="143" max="143"/>
+    <col width="10" customWidth="1" min="144" max="144"/>
+    <col width="10" customWidth="1" min="145" max="145"/>
+    <col width="10" customWidth="1" min="146" max="146"/>
+    <col width="10" customWidth="1" min="147" max="147"/>
+    <col width="10" customWidth="1" min="148" max="148"/>
+    <col width="10" customWidth="1" min="149" max="149"/>
+    <col width="10" customWidth="1" min="150" max="150"/>
+    <col width="10" customWidth="1" min="151" max="151"/>
+    <col width="10" customWidth="1" min="152" max="152"/>
+    <col width="10" customWidth="1" min="153" max="153"/>
+    <col width="10" customWidth="1" min="154" max="154"/>
+    <col width="10" customWidth="1" min="155" max="155"/>
+    <col width="10" customWidth="1" min="156" max="156"/>
+    <col width="10" customWidth="1" min="157" max="157"/>
+    <col width="10" customWidth="1" min="158" max="158"/>
+    <col width="10" customWidth="1" min="159" max="159"/>
+    <col width="10" customWidth="1" min="160" max="160"/>
+    <col width="10" customWidth="1" min="161" max="161"/>
+    <col width="10" customWidth="1" min="162" max="162"/>
+    <col width="10" customWidth="1" min="163" max="163"/>
+    <col width="10" customWidth="1" min="164" max="164"/>
+    <col width="10" customWidth="1" min="165" max="165"/>
+    <col width="10" customWidth="1" min="166" max="166"/>
+    <col width="10" customWidth="1" min="167" max="167"/>
+    <col width="10" customWidth="1" min="168" max="168"/>
+    <col width="10" customWidth="1" min="169" max="169"/>
+    <col width="10" customWidth="1" min="170" max="170"/>
+    <col width="10" customWidth="1" min="171" max="171"/>
+    <col width="10" customWidth="1" min="172" max="172"/>
+    <col width="10" customWidth="1" min="173" max="173"/>
+    <col width="10" customWidth="1" min="174" max="174"/>
+    <col width="10" customWidth="1" min="175" max="175"/>
+    <col width="10" customWidth="1" min="176" max="176"/>
+    <col width="10" customWidth="1" min="177" max="177"/>
+    <col width="10" customWidth="1" min="178" max="178"/>
+    <col width="10" customWidth="1" min="179" max="179"/>
+    <col width="10" customWidth="1" min="180" max="180"/>
+    <col width="10" customWidth="1" min="181" max="181"/>
+    <col width="10" customWidth="1" min="182" max="182"/>
+    <col width="10" customWidth="1" min="183" max="183"/>
+    <col width="10" customWidth="1" min="184" max="184"/>
+    <col width="10" customWidth="1" min="185" max="185"/>
+    <col width="10" customWidth="1" min="186" max="186"/>
+    <col width="10" customWidth="1" min="187" max="187"/>
+    <col width="10" customWidth="1" min="188" max="188"/>
+    <col width="10" customWidth="1" min="189" max="189"/>
+    <col width="10" customWidth="1" min="190" max="190"/>
+    <col width="10" customWidth="1" min="191" max="191"/>
+    <col width="10" customWidth="1" min="192" max="192"/>
+    <col width="10" customWidth="1" min="193" max="193"/>
+    <col width="10" customWidth="1" min="194" max="194"/>
+    <col width="10" customWidth="1" min="195" max="195"/>
+    <col width="10" customWidth="1" min="196" max="196"/>
+    <col width="10" customWidth="1" min="197" max="197"/>
+    <col width="10" customWidth="1" min="198" max="198"/>
+    <col width="10" customWidth="1" min="199" max="199"/>
+    <col width="10" customWidth="1" min="200" max="200"/>
+    <col width="10" customWidth="1" min="201" max="201"/>
+    <col width="10" customWidth="1" min="202" max="202"/>
+    <col width="10" customWidth="1" min="203" max="203"/>
+    <col width="10" customWidth="1" min="204" max="204"/>
+    <col width="10" customWidth="1" min="205" max="205"/>
+    <col width="10" customWidth="1" min="206" max="206"/>
+    <col width="10" customWidth="1" min="207" max="207"/>
+    <col width="10" customWidth="1" min="208" max="208"/>
+    <col width="10" customWidth="1" min="209" max="209"/>
+    <col width="10" customWidth="1" min="210" max="210"/>
+    <col width="10" customWidth="1" min="211" max="211"/>
+    <col width="10" customWidth="1" min="212" max="212"/>
+    <col width="10" customWidth="1" min="213" max="213"/>
+    <col width="10" customWidth="1" min="214" max="214"/>
+    <col width="10" customWidth="1" min="215" max="215"/>
+    <col width="10" customWidth="1" min="216" max="216"/>
+    <col width="10" customWidth="1" min="217" max="217"/>
+    <col width="10" customWidth="1" min="218" max="218"/>
+    <col width="10" customWidth="1" min="219" max="219"/>
+    <col width="10" customWidth="1" min="220" max="220"/>
+    <col width="10" customWidth="1" min="221" max="221"/>
+    <col width="10" customWidth="1" min="222" max="222"/>
+    <col width="10" customWidth="1" min="223" max="223"/>
+    <col width="10" customWidth="1" min="224" max="224"/>
+    <col width="10" customWidth="1" min="225" max="225"/>
+    <col width="10" customWidth="1" min="226" max="226"/>
+    <col width="10" customWidth="1" min="227" max="227"/>
+    <col width="10" customWidth="1" min="228" max="228"/>
+    <col width="10" customWidth="1" min="229" max="229"/>
+    <col width="10" customWidth="1" min="230" max="230"/>
+    <col width="10" customWidth="1" min="231" max="231"/>
+    <col width="10" customWidth="1" min="232" max="232"/>
+    <col width="10" customWidth="1" min="233" max="233"/>
+    <col width="10" customWidth="1" min="234" max="234"/>
+    <col width="10" customWidth="1" min="235" max="235"/>
+    <col width="10" customWidth="1" min="236" max="236"/>
+    <col width="10" customWidth="1" min="237" max="237"/>
+    <col width="10" customWidth="1" min="238" max="238"/>
+    <col width="10" customWidth="1" min="239" max="239"/>
+    <col width="10" customWidth="1" min="240" max="240"/>
+    <col width="10" customWidth="1" min="241" max="241"/>
+    <col width="10" customWidth="1" min="242" max="242"/>
+    <col width="10" customWidth="1" min="243" max="243"/>
+    <col width="10" customWidth="1" min="244" max="244"/>
+    <col width="10" customWidth="1" min="245" max="245"/>
+    <col width="10" customWidth="1" min="246" max="246"/>
+    <col width="10" customWidth="1" min="247" max="247"/>
+    <col width="10" customWidth="1" min="248" max="248"/>
+    <col width="10" customWidth="1" min="249" max="249"/>
+    <col width="10" customWidth="1" min="250" max="250"/>
+    <col width="10" customWidth="1" min="251" max="251"/>
+    <col width="10" customWidth="1" min="252" max="252"/>
+    <col width="10" customWidth="1" min="253" max="253"/>
+    <col width="10" customWidth="1" min="254" max="254"/>
+    <col width="10" customWidth="1" min="255" max="255"/>
+    <col width="10" customWidth="1" min="256" max="256"/>
+    <col width="10" customWidth="1" min="257" max="257"/>
+    <col width="10" customWidth="1" min="258" max="258"/>
+    <col width="10" customWidth="1" min="259" max="259"/>
+    <col width="10" customWidth="1" min="260" max="260"/>
+    <col width="10" customWidth="1" min="261" max="261"/>
+    <col width="10" customWidth="1" min="262" max="262"/>
+    <col width="10" customWidth="1" min="263" max="263"/>
+    <col width="10" customWidth="1" min="264" max="264"/>
+    <col width="10" customWidth="1" min="265" max="265"/>
+    <col width="10" customWidth="1" min="266" max="266"/>
+    <col width="10" customWidth="1" min="267" max="267"/>
+    <col width="10" customWidth="1" min="268" max="268"/>
+    <col width="10" customWidth="1" min="269" max="269"/>
+    <col width="10" customWidth="1" min="270" max="270"/>
+    <col width="10" customWidth="1" min="271" max="271"/>
+    <col width="10" customWidth="1" min="272" max="272"/>
+    <col width="10" customWidth="1" min="273" max="273"/>
+    <col width="10" customWidth="1" min="274" max="274"/>
+    <col width="10" customWidth="1" min="275" max="275"/>
+    <col width="10" customWidth="1" min="276" max="276"/>
+    <col width="10" customWidth="1" min="277" max="277"/>
+    <col width="10" customWidth="1" min="278" max="278"/>
+    <col width="10" customWidth="1" min="279" max="279"/>
+    <col width="10" customWidth="1" min="280" max="280"/>
+    <col width="10" customWidth="1" min="281" max="281"/>
+    <col width="10" customWidth="1" min="282" max="282"/>
+    <col width="10" customWidth="1" min="283" max="283"/>
+    <col width="10" customWidth="1" min="284" max="284"/>
+    <col width="10" customWidth="1" min="285" max="285"/>
+    <col width="10" customWidth="1" min="286" max="286"/>
+    <col width="10" customWidth="1" min="287" max="287"/>
+    <col width="10" customWidth="1" min="288" max="288"/>
+    <col width="10" customWidth="1" min="289" max="289"/>
+    <col width="10" customWidth="1" min="290" max="290"/>
+    <col width="10" customWidth="1" min="291" max="291"/>
+    <col width="10" customWidth="1" min="292" max="292"/>
+    <col width="10" customWidth="1" min="293" max="293"/>
+    <col width="10" customWidth="1" min="294" max="294"/>
+    <col width="10" customWidth="1" min="295" max="295"/>
+    <col width="10" customWidth="1" min="296" max="296"/>
+    <col width="10" customWidth="1" min="297" max="297"/>
+    <col width="10" customWidth="1" min="298" max="298"/>
+    <col width="10" customWidth="1" min="299" max="299"/>
+    <col width="10" customWidth="1" min="300" max="300"/>
+    <col width="10" customWidth="1" min="301" max="301"/>
+    <col width="10" customWidth="1" min="302" max="302"/>
+    <col width="10" customWidth="1" min="303" max="303"/>
+    <col width="10" customWidth="1" min="304" max="304"/>
+    <col width="10" customWidth="1" min="305" max="305"/>
+    <col width="10" customWidth="1" min="306" max="306"/>
+    <col width="10" customWidth="1" min="307" max="307"/>
+    <col width="10" customWidth="1" min="308" max="308"/>
+    <col width="10" customWidth="1" min="309" max="309"/>
+    <col width="10" customWidth="1" min="310" max="310"/>
+    <col width="10" customWidth="1" min="311" max="311"/>
+    <col width="10" customWidth="1" min="312" max="312"/>
+    <col width="10" customWidth="1" min="313" max="313"/>
+    <col width="10" customWidth="1" min="314" max="314"/>
+    <col width="10" customWidth="1" min="315" max="315"/>
+    <col width="10" customWidth="1" min="316" max="316"/>
+    <col width="10" customWidth="1" min="317" max="317"/>
+    <col width="10" customWidth="1" min="318" max="318"/>
+    <col width="10" customWidth="1" min="319" max="319"/>
+    <col width="10" customWidth="1" min="320" max="320"/>
+    <col width="10" customWidth="1" min="321" max="321"/>
+    <col width="10" customWidth="1" min="322" max="322"/>
+    <col width="10" customWidth="1" min="323" max="323"/>
+    <col width="10" customWidth="1" min="324" max="324"/>
+    <col width="10" customWidth="1" min="325" max="325"/>
+    <col width="10" customWidth="1" min="326" max="326"/>
+    <col width="10" customWidth="1" min="327" max="327"/>
+    <col width="10" customWidth="1" min="328" max="328"/>
+    <col width="10" customWidth="1" min="329" max="329"/>
+    <col width="10" customWidth="1" min="330" max="330"/>
+    <col width="10" customWidth="1" min="331" max="331"/>
+    <col width="10" customWidth="1" min="332" max="332"/>
+    <col width="10" customWidth="1" min="333" max="333"/>
+    <col width="10" customWidth="1" min="334" max="334"/>
+    <col width="10" customWidth="1" min="335" max="335"/>
+    <col width="10" customWidth="1" min="336" max="336"/>
+    <col width="10" customWidth="1" min="337" max="337"/>
+    <col width="10" customWidth="1" min="338" max="338"/>
+    <col width="10" customWidth="1" min="339" max="339"/>
+    <col width="10" customWidth="1" min="340" max="340"/>
+    <col width="10" customWidth="1" min="341" max="341"/>
+    <col width="10" customWidth="1" min="342" max="342"/>
+    <col width="10" customWidth="1" min="343" max="343"/>
+    <col width="10" customWidth="1" min="344" max="344"/>
+    <col width="10" customWidth="1" min="345" max="345"/>
+    <col width="10" customWidth="1" min="346" max="346"/>
+    <col width="10" customWidth="1" min="347" max="347"/>
+    <col width="10" customWidth="1" min="348" max="348"/>
+    <col width="10" customWidth="1" min="349" max="349"/>
+    <col width="10" customWidth="1" min="350" max="350"/>
+    <col width="10" customWidth="1" min="351" max="351"/>
+    <col width="10" customWidth="1" min="352" max="352"/>
+    <col width="10" customWidth="1" min="353" max="353"/>
+    <col width="10" customWidth="1" min="354" max="354"/>
+    <col width="10" customWidth="1" min="355" max="355"/>
+    <col width="10" customWidth="1" min="356" max="356"/>
+    <col width="10" customWidth="1" min="357" max="357"/>
+    <col width="10" customWidth="1" min="358" max="358"/>
+    <col width="10" customWidth="1" min="359" max="359"/>
+    <col width="10" customWidth="1" min="360" max="360"/>
+    <col width="10" customWidth="1" min="361" max="361"/>
+    <col width="10" customWidth="1" min="362" max="362"/>
+    <col width="10" customWidth="1" min="363" max="363"/>
+    <col width="10" customWidth="1" min="364" max="364"/>
+    <col width="10" customWidth="1" min="365" max="365"/>
+    <col width="10" customWidth="1" min="366" max="366"/>
+    <col width="10" customWidth="1" min="367" max="367"/>
+    <col width="10" customWidth="1" min="368" max="368"/>
+    <col width="10" customWidth="1" min="369" max="369"/>
+    <col width="10" customWidth="1" min="370" max="370"/>
+    <col width="10" customWidth="1" min="371" max="371"/>
+    <col width="10" customWidth="1" min="372" max="372"/>
+    <col width="10" customWidth="1" min="373" max="373"/>
+    <col width="10" customWidth="1" min="374" max="374"/>
+    <col width="10" customWidth="1" min="375" max="375"/>
+    <col width="10" customWidth="1" min="376" max="376"/>
+    <col width="10" customWidth="1" min="377" max="377"/>
+    <col width="10" customWidth="1" min="378" max="378"/>
+    <col width="10" customWidth="1" min="379" max="379"/>
+    <col width="10" customWidth="1" min="380" max="380"/>
+    <col width="10" customWidth="1" min="381" max="381"/>
+    <col width="10" customWidth="1" min="382" max="382"/>
+    <col width="10" customWidth="1" min="383" max="383"/>
+    <col width="10" customWidth="1" min="384" max="384"/>
+    <col width="10" customWidth="1" min="385" max="385"/>
+    <col width="10" customWidth="1" min="386" max="386"/>
+    <col width="10" customWidth="1" min="387" max="387"/>
+    <col width="10" customWidth="1" min="388" max="388"/>
+    <col width="10" customWidth="1" min="389" max="389"/>
+    <col width="10" customWidth="1" min="390" max="390"/>
+    <col width="10" customWidth="1" min="391" max="391"/>
+    <col width="10" customWidth="1" min="392" max="392"/>
+    <col width="10" customWidth="1" min="393" max="393"/>
+    <col width="10" customWidth="1" min="394" max="394"/>
+    <col width="10" customWidth="1" min="395" max="395"/>
+    <col width="10" customWidth="1" min="396" max="396"/>
+    <col width="10" customWidth="1" min="397" max="397"/>
+    <col width="10" customWidth="1" min="398" max="398"/>
+    <col width="10" customWidth="1" min="399" max="399"/>
+    <col width="10" customWidth="1" min="400" max="400"/>
+    <col width="10" customWidth="1" min="401" max="401"/>
+    <col width="10" customWidth="1" min="402" max="402"/>
+    <col width="10" customWidth="1" min="403" max="403"/>
+    <col width="10" customWidth="1" min="404" max="404"/>
+    <col width="10" customWidth="1" min="405" max="405"/>
+    <col width="10" customWidth="1" min="406" max="406"/>
+    <col width="10" customWidth="1" min="407" max="407"/>
+    <col width="10" customWidth="1" min="408" max="408"/>
+    <col width="10" customWidth="1" min="409" max="409"/>
+    <col width="10" customWidth="1" min="410" max="410"/>
+    <col width="10" customWidth="1" min="411" max="411"/>
+    <col width="10" customWidth="1" min="412" max="412"/>
+    <col width="10" customWidth="1" min="413" max="413"/>
+    <col width="10" customWidth="1" min="414" max="414"/>
+    <col width="10" customWidth="1" min="415" max="415"/>
+    <col width="10" customWidth="1" min="416" max="416"/>
+    <col width="10" customWidth="1" min="417" max="417"/>
+    <col width="10" customWidth="1" min="418" max="418"/>
+    <col width="10" customWidth="1" min="419" max="419"/>
+    <col width="10" customWidth="1" min="420" max="420"/>
+    <col width="10" customWidth="1" min="421" max="421"/>
+    <col width="10" customWidth="1" min="422" max="422"/>
+    <col width="10" customWidth="1" min="423" max="423"/>
+    <col width="10" customWidth="1" min="424" max="424"/>
+    <col width="10" customWidth="1" min="425" max="425"/>
+    <col width="10" customWidth="1" min="426" max="426"/>
+    <col width="10" customWidth="1" min="427" max="427"/>
+    <col width="10" customWidth="1" min="428" max="428"/>
+    <col width="10" customWidth="1" min="429" max="429"/>
+    <col width="10" customWidth="1" min="430" max="430"/>
+    <col width="10" customWidth="1" min="431" max="431"/>
+    <col width="10" customWidth="1" min="432" max="432"/>
+    <col width="10" customWidth="1" min="433" max="433"/>
+    <col width="10" customWidth="1" min="434" max="434"/>
+    <col width="10" customWidth="1" min="435" max="435"/>
+    <col width="10" customWidth="1" min="436" max="436"/>
+    <col width="10" customWidth="1" min="437" max="437"/>
+    <col width="10" customWidth="1" min="438" max="438"/>
+    <col width="10" customWidth="1" min="439" max="439"/>
+    <col width="10" customWidth="1" min="440" max="440"/>
+    <col width="10" customWidth="1" min="441" max="441"/>
+    <col width="10" customWidth="1" min="442" max="442"/>
+    <col width="10" customWidth="1" min="443" max="443"/>
+    <col width="10" customWidth="1" min="444" max="444"/>
+    <col width="10" customWidth="1" min="445" max="445"/>
+    <col width="10" customWidth="1" min="446" max="446"/>
+    <col width="10" customWidth="1" min="447" max="447"/>
+    <col width="10" customWidth="1" min="448" max="448"/>
+    <col width="10" customWidth="1" min="449" max="449"/>
+    <col width="10" customWidth="1" min="450" max="450"/>
+    <col width="10" customWidth="1" min="451" max="451"/>
+    <col width="10" customWidth="1" min="452" max="452"/>
+    <col width="10" customWidth="1" min="453" max="453"/>
+    <col width="10" customWidth="1" min="454" max="454"/>
+    <col width="10" customWidth="1" min="455" max="455"/>
+    <col width="10" customWidth="1" min="456" max="456"/>
+    <col width="10" customWidth="1" min="457" max="457"/>
+    <col width="10" customWidth="1" min="458" max="458"/>
+    <col width="10" customWidth="1" min="459" max="459"/>
+    <col width="10" customWidth="1" min="460" max="460"/>
+    <col width="10" customWidth="1" min="461" max="461"/>
+    <col width="10" customWidth="1" min="462" max="462"/>
+    <col width="10" customWidth="1" min="463" max="463"/>
+    <col width="10" customWidth="1" min="464" max="464"/>
+    <col width="10" customWidth="1" min="465" max="465"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>96%Al Secondary Aluminum Ingots CIF Nansha Port China (USD/t)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>96%Al Secondary Aluminum Ingots CIF Ningbo Port China (USD/t)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>96%Al Secondary Aluminum Ingots CIF Qingdao Port China (USD/t)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>96%Al Secondary Aluminum Ingots CIF Qinzhou Port China (USD/t)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>98%Al Secondary Aluminum Ingots CIF Nansha Port China (USD/t)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>98%Al Secondary Aluminum Ingots CIF Ningbo Port China (USD/t)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>98%Al Secondary Aluminum Ingots CIF Qingdao Port China (USD/t)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>98%Al Secondary Aluminum Ingots CIF Qinzhou Port China (USD/t)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Al Secondary Aluminum Ingots CIF Nansha Port China (USD/t)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Al Secondary Aluminum Ingots CIF Ningbo Port China (USD/t)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Al Secondary Aluminum Ingots CIF Qingdao Port China (USD/t)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Al Secondary Aluminum Ingots CIF Qinzhou Port China (USD/t)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>SMM A00 Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SMM AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>SMM Chongqing A00 Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>SMM Chongqing AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>SMM Foshan A00 Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>SMM Foshan AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SMM Guangyuan A00 Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SMM Guangyuan AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>SMM Hangzhou A00 Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>SMM Hangzhou AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>SMM Henan A00 Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>SMM Henan AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SMM Linyi A00 Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SMM Linyi AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SMM Shenyang A00 Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>SMM Shenyang AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>SMM Southern China die-cast Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>SMM Tianjin A00 Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>SMM Tianjin AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>SMM Wuxi A00 Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>SMM Wuxi AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>UBC Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot A (USD/t)</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot A356 (USD/t)</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot A360 (USD/t)</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot A380 (USD/t)</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AC4B (USD/t)</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot ACB (USD/t)</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot ADC12 CIF Japan (USD/t)</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot ADC12 CIF Ningbo (USD/t)</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot ADCCIF Japan (USD/t)</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot ADCCIF Ningbo (USD/t)</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AlSi(Fe) (USD/t)</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AlSi10Mg(Fe) (USD/t)</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AlSi10MnMg (USD/t)</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AlSi12(Fe) (USD/t)</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AlSi9Cu3 (USD/t)</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AlSiCu (USD/t)</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AlSiMg(Fe) (USD/t)</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AlSiMnMg (USD/t)</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot ZLD (USD/t)</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot ZLD102 (USD/t)</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot ZLD104 (USD/t)</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>East China Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>East China Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Guizhou Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Guizhou Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Hunan Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Hunan Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Low-Carbon Aluminum Alloy Ingot A (USD/t)</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Low-Carbon Aluminum Alloy Ingot A356 (USD/t)</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Low-Carbon Aluminum Alloy Ingot ZLD (USD/t)</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>Low-Carbon Aluminum Alloy Ingot ZLD102 (USD/t)</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Low-Carbon Aluminum Alloy Ingot ZLD104 (USD/t)</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Malaysia Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Malaysia Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Malaysia Aluminum Alloy Ingot ADC12 FOB (USD/t)</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>Malaysia Aluminum Alloy Ingot ADCFOB (USD/t)</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>Ningbo Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Ningbo Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Northeast China Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Northeast China Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Recycled Low-Carbon Aluminum Alloy Ingot A (USD/t)</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>Recycled Low-Carbon Aluminum Alloy Ingot A356 (USD/t)</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>SMM Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SMM Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>South China Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>South China Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>Southwest China Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>Southwest China Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>Thailand Aluminum Alloy Ingot ADC12 FOB (USD/t)</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>Thailand Aluminum Alloy Ingot ADCFOB (USD/t)</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>Thailand aluminium Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>Thailand aluminium Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>Yunnan Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>Yunnan Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Low-Carbon P1020A Premium Index (USD/t)</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Low-Carbon PA Premium Index (USD/t)</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>SMM Aluminum Index (USD/t)</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>-series Low Carbon Double Zero Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>1-series Low Carbon Double Zero Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>1070 Aluminum Rod Premium (Inner Mongolia) (USD/t)</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>1070 Aluminum Rod Premium (Yunan) (USD/t)</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>12μ C-Coated Li Battery Al Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>12μ Li Battery Al Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>13μ C-Coated Li Battery Al Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>13μ Li Battery Al Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>15μ Li Battery Al Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>8-series Low Carbon Double Zero Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>Aluminium P1020A premium, DDP Midwest US (USD/t)</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>Aluminium PA premium, DDP Midwest US (USD/t)</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>Aluminum P0610A Premium FOB Indonesia (USD/t)</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>Aluminum P1020A Premium FOB Indonesia (USD/t)</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>Aluminum P1020A Premium in-whs dp Rotterdam (USD/t)</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>Aluminum P1020A Premium in-whs dup Rotterdam (USD/t)</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>Aluminum PA Premium FOB Indonesia (USD/t)</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>Aluminum PA Premium in-whs dp Rotterdam (USD/t)</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>Aluminum PA Premium in-whs dup Rotterdam (USD/t)</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Premium CIF Shanghai (USD/t)</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Premium CIF South Korea (USD/t)</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Premium CIF Thailand (USD/t)</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Premium FCA South Korea (USD/t)</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Premium In-whs Shanghai (USD/t)</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Quarterly Premium CIF Japan (USD/t)</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Rod Premium (Inner Mongolia) (USD/t)</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Rod Premium (Yunan) (USD/t)</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Spot Premium CIF Japan (USD/t)</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>Baotou φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>Baotou φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>Baotou φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>Baotou φAluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>Foshan 6061 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>Foshan 6082 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>Foshan Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>Foshan φ100 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>Foshan φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>Foshan φ150 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>Foshan φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>Foshan φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>Foshan φAluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>Guangdong /Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>Guangdong 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>Guangdong 6101/6201 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>Guangdong 8030 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>Guangdong 99.70% Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>Guangdong AAluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>Guangdong Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>Guangdong Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>Hebei 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>Hebei AAluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>Henan /Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>Henan 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>Henan 6101/6201 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>Henan 8030 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>Henan 99.70% Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>Henan AAluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>Henan Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>Henan Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>Henan φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>Henan φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>Henan φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>Henan φAluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>Inner Mongolia 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>Inner Mongolia 99.70% Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>Inner Mongolia AAluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>Inner Mongolia Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>Jiangsu 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>Jiangsu AAluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>Linyi φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>Linyi φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>Linyi φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>Linyi φAluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>Nanchang φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>Nanchang φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FM1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>Nanchang φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FN1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>Nanchang φAluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FO1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>Photovoltaic Frame Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FP1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>SMM A00 Aluminum Ingot Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FQ1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>SMM AAluminum Ingot Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FR1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>SMM Foshan A00 Aluminum Ingot Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FS1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>SMM Foshan AAluminum Ingot Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FT1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>SMM Guangyuan A00 Aluminum Ingot Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FU1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>SMM Guangyuan AAluminum Ingot Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FV1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>SMM Henan A00 Aluminum Ingot Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FW1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>SMM Henan AAluminum Ingot Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FX1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>Shandong /Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FY1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>Shandong 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FZ1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>Shandong 61.5% IACS High-conductivity Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GA1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>Shandong 6101/6201 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GB1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>Shandong 62.5% IACS High-conductivity Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GC1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>Shandong 8030 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GD1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>Shandong 99.70% Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GE1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>Shandong AAluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GF1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>Shandong Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GG1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>Shandong Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GH1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>Shandong IACS High-conductivity Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GI1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>Wuxi 6061 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GJ1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>Wuxi 6082 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GK1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>Wuxi Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GL1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>Wuxi φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GM1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>Wuxi φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GN1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>Wuxi φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GO1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>Wuxi φAluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GP1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>Xinjiang φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GQ1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>Xinjiang φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GR1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>Xinjiang φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GS1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>Xinjiang φAluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GT1" t="inlineStr">
+      <c r="GT1" s="1" t="inlineStr">
         <is>
           <t>Yuannan Low Carbon /Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GU1" t="inlineStr">
+      <c r="GU1" s="1" t="inlineStr">
         <is>
           <t>Yuannan Low Carbon 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GV1" t="inlineStr">
+      <c r="GV1" s="1" t="inlineStr">
         <is>
           <t>Yuannan Low Carbon 6101/6201 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GW1" t="inlineStr">
+      <c r="GW1" s="1" t="inlineStr">
         <is>
           <t>Yuannan Low Carbon 8030 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GX1" t="inlineStr">
+      <c r="GX1" s="1" t="inlineStr">
         <is>
           <t>Yuannan Low Carbon AAluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GY1" t="inlineStr">
+      <c r="GY1" s="1" t="inlineStr">
         <is>
           <t>Yuannan Low Carbon Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GZ1" t="inlineStr">
+      <c r="GZ1" s="1" t="inlineStr">
         <is>
           <t>Yunan Low Carbon φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="HA1" t="inlineStr">
+      <c r="HA1" s="1" t="inlineStr">
         <is>
           <t>Yunan Low Carbon φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="HB1" t="inlineStr">
+      <c r="HB1" s="1" t="inlineStr">
         <is>
           <t>Yunan Low Carbon φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="HC1" t="inlineStr">
+      <c r="HC1" s="1" t="inlineStr">
         <is>
           <t>Yunan Low Carbon φAluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="HD1" t="inlineStr">
+      <c r="HD1" s="1" t="inlineStr">
         <is>
           <t>μ C-Coated Li Battery Al Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="HE1" t="inlineStr">
+      <c r="HE1" s="1" t="inlineStr">
         <is>
           <t>μ Li Battery Al Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="HF1" t="inlineStr">
+      <c r="HF1" s="1" t="inlineStr">
         <is>
           <t>3N High-Purity Alumina (Al₂O₃≥99.9%, 1um＜D50≤5um) (USD/t)</t>
         </is>
       </c>
-      <c r="HG1" t="inlineStr">
+      <c r="HG1" s="1" t="inlineStr">
         <is>
           <t>3N High-Purity Alumina (Al₂O₃≥99.9%, D50=0.4μm) (USD/t)</t>
         </is>
       </c>
-      <c r="HH1" t="inlineStr">
+      <c r="HH1" s="1" t="inlineStr">
         <is>
           <t>3N High-Purity Alumina (Al₂O₃≥99.9%, D50=0.8um) (USD/t)</t>
         </is>
       </c>
-      <c r="HI1" t="inlineStr">
+      <c r="HI1" s="1" t="inlineStr">
         <is>
           <t>3N High-Purity Alumina (Al₂O₃≥99.9%, D50=1um) (USD/t)</t>
         </is>
       </c>
-      <c r="HJ1" t="inlineStr">
+      <c r="HJ1" s="1" t="inlineStr">
         <is>
           <t>4N High-Purity Alumina (Al₂O₃≥99.99%, 0.5um＜D50≤1um) (USD/t)</t>
         </is>
       </c>
-      <c r="HK1" t="inlineStr">
+      <c r="HK1" s="1" t="inlineStr">
         <is>
           <t>4N High-Purity Alumina (Al₂O₃≥99.99%, 1um＜D50≤3um) (USD/t)</t>
         </is>
       </c>
-      <c r="HL1" t="inlineStr">
+      <c r="HL1" s="1" t="inlineStr">
         <is>
           <t>4N High-Purity Alumina (Al₂O₃≥99.99%, 3um＜D50≤5um) (USD/t)</t>
         </is>
       </c>
-      <c r="HM1" t="inlineStr">
+      <c r="HM1" s="1" t="inlineStr">
         <is>
           <t>4N High-Purity Alumina (Al₂O₃≥99.99%, D50=0.1um and D97=0.3um) (USD/t)</t>
         </is>
       </c>
-      <c r="HN1" t="inlineStr">
+      <c r="HN1" s="1" t="inlineStr">
         <is>
           <t>4N5 High-Purity Alumina (Al₂O₃≥99.995%, 30um＜D50≤40um) (USD/t)</t>
         </is>
       </c>
-      <c r="HO1" t="inlineStr">
+      <c r="HO1" s="1" t="inlineStr">
         <is>
           <t>5N High-Purity Alumina (Al₂O₃≥99.999%, 0.2um≤D50≤3um) (USD/t)</t>
         </is>
       </c>
-      <c r="HP1" t="inlineStr">
+      <c r="HP1" s="1" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥) FOB Brazil (USD/t)</t>
         </is>
       </c>
-      <c r="HQ1" t="inlineStr">
+      <c r="HQ1" s="1" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥) FOB Easten Australia (USD/t)</t>
         </is>
       </c>
-      <c r="HR1" t="inlineStr">
+      <c r="HR1" s="1" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥) FOB Vietnam (USD/t)</t>
         </is>
       </c>
-      <c r="HS1" t="inlineStr">
+      <c r="HS1" s="1" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥) FOB Western Australia (USD/t)</t>
         </is>
       </c>
-      <c r="HT1" t="inlineStr">
+      <c r="HT1" s="1" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥) Fob Indonesia (USD/t)</t>
         </is>
       </c>
-      <c r="HU1" t="inlineStr">
+      <c r="HU1" s="1" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥98.5%) FOB Brazil (USD/t)</t>
         </is>
       </c>
-      <c r="HV1" t="inlineStr">
+      <c r="HV1" s="1" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥98.5%) FOB Easten Australia (USD/t)</t>
         </is>
       </c>
-      <c r="HW1" t="inlineStr">
+      <c r="HW1" s="1" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥98.5%) FOB Vietnam (USD/t)</t>
         </is>
       </c>
-      <c r="HX1" t="inlineStr">
+      <c r="HX1" s="1" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥98.5%) FOB Western Australia (USD/t)</t>
         </is>
       </c>
-      <c r="HY1" t="inlineStr">
+      <c r="HY1" s="1" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥98.5%) Fob Indonesia (USD/t)</t>
         </is>
       </c>
-      <c r="HZ1" t="inlineStr">
+      <c r="HZ1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Hydroxide (USD/t)</t>
         </is>
       </c>
-      <c r="IA1" t="inlineStr">
+      <c r="IA1" s="1" t="inlineStr">
         <is>
           <t>Australia Bauxite (High-Temperature) CIF China (USD/t)</t>
         </is>
       </c>
-      <c r="IB1" t="inlineStr">
+      <c r="IB1" s="1" t="inlineStr">
         <is>
           <t>Australia Bauxite (Low-Temperature) CIF China (USD/t)</t>
         </is>
       </c>
-      <c r="IC1" t="inlineStr">
+      <c r="IC1" s="1" t="inlineStr">
         <is>
           <t>Bauxite CFR Turkey (USD/t)</t>
         </is>
       </c>
-      <c r="ID1" t="inlineStr">
+      <c r="ID1" s="1" t="inlineStr">
         <is>
           <t>Bauxite FOB Guinea (USD/t)</t>
         </is>
       </c>
-      <c r="IE1" t="inlineStr">
+      <c r="IE1" s="1" t="inlineStr">
         <is>
           <t>China Aluminum Hydroxide (USD/t)</t>
         </is>
       </c>
-      <c r="IF1" t="inlineStr">
+      <c r="IF1" s="1" t="inlineStr">
         <is>
           <t>Guangxi Aluminum Hydroxide (USD/t)</t>
         </is>
       </c>
-      <c r="IG1" t="inlineStr">
+      <c r="IG1" s="1" t="inlineStr">
         <is>
           <t>Guangxi Bauxite (A/S ratio , Al₂O₃ ) (USD/t)</t>
         </is>
       </c>
-      <c r="IH1" t="inlineStr">
+      <c r="IH1" s="1" t="inlineStr">
         <is>
           <t>Guangxi Bauxite (A/S ratio 6, Al₂O₃ 53%) (USD/t)</t>
         </is>
       </c>
-      <c r="II1" t="inlineStr">
+      <c r="II1" s="1" t="inlineStr">
         <is>
           <t>Guangxi Bauxite (A/S ratio 7, Al₂O₃ 53%) (USD/t)</t>
         </is>
       </c>
-      <c r="IJ1" t="inlineStr">
+      <c r="IJ1" s="1" t="inlineStr">
         <is>
           <t>Guinean Bauxite CIF China (USD/t)</t>
         </is>
       </c>
-      <c r="IK1" t="inlineStr">
+      <c r="IK1" s="1" t="inlineStr">
         <is>
           <t>Guiyang Bauxite (A/S ratio , Al₂O₃ ) (USD/t)</t>
         </is>
       </c>
-      <c r="IL1" t="inlineStr">
+      <c r="IL1" s="1" t="inlineStr">
         <is>
           <t>Guiyang Bauxite (A/S ratio 6, Al₂O₃ 60%) (USD/t)</t>
         </is>
       </c>
-      <c r="IM1" t="inlineStr">
+      <c r="IM1" s="1" t="inlineStr">
         <is>
           <t>Guizhou Aluminum Hydroxide (USD/t)</t>
         </is>
       </c>
-      <c r="IN1" t="inlineStr">
+      <c r="IN1" s="1" t="inlineStr">
         <is>
           <t>Guizhou Bauxite (USD/t)</t>
         </is>
       </c>
-      <c r="IO1" t="inlineStr">
+      <c r="IO1" s="1" t="inlineStr">
         <is>
           <t>Guizhou Bauxite (A/S ratio , Al₂O₃ ) (USD/t)</t>
         </is>
       </c>
-      <c r="IP1" t="inlineStr">
+      <c r="IP1" s="1" t="inlineStr">
         <is>
           <t>Guizhou Bauxite (A/S ratio 5.5, Al₂O₃ 58%) (USD/t)</t>
         </is>
       </c>
-      <c r="IQ1" t="inlineStr">
+      <c r="IQ1" s="1" t="inlineStr">
         <is>
           <t>Henan Aluminum Hydroxide (USD/t)</t>
         </is>
       </c>
-      <c r="IR1" t="inlineStr">
+      <c r="IR1" s="1" t="inlineStr">
         <is>
           <t>Henan Bauxite (A/S ratio , Al₂O₃ ) (USD/t)</t>
         </is>
       </c>
-      <c r="IS1" t="inlineStr">
+      <c r="IS1" s="1" t="inlineStr">
         <is>
           <t>Henan Bauxite (A/S ratio 5, Al₂O₃ 60%) (USD/t)</t>
         </is>
       </c>
-      <c r="IT1" t="inlineStr">
+      <c r="IT1" s="1" t="inlineStr">
         <is>
           <t>Henan Bauxite (A/S ratio 6, Al₂O₃ 62%) (USD/t)</t>
         </is>
       </c>
-      <c r="IU1" t="inlineStr">
+      <c r="IU1" s="1" t="inlineStr">
         <is>
           <t>High - Purity Alumina (USD/t)</t>
         </is>
       </c>
-      <c r="IV1" t="inlineStr">
+      <c r="IV1" s="1" t="inlineStr">
         <is>
           <t>Indonesia Bauxite (USD/t)</t>
         </is>
       </c>
-      <c r="IW1" t="inlineStr">
+      <c r="IW1" s="1" t="inlineStr">
         <is>
           <t>Malaysia Bauxite CIF China (USD/t)</t>
         </is>
       </c>
-      <c r="IX1" t="inlineStr">
+      <c r="IX1" s="1" t="inlineStr">
         <is>
           <t>Malaysia Washed Bauxite CIF China (USD/t)</t>
         </is>
       </c>
-      <c r="IY1" t="inlineStr">
+      <c r="IY1" s="1" t="inlineStr">
         <is>
           <t>N High-Purity Alumina (Al₂O₃≥, D=um and D=um) (USD/t)</t>
         </is>
       </c>
-      <c r="IZ1" t="inlineStr">
+      <c r="IZ1" s="1" t="inlineStr">
         <is>
           <t>N High-Purity Alumina (Al₂O₃≥, D=um) (USD/t)</t>
         </is>
       </c>
-      <c r="JA1" t="inlineStr">
+      <c r="JA1" s="1" t="inlineStr">
         <is>
           <t>N High-Purity Alumina (Al₂O₃≥, D=μm) (USD/t)</t>
         </is>
       </c>
-      <c r="JB1" t="inlineStr">
+      <c r="JB1" s="1" t="inlineStr">
         <is>
           <t>N High-Purity Alumina (Al₂O₃≥, um≤D≤um) (USD/t)</t>
         </is>
       </c>
-      <c r="JC1" t="inlineStr">
+      <c r="JC1" s="1" t="inlineStr">
         <is>
           <t>N High-Purity Alumina (Al₂O₃≥, um＜D≤um) (USD/t)</t>
         </is>
       </c>
-      <c r="JD1" t="inlineStr">
+      <c r="JD1" s="1" t="inlineStr">
         <is>
           <t>NHigh-Purity Alumina (Al₂O₃≥, um＜D≤um) (USD/t)</t>
         </is>
       </c>
-      <c r="JE1" t="inlineStr">
+      <c r="JE1" s="1" t="inlineStr">
         <is>
           <t>SMM Bayuquan Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JF1" t="inlineStr">
+      <c r="JF1" s="1" t="inlineStr">
         <is>
           <t>SMM Bayuquan Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="JG1" t="inlineStr">
+      <c r="JG1" s="1" t="inlineStr">
         <is>
           <t>SMM Guangxi Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JH1" t="inlineStr">
+      <c r="JH1" s="1" t="inlineStr">
         <is>
           <t>SMM Guangxi Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="JI1" t="inlineStr">
+      <c r="JI1" s="1" t="inlineStr">
         <is>
           <t>SMM Guizhou Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JJ1" t="inlineStr">
+      <c r="JJ1" s="1" t="inlineStr">
         <is>
           <t>SMM Guizhou Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="JK1" t="inlineStr">
+      <c r="JK1" s="1" t="inlineStr">
         <is>
           <t>SMM Henan Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JL1" t="inlineStr">
+      <c r="JL1" s="1" t="inlineStr">
         <is>
           <t>SMM Henan Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="JM1" t="inlineStr">
+      <c r="JM1" s="1" t="inlineStr">
         <is>
           <t>SMM Lianyungang Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JN1" t="inlineStr">
+      <c r="JN1" s="1" t="inlineStr">
         <is>
           <t>SMM Lianyungang Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="JO1" t="inlineStr">
+      <c r="JO1" s="1" t="inlineStr">
         <is>
           <t>SMM Shandong Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JP1" t="inlineStr">
+      <c r="JP1" s="1" t="inlineStr">
         <is>
           <t>SMM Shandong Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="JQ1" t="inlineStr">
+      <c r="JQ1" s="1" t="inlineStr">
         <is>
           <t>SMM Shanxi Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JR1" t="inlineStr">
+      <c r="JR1" s="1" t="inlineStr">
         <is>
           <t>SMM Shanxi Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="JS1" t="inlineStr">
+      <c r="JS1" s="1" t="inlineStr">
         <is>
           <t>Shandong Aluminum Hydroxide (USD/t)</t>
         </is>
       </c>
-      <c r="JT1" t="inlineStr">
+      <c r="JT1" s="1" t="inlineStr">
         <is>
           <t>Shanxi Aluminum Hydroxide (USD/t)</t>
         </is>
       </c>
-      <c r="JU1" t="inlineStr">
+      <c r="JU1" s="1" t="inlineStr">
         <is>
           <t>Shanxi Bauxite (USD/t)</t>
         </is>
       </c>
-      <c r="JV1" t="inlineStr">
+      <c r="JV1" s="1" t="inlineStr">
         <is>
           <t>Shanxi Bauxite (A/S ratio , Al₂O₃ ) (USD/t)</t>
         </is>
       </c>
-      <c r="JW1" t="inlineStr">
+      <c r="JW1" s="1" t="inlineStr">
         <is>
           <t>Shanxi Bauxite (A/S ratio 5, Al₂O₃ 60%) (USD/t)</t>
         </is>
       </c>
-      <c r="JX1" t="inlineStr">
+      <c r="JX1" s="1" t="inlineStr">
         <is>
           <t>The Republic of Ghana Bauxite CIF China (USD/t)</t>
         </is>
       </c>
-      <c r="JY1" t="inlineStr">
+      <c r="JY1" s="1" t="inlineStr">
         <is>
           <t>SMM Alumina Index (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JZ1" t="inlineStr">
+      <c r="JZ1" s="1" t="inlineStr">
         <is>
           <t>SMM Alumina Index (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="KA1" t="inlineStr">
+      <c r="KA1" s="1" t="inlineStr">
         <is>
           <t>SMM Bauxite Index (USD/t)</t>
         </is>
       </c>
-      <c r="KB1" t="inlineStr">
+      <c r="KB1" s="1" t="inlineStr">
         <is>
           <t>SMM Guangxi Alumina Index (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="KC1" t="inlineStr">
+      <c r="KC1" s="1" t="inlineStr">
         <is>
           <t>SMM Guangxi Alumina Index (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="KD1" t="inlineStr">
+      <c r="KD1" s="1" t="inlineStr">
         <is>
           <t>SMM Guizhou Alumina Index (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="KE1" t="inlineStr">
+      <c r="KE1" s="1" t="inlineStr">
         <is>
           <t>SMM Guizhou Alumina Index (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="KF1" t="inlineStr">
+      <c r="KF1" s="1" t="inlineStr">
         <is>
           <t>SMM Henan Alumina Index (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="KG1" t="inlineStr">
+      <c r="KG1" s="1" t="inlineStr">
         <is>
           <t>SMM Henan Alumina Index (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="KH1" t="inlineStr">
+      <c r="KH1" s="1" t="inlineStr">
         <is>
           <t>SMM Shandong Alumina Index (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="KI1" t="inlineStr">
+      <c r="KI1" s="1" t="inlineStr">
         <is>
           <t>SMM Shandong Alumina Index (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="KJ1" t="inlineStr">
+      <c r="KJ1" s="1" t="inlineStr">
         <is>
           <t>SMM Shanxi Alumina Index (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="KK1" t="inlineStr">
+      <c r="KK1" s="1" t="inlineStr">
         <is>
           <t>SMM Shanxi Alumina Index (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="KL1" t="inlineStr">
+      <c r="KL1" s="1" t="inlineStr">
         <is>
           <t>East China High Sulfur Ordinary Calcined Petroleum Coke (USD/t)</t>
         </is>
       </c>
-      <c r="KM1" t="inlineStr">
+      <c r="KM1" s="1" t="inlineStr">
         <is>
           <t>East China Medium-High Sulfur Low Vanadium Calcined Petroleum Coke (USD/t)</t>
         </is>
       </c>
-      <c r="KN1" t="inlineStr">
+      <c r="KN1" s="1" t="inlineStr">
         <is>
           <t>East China Medium-High Sulfur Ordinary Calcined Petroleum Coke (USD/t)</t>
         </is>
       </c>
-      <c r="KO1" t="inlineStr">
+      <c r="KO1" s="1" t="inlineStr">
         <is>
           <t>East China Medium-Sulfur Low Vanadium Calcined Petroleum Coke (USD/t)</t>
         </is>
       </c>
-      <c r="KP1" t="inlineStr">
+      <c r="KP1" s="1" t="inlineStr">
         <is>
           <t>East China Medium-Sulfur Ordinary Calcined Petroleum Coke (USD/t)</t>
         </is>
       </c>
-      <c r="KQ1" t="inlineStr">
+      <c r="KQ1" s="1" t="inlineStr">
         <is>
           <t>Northeast China Low-Sulfur Calcined Petroleum Coke (USD/t)</t>
         </is>
       </c>
-      <c r="KR1" t="inlineStr">
+      <c r="KR1" s="1" t="inlineStr">
         <is>
           <t>Northeast China SMM # Petroleum Coke Spot price Index (USD/t)</t>
         </is>
       </c>
-      <c r="KS1" t="inlineStr">
+      <c r="KS1" s="1" t="inlineStr">
         <is>
           <t>Northeast China SMM 1# Petroleum Coke Spot price Index (USD/t)</t>
         </is>
       </c>
-      <c r="KT1" t="inlineStr">
+      <c r="KT1" s="1" t="inlineStr">
         <is>
           <t>Northwest China SMM # Petroleum Coke Spot Price Index (USD/t)</t>
         </is>
       </c>
-      <c r="KU1" t="inlineStr">
+      <c r="KU1" s="1" t="inlineStr">
         <is>
           <t>Northwest China SMM 3# Petroleum Coke Spot Price Index (USD/t)</t>
         </is>
       </c>
-      <c r="KV1" t="inlineStr">
+      <c r="KV1" s="1" t="inlineStr">
         <is>
           <t>Petroleum Coke Index (USD/t)</t>
         </is>
       </c>
-      <c r="KW1" t="inlineStr">
+      <c r="KW1" s="1" t="inlineStr">
         <is>
           <t>Shandong SMM # Petroleum Coke Spot price Index (USD/t)</t>
         </is>
       </c>
-      <c r="KX1" t="inlineStr">
+      <c r="KX1" s="1" t="inlineStr">
         <is>
           <t>Shandong SMM 2# Petroleum Coke Spot price Index (USD/t)</t>
         </is>
       </c>
-      <c r="KY1" t="inlineStr">
+      <c r="KY1" s="1" t="inlineStr">
         <is>
           <t>Shandong SMM 3# Petroleum Coke Spot price Index (USD/t)</t>
         </is>
       </c>
-      <c r="KZ1" t="inlineStr">
+      <c r="KZ1" s="1" t="inlineStr">
         <is>
           <t>Shandong SMM 4# Petroleum Coke Spot price Index (USD/t)</t>
         </is>
       </c>
-      <c r="LA1" t="inlineStr">
+      <c r="LA1" s="1" t="inlineStr">
         <is>
           <t>Coal Tar Pitch (USD/t)</t>
         </is>
       </c>
-      <c r="LB1" t="inlineStr">
+      <c r="LB1" s="1" t="inlineStr">
         <is>
           <t>Coal tar pitch (Hebei) (USD/t)</t>
         </is>
       </c>
-      <c r="LC1" t="inlineStr">
+      <c r="LC1" s="1" t="inlineStr">
         <is>
           <t>Coal tar pitch (Shandong) (USD/t)</t>
         </is>
       </c>
-      <c r="LD1" t="inlineStr">
+      <c r="LD1" s="1" t="inlineStr">
         <is>
           <t>Coal tar pitch (Shanxi) (USD/t)</t>
         </is>
       </c>
-      <c r="LE1" t="inlineStr">
+      <c r="LE1" s="1" t="inlineStr">
         <is>
           <t>Central China Prebaked Anode (USD/t)</t>
         </is>
       </c>
-      <c r="LF1" t="inlineStr">
+      <c r="LF1" s="1" t="inlineStr">
         <is>
           <t>East China Prebaked Anode (USD/t)</t>
         </is>
       </c>
-      <c r="LG1" t="inlineStr">
+      <c r="LG1" s="1" t="inlineStr">
         <is>
           <t>Northwest China Prebaked Anode (USD/t)</t>
         </is>
       </c>
-      <c r="LH1" t="inlineStr">
+      <c r="LH1" s="1" t="inlineStr">
         <is>
           <t>Prebaked Anode (USD/t)</t>
         </is>
       </c>
-      <c r="LI1" t="inlineStr">
+      <c r="LI1" s="1" t="inlineStr">
         <is>
           <t>Prebaked Anode for High-Purity Aluminum FOB China (USD/t)</t>
         </is>
       </c>
-      <c r="LJ1" t="inlineStr">
+      <c r="LJ1" s="1" t="inlineStr">
         <is>
           <t>Prebaked Anode for High-end Aluminum FOB China (USD/t)</t>
         </is>
       </c>
-      <c r="LK1" t="inlineStr">
+      <c r="LK1" s="1" t="inlineStr">
         <is>
           <t>Southwest China Prebaked Anode (USD/t)</t>
         </is>
       </c>
-      <c r="LL1" t="inlineStr">
+      <c r="LL1" s="1" t="inlineStr">
         <is>
           <t>5182 Aluminum Alloy Sheets and Strips Used for Motor (USD/t)</t>
         </is>
       </c>
-      <c r="LM1" t="inlineStr">
+      <c r="LM1" s="1" t="inlineStr">
         <is>
           <t>5754 Aluminum Alloy Sheets and Strips Used for Motor (USD/t)</t>
         </is>
       </c>
-      <c r="LN1" t="inlineStr">
+      <c r="LN1" s="1" t="inlineStr">
         <is>
           <t>6061 Aluminum Alloy Sheets and Strips Used for Motor (USD/t)</t>
         </is>
       </c>
-      <c r="LO1" t="inlineStr">
+      <c r="LO1" s="1" t="inlineStr">
         <is>
           <t>Al-Ti-B Wires A, Aluminum Based Master Alloy (USD/t)</t>
         </is>
       </c>
-      <c r="LP1" t="inlineStr">
+      <c r="LP1" s="1" t="inlineStr">
         <is>
           <t>Al-Ti-B Wires B, Aluminum Based Master Alloy (USD/t)</t>
         </is>
       </c>
-      <c r="LQ1" t="inlineStr">
+      <c r="LQ1" s="1" t="inlineStr">
         <is>
           <t>Al-Ti-B Wires C, Aluminum Based Master Alloy (USD/t)</t>
         </is>
       </c>
-      <c r="LR1" t="inlineStr">
+      <c r="LR1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Alloy Sheets and Strips Used for Motor (USD/t)</t>
         </is>
       </c>
-      <c r="LS1" t="inlineStr">
+      <c r="LS1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Based Master Alloy (USD/t)</t>
         </is>
       </c>
-      <c r="LT1" t="inlineStr">
+      <c r="LT1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Based Master Alloy AlSi (USD/t)</t>
         </is>
       </c>
-      <c r="LU1" t="inlineStr">
+      <c r="LU1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Based Master Alloy AlSi12 (USD/t)</t>
         </is>
       </c>
-      <c r="LV1" t="inlineStr">
+      <c r="LV1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Based Master Alloy AlSi20 (USD/t)</t>
         </is>
       </c>
-      <c r="LW1" t="inlineStr">
+      <c r="LW1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Based Master Alloy AlSi50 (USD/t)</t>
         </is>
       </c>
-      <c r="LX1" t="inlineStr">
+      <c r="LX1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Strontium Alloy AlSr (USD/t)</t>
         </is>
       </c>
-      <c r="LY1" t="inlineStr">
+      <c r="LY1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Strontium Alloy AlSr10 (USD/t)</t>
         </is>
       </c>
-      <c r="LZ1" t="inlineStr">
+      <c r="LZ1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MA1" t="inlineStr">
+      <c r="MA1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.2-0.25% Foshan Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MB1" t="inlineStr">
+      <c r="MB1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.2-0.25% Hubei Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MC1" t="inlineStr">
+      <c r="MC1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.2-0.25% Linyi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MD1" t="inlineStr">
+      <c r="MD1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.2-0.25% Nanchang Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="ME1" t="inlineStr">
+      <c r="ME1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.2-0.25% Wuxi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MF1" t="inlineStr">
+      <c r="MF1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.2-0.25% Xuchang Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MG1" t="inlineStr">
+      <c r="MG1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.25-0.35% Foshan Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MH1" t="inlineStr">
+      <c r="MH1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.25-0.35% Hubei Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MI1" t="inlineStr">
+      <c r="MI1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.25-0.35% Linyi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MJ1" t="inlineStr">
+      <c r="MJ1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.25-0.35% Nanchang Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MK1" t="inlineStr">
+      <c r="MK1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.25-0.35% Wuxi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="ML1" t="inlineStr">
+      <c r="ML1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.25-0.35% Xuchang Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MM1" t="inlineStr">
+      <c r="MM1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.35-0.5% Foshan Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MN1" t="inlineStr">
+      <c r="MN1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.35-0.5% Hubei Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MO1" t="inlineStr">
+      <c r="MO1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.35-0.5% Linyi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MP1" t="inlineStr">
+      <c r="MP1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.35-0.5% Nanchang Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MQ1" t="inlineStr">
+      <c r="MQ1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.35-0.5% Wuxi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MR1" t="inlineStr">
+      <c r="MR1" s="1" t="inlineStr">
         <is>
           <t>Fe 0.35-0.5% Xuchang Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MS1" t="inlineStr">
+      <c r="MS1" s="1" t="inlineStr">
         <is>
           <t>Fe Foshan Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MT1" t="inlineStr">
+      <c r="MT1" s="1" t="inlineStr">
         <is>
           <t>Fe Hubei Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MU1" t="inlineStr">
+      <c r="MU1" s="1" t="inlineStr">
         <is>
           <t>Fe Linyi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MV1" t="inlineStr">
+      <c r="MV1" s="1" t="inlineStr">
         <is>
           <t>Fe Nanchang Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MW1" t="inlineStr">
+      <c r="MW1" s="1" t="inlineStr">
         <is>
           <t>Fe Wuxi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MX1" t="inlineStr">
+      <c r="MX1" s="1" t="inlineStr">
         <is>
           <t>Fe Xuchang Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MY1" t="inlineStr">
+      <c r="MY1" s="1" t="inlineStr">
         <is>
           <t>Foshan Aluminum Extrusions Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MZ1" t="inlineStr">
+      <c r="MZ1" s="1" t="inlineStr">
         <is>
           <t>Low Carbon φ120 Aluminum Billet (USD/t)</t>
         </is>
       </c>
-      <c r="NA1" t="inlineStr">
+      <c r="NA1" s="1" t="inlineStr">
         <is>
           <t>Low Carbon φ178 Aluminum Billet (USD/t)</t>
         </is>
       </c>
-      <c r="NB1" t="inlineStr">
+      <c r="NB1" s="1" t="inlineStr">
         <is>
           <t>Low Carbon φ90 Aluminum Billet (USD/t)</t>
         </is>
       </c>
-      <c r="NC1" t="inlineStr">
+      <c r="NC1" s="1" t="inlineStr">
         <is>
           <t>Low Carbon φAluminum Billet (USD/t)</t>
         </is>
       </c>
-      <c r="ND1" t="inlineStr">
+      <c r="ND1" s="1" t="inlineStr">
         <is>
           <t>Nanchang Aluminum Extrusions Billet (USD/t)</t>
         </is>
       </c>
-      <c r="NE1" t="inlineStr">
+      <c r="NE1" s="1" t="inlineStr">
         <is>
           <t>Remelting Billet (USD/t)</t>
         </is>
       </c>
-      <c r="NF1" t="inlineStr">
+      <c r="NF1" s="1" t="inlineStr">
         <is>
           <t>Shandong Aluminum Extrusions Billet (USD/t)</t>
         </is>
       </c>
-      <c r="NG1" t="inlineStr">
+      <c r="NG1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Cast - rolled Coil (USD/t)</t>
         </is>
       </c>
-      <c r="NH1" t="inlineStr">
+      <c r="NH1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NI1" t="inlineStr">
+      <c r="NI1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Extrusions formwork (USD/t)</t>
         </is>
       </c>
-      <c r="NJ1" t="inlineStr">
+      <c r="NJ1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Extrusions formwork (Lease) (USD/t)</t>
         </is>
       </c>
-      <c r="NK1" t="inlineStr">
+      <c r="NK1" s="1" t="inlineStr">
         <is>
           <t>Foshan Anodized Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NL1" t="inlineStr">
+      <c r="NL1" s="1" t="inlineStr">
         <is>
           <t>Foshan Surface Electrophoresis Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NM1" t="inlineStr">
+      <c r="NM1" s="1" t="inlineStr">
         <is>
           <t>Foshan Surface Sprayed Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NN1" t="inlineStr">
+      <c r="NN1" s="1" t="inlineStr">
         <is>
           <t>Foshan Thermal Break Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NO1" t="inlineStr">
+      <c r="NO1" s="1" t="inlineStr">
         <is>
           <t>Jiangxi Anodized Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NP1" t="inlineStr">
+      <c r="NP1" s="1" t="inlineStr">
         <is>
           <t>Nanchang Surface Electrophoresis Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NQ1" t="inlineStr">
+      <c r="NQ1" s="1" t="inlineStr">
         <is>
           <t>Nanchang Surface Sprayed Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NR1" t="inlineStr">
+      <c r="NR1" s="1" t="inlineStr">
         <is>
           <t>Nanchang Thermal Break Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NS1" t="inlineStr">
+      <c r="NS1" s="1" t="inlineStr">
         <is>
           <t>Shandong Anodized Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NT1" t="inlineStr">
+      <c r="NT1" s="1" t="inlineStr">
         <is>
           <t>Shandong Surface Electrophoresis Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NU1" t="inlineStr">
+      <c r="NU1" s="1" t="inlineStr">
         <is>
           <t>Shandong Surface Sprayed Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NV1" t="inlineStr">
+      <c r="NV1" s="1" t="inlineStr">
         <is>
           <t>Shandong Thermal Break Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NW1" t="inlineStr">
+      <c r="NW1" s="1" t="inlineStr">
         <is>
           <t>-series Secondary Aluminum Plate/Sheet and Strip (USD/t)</t>
         </is>
       </c>
-      <c r="NX1" t="inlineStr">
+      <c r="NX1" s="1" t="inlineStr">
         <is>
           <t>1-series Secondary Aluminum Plate/Sheet and Strip (USD/t)</t>
         </is>
       </c>
-      <c r="NY1" t="inlineStr">
+      <c r="NY1" s="1" t="inlineStr">
         <is>
           <t>3-series Secondary Aluminum Plate/Sheet and Strip (USD/t)</t>
         </is>
       </c>
-      <c r="NZ1" t="inlineStr">
+      <c r="NZ1" s="1" t="inlineStr">
         <is>
           <t>3003 Aluminum Plate/Sheet and Strip for Battery Case (USD/t)</t>
         </is>
       </c>
-      <c r="OA1" t="inlineStr">
+      <c r="OA1" s="1" t="inlineStr">
         <is>
           <t>5-series Secondary Aluminum Plate/Sheet and Strip (USD/t)</t>
         </is>
       </c>
-      <c r="OB1" t="inlineStr">
+      <c r="OB1" s="1" t="inlineStr">
         <is>
           <t>6-series Secondary Aluminum Plate/Sheet and Strip (USD/t)</t>
         </is>
       </c>
-      <c r="OC1" t="inlineStr">
+      <c r="OC1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Plate / Sheet and Strip (USD/t)</t>
         </is>
       </c>
-      <c r="OD1" t="inlineStr">
+      <c r="OD1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Plate/Sheet and Strip for Battery Case (USD/t)</t>
         </is>
       </c>
-      <c r="OE1" t="inlineStr">
+      <c r="OE1" s="1" t="inlineStr">
         <is>
           <t>Henan /Presensitized Plate Substrate (USD/t)</t>
         </is>
       </c>
-      <c r="OF1" t="inlineStr">
+      <c r="OF1" s="1" t="inlineStr">
         <is>
           <t>Henan 1050/1060 Presensitized Plate Substrate (USD/t)</t>
         </is>
       </c>
-      <c r="OG1" t="inlineStr">
+      <c r="OG1" s="1" t="inlineStr">
         <is>
           <t>Henan 1100 Decorative Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OH1" t="inlineStr">
+      <c r="OH1" s="1" t="inlineStr">
         <is>
           <t>Henan 3003 Oil Tank Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OI1" t="inlineStr">
+      <c r="OI1" s="1" t="inlineStr">
         <is>
           <t>Henan Decorative Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OJ1" t="inlineStr">
+      <c r="OJ1" s="1" t="inlineStr">
         <is>
           <t>Henan Oil Tank Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OK1" t="inlineStr">
+      <c r="OK1" s="1" t="inlineStr">
         <is>
           <t>Neimenggu /Presensitized Plate Substrate (USD/t)</t>
         </is>
       </c>
-      <c r="OL1" t="inlineStr">
+      <c r="OL1" s="1" t="inlineStr">
         <is>
           <t>Neimenggu 1050/1060 Presensitized Plate Substrate (USD/t)</t>
         </is>
       </c>
-      <c r="OM1" t="inlineStr">
+      <c r="OM1" s="1" t="inlineStr">
         <is>
           <t>Neimenggu 1100 Decorative Plate (USD/t)</t>
         </is>
       </c>
-      <c r="ON1" t="inlineStr">
+      <c r="ON1" s="1" t="inlineStr">
         <is>
           <t>Neimenggu 3003 Oil Tank Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OO1" t="inlineStr">
+      <c r="OO1" s="1" t="inlineStr">
         <is>
           <t>Neimenggu Decorative Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OP1" t="inlineStr">
+      <c r="OP1" s="1" t="inlineStr">
         <is>
           <t>Neimenggu Oil Tank Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OQ1" t="inlineStr">
+      <c r="OQ1" s="1" t="inlineStr">
         <is>
           <t>Shandong /Presensitized Plate Substrate (USD/t)</t>
         </is>
       </c>
-      <c r="OR1" t="inlineStr">
+      <c r="OR1" s="1" t="inlineStr">
         <is>
           <t>Shandong 1050/1060 Presensitized Plate Substrate (USD/t)</t>
         </is>
       </c>
-      <c r="OS1" t="inlineStr">
+      <c r="OS1" s="1" t="inlineStr">
         <is>
           <t>Shandong 1100 Decorative Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OT1" t="inlineStr">
+      <c r="OT1" s="1" t="inlineStr">
         <is>
           <t>Shandong 3003 Oil Tank Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OU1" t="inlineStr">
+      <c r="OU1" s="1" t="inlineStr">
         <is>
           <t>Shandong Decorative Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OV1" t="inlineStr">
+      <c r="OV1" s="1" t="inlineStr">
         <is>
           <t>Shandong Oil Tank Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OW1" t="inlineStr">
+      <c r="OW1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Foil (USD/t)</t>
         </is>
       </c>
-      <c r="OX1" t="inlineStr">
+      <c r="OX1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Foil Processing Fee (USD/t)</t>
         </is>
       </c>
-      <c r="OY1" t="inlineStr">
+      <c r="OY1" s="1" t="inlineStr">
         <is>
           <t>Carbon-Coated Lithium Battery Aluminum Foil (12μ) (USD/t)</t>
         </is>
       </c>
-      <c r="OZ1" t="inlineStr">
+      <c r="OZ1" s="1" t="inlineStr">
         <is>
           <t>Carbon-Coated Lithium Battery Aluminum Foil (13μ) (USD/t)</t>
         </is>
       </c>
-      <c r="PA1" t="inlineStr">
+      <c r="PA1" s="1" t="inlineStr">
         <is>
           <t>Carbon-Coated Lithium Battery Aluminum Foil (μ) (USD/t)</t>
         </is>
       </c>
-      <c r="PB1" t="inlineStr">
+      <c r="PB1" s="1" t="inlineStr">
         <is>
           <t>Lithium Battery Aluminum Foil (12μ) (USD/t)</t>
         </is>
       </c>
-      <c r="PC1" t="inlineStr">
+      <c r="PC1" s="1" t="inlineStr">
         <is>
           <t>Lithium Battery Aluminum Foil (13μ) (USD/t)</t>
         </is>
       </c>
-      <c r="PD1" t="inlineStr">
+      <c r="PD1" s="1" t="inlineStr">
         <is>
           <t>Lithium Battery Aluminum Foil (15μ) (USD/t)</t>
         </is>
       </c>
-      <c r="PE1" t="inlineStr">
+      <c r="PE1" s="1" t="inlineStr">
         <is>
           <t>Lithium Battery Aluminum Foil (μ) (USD/t)</t>
         </is>
       </c>
-      <c r="PF1" t="inlineStr">
+      <c r="PF1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Rod (USD/t)</t>
         </is>
       </c>
-      <c r="PG1" t="inlineStr">
+      <c r="PG1" s="1" t="inlineStr">
         <is>
           <t>Low Carbon /Aluminum Rod (Guangdong) (USD/t)</t>
         </is>
       </c>
-      <c r="PH1" t="inlineStr">
+      <c r="PH1" s="1" t="inlineStr">
         <is>
           <t>Low Carbon 1A60 Aluminum Rod (Guangdong) (USD/t)</t>
         </is>
       </c>
-      <c r="PI1" t="inlineStr">
+      <c r="PI1" s="1" t="inlineStr">
         <is>
           <t>Low Carbon 6101/6201 Aluminum Rod (Guangdong) (USD/t)</t>
         </is>
       </c>
-      <c r="PJ1" t="inlineStr">
+      <c r="PJ1" s="1" t="inlineStr">
         <is>
           <t>Low Carbon 8030 Aluminum Rod (Guangdong) (USD/t)</t>
         </is>
       </c>
-      <c r="PK1" t="inlineStr">
+      <c r="PK1" s="1" t="inlineStr">
         <is>
           <t>Low Carbon AAluminum Rod (Guangdong) (USD/t)</t>
         </is>
       </c>
-      <c r="PL1" t="inlineStr">
+      <c r="PL1" s="1" t="inlineStr">
         <is>
           <t>Low Carbon Aluminum Rod (Guangdong) (USD/t)</t>
         </is>
       </c>
-      <c r="PM1" t="inlineStr">
+      <c r="PM1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Scrap quotations outside China (USD/t)</t>
         </is>
       </c>
-      <c r="PN1" t="inlineStr">
+      <c r="PN1" s="1" t="inlineStr">
         <is>
           <t>Malaysia Scrap Mixed Aluminium Castings (Tense) (USD/t)</t>
         </is>
       </c>
-      <c r="PO1" t="inlineStr">
+      <c r="PO1" s="1" t="inlineStr">
         <is>
           <t>Ningbo Port Imported Twitch Scrap (USD/t)</t>
         </is>
       </c>
-      <c r="PP1" t="inlineStr">
+      <c r="PP1" s="1" t="inlineStr">
         <is>
           <t>Scrap Mixed Aluminium Castings (Tense) FOB Malaysia (USD/t)</t>
         </is>
       </c>
-      <c r="PQ1" t="inlineStr">
+      <c r="PQ1" s="1" t="inlineStr">
         <is>
           <t>Tianjin Port Imported Twitch Scrap (USD/t)</t>
         </is>
       </c>
-      <c r="PR1" t="inlineStr">
+      <c r="PR1" s="1" t="inlineStr">
         <is>
           <t>99.70% Deoxidized Aluminum Granules (Guangdong) (USD/t)</t>
         </is>
       </c>
-      <c r="PS1" t="inlineStr">
+      <c r="PS1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Low-Carbon P1020A (USD/t)</t>
         </is>
       </c>
-      <c r="PT1" t="inlineStr">
+      <c r="PT1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Low-Carbon PA (USD/t)</t>
         </is>
       </c>
-      <c r="PU1" t="inlineStr">
+      <c r="PU1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Powder (USD/t)</t>
         </is>
       </c>
-      <c r="PV1" t="inlineStr">
+      <c r="PV1" s="1" t="inlineStr">
         <is>
           <t>Aluminum Slab (USD/t)</t>
         </is>
       </c>
-      <c r="PW1" t="inlineStr">
+      <c r="PW1" s="1" t="inlineStr">
         <is>
           <t>Aluminum fluoride (USD/t)</t>
         </is>
       </c>
-      <c r="PX1" t="inlineStr">
+      <c r="PX1" s="1" t="inlineStr">
         <is>
           <t>Aluminum import arbitrage(AL) (USD/t)</t>
         </is>
       </c>
-      <c r="PY1" t="inlineStr">
+      <c r="PY1" s="1" t="inlineStr">
         <is>
           <t>Aluminum import arbitrage(AL) CNY/mt (USD/t)</t>
         </is>
       </c>
-      <c r="PZ1" t="inlineStr">
+      <c r="PZ1" s="1" t="inlineStr">
         <is>
           <t>Aluminum import arbitrage(Spot) (USD/t)</t>
         </is>
       </c>
-      <c r="QA1" t="inlineStr">
+      <c r="QA1" s="1" t="inlineStr">
         <is>
           <t>Aluminum import arbitrage(Spot) CNY/mt (USD/t)</t>
         </is>
       </c>
-      <c r="QB1" t="inlineStr">
+      <c r="QB1" s="1" t="inlineStr">
         <is>
           <t>Deoxidized Aluminum Granules (Guangdong) (USD/t)</t>
         </is>
       </c>
-      <c r="QC1" t="inlineStr">
+      <c r="QC1" s="1" t="inlineStr">
         <is>
           <t>LME Name Unit Open High Low Latest Change Vol. LMEselect Aluminum Month USD/mt (USD/t)</t>
         </is>
       </c>
-      <c r="QD1" t="inlineStr">
+      <c r="QD1" s="1" t="inlineStr">
         <is>
           <t>LMEselect Aluminum Month (USD/t)</t>
         </is>
       </c>
-      <c r="QE1" t="inlineStr">
+      <c r="QE1" s="1" t="inlineStr">
         <is>
           <t>LMEselect Aluminum Month USD/mt (USD/t)</t>
         </is>
       </c>
-      <c r="QF1" t="inlineStr">
+      <c r="QF1" s="1" t="inlineStr">
         <is>
           <t>Name Unit Open High Low Latest Change Vol. LMEselect Aluminum Month USD/mt (USD/t)</t>
         </is>
       </c>
-      <c r="QG1" t="inlineStr">
+      <c r="QG1" s="1" t="inlineStr">
         <is>
           <t>SMM Aluminum Spot/LME M (USD/t)</t>
         </is>
       </c>
-      <c r="QH1" t="inlineStr">
+      <c r="QH1" s="1" t="inlineStr">
         <is>
           <t>SMM Low - Carbon Aluminum (USD/t)</t>
         </is>
       </c>
-      <c r="QI1" t="inlineStr">
+      <c r="QI1" s="1" t="inlineStr">
         <is>
           <t>Shanghai -series Brazing Aluminum Semis (USD/t)</t>
         </is>
       </c>
-      <c r="QJ1" t="inlineStr">
+      <c r="QJ1" s="1" t="inlineStr">
         <is>
           <t>Shanghai 1-series Brazing Aluminum Semis (USD/t)</t>
         </is>
       </c>
-      <c r="QK1" t="inlineStr">
+      <c r="QK1" s="1" t="inlineStr">
         <is>
           <t>Shanghai 3-series Brazing Aluminum Semis (USD/t)</t>
         </is>
       </c>
-      <c r="QL1" t="inlineStr">
+      <c r="QL1" s="1" t="inlineStr">
         <is>
           <t>Shanghai 7-series Brazing Aluminum Semis (USD/t)</t>
         </is>
       </c>
-      <c r="QM1" t="inlineStr">
+      <c r="QM1" s="1" t="inlineStr">
         <is>
           <t>Shanghai Atomized Aluminum Powder (USD/t)</t>
         </is>
       </c>
-      <c r="QN1" t="inlineStr">
+      <c r="QN1" s="1" t="inlineStr">
         <is>
           <t>Xinjiang 99.99% High Purity Aluminum (USD/t)</t>
         </is>
       </c>
-      <c r="QO1" t="inlineStr">
+      <c r="QO1" s="1" t="inlineStr">
         <is>
           <t>Xinjiang 99.996% High Purity Aluminum (USD/t)</t>
         </is>
       </c>
-      <c r="QP1" t="inlineStr">
+      <c r="QP1" s="1" t="inlineStr">
         <is>
           <t>Xinjiang High Purity Aluminum (USD/t)</t>
         </is>
       </c>
-      <c r="QQ1" t="inlineStr">
+      <c r="QQ1" s="1" t="inlineStr">
         <is>
           <t>Yunnan -series Aluminum Slab (USD/t)</t>
         </is>
       </c>
-      <c r="QR1" t="inlineStr">
+      <c r="QR1" s="1" t="inlineStr">
         <is>
           <t>Yunnan 1-series Aluminum Slab (USD/t)</t>
         </is>
       </c>
-      <c r="QS1" t="inlineStr">
+      <c r="QS1" s="1" t="inlineStr">
         <is>
           <t>Yunnan 3-series Aluminum Slab (USD/t)</t>
         </is>
       </c>
-      <c r="QT1" t="inlineStr">
+      <c r="QT1" s="1" t="inlineStr">
         <is>
           <t>Yunnan 5-series Aluminum Slab (USD/t)</t>
         </is>
       </c>
-      <c r="QU1" t="inlineStr">
+      <c r="QU1" s="1" t="inlineStr">
         <is>
           <t>Yunnan 6-series Aluminum Slab (USD/t)</t>
         </is>
       </c>
-      <c r="QV1" t="inlineStr">
+      <c r="QV1" s="1" t="inlineStr">
         <is>
           <t>Index (USD/t)</t>
         </is>
       </c>
-      <c r="QW1" t="inlineStr">
+      <c r="QW1" s="1" t="inlineStr">
         <is>
           <t>Name Unit Index Change Date (USD/t)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
-      <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="inlineStr"/>
-      <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="inlineStr"/>
-      <c r="CC2" t="inlineStr"/>
-      <c r="CD2" t="inlineStr"/>
-      <c r="CE2" t="inlineStr"/>
-      <c r="CF2" t="inlineStr"/>
-      <c r="CG2" t="inlineStr"/>
-      <c r="CH2" t="inlineStr"/>
-      <c r="CI2" t="inlineStr"/>
-      <c r="CJ2" t="inlineStr"/>
-      <c r="CK2" t="inlineStr"/>
-      <c r="CL2" t="inlineStr"/>
-      <c r="CM2" t="inlineStr"/>
-      <c r="CN2" t="inlineStr"/>
-      <c r="CO2" t="inlineStr"/>
-      <c r="CP2" t="inlineStr"/>
-      <c r="CQ2" t="inlineStr"/>
-      <c r="CR2" t="inlineStr"/>
-      <c r="CS2" t="inlineStr"/>
-      <c r="CT2" t="inlineStr"/>
-      <c r="CU2" t="inlineStr"/>
-      <c r="CV2" t="inlineStr"/>
-      <c r="CW2" t="inlineStr"/>
-      <c r="CX2" t="inlineStr"/>
-      <c r="CY2" t="inlineStr"/>
-      <c r="CZ2" t="inlineStr"/>
-      <c r="DA2" t="inlineStr"/>
-      <c r="DB2" t="inlineStr"/>
-      <c r="DC2" t="inlineStr"/>
-      <c r="DD2" t="inlineStr"/>
-      <c r="DE2" t="inlineStr"/>
-      <c r="DF2" t="inlineStr"/>
-      <c r="DG2" t="inlineStr"/>
-      <c r="DH2" t="inlineStr"/>
-      <c r="DI2" t="inlineStr"/>
-      <c r="DJ2" t="inlineStr"/>
-      <c r="DK2" t="inlineStr"/>
-      <c r="DL2" t="inlineStr"/>
-      <c r="DM2" t="inlineStr"/>
-      <c r="DN2" t="inlineStr"/>
-      <c r="DO2" t="inlineStr"/>
-      <c r="DP2" t="inlineStr"/>
-      <c r="DQ2" t="inlineStr"/>
-      <c r="DR2" t="inlineStr"/>
-      <c r="DS2" t="inlineStr"/>
-      <c r="DT2" t="inlineStr"/>
-      <c r="DU2" t="inlineStr"/>
-      <c r="DV2" t="inlineStr"/>
-      <c r="DW2" t="inlineStr"/>
-      <c r="DX2" t="inlineStr"/>
-      <c r="DY2" t="inlineStr"/>
-      <c r="DZ2" t="inlineStr"/>
-      <c r="EA2" t="inlineStr"/>
-      <c r="EB2" t="inlineStr"/>
-      <c r="EC2" t="inlineStr"/>
-      <c r="ED2" t="inlineStr"/>
-      <c r="EE2" t="inlineStr"/>
-      <c r="EF2" t="inlineStr"/>
-      <c r="EG2" t="inlineStr"/>
-      <c r="EH2" t="inlineStr"/>
-      <c r="EI2" t="inlineStr"/>
-      <c r="EJ2" t="inlineStr"/>
-      <c r="EK2" t="inlineStr"/>
-      <c r="EL2" t="inlineStr"/>
-      <c r="EM2" t="inlineStr"/>
-      <c r="EN2" t="inlineStr"/>
-      <c r="EO2" t="inlineStr"/>
-      <c r="EP2" t="inlineStr"/>
-      <c r="EQ2" t="inlineStr"/>
-      <c r="ER2" t="inlineStr"/>
-      <c r="ES2" t="inlineStr"/>
-      <c r="ET2" t="inlineStr"/>
-      <c r="EU2" t="inlineStr"/>
-      <c r="EV2" t="inlineStr"/>
-      <c r="EW2" t="inlineStr"/>
-      <c r="EX2" t="inlineStr"/>
-      <c r="EY2" t="inlineStr"/>
-      <c r="EZ2" t="inlineStr"/>
-      <c r="FA2" t="inlineStr"/>
-      <c r="FB2" t="inlineStr"/>
-      <c r="FC2" t="inlineStr"/>
-      <c r="FD2" t="inlineStr"/>
-      <c r="FE2" t="inlineStr"/>
-      <c r="FF2" t="inlineStr"/>
-      <c r="FG2" t="inlineStr"/>
-      <c r="FH2" t="inlineStr"/>
-      <c r="FI2" t="inlineStr"/>
-      <c r="FJ2" t="inlineStr"/>
-      <c r="FK2" t="inlineStr"/>
-      <c r="FL2" t="inlineStr"/>
-      <c r="FM2" t="inlineStr"/>
-      <c r="FN2" t="inlineStr"/>
-      <c r="FO2" t="inlineStr"/>
-      <c r="FP2" t="inlineStr"/>
-      <c r="FQ2" t="inlineStr"/>
-      <c r="FR2" t="inlineStr"/>
-      <c r="FS2" t="inlineStr"/>
-      <c r="FT2" t="inlineStr"/>
-      <c r="FU2" t="inlineStr"/>
-      <c r="FV2" t="inlineStr"/>
-      <c r="FW2" t="inlineStr"/>
-      <c r="FX2" t="inlineStr"/>
-      <c r="FY2" t="inlineStr"/>
-      <c r="FZ2" t="inlineStr"/>
-      <c r="GA2" t="inlineStr"/>
-      <c r="GB2" t="inlineStr"/>
-      <c r="GC2" t="inlineStr"/>
-      <c r="GD2" t="inlineStr"/>
-      <c r="GE2" t="inlineStr"/>
-      <c r="GF2" t="inlineStr"/>
-      <c r="GG2" t="inlineStr"/>
-      <c r="GH2" t="inlineStr"/>
-      <c r="GI2" t="inlineStr"/>
-      <c r="GJ2" t="inlineStr"/>
-      <c r="GK2" t="inlineStr"/>
-      <c r="GL2" t="inlineStr"/>
-      <c r="GM2" t="inlineStr"/>
-      <c r="GN2" t="inlineStr"/>
-      <c r="GO2" t="inlineStr"/>
-      <c r="GP2" t="inlineStr"/>
-      <c r="GQ2" t="inlineStr"/>
-      <c r="GR2" t="inlineStr"/>
-      <c r="GS2" t="inlineStr"/>
-      <c r="GT2" t="inlineStr"/>
-      <c r="GU2" t="inlineStr"/>
-      <c r="GV2" t="inlineStr"/>
-      <c r="GW2" t="inlineStr"/>
-      <c r="GX2" t="inlineStr"/>
-      <c r="GY2" t="inlineStr"/>
-      <c r="GZ2" t="inlineStr"/>
-      <c r="HA2" t="inlineStr"/>
-      <c r="HB2" t="inlineStr"/>
-      <c r="HC2" t="inlineStr"/>
-      <c r="HD2" t="inlineStr"/>
-      <c r="HE2" t="inlineStr"/>
-      <c r="HF2" t="inlineStr"/>
-      <c r="HG2" t="inlineStr"/>
-      <c r="HH2" t="inlineStr"/>
-      <c r="HI2" t="inlineStr"/>
-      <c r="HJ2" t="inlineStr"/>
-      <c r="HK2" t="inlineStr"/>
-      <c r="HL2" t="inlineStr"/>
-      <c r="HM2" t="inlineStr"/>
-      <c r="HN2" t="inlineStr"/>
-      <c r="HO2" t="inlineStr"/>
-      <c r="HP2" t="inlineStr"/>
-      <c r="HQ2" t="inlineStr"/>
-      <c r="HR2" t="inlineStr"/>
-      <c r="HS2" t="inlineStr"/>
-      <c r="HT2" t="inlineStr"/>
-      <c r="HU2" t="inlineStr"/>
-      <c r="HV2" t="inlineStr"/>
-      <c r="HW2" t="inlineStr"/>
-      <c r="HX2" t="inlineStr"/>
-      <c r="HY2" t="inlineStr"/>
-      <c r="HZ2" t="inlineStr"/>
-      <c r="IA2" t="inlineStr"/>
-      <c r="IB2" t="inlineStr"/>
-      <c r="IC2" t="inlineStr"/>
-      <c r="ID2" t="inlineStr"/>
-      <c r="IE2" t="inlineStr"/>
-      <c r="IF2" t="inlineStr"/>
-      <c r="IG2" t="inlineStr"/>
-      <c r="IH2" t="inlineStr"/>
-      <c r="II2" t="inlineStr"/>
-      <c r="IJ2" t="inlineStr"/>
-      <c r="IK2" t="inlineStr"/>
-      <c r="IL2" t="inlineStr"/>
-      <c r="IM2" t="inlineStr"/>
-      <c r="IN2" t="inlineStr"/>
-      <c r="IO2" t="inlineStr"/>
-      <c r="IP2" t="inlineStr"/>
-      <c r="IQ2" t="inlineStr"/>
-      <c r="IR2" t="inlineStr"/>
-      <c r="IS2" t="inlineStr"/>
-      <c r="IT2" t="inlineStr"/>
-      <c r="IU2" t="inlineStr"/>
-      <c r="IV2" t="inlineStr"/>
-      <c r="IW2" t="inlineStr"/>
-      <c r="IX2" t="inlineStr"/>
-      <c r="IY2" t="inlineStr"/>
-      <c r="IZ2" t="inlineStr"/>
-      <c r="JA2" t="inlineStr"/>
-      <c r="JB2" t="inlineStr"/>
-      <c r="JC2" t="inlineStr"/>
-      <c r="JD2" t="inlineStr"/>
-      <c r="JE2" t="inlineStr"/>
-      <c r="JF2" t="inlineStr"/>
-      <c r="JG2" t="inlineStr"/>
-      <c r="JH2" t="inlineStr"/>
-      <c r="JI2" t="inlineStr"/>
-      <c r="JJ2" t="inlineStr"/>
-      <c r="JK2" t="inlineStr"/>
-      <c r="JL2" t="inlineStr"/>
-      <c r="JM2" t="inlineStr"/>
-      <c r="JN2" t="inlineStr"/>
-      <c r="JO2" t="inlineStr"/>
-      <c r="JP2" t="inlineStr"/>
-      <c r="JQ2" t="inlineStr"/>
-      <c r="JR2" t="inlineStr"/>
-      <c r="JS2" t="inlineStr"/>
-      <c r="JT2" t="inlineStr"/>
-      <c r="JU2" t="inlineStr"/>
-      <c r="JV2" t="inlineStr"/>
-      <c r="JW2" t="inlineStr"/>
-      <c r="JX2" t="inlineStr"/>
-      <c r="JY2" t="inlineStr"/>
-      <c r="JZ2" t="inlineStr"/>
-      <c r="KA2" t="inlineStr"/>
-      <c r="KB2" t="inlineStr"/>
-      <c r="KC2" t="inlineStr"/>
-      <c r="KD2" t="inlineStr"/>
-      <c r="KE2" t="inlineStr"/>
-      <c r="KF2" t="inlineStr"/>
-      <c r="KG2" t="inlineStr"/>
-      <c r="KH2" t="inlineStr"/>
-      <c r="KI2" t="inlineStr"/>
-      <c r="KJ2" t="inlineStr"/>
-      <c r="KK2" t="inlineStr"/>
-      <c r="KL2" t="inlineStr"/>
-      <c r="KM2" t="inlineStr"/>
-      <c r="KN2" t="inlineStr"/>
-      <c r="KO2" t="inlineStr"/>
-      <c r="KP2" t="inlineStr"/>
-      <c r="KQ2" t="inlineStr"/>
-      <c r="KR2" t="inlineStr"/>
-      <c r="KS2" t="inlineStr"/>
-      <c r="KT2" t="inlineStr"/>
-      <c r="KU2" t="inlineStr"/>
-      <c r="KV2" t="inlineStr"/>
-      <c r="KW2" t="inlineStr"/>
-      <c r="KX2" t="inlineStr"/>
-      <c r="KY2" t="inlineStr"/>
-      <c r="KZ2" t="inlineStr"/>
-      <c r="LA2" t="inlineStr"/>
-      <c r="LB2" t="inlineStr"/>
-      <c r="LC2" t="inlineStr"/>
-      <c r="LD2" t="inlineStr"/>
-      <c r="LE2" t="inlineStr"/>
-      <c r="LF2" t="inlineStr"/>
-      <c r="LG2" t="inlineStr"/>
-      <c r="LH2" t="inlineStr"/>
-      <c r="LI2" t="inlineStr"/>
-      <c r="LJ2" t="inlineStr"/>
-      <c r="LK2" t="inlineStr"/>
-      <c r="LL2" t="inlineStr"/>
-      <c r="LM2" t="inlineStr"/>
-      <c r="LN2" t="inlineStr"/>
-      <c r="LO2" t="inlineStr"/>
-      <c r="LP2" t="inlineStr"/>
-      <c r="LQ2" t="inlineStr"/>
-      <c r="LR2" t="inlineStr"/>
-      <c r="LS2" t="inlineStr"/>
-      <c r="LT2" t="inlineStr"/>
-      <c r="LU2" t="inlineStr"/>
-      <c r="LV2" t="inlineStr"/>
-      <c r="LW2" t="inlineStr"/>
-      <c r="LX2" t="inlineStr"/>
-      <c r="LY2" t="inlineStr"/>
-      <c r="LZ2" t="inlineStr"/>
-      <c r="MA2" t="inlineStr"/>
-      <c r="MB2" t="inlineStr"/>
-      <c r="MC2" t="inlineStr"/>
-      <c r="MD2" t="inlineStr"/>
-      <c r="ME2" t="inlineStr"/>
-      <c r="MF2" t="inlineStr"/>
-      <c r="MG2" t="inlineStr"/>
-      <c r="MH2" t="inlineStr"/>
-      <c r="MI2" t="inlineStr"/>
-      <c r="MJ2" t="inlineStr"/>
-      <c r="MK2" t="inlineStr"/>
-      <c r="ML2" t="inlineStr"/>
-      <c r="MM2" t="inlineStr"/>
-      <c r="MN2" t="inlineStr"/>
-      <c r="MO2" t="inlineStr"/>
-      <c r="MP2" t="inlineStr"/>
-      <c r="MQ2" t="inlineStr"/>
-      <c r="MR2" t="inlineStr"/>
-      <c r="MS2" t="inlineStr"/>
-      <c r="MT2" t="inlineStr"/>
-      <c r="MU2" t="inlineStr"/>
-      <c r="MV2" t="inlineStr"/>
-      <c r="MW2" t="inlineStr"/>
-      <c r="MX2" t="inlineStr"/>
-      <c r="MY2" t="inlineStr"/>
-      <c r="MZ2" t="inlineStr"/>
-      <c r="NA2" t="inlineStr"/>
-      <c r="NB2" t="inlineStr"/>
-      <c r="NC2" t="inlineStr"/>
-      <c r="ND2" t="inlineStr"/>
-      <c r="NE2" t="inlineStr"/>
-      <c r="NF2" t="inlineStr"/>
-      <c r="NG2" t="inlineStr"/>
-      <c r="NH2" t="inlineStr"/>
-      <c r="NI2" t="inlineStr"/>
-      <c r="NJ2" t="inlineStr"/>
-      <c r="NK2" t="inlineStr"/>
-      <c r="NL2" t="inlineStr"/>
-      <c r="NM2" t="inlineStr"/>
-      <c r="NN2" t="inlineStr"/>
-      <c r="NO2" t="inlineStr"/>
-      <c r="NP2" t="inlineStr"/>
-      <c r="NQ2" t="inlineStr"/>
-      <c r="NR2" t="inlineStr"/>
-      <c r="NS2" t="inlineStr"/>
-      <c r="NT2" t="inlineStr"/>
-      <c r="NU2" t="inlineStr"/>
-      <c r="NV2" t="inlineStr"/>
-      <c r="NW2" t="inlineStr"/>
-      <c r="NX2" t="inlineStr"/>
-      <c r="NY2" t="inlineStr"/>
-      <c r="NZ2" t="inlineStr"/>
-      <c r="OA2" t="inlineStr"/>
-      <c r="OB2" t="inlineStr"/>
-      <c r="OC2" t="inlineStr"/>
-      <c r="OD2" t="inlineStr"/>
-      <c r="OE2" t="inlineStr"/>
-      <c r="OF2" t="inlineStr"/>
-      <c r="OG2" t="inlineStr"/>
-      <c r="OH2" t="inlineStr"/>
-      <c r="OI2" t="inlineStr"/>
-      <c r="OJ2" t="inlineStr"/>
-      <c r="OK2" t="inlineStr"/>
-      <c r="OL2" t="inlineStr"/>
-      <c r="OM2" t="inlineStr"/>
-      <c r="ON2" t="inlineStr"/>
-      <c r="OO2" t="inlineStr"/>
-      <c r="OP2" t="inlineStr"/>
-      <c r="OQ2" t="inlineStr"/>
-      <c r="OR2" t="inlineStr"/>
-      <c r="OS2" t="inlineStr"/>
-      <c r="OT2" t="inlineStr"/>
-      <c r="OU2" t="inlineStr"/>
-      <c r="OV2" t="inlineStr"/>
-      <c r="OW2" t="inlineStr"/>
-      <c r="OX2" t="inlineStr"/>
-      <c r="OY2" t="inlineStr"/>
-      <c r="OZ2" t="inlineStr"/>
-      <c r="PA2" t="inlineStr"/>
-      <c r="PB2" t="inlineStr"/>
-      <c r="PC2" t="inlineStr"/>
-      <c r="PD2" t="inlineStr"/>
-      <c r="PE2" t="inlineStr"/>
-      <c r="PF2" t="inlineStr"/>
-      <c r="PG2" t="inlineStr"/>
-      <c r="PH2" t="inlineStr"/>
-      <c r="PI2" t="inlineStr"/>
-      <c r="PJ2" t="inlineStr"/>
-      <c r="PK2" t="inlineStr"/>
-      <c r="PL2" t="inlineStr"/>
-      <c r="PM2" t="inlineStr"/>
-      <c r="PN2" t="inlineStr"/>
-      <c r="PO2" t="inlineStr"/>
-      <c r="PP2" t="inlineStr"/>
-      <c r="PQ2" t="inlineStr"/>
-      <c r="PR2" t="inlineStr"/>
-      <c r="PS2" t="inlineStr"/>
-      <c r="PT2" t="inlineStr"/>
-      <c r="PU2" t="inlineStr"/>
-      <c r="PV2" t="inlineStr"/>
-      <c r="PW2" t="inlineStr"/>
-      <c r="PX2" t="inlineStr"/>
-      <c r="PY2" t="inlineStr"/>
-      <c r="PZ2" t="inlineStr"/>
-      <c r="QA2" t="inlineStr"/>
-      <c r="QB2" t="inlineStr"/>
-      <c r="QC2" t="inlineStr"/>
-      <c r="QD2" t="inlineStr"/>
-      <c r="QE2" t="inlineStr"/>
-      <c r="QF2" t="inlineStr"/>
-      <c r="QG2" t="inlineStr"/>
-      <c r="QH2" t="inlineStr"/>
-      <c r="QI2" t="inlineStr"/>
-      <c r="QJ2" t="inlineStr"/>
-      <c r="QK2" t="inlineStr"/>
-      <c r="QL2" t="inlineStr"/>
-      <c r="QM2" t="inlineStr"/>
-      <c r="QN2" t="inlineStr"/>
-      <c r="QO2" t="inlineStr"/>
-      <c r="QP2" t="inlineStr"/>
-      <c r="QQ2" t="inlineStr"/>
-      <c r="QR2" t="inlineStr"/>
-      <c r="QS2" t="inlineStr"/>
-      <c r="QT2" t="inlineStr"/>
-      <c r="QU2" t="inlineStr"/>
-      <c r="QV2" t="inlineStr"/>
-      <c r="QW2" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr"/>
+      <c r="I2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr"/>
+      <c r="K2" s="1" t="inlineStr"/>
+      <c r="L2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr"/>
+      <c r="N2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr"/>
+      <c r="P2" s="1" t="inlineStr"/>
+      <c r="Q2" s="1" t="inlineStr"/>
+      <c r="R2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr"/>
+      <c r="T2" s="1" t="inlineStr"/>
+      <c r="U2" s="1" t="inlineStr"/>
+      <c r="V2" s="1" t="inlineStr"/>
+      <c r="W2" s="1" t="inlineStr"/>
+      <c r="X2" s="1" t="inlineStr"/>
+      <c r="Y2" s="1" t="inlineStr"/>
+      <c r="Z2" s="1" t="inlineStr"/>
+      <c r="AA2" s="1" t="inlineStr"/>
+      <c r="AB2" s="1" t="inlineStr"/>
+      <c r="AC2" s="1" t="inlineStr"/>
+      <c r="AD2" s="1" t="inlineStr"/>
+      <c r="AE2" s="1" t="inlineStr"/>
+      <c r="AF2" s="1" t="inlineStr"/>
+      <c r="AG2" s="1" t="inlineStr"/>
+      <c r="AH2" s="1" t="inlineStr"/>
+      <c r="AI2" s="1" t="inlineStr"/>
+      <c r="AJ2" s="1" t="inlineStr"/>
+      <c r="AK2" s="1" t="inlineStr"/>
+      <c r="AL2" s="1" t="inlineStr"/>
+      <c r="AM2" s="1" t="inlineStr"/>
+      <c r="AN2" s="1" t="inlineStr"/>
+      <c r="AO2" s="1" t="inlineStr"/>
+      <c r="AP2" s="1" t="inlineStr"/>
+      <c r="AQ2" s="1" t="inlineStr"/>
+      <c r="AR2" s="1" t="inlineStr"/>
+      <c r="AS2" s="1" t="inlineStr"/>
+      <c r="AT2" s="1" t="inlineStr"/>
+      <c r="AU2" s="1" t="inlineStr"/>
+      <c r="AV2" s="1" t="inlineStr"/>
+      <c r="AW2" s="1" t="inlineStr"/>
+      <c r="AX2" s="1" t="inlineStr"/>
+      <c r="AY2" s="1" t="inlineStr"/>
+      <c r="AZ2" s="1" t="inlineStr"/>
+      <c r="BA2" s="1" t="inlineStr"/>
+      <c r="BB2" s="1" t="inlineStr"/>
+      <c r="BC2" s="1" t="inlineStr"/>
+      <c r="BD2" s="1" t="inlineStr"/>
+      <c r="BE2" s="1" t="inlineStr"/>
+      <c r="BF2" s="1" t="inlineStr"/>
+      <c r="BG2" s="1" t="inlineStr"/>
+      <c r="BH2" s="1" t="inlineStr"/>
+      <c r="BI2" s="1" t="inlineStr"/>
+      <c r="BJ2" s="1" t="inlineStr"/>
+      <c r="BK2" s="1" t="inlineStr"/>
+      <c r="BL2" s="1" t="inlineStr"/>
+      <c r="BM2" s="1" t="inlineStr"/>
+      <c r="BN2" s="1" t="inlineStr"/>
+      <c r="BO2" s="1" t="inlineStr"/>
+      <c r="BP2" s="1" t="inlineStr"/>
+      <c r="BQ2" s="1" t="inlineStr"/>
+      <c r="BR2" s="1" t="inlineStr"/>
+      <c r="BS2" s="1" t="inlineStr"/>
+      <c r="BT2" s="1" t="inlineStr"/>
+      <c r="BU2" s="1" t="inlineStr"/>
+      <c r="BV2" s="1" t="inlineStr"/>
+      <c r="BW2" s="1" t="inlineStr"/>
+      <c r="BX2" s="1" t="inlineStr"/>
+      <c r="BY2" s="1" t="inlineStr"/>
+      <c r="BZ2" s="1" t="inlineStr"/>
+      <c r="CA2" s="1" t="inlineStr"/>
+      <c r="CB2" s="1" t="inlineStr"/>
+      <c r="CC2" s="1" t="inlineStr"/>
+      <c r="CD2" s="1" t="inlineStr"/>
+      <c r="CE2" s="1" t="inlineStr"/>
+      <c r="CF2" s="1" t="inlineStr"/>
+      <c r="CG2" s="1" t="inlineStr"/>
+      <c r="CH2" s="1" t="inlineStr"/>
+      <c r="CI2" s="1" t="inlineStr"/>
+      <c r="CJ2" s="1" t="inlineStr"/>
+      <c r="CK2" s="1" t="inlineStr"/>
+      <c r="CL2" s="1" t="inlineStr"/>
+      <c r="CM2" s="1" t="inlineStr"/>
+      <c r="CN2" s="1" t="inlineStr"/>
+      <c r="CO2" s="1" t="inlineStr"/>
+      <c r="CP2" s="1" t="inlineStr"/>
+      <c r="CQ2" s="1" t="inlineStr"/>
+      <c r="CR2" s="1" t="inlineStr"/>
+      <c r="CS2" s="1" t="inlineStr"/>
+      <c r="CT2" s="1" t="inlineStr"/>
+      <c r="CU2" s="1" t="inlineStr"/>
+      <c r="CV2" s="1" t="inlineStr"/>
+      <c r="CW2" s="1" t="inlineStr"/>
+      <c r="CX2" s="1" t="inlineStr"/>
+      <c r="CY2" s="1" t="inlineStr"/>
+      <c r="CZ2" s="1" t="inlineStr"/>
+      <c r="DA2" s="1" t="inlineStr"/>
+      <c r="DB2" s="1" t="inlineStr"/>
+      <c r="DC2" s="1" t="inlineStr"/>
+      <c r="DD2" s="1" t="inlineStr"/>
+      <c r="DE2" s="1" t="inlineStr"/>
+      <c r="DF2" s="1" t="inlineStr"/>
+      <c r="DG2" s="1" t="inlineStr"/>
+      <c r="DH2" s="1" t="inlineStr"/>
+      <c r="DI2" s="1" t="inlineStr"/>
+      <c r="DJ2" s="1" t="inlineStr"/>
+      <c r="DK2" s="1" t="inlineStr"/>
+      <c r="DL2" s="1" t="inlineStr"/>
+      <c r="DM2" s="1" t="inlineStr"/>
+      <c r="DN2" s="1" t="inlineStr"/>
+      <c r="DO2" s="1" t="inlineStr"/>
+      <c r="DP2" s="1" t="inlineStr"/>
+      <c r="DQ2" s="1" t="inlineStr"/>
+      <c r="DR2" s="1" t="inlineStr"/>
+      <c r="DS2" s="1" t="inlineStr"/>
+      <c r="DT2" s="1" t="inlineStr"/>
+      <c r="DU2" s="1" t="inlineStr"/>
+      <c r="DV2" s="1" t="inlineStr"/>
+      <c r="DW2" s="1" t="inlineStr"/>
+      <c r="DX2" s="1" t="inlineStr"/>
+      <c r="DY2" s="1" t="inlineStr"/>
+      <c r="DZ2" s="1" t="inlineStr"/>
+      <c r="EA2" s="1" t="inlineStr"/>
+      <c r="EB2" s="1" t="inlineStr"/>
+      <c r="EC2" s="1" t="inlineStr"/>
+      <c r="ED2" s="1" t="inlineStr"/>
+      <c r="EE2" s="1" t="inlineStr"/>
+      <c r="EF2" s="1" t="inlineStr"/>
+      <c r="EG2" s="1" t="inlineStr"/>
+      <c r="EH2" s="1" t="inlineStr"/>
+      <c r="EI2" s="1" t="inlineStr"/>
+      <c r="EJ2" s="1" t="inlineStr"/>
+      <c r="EK2" s="1" t="inlineStr"/>
+      <c r="EL2" s="1" t="inlineStr"/>
+      <c r="EM2" s="1" t="inlineStr"/>
+      <c r="EN2" s="1" t="inlineStr"/>
+      <c r="EO2" s="1" t="inlineStr"/>
+      <c r="EP2" s="1" t="inlineStr"/>
+      <c r="EQ2" s="1" t="inlineStr"/>
+      <c r="ER2" s="1" t="inlineStr"/>
+      <c r="ES2" s="1" t="inlineStr"/>
+      <c r="ET2" s="1" t="inlineStr"/>
+      <c r="EU2" s="1" t="inlineStr"/>
+      <c r="EV2" s="1" t="inlineStr"/>
+      <c r="EW2" s="1" t="inlineStr"/>
+      <c r="EX2" s="1" t="inlineStr"/>
+      <c r="EY2" s="1" t="inlineStr"/>
+      <c r="EZ2" s="1" t="inlineStr"/>
+      <c r="FA2" s="1" t="inlineStr"/>
+      <c r="FB2" s="1" t="inlineStr"/>
+      <c r="FC2" s="1" t="inlineStr"/>
+      <c r="FD2" s="1" t="inlineStr"/>
+      <c r="FE2" s="1" t="inlineStr"/>
+      <c r="FF2" s="1" t="inlineStr"/>
+      <c r="FG2" s="1" t="inlineStr"/>
+      <c r="FH2" s="1" t="inlineStr"/>
+      <c r="FI2" s="1" t="inlineStr"/>
+      <c r="FJ2" s="1" t="inlineStr"/>
+      <c r="FK2" s="1" t="inlineStr"/>
+      <c r="FL2" s="1" t="inlineStr"/>
+      <c r="FM2" s="1" t="inlineStr"/>
+      <c r="FN2" s="1" t="inlineStr"/>
+      <c r="FO2" s="1" t="inlineStr"/>
+      <c r="FP2" s="1" t="inlineStr"/>
+      <c r="FQ2" s="1" t="inlineStr"/>
+      <c r="FR2" s="1" t="inlineStr"/>
+      <c r="FS2" s="1" t="inlineStr"/>
+      <c r="FT2" s="1" t="inlineStr"/>
+      <c r="FU2" s="1" t="inlineStr"/>
+      <c r="FV2" s="1" t="inlineStr"/>
+      <c r="FW2" s="1" t="inlineStr"/>
+      <c r="FX2" s="1" t="inlineStr"/>
+      <c r="FY2" s="1" t="inlineStr"/>
+      <c r="FZ2" s="1" t="inlineStr"/>
+      <c r="GA2" s="1" t="inlineStr"/>
+      <c r="GB2" s="1" t="inlineStr"/>
+      <c r="GC2" s="1" t="inlineStr"/>
+      <c r="GD2" s="1" t="inlineStr"/>
+      <c r="GE2" s="1" t="inlineStr"/>
+      <c r="GF2" s="1" t="inlineStr"/>
+      <c r="GG2" s="1" t="inlineStr"/>
+      <c r="GH2" s="1" t="inlineStr"/>
+      <c r="GI2" s="1" t="inlineStr"/>
+      <c r="GJ2" s="1" t="inlineStr"/>
+      <c r="GK2" s="1" t="inlineStr"/>
+      <c r="GL2" s="1" t="inlineStr"/>
+      <c r="GM2" s="1" t="inlineStr"/>
+      <c r="GN2" s="1" t="inlineStr"/>
+      <c r="GO2" s="1" t="inlineStr"/>
+      <c r="GP2" s="1" t="inlineStr"/>
+      <c r="GQ2" s="1" t="inlineStr"/>
+      <c r="GR2" s="1" t="inlineStr"/>
+      <c r="GS2" s="1" t="inlineStr"/>
+      <c r="GT2" s="1" t="inlineStr"/>
+      <c r="GU2" s="1" t="inlineStr"/>
+      <c r="GV2" s="1" t="inlineStr"/>
+      <c r="GW2" s="1" t="inlineStr"/>
+      <c r="GX2" s="1" t="inlineStr"/>
+      <c r="GY2" s="1" t="inlineStr"/>
+      <c r="GZ2" s="1" t="inlineStr"/>
+      <c r="HA2" s="1" t="inlineStr"/>
+      <c r="HB2" s="1" t="inlineStr"/>
+      <c r="HC2" s="1" t="inlineStr"/>
+      <c r="HD2" s="1" t="inlineStr"/>
+      <c r="HE2" s="1" t="inlineStr"/>
+      <c r="HF2" s="1" t="inlineStr"/>
+      <c r="HG2" s="1" t="inlineStr"/>
+      <c r="HH2" s="1" t="inlineStr"/>
+      <c r="HI2" s="1" t="inlineStr"/>
+      <c r="HJ2" s="1" t="inlineStr"/>
+      <c r="HK2" s="1" t="inlineStr"/>
+      <c r="HL2" s="1" t="inlineStr"/>
+      <c r="HM2" s="1" t="inlineStr"/>
+      <c r="HN2" s="1" t="inlineStr"/>
+      <c r="HO2" s="1" t="inlineStr"/>
+      <c r="HP2" s="1" t="inlineStr"/>
+      <c r="HQ2" s="1" t="inlineStr"/>
+      <c r="HR2" s="1" t="inlineStr"/>
+      <c r="HS2" s="1" t="inlineStr"/>
+      <c r="HT2" s="1" t="inlineStr"/>
+      <c r="HU2" s="1" t="inlineStr"/>
+      <c r="HV2" s="1" t="inlineStr"/>
+      <c r="HW2" s="1" t="inlineStr"/>
+      <c r="HX2" s="1" t="inlineStr"/>
+      <c r="HY2" s="1" t="inlineStr"/>
+      <c r="HZ2" s="1" t="inlineStr"/>
+      <c r="IA2" s="1" t="inlineStr"/>
+      <c r="IB2" s="1" t="inlineStr"/>
+      <c r="IC2" s="1" t="inlineStr"/>
+      <c r="ID2" s="1" t="inlineStr"/>
+      <c r="IE2" s="1" t="inlineStr"/>
+      <c r="IF2" s="1" t="inlineStr"/>
+      <c r="IG2" s="1" t="inlineStr"/>
+      <c r="IH2" s="1" t="inlineStr"/>
+      <c r="II2" s="1" t="inlineStr"/>
+      <c r="IJ2" s="1" t="inlineStr"/>
+      <c r="IK2" s="1" t="inlineStr"/>
+      <c r="IL2" s="1" t="inlineStr"/>
+      <c r="IM2" s="1" t="inlineStr"/>
+      <c r="IN2" s="1" t="inlineStr"/>
+      <c r="IO2" s="1" t="inlineStr"/>
+      <c r="IP2" s="1" t="inlineStr"/>
+      <c r="IQ2" s="1" t="inlineStr"/>
+      <c r="IR2" s="1" t="inlineStr"/>
+      <c r="IS2" s="1" t="inlineStr"/>
+      <c r="IT2" s="1" t="inlineStr"/>
+      <c r="IU2" s="1" t="inlineStr"/>
+      <c r="IV2" s="1" t="inlineStr"/>
+      <c r="IW2" s="1" t="inlineStr"/>
+      <c r="IX2" s="1" t="inlineStr"/>
+      <c r="IY2" s="1" t="inlineStr"/>
+      <c r="IZ2" s="1" t="inlineStr"/>
+      <c r="JA2" s="1" t="inlineStr"/>
+      <c r="JB2" s="1" t="inlineStr"/>
+      <c r="JC2" s="1" t="inlineStr"/>
+      <c r="JD2" s="1" t="inlineStr"/>
+      <c r="JE2" s="1" t="inlineStr"/>
+      <c r="JF2" s="1" t="inlineStr"/>
+      <c r="JG2" s="1" t="inlineStr"/>
+      <c r="JH2" s="1" t="inlineStr"/>
+      <c r="JI2" s="1" t="inlineStr"/>
+      <c r="JJ2" s="1" t="inlineStr"/>
+      <c r="JK2" s="1" t="inlineStr"/>
+      <c r="JL2" s="1" t="inlineStr"/>
+      <c r="JM2" s="1" t="inlineStr"/>
+      <c r="JN2" s="1" t="inlineStr"/>
+      <c r="JO2" s="1" t="inlineStr"/>
+      <c r="JP2" s="1" t="inlineStr"/>
+      <c r="JQ2" s="1" t="inlineStr"/>
+      <c r="JR2" s="1" t="inlineStr"/>
+      <c r="JS2" s="1" t="inlineStr"/>
+      <c r="JT2" s="1" t="inlineStr"/>
+      <c r="JU2" s="1" t="inlineStr"/>
+      <c r="JV2" s="1" t="inlineStr"/>
+      <c r="JW2" s="1" t="inlineStr"/>
+      <c r="JX2" s="1" t="inlineStr"/>
+      <c r="JY2" s="1" t="inlineStr"/>
+      <c r="JZ2" s="1" t="inlineStr"/>
+      <c r="KA2" s="1" t="inlineStr"/>
+      <c r="KB2" s="1" t="inlineStr"/>
+      <c r="KC2" s="1" t="inlineStr"/>
+      <c r="KD2" s="1" t="inlineStr"/>
+      <c r="KE2" s="1" t="inlineStr"/>
+      <c r="KF2" s="1" t="inlineStr"/>
+      <c r="KG2" s="1" t="inlineStr"/>
+      <c r="KH2" s="1" t="inlineStr"/>
+      <c r="KI2" s="1" t="inlineStr"/>
+      <c r="KJ2" s="1" t="inlineStr"/>
+      <c r="KK2" s="1" t="inlineStr"/>
+      <c r="KL2" s="1" t="inlineStr"/>
+      <c r="KM2" s="1" t="inlineStr"/>
+      <c r="KN2" s="1" t="inlineStr"/>
+      <c r="KO2" s="1" t="inlineStr"/>
+      <c r="KP2" s="1" t="inlineStr"/>
+      <c r="KQ2" s="1" t="inlineStr"/>
+      <c r="KR2" s="1" t="inlineStr"/>
+      <c r="KS2" s="1" t="inlineStr"/>
+      <c r="KT2" s="1" t="inlineStr"/>
+      <c r="KU2" s="1" t="inlineStr"/>
+      <c r="KV2" s="1" t="inlineStr"/>
+      <c r="KW2" s="1" t="inlineStr"/>
+      <c r="KX2" s="1" t="inlineStr"/>
+      <c r="KY2" s="1" t="inlineStr"/>
+      <c r="KZ2" s="1" t="inlineStr"/>
+      <c r="LA2" s="1" t="inlineStr"/>
+      <c r="LB2" s="1" t="inlineStr"/>
+      <c r="LC2" s="1" t="inlineStr"/>
+      <c r="LD2" s="1" t="inlineStr"/>
+      <c r="LE2" s="1" t="inlineStr"/>
+      <c r="LF2" s="1" t="inlineStr"/>
+      <c r="LG2" s="1" t="inlineStr"/>
+      <c r="LH2" s="1" t="inlineStr"/>
+      <c r="LI2" s="1" t="inlineStr"/>
+      <c r="LJ2" s="1" t="inlineStr"/>
+      <c r="LK2" s="1" t="inlineStr"/>
+      <c r="LL2" s="1" t="inlineStr"/>
+      <c r="LM2" s="1" t="inlineStr"/>
+      <c r="LN2" s="1" t="inlineStr"/>
+      <c r="LO2" s="1" t="inlineStr"/>
+      <c r="LP2" s="1" t="inlineStr"/>
+      <c r="LQ2" s="1" t="inlineStr"/>
+      <c r="LR2" s="1" t="inlineStr"/>
+      <c r="LS2" s="1" t="inlineStr"/>
+      <c r="LT2" s="1" t="inlineStr"/>
+      <c r="LU2" s="1" t="inlineStr"/>
+      <c r="LV2" s="1" t="inlineStr"/>
+      <c r="LW2" s="1" t="inlineStr"/>
+      <c r="LX2" s="1" t="inlineStr"/>
+      <c r="LY2" s="1" t="inlineStr"/>
+      <c r="LZ2" s="1" t="inlineStr"/>
+      <c r="MA2" s="1" t="inlineStr"/>
+      <c r="MB2" s="1" t="inlineStr"/>
+      <c r="MC2" s="1" t="inlineStr"/>
+      <c r="MD2" s="1" t="inlineStr"/>
+      <c r="ME2" s="1" t="inlineStr"/>
+      <c r="MF2" s="1" t="inlineStr"/>
+      <c r="MG2" s="1" t="inlineStr"/>
+      <c r="MH2" s="1" t="inlineStr"/>
+      <c r="MI2" s="1" t="inlineStr"/>
+      <c r="MJ2" s="1" t="inlineStr"/>
+      <c r="MK2" s="1" t="inlineStr"/>
+      <c r="ML2" s="1" t="inlineStr"/>
+      <c r="MM2" s="1" t="inlineStr"/>
+      <c r="MN2" s="1" t="inlineStr"/>
+      <c r="MO2" s="1" t="inlineStr"/>
+      <c r="MP2" s="1" t="inlineStr"/>
+      <c r="MQ2" s="1" t="inlineStr"/>
+      <c r="MR2" s="1" t="inlineStr"/>
+      <c r="MS2" s="1" t="inlineStr"/>
+      <c r="MT2" s="1" t="inlineStr"/>
+      <c r="MU2" s="1" t="inlineStr"/>
+      <c r="MV2" s="1" t="inlineStr"/>
+      <c r="MW2" s="1" t="inlineStr"/>
+      <c r="MX2" s="1" t="inlineStr"/>
+      <c r="MY2" s="1" t="inlineStr"/>
+      <c r="MZ2" s="1" t="inlineStr"/>
+      <c r="NA2" s="1" t="inlineStr"/>
+      <c r="NB2" s="1" t="inlineStr"/>
+      <c r="NC2" s="1" t="inlineStr"/>
+      <c r="ND2" s="1" t="inlineStr"/>
+      <c r="NE2" s="1" t="inlineStr"/>
+      <c r="NF2" s="1" t="inlineStr"/>
+      <c r="NG2" s="1" t="inlineStr"/>
+      <c r="NH2" s="1" t="inlineStr"/>
+      <c r="NI2" s="1" t="inlineStr"/>
+      <c r="NJ2" s="1" t="inlineStr"/>
+      <c r="NK2" s="1" t="inlineStr"/>
+      <c r="NL2" s="1" t="inlineStr"/>
+      <c r="NM2" s="1" t="inlineStr"/>
+      <c r="NN2" s="1" t="inlineStr"/>
+      <c r="NO2" s="1" t="inlineStr"/>
+      <c r="NP2" s="1" t="inlineStr"/>
+      <c r="NQ2" s="1" t="inlineStr"/>
+      <c r="NR2" s="1" t="inlineStr"/>
+      <c r="NS2" s="1" t="inlineStr"/>
+      <c r="NT2" s="1" t="inlineStr"/>
+      <c r="NU2" s="1" t="inlineStr"/>
+      <c r="NV2" s="1" t="inlineStr"/>
+      <c r="NW2" s="1" t="inlineStr"/>
+      <c r="NX2" s="1" t="inlineStr"/>
+      <c r="NY2" s="1" t="inlineStr"/>
+      <c r="NZ2" s="1" t="inlineStr"/>
+      <c r="OA2" s="1" t="inlineStr"/>
+      <c r="OB2" s="1" t="inlineStr"/>
+      <c r="OC2" s="1" t="inlineStr"/>
+      <c r="OD2" s="1" t="inlineStr"/>
+      <c r="OE2" s="1" t="inlineStr"/>
+      <c r="OF2" s="1" t="inlineStr"/>
+      <c r="OG2" s="1" t="inlineStr"/>
+      <c r="OH2" s="1" t="inlineStr"/>
+      <c r="OI2" s="1" t="inlineStr"/>
+      <c r="OJ2" s="1" t="inlineStr"/>
+      <c r="OK2" s="1" t="inlineStr"/>
+      <c r="OL2" s="1" t="inlineStr"/>
+      <c r="OM2" s="1" t="inlineStr"/>
+      <c r="ON2" s="1" t="inlineStr"/>
+      <c r="OO2" s="1" t="inlineStr"/>
+      <c r="OP2" s="1" t="inlineStr"/>
+      <c r="OQ2" s="1" t="inlineStr"/>
+      <c r="OR2" s="1" t="inlineStr"/>
+      <c r="OS2" s="1" t="inlineStr"/>
+      <c r="OT2" s="1" t="inlineStr"/>
+      <c r="OU2" s="1" t="inlineStr"/>
+      <c r="OV2" s="1" t="inlineStr"/>
+      <c r="OW2" s="1" t="inlineStr"/>
+      <c r="OX2" s="1" t="inlineStr"/>
+      <c r="OY2" s="1" t="inlineStr"/>
+      <c r="OZ2" s="1" t="inlineStr"/>
+      <c r="PA2" s="1" t="inlineStr"/>
+      <c r="PB2" s="1" t="inlineStr"/>
+      <c r="PC2" s="1" t="inlineStr"/>
+      <c r="PD2" s="1" t="inlineStr"/>
+      <c r="PE2" s="1" t="inlineStr"/>
+      <c r="PF2" s="1" t="inlineStr"/>
+      <c r="PG2" s="1" t="inlineStr"/>
+      <c r="PH2" s="1" t="inlineStr"/>
+      <c r="PI2" s="1" t="inlineStr"/>
+      <c r="PJ2" s="1" t="inlineStr"/>
+      <c r="PK2" s="1" t="inlineStr"/>
+      <c r="PL2" s="1" t="inlineStr"/>
+      <c r="PM2" s="1" t="inlineStr"/>
+      <c r="PN2" s="1" t="inlineStr"/>
+      <c r="PO2" s="1" t="inlineStr"/>
+      <c r="PP2" s="1" t="inlineStr"/>
+      <c r="PQ2" s="1" t="inlineStr"/>
+      <c r="PR2" s="1" t="inlineStr"/>
+      <c r="PS2" s="1" t="inlineStr"/>
+      <c r="PT2" s="1" t="inlineStr"/>
+      <c r="PU2" s="1" t="inlineStr"/>
+      <c r="PV2" s="1" t="inlineStr"/>
+      <c r="PW2" s="1" t="inlineStr"/>
+      <c r="PX2" s="1" t="inlineStr"/>
+      <c r="PY2" s="1" t="inlineStr"/>
+      <c r="PZ2" s="1" t="inlineStr"/>
+      <c r="QA2" s="1" t="inlineStr"/>
+      <c r="QB2" s="1" t="inlineStr"/>
+      <c r="QC2" s="1" t="inlineStr"/>
+      <c r="QD2" s="1" t="inlineStr"/>
+      <c r="QE2" s="1" t="inlineStr"/>
+      <c r="QF2" s="1" t="inlineStr"/>
+      <c r="QG2" s="1" t="inlineStr"/>
+      <c r="QH2" s="1" t="inlineStr"/>
+      <c r="QI2" s="1" t="inlineStr"/>
+      <c r="QJ2" s="1" t="inlineStr"/>
+      <c r="QK2" s="1" t="inlineStr"/>
+      <c r="QL2" s="1" t="inlineStr"/>
+      <c r="QM2" s="1" t="inlineStr"/>
+      <c r="QN2" s="1" t="inlineStr"/>
+      <c r="QO2" s="1" t="inlineStr"/>
+      <c r="QP2" s="1" t="inlineStr"/>
+      <c r="QQ2" s="1" t="inlineStr"/>
+      <c r="QR2" s="1" t="inlineStr"/>
+      <c r="QS2" s="1" t="inlineStr"/>
+      <c r="QT2" s="1" t="inlineStr"/>
+      <c r="QU2" s="1" t="inlineStr"/>
+      <c r="QV2" s="1" t="inlineStr"/>
+      <c r="QW2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
-      <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
-      <c r="CC3" t="inlineStr"/>
-      <c r="CD3" t="inlineStr"/>
-      <c r="CE3" t="inlineStr"/>
-      <c r="CF3" t="inlineStr"/>
-      <c r="CG3" t="inlineStr"/>
-      <c r="CH3" t="inlineStr"/>
-      <c r="CI3" t="inlineStr"/>
-      <c r="CJ3" t="inlineStr"/>
-      <c r="CK3" t="inlineStr"/>
-      <c r="CL3" t="inlineStr"/>
-      <c r="CM3" t="inlineStr"/>
-      <c r="CN3" t="inlineStr"/>
-      <c r="CO3" t="inlineStr"/>
-      <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="inlineStr"/>
-      <c r="CR3" t="inlineStr"/>
-      <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="inlineStr"/>
-      <c r="CV3" t="inlineStr"/>
-      <c r="CW3" t="inlineStr"/>
-      <c r="CX3" t="inlineStr"/>
-      <c r="CY3" t="inlineStr"/>
-      <c r="CZ3" t="inlineStr"/>
-      <c r="DA3" t="inlineStr"/>
-      <c r="DB3" t="inlineStr"/>
-      <c r="DC3" t="inlineStr"/>
-      <c r="DD3" t="inlineStr"/>
-      <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="inlineStr"/>
-      <c r="DG3" t="inlineStr"/>
-      <c r="DH3" t="inlineStr"/>
-      <c r="DI3" t="inlineStr"/>
-      <c r="DJ3" t="inlineStr"/>
-      <c r="DK3" t="inlineStr"/>
-      <c r="DL3" t="inlineStr"/>
-      <c r="DM3" t="inlineStr"/>
-      <c r="DN3" t="inlineStr"/>
-      <c r="DO3" t="inlineStr"/>
-      <c r="DP3" t="inlineStr"/>
-      <c r="DQ3" t="inlineStr"/>
-      <c r="DR3" t="inlineStr"/>
-      <c r="DS3" t="inlineStr"/>
-      <c r="DT3" t="inlineStr"/>
-      <c r="DU3" t="inlineStr"/>
-      <c r="DV3" t="inlineStr"/>
-      <c r="DW3" t="inlineStr"/>
-      <c r="DX3" t="inlineStr"/>
-      <c r="DY3" t="inlineStr"/>
-      <c r="DZ3" t="inlineStr"/>
-      <c r="EA3" t="inlineStr"/>
-      <c r="EB3" t="inlineStr"/>
-      <c r="EC3" t="inlineStr"/>
-      <c r="ED3" t="inlineStr"/>
-      <c r="EE3" t="inlineStr"/>
-      <c r="EF3" t="inlineStr"/>
-      <c r="EG3" t="inlineStr"/>
-      <c r="EH3" t="inlineStr"/>
-      <c r="EI3" t="inlineStr"/>
-      <c r="EJ3" t="inlineStr"/>
-      <c r="EK3" t="inlineStr"/>
-      <c r="EL3" t="inlineStr"/>
-      <c r="EM3" t="inlineStr"/>
-      <c r="EN3" t="inlineStr"/>
-      <c r="EO3" t="inlineStr"/>
-      <c r="EP3" t="inlineStr"/>
-      <c r="EQ3" t="inlineStr"/>
-      <c r="ER3" t="inlineStr"/>
-      <c r="ES3" t="inlineStr"/>
-      <c r="ET3" t="inlineStr"/>
-      <c r="EU3" t="inlineStr"/>
-      <c r="EV3" t="inlineStr"/>
-      <c r="EW3" t="inlineStr"/>
-      <c r="EX3" t="inlineStr"/>
-      <c r="EY3" t="inlineStr"/>
-      <c r="EZ3" t="inlineStr"/>
-      <c r="FA3" t="inlineStr"/>
-      <c r="FB3" t="inlineStr"/>
-      <c r="FC3" t="inlineStr"/>
-      <c r="FD3" t="inlineStr"/>
-      <c r="FE3" t="inlineStr"/>
-      <c r="FF3" t="inlineStr"/>
-      <c r="FG3" t="inlineStr"/>
-      <c r="FH3" t="inlineStr"/>
-      <c r="FI3" t="inlineStr"/>
-      <c r="FJ3" t="inlineStr"/>
-      <c r="FK3" t="inlineStr"/>
-      <c r="FL3" t="inlineStr"/>
-      <c r="FM3" t="inlineStr"/>
-      <c r="FN3" t="inlineStr"/>
-      <c r="FO3" t="inlineStr"/>
-      <c r="FP3" t="inlineStr"/>
-      <c r="FQ3" t="inlineStr"/>
-      <c r="FR3" t="inlineStr"/>
-      <c r="FS3" t="inlineStr"/>
-      <c r="FT3" t="inlineStr"/>
-      <c r="FU3" t="inlineStr"/>
-      <c r="FV3" t="inlineStr"/>
-      <c r="FW3" t="inlineStr"/>
-      <c r="FX3" t="inlineStr"/>
-      <c r="FY3" t="inlineStr"/>
-      <c r="FZ3" t="inlineStr"/>
-      <c r="GA3" t="inlineStr"/>
-      <c r="GB3" t="inlineStr"/>
-      <c r="GC3" t="inlineStr"/>
-      <c r="GD3" t="inlineStr"/>
-      <c r="GE3" t="inlineStr"/>
-      <c r="GF3" t="inlineStr"/>
-      <c r="GG3" t="inlineStr"/>
-      <c r="GH3" t="inlineStr"/>
-      <c r="GI3" t="inlineStr"/>
-      <c r="GJ3" t="inlineStr"/>
-      <c r="GK3" t="inlineStr"/>
-      <c r="GL3" t="inlineStr"/>
-      <c r="GM3" t="inlineStr"/>
-      <c r="GN3" t="inlineStr"/>
-      <c r="GO3" t="inlineStr"/>
-      <c r="GP3" t="inlineStr"/>
-      <c r="GQ3" t="inlineStr"/>
-      <c r="GR3" t="inlineStr"/>
-      <c r="GS3" t="inlineStr"/>
-      <c r="GT3" t="inlineStr"/>
-      <c r="GU3" t="inlineStr"/>
-      <c r="GV3" t="inlineStr"/>
-      <c r="GW3" t="inlineStr"/>
-      <c r="GX3" t="inlineStr"/>
-      <c r="GY3" t="inlineStr"/>
-      <c r="GZ3" t="inlineStr"/>
-      <c r="HA3" t="inlineStr"/>
-      <c r="HB3" t="inlineStr"/>
-      <c r="HC3" t="inlineStr"/>
-      <c r="HD3" t="inlineStr"/>
-      <c r="HE3" t="inlineStr"/>
-      <c r="HF3" t="inlineStr"/>
-      <c r="HG3" t="inlineStr"/>
-      <c r="HH3" t="inlineStr"/>
-      <c r="HI3" t="inlineStr"/>
-      <c r="HJ3" t="inlineStr"/>
-      <c r="HK3" t="inlineStr"/>
-      <c r="HL3" t="inlineStr"/>
-      <c r="HM3" t="inlineStr"/>
-      <c r="HN3" t="inlineStr"/>
-      <c r="HO3" t="inlineStr"/>
-      <c r="HP3" t="inlineStr"/>
-      <c r="HQ3" t="inlineStr"/>
-      <c r="HR3" t="inlineStr"/>
-      <c r="HS3" t="inlineStr"/>
-      <c r="HT3" t="inlineStr"/>
-      <c r="HU3" t="inlineStr"/>
-      <c r="HV3" t="inlineStr"/>
-      <c r="HW3" t="inlineStr"/>
-      <c r="HX3" t="inlineStr"/>
-      <c r="HY3" t="inlineStr"/>
-      <c r="HZ3" t="inlineStr"/>
-      <c r="IA3" t="inlineStr"/>
-      <c r="IB3" t="inlineStr"/>
-      <c r="IC3" t="inlineStr"/>
-      <c r="ID3" t="inlineStr"/>
-      <c r="IE3" t="inlineStr"/>
-      <c r="IF3" t="inlineStr"/>
-      <c r="IG3" t="inlineStr"/>
-      <c r="IH3" t="inlineStr"/>
-      <c r="II3" t="inlineStr"/>
-      <c r="IJ3" t="inlineStr"/>
-      <c r="IK3" t="inlineStr"/>
-      <c r="IL3" t="inlineStr"/>
-      <c r="IM3" t="inlineStr"/>
-      <c r="IN3" t="inlineStr"/>
-      <c r="IO3" t="inlineStr"/>
-      <c r="IP3" t="inlineStr"/>
-      <c r="IQ3" t="inlineStr"/>
-      <c r="IR3" t="inlineStr"/>
-      <c r="IS3" t="inlineStr"/>
-      <c r="IT3" t="inlineStr"/>
-      <c r="IU3" t="inlineStr"/>
-      <c r="IV3" t="inlineStr"/>
-      <c r="IW3" t="inlineStr"/>
-      <c r="IX3" t="inlineStr"/>
-      <c r="IY3" t="inlineStr"/>
-      <c r="IZ3" t="inlineStr"/>
-      <c r="JA3" t="inlineStr"/>
-      <c r="JB3" t="inlineStr"/>
-      <c r="JC3" t="inlineStr"/>
-      <c r="JD3" t="inlineStr"/>
-      <c r="JE3" t="inlineStr"/>
-      <c r="JF3" t="inlineStr"/>
-      <c r="JG3" t="inlineStr"/>
-      <c r="JH3" t="inlineStr"/>
-      <c r="JI3" t="inlineStr"/>
-      <c r="JJ3" t="inlineStr"/>
-      <c r="JK3" t="inlineStr"/>
-      <c r="JL3" t="inlineStr"/>
-      <c r="JM3" t="inlineStr"/>
-      <c r="JN3" t="inlineStr"/>
-      <c r="JO3" t="inlineStr"/>
-      <c r="JP3" t="inlineStr"/>
-      <c r="JQ3" t="inlineStr"/>
-      <c r="JR3" t="inlineStr"/>
-      <c r="JS3" t="inlineStr"/>
-      <c r="JT3" t="inlineStr"/>
-      <c r="JU3" t="inlineStr"/>
-      <c r="JV3" t="inlineStr"/>
-      <c r="JW3" t="inlineStr"/>
-      <c r="JX3" t="inlineStr"/>
-      <c r="JY3" t="inlineStr"/>
-      <c r="JZ3" t="inlineStr"/>
-      <c r="KA3" t="inlineStr"/>
-      <c r="KB3" t="inlineStr"/>
-      <c r="KC3" t="inlineStr"/>
-      <c r="KD3" t="inlineStr"/>
-      <c r="KE3" t="inlineStr"/>
-      <c r="KF3" t="inlineStr"/>
-      <c r="KG3" t="inlineStr"/>
-      <c r="KH3" t="inlineStr"/>
-      <c r="KI3" t="inlineStr"/>
-      <c r="KJ3" t="inlineStr"/>
-      <c r="KK3" t="inlineStr"/>
-      <c r="KL3" t="inlineStr"/>
-      <c r="KM3" t="inlineStr"/>
-      <c r="KN3" t="inlineStr"/>
-      <c r="KO3" t="inlineStr"/>
-      <c r="KP3" t="inlineStr"/>
-      <c r="KQ3" t="inlineStr"/>
-      <c r="KR3" t="inlineStr"/>
-      <c r="KS3" t="inlineStr"/>
-      <c r="KT3" t="inlineStr"/>
-      <c r="KU3" t="inlineStr"/>
-      <c r="KV3" t="inlineStr"/>
-      <c r="KW3" t="inlineStr"/>
-      <c r="KX3" t="inlineStr"/>
-      <c r="KY3" t="inlineStr"/>
-      <c r="KZ3" t="inlineStr"/>
-      <c r="LA3" t="inlineStr"/>
-      <c r="LB3" t="inlineStr"/>
-      <c r="LC3" t="inlineStr"/>
-      <c r="LD3" t="inlineStr"/>
-      <c r="LE3" t="inlineStr"/>
-      <c r="LF3" t="inlineStr"/>
-      <c r="LG3" t="inlineStr"/>
-      <c r="LH3" t="inlineStr"/>
-      <c r="LI3" t="inlineStr"/>
-      <c r="LJ3" t="inlineStr"/>
-      <c r="LK3" t="inlineStr"/>
-      <c r="LL3" t="inlineStr"/>
-      <c r="LM3" t="inlineStr"/>
-      <c r="LN3" t="inlineStr"/>
-      <c r="LO3" t="inlineStr"/>
-      <c r="LP3" t="inlineStr"/>
-      <c r="LQ3" t="inlineStr"/>
-      <c r="LR3" t="inlineStr"/>
-      <c r="LS3" t="inlineStr"/>
-      <c r="LT3" t="inlineStr"/>
-      <c r="LU3" t="inlineStr"/>
-      <c r="LV3" t="inlineStr"/>
-      <c r="LW3" t="inlineStr"/>
-      <c r="LX3" t="inlineStr"/>
-      <c r="LY3" t="inlineStr"/>
-      <c r="LZ3" t="inlineStr"/>
-      <c r="MA3" t="inlineStr"/>
-      <c r="MB3" t="inlineStr"/>
-      <c r="MC3" t="inlineStr"/>
-      <c r="MD3" t="inlineStr"/>
-      <c r="ME3" t="inlineStr"/>
-      <c r="MF3" t="inlineStr"/>
-      <c r="MG3" t="inlineStr"/>
-      <c r="MH3" t="inlineStr"/>
-      <c r="MI3" t="inlineStr"/>
-      <c r="MJ3" t="inlineStr"/>
-      <c r="MK3" t="inlineStr"/>
-      <c r="ML3" t="inlineStr"/>
-      <c r="MM3" t="inlineStr"/>
-      <c r="MN3" t="inlineStr"/>
-      <c r="MO3" t="inlineStr"/>
-      <c r="MP3" t="inlineStr"/>
-      <c r="MQ3" t="inlineStr"/>
-      <c r="MR3" t="inlineStr"/>
-      <c r="MS3" t="inlineStr"/>
-      <c r="MT3" t="inlineStr"/>
-      <c r="MU3" t="inlineStr"/>
-      <c r="MV3" t="inlineStr"/>
-      <c r="MW3" t="inlineStr"/>
-      <c r="MX3" t="inlineStr"/>
-      <c r="MY3" t="inlineStr"/>
-      <c r="MZ3" t="inlineStr"/>
-      <c r="NA3" t="inlineStr"/>
-      <c r="NB3" t="inlineStr"/>
-      <c r="NC3" t="inlineStr"/>
-      <c r="ND3" t="inlineStr"/>
-      <c r="NE3" t="inlineStr"/>
-      <c r="NF3" t="inlineStr"/>
-      <c r="NG3" t="inlineStr"/>
-      <c r="NH3" t="inlineStr"/>
-      <c r="NI3" t="inlineStr"/>
-      <c r="NJ3" t="inlineStr"/>
-      <c r="NK3" t="inlineStr"/>
-      <c r="NL3" t="inlineStr"/>
-      <c r="NM3" t="inlineStr"/>
-      <c r="NN3" t="inlineStr"/>
-      <c r="NO3" t="inlineStr"/>
-      <c r="NP3" t="inlineStr"/>
-      <c r="NQ3" t="inlineStr"/>
-      <c r="NR3" t="inlineStr"/>
-      <c r="NS3" t="inlineStr"/>
-      <c r="NT3" t="inlineStr"/>
-      <c r="NU3" t="inlineStr"/>
-      <c r="NV3" t="inlineStr"/>
-      <c r="NW3" t="inlineStr"/>
-      <c r="NX3" t="inlineStr"/>
-      <c r="NY3" t="inlineStr"/>
-      <c r="NZ3" t="inlineStr"/>
-      <c r="OA3" t="inlineStr"/>
-      <c r="OB3" t="inlineStr"/>
-      <c r="OC3" t="inlineStr"/>
-      <c r="OD3" t="inlineStr"/>
-      <c r="OE3" t="inlineStr"/>
-      <c r="OF3" t="inlineStr"/>
-      <c r="OG3" t="inlineStr"/>
-      <c r="OH3" t="inlineStr"/>
-      <c r="OI3" t="inlineStr"/>
-      <c r="OJ3" t="inlineStr"/>
-      <c r="OK3" t="inlineStr"/>
-      <c r="OL3" t="inlineStr"/>
-      <c r="OM3" t="inlineStr"/>
-      <c r="ON3" t="inlineStr"/>
-      <c r="OO3" t="inlineStr"/>
-      <c r="OP3" t="inlineStr"/>
-      <c r="OQ3" t="inlineStr"/>
-      <c r="OR3" t="inlineStr"/>
-      <c r="OS3" t="inlineStr"/>
-      <c r="OT3" t="inlineStr"/>
-      <c r="OU3" t="inlineStr"/>
-      <c r="OV3" t="inlineStr"/>
-      <c r="OW3" t="inlineStr"/>
-      <c r="OX3" t="inlineStr"/>
-      <c r="OY3" t="inlineStr"/>
-      <c r="OZ3" t="inlineStr"/>
-      <c r="PA3" t="inlineStr"/>
-      <c r="PB3" t="inlineStr"/>
-      <c r="PC3" t="inlineStr"/>
-      <c r="PD3" t="inlineStr"/>
-      <c r="PE3" t="inlineStr"/>
-      <c r="PF3" t="inlineStr"/>
-      <c r="PG3" t="inlineStr"/>
-      <c r="PH3" t="inlineStr"/>
-      <c r="PI3" t="inlineStr"/>
-      <c r="PJ3" t="inlineStr"/>
-      <c r="PK3" t="inlineStr"/>
-      <c r="PL3" t="inlineStr"/>
-      <c r="PM3" t="inlineStr"/>
-      <c r="PN3" t="inlineStr"/>
-      <c r="PO3" t="inlineStr"/>
-      <c r="PP3" t="inlineStr"/>
-      <c r="PQ3" t="inlineStr"/>
-      <c r="PR3" t="inlineStr"/>
-      <c r="PS3" t="inlineStr"/>
-      <c r="PT3" t="inlineStr"/>
-      <c r="PU3" t="inlineStr"/>
-      <c r="PV3" t="inlineStr"/>
-      <c r="PW3" t="inlineStr"/>
-      <c r="PX3" t="inlineStr"/>
-      <c r="PY3" t="inlineStr"/>
-      <c r="PZ3" t="inlineStr"/>
-      <c r="QA3" t="inlineStr"/>
-      <c r="QB3" t="inlineStr"/>
-      <c r="QC3" t="inlineStr"/>
-      <c r="QD3" t="inlineStr"/>
-      <c r="QE3" t="inlineStr"/>
-      <c r="QF3" t="inlineStr"/>
-      <c r="QG3" t="inlineStr"/>
-      <c r="QH3" t="inlineStr"/>
-      <c r="QI3" t="inlineStr"/>
-      <c r="QJ3" t="inlineStr"/>
-      <c r="QK3" t="inlineStr"/>
-      <c r="QL3" t="inlineStr"/>
-      <c r="QM3" t="inlineStr"/>
-      <c r="QN3" t="inlineStr"/>
-      <c r="QO3" t="inlineStr"/>
-      <c r="QP3" t="inlineStr"/>
-      <c r="QQ3" t="inlineStr"/>
-      <c r="QR3" t="inlineStr"/>
-      <c r="QS3" t="inlineStr"/>
-      <c r="QT3" t="inlineStr"/>
-      <c r="QU3" t="inlineStr"/>
-      <c r="QV3" t="inlineStr"/>
-      <c r="QW3" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr"/>
+      <c r="G3" s="1" t="inlineStr"/>
+      <c r="H3" s="1" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
+      <c r="L3" s="1" t="inlineStr"/>
+      <c r="M3" s="1" t="inlineStr"/>
+      <c r="N3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr"/>
+      <c r="P3" s="1" t="inlineStr"/>
+      <c r="Q3" s="1" t="inlineStr"/>
+      <c r="R3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr"/>
+      <c r="T3" s="1" t="inlineStr"/>
+      <c r="U3" s="1" t="inlineStr"/>
+      <c r="V3" s="1" t="inlineStr"/>
+      <c r="W3" s="1" t="inlineStr"/>
+      <c r="X3" s="1" t="inlineStr"/>
+      <c r="Y3" s="1" t="inlineStr"/>
+      <c r="Z3" s="1" t="inlineStr"/>
+      <c r="AA3" s="1" t="inlineStr"/>
+      <c r="AB3" s="1" t="inlineStr"/>
+      <c r="AC3" s="1" t="inlineStr"/>
+      <c r="AD3" s="1" t="inlineStr"/>
+      <c r="AE3" s="1" t="inlineStr"/>
+      <c r="AF3" s="1" t="inlineStr"/>
+      <c r="AG3" s="1" t="inlineStr"/>
+      <c r="AH3" s="1" t="inlineStr"/>
+      <c r="AI3" s="1" t="inlineStr"/>
+      <c r="AJ3" s="1" t="inlineStr"/>
+      <c r="AK3" s="1" t="inlineStr"/>
+      <c r="AL3" s="1" t="inlineStr"/>
+      <c r="AM3" s="1" t="inlineStr"/>
+      <c r="AN3" s="1" t="inlineStr"/>
+      <c r="AO3" s="1" t="inlineStr"/>
+      <c r="AP3" s="1" t="inlineStr"/>
+      <c r="AQ3" s="1" t="inlineStr"/>
+      <c r="AR3" s="1" t="inlineStr"/>
+      <c r="AS3" s="1" t="inlineStr"/>
+      <c r="AT3" s="1" t="inlineStr"/>
+      <c r="AU3" s="1" t="inlineStr"/>
+      <c r="AV3" s="1" t="inlineStr"/>
+      <c r="AW3" s="1" t="inlineStr"/>
+      <c r="AX3" s="1" t="inlineStr"/>
+      <c r="AY3" s="1" t="inlineStr"/>
+      <c r="AZ3" s="1" t="inlineStr"/>
+      <c r="BA3" s="1" t="inlineStr"/>
+      <c r="BB3" s="1" t="inlineStr"/>
+      <c r="BC3" s="1" t="inlineStr"/>
+      <c r="BD3" s="1" t="inlineStr"/>
+      <c r="BE3" s="1" t="inlineStr"/>
+      <c r="BF3" s="1" t="inlineStr"/>
+      <c r="BG3" s="1" t="inlineStr"/>
+      <c r="BH3" s="1" t="inlineStr"/>
+      <c r="BI3" s="1" t="inlineStr"/>
+      <c r="BJ3" s="1" t="inlineStr"/>
+      <c r="BK3" s="1" t="inlineStr"/>
+      <c r="BL3" s="1" t="inlineStr"/>
+      <c r="BM3" s="1" t="inlineStr"/>
+      <c r="BN3" s="1" t="inlineStr"/>
+      <c r="BO3" s="1" t="inlineStr"/>
+      <c r="BP3" s="1" t="inlineStr"/>
+      <c r="BQ3" s="1" t="inlineStr"/>
+      <c r="BR3" s="1" t="inlineStr"/>
+      <c r="BS3" s="1" t="inlineStr"/>
+      <c r="BT3" s="1" t="inlineStr"/>
+      <c r="BU3" s="1" t="inlineStr"/>
+      <c r="BV3" s="1" t="inlineStr"/>
+      <c r="BW3" s="1" t="inlineStr"/>
+      <c r="BX3" s="1" t="inlineStr"/>
+      <c r="BY3" s="1" t="inlineStr"/>
+      <c r="BZ3" s="1" t="inlineStr"/>
+      <c r="CA3" s="1" t="inlineStr"/>
+      <c r="CB3" s="1" t="inlineStr"/>
+      <c r="CC3" s="1" t="inlineStr"/>
+      <c r="CD3" s="1" t="inlineStr"/>
+      <c r="CE3" s="1" t="inlineStr"/>
+      <c r="CF3" s="1" t="inlineStr"/>
+      <c r="CG3" s="1" t="inlineStr"/>
+      <c r="CH3" s="1" t="inlineStr"/>
+      <c r="CI3" s="1" t="inlineStr"/>
+      <c r="CJ3" s="1" t="inlineStr"/>
+      <c r="CK3" s="1" t="inlineStr"/>
+      <c r="CL3" s="1" t="inlineStr"/>
+      <c r="CM3" s="1" t="inlineStr"/>
+      <c r="CN3" s="1" t="inlineStr"/>
+      <c r="CO3" s="1" t="inlineStr"/>
+      <c r="CP3" s="1" t="inlineStr"/>
+      <c r="CQ3" s="1" t="inlineStr"/>
+      <c r="CR3" s="1" t="inlineStr"/>
+      <c r="CS3" s="1" t="inlineStr"/>
+      <c r="CT3" s="1" t="inlineStr"/>
+      <c r="CU3" s="1" t="inlineStr"/>
+      <c r="CV3" s="1" t="inlineStr"/>
+      <c r="CW3" s="1" t="inlineStr"/>
+      <c r="CX3" s="1" t="inlineStr"/>
+      <c r="CY3" s="1" t="inlineStr"/>
+      <c r="CZ3" s="1" t="inlineStr"/>
+      <c r="DA3" s="1" t="inlineStr"/>
+      <c r="DB3" s="1" t="inlineStr"/>
+      <c r="DC3" s="1" t="inlineStr"/>
+      <c r="DD3" s="1" t="inlineStr"/>
+      <c r="DE3" s="1" t="inlineStr"/>
+      <c r="DF3" s="1" t="inlineStr"/>
+      <c r="DG3" s="1" t="inlineStr"/>
+      <c r="DH3" s="1" t="inlineStr"/>
+      <c r="DI3" s="1" t="inlineStr"/>
+      <c r="DJ3" s="1" t="inlineStr"/>
+      <c r="DK3" s="1" t="inlineStr"/>
+      <c r="DL3" s="1" t="inlineStr"/>
+      <c r="DM3" s="1" t="inlineStr"/>
+      <c r="DN3" s="1" t="inlineStr"/>
+      <c r="DO3" s="1" t="inlineStr"/>
+      <c r="DP3" s="1" t="inlineStr"/>
+      <c r="DQ3" s="1" t="inlineStr"/>
+      <c r="DR3" s="1" t="inlineStr"/>
+      <c r="DS3" s="1" t="inlineStr"/>
+      <c r="DT3" s="1" t="inlineStr"/>
+      <c r="DU3" s="1" t="inlineStr"/>
+      <c r="DV3" s="1" t="inlineStr"/>
+      <c r="DW3" s="1" t="inlineStr"/>
+      <c r="DX3" s="1" t="inlineStr"/>
+      <c r="DY3" s="1" t="inlineStr"/>
+      <c r="DZ3" s="1" t="inlineStr"/>
+      <c r="EA3" s="1" t="inlineStr"/>
+      <c r="EB3" s="1" t="inlineStr"/>
+      <c r="EC3" s="1" t="inlineStr"/>
+      <c r="ED3" s="1" t="inlineStr"/>
+      <c r="EE3" s="1" t="inlineStr"/>
+      <c r="EF3" s="1" t="inlineStr"/>
+      <c r="EG3" s="1" t="inlineStr"/>
+      <c r="EH3" s="1" t="inlineStr"/>
+      <c r="EI3" s="1" t="inlineStr"/>
+      <c r="EJ3" s="1" t="inlineStr"/>
+      <c r="EK3" s="1" t="inlineStr"/>
+      <c r="EL3" s="1" t="inlineStr"/>
+      <c r="EM3" s="1" t="inlineStr"/>
+      <c r="EN3" s="1" t="inlineStr"/>
+      <c r="EO3" s="1" t="inlineStr"/>
+      <c r="EP3" s="1" t="inlineStr"/>
+      <c r="EQ3" s="1" t="inlineStr"/>
+      <c r="ER3" s="1" t="inlineStr"/>
+      <c r="ES3" s="1" t="inlineStr"/>
+      <c r="ET3" s="1" t="inlineStr"/>
+      <c r="EU3" s="1" t="inlineStr"/>
+      <c r="EV3" s="1" t="inlineStr"/>
+      <c r="EW3" s="1" t="inlineStr"/>
+      <c r="EX3" s="1" t="inlineStr"/>
+      <c r="EY3" s="1" t="inlineStr"/>
+      <c r="EZ3" s="1" t="inlineStr"/>
+      <c r="FA3" s="1" t="inlineStr"/>
+      <c r="FB3" s="1" t="inlineStr"/>
+      <c r="FC3" s="1" t="inlineStr"/>
+      <c r="FD3" s="1" t="inlineStr"/>
+      <c r="FE3" s="1" t="inlineStr"/>
+      <c r="FF3" s="1" t="inlineStr"/>
+      <c r="FG3" s="1" t="inlineStr"/>
+      <c r="FH3" s="1" t="inlineStr"/>
+      <c r="FI3" s="1" t="inlineStr"/>
+      <c r="FJ3" s="1" t="inlineStr"/>
+      <c r="FK3" s="1" t="inlineStr"/>
+      <c r="FL3" s="1" t="inlineStr"/>
+      <c r="FM3" s="1" t="inlineStr"/>
+      <c r="FN3" s="1" t="inlineStr"/>
+      <c r="FO3" s="1" t="inlineStr"/>
+      <c r="FP3" s="1" t="inlineStr"/>
+      <c r="FQ3" s="1" t="inlineStr"/>
+      <c r="FR3" s="1" t="inlineStr"/>
+      <c r="FS3" s="1" t="inlineStr"/>
+      <c r="FT3" s="1" t="inlineStr"/>
+      <c r="FU3" s="1" t="inlineStr"/>
+      <c r="FV3" s="1" t="inlineStr"/>
+      <c r="FW3" s="1" t="inlineStr"/>
+      <c r="FX3" s="1" t="inlineStr"/>
+      <c r="FY3" s="1" t="inlineStr"/>
+      <c r="FZ3" s="1" t="inlineStr"/>
+      <c r="GA3" s="1" t="inlineStr"/>
+      <c r="GB3" s="1" t="inlineStr"/>
+      <c r="GC3" s="1" t="inlineStr"/>
+      <c r="GD3" s="1" t="inlineStr"/>
+      <c r="GE3" s="1" t="inlineStr"/>
+      <c r="GF3" s="1" t="inlineStr"/>
+      <c r="GG3" s="1" t="inlineStr"/>
+      <c r="GH3" s="1" t="inlineStr"/>
+      <c r="GI3" s="1" t="inlineStr"/>
+      <c r="GJ3" s="1" t="inlineStr"/>
+      <c r="GK3" s="1" t="inlineStr"/>
+      <c r="GL3" s="1" t="inlineStr"/>
+      <c r="GM3" s="1" t="inlineStr"/>
+      <c r="GN3" s="1" t="inlineStr"/>
+      <c r="GO3" s="1" t="inlineStr"/>
+      <c r="GP3" s="1" t="inlineStr"/>
+      <c r="GQ3" s="1" t="inlineStr"/>
+      <c r="GR3" s="1" t="inlineStr"/>
+      <c r="GS3" s="1" t="inlineStr"/>
+      <c r="GT3" s="1" t="inlineStr"/>
+      <c r="GU3" s="1" t="inlineStr"/>
+      <c r="GV3" s="1" t="inlineStr"/>
+      <c r="GW3" s="1" t="inlineStr"/>
+      <c r="GX3" s="1" t="inlineStr"/>
+      <c r="GY3" s="1" t="inlineStr"/>
+      <c r="GZ3" s="1" t="inlineStr"/>
+      <c r="HA3" s="1" t="inlineStr"/>
+      <c r="HB3" s="1" t="inlineStr"/>
+      <c r="HC3" s="1" t="inlineStr"/>
+      <c r="HD3" s="1" t="inlineStr"/>
+      <c r="HE3" s="1" t="inlineStr"/>
+      <c r="HF3" s="1" t="inlineStr"/>
+      <c r="HG3" s="1" t="inlineStr"/>
+      <c r="HH3" s="1" t="inlineStr"/>
+      <c r="HI3" s="1" t="inlineStr"/>
+      <c r="HJ3" s="1" t="inlineStr"/>
+      <c r="HK3" s="1" t="inlineStr"/>
+      <c r="HL3" s="1" t="inlineStr"/>
+      <c r="HM3" s="1" t="inlineStr"/>
+      <c r="HN3" s="1" t="inlineStr"/>
+      <c r="HO3" s="1" t="inlineStr"/>
+      <c r="HP3" s="1" t="inlineStr"/>
+      <c r="HQ3" s="1" t="inlineStr"/>
+      <c r="HR3" s="1" t="inlineStr"/>
+      <c r="HS3" s="1" t="inlineStr"/>
+      <c r="HT3" s="1" t="inlineStr"/>
+      <c r="HU3" s="1" t="inlineStr"/>
+      <c r="HV3" s="1" t="inlineStr"/>
+      <c r="HW3" s="1" t="inlineStr"/>
+      <c r="HX3" s="1" t="inlineStr"/>
+      <c r="HY3" s="1" t="inlineStr"/>
+      <c r="HZ3" s="1" t="inlineStr"/>
+      <c r="IA3" s="1" t="inlineStr"/>
+      <c r="IB3" s="1" t="inlineStr"/>
+      <c r="IC3" s="1" t="inlineStr"/>
+      <c r="ID3" s="1" t="inlineStr"/>
+      <c r="IE3" s="1" t="inlineStr"/>
+      <c r="IF3" s="1" t="inlineStr"/>
+      <c r="IG3" s="1" t="inlineStr"/>
+      <c r="IH3" s="1" t="inlineStr"/>
+      <c r="II3" s="1" t="inlineStr"/>
+      <c r="IJ3" s="1" t="inlineStr"/>
+      <c r="IK3" s="1" t="inlineStr"/>
+      <c r="IL3" s="1" t="inlineStr"/>
+      <c r="IM3" s="1" t="inlineStr"/>
+      <c r="IN3" s="1" t="inlineStr"/>
+      <c r="IO3" s="1" t="inlineStr"/>
+      <c r="IP3" s="1" t="inlineStr"/>
+      <c r="IQ3" s="1" t="inlineStr"/>
+      <c r="IR3" s="1" t="inlineStr"/>
+      <c r="IS3" s="1" t="inlineStr"/>
+      <c r="IT3" s="1" t="inlineStr"/>
+      <c r="IU3" s="1" t="inlineStr"/>
+      <c r="IV3" s="1" t="inlineStr"/>
+      <c r="IW3" s="1" t="inlineStr"/>
+      <c r="IX3" s="1" t="inlineStr"/>
+      <c r="IY3" s="1" t="inlineStr"/>
+      <c r="IZ3" s="1" t="inlineStr"/>
+      <c r="JA3" s="1" t="inlineStr"/>
+      <c r="JB3" s="1" t="inlineStr"/>
+      <c r="JC3" s="1" t="inlineStr"/>
+      <c r="JD3" s="1" t="inlineStr"/>
+      <c r="JE3" s="1" t="inlineStr"/>
+      <c r="JF3" s="1" t="inlineStr"/>
+      <c r="JG3" s="1" t="inlineStr"/>
+      <c r="JH3" s="1" t="inlineStr"/>
+      <c r="JI3" s="1" t="inlineStr"/>
+      <c r="JJ3" s="1" t="inlineStr"/>
+      <c r="JK3" s="1" t="inlineStr"/>
+      <c r="JL3" s="1" t="inlineStr"/>
+      <c r="JM3" s="1" t="inlineStr"/>
+      <c r="JN3" s="1" t="inlineStr"/>
+      <c r="JO3" s="1" t="inlineStr"/>
+      <c r="JP3" s="1" t="inlineStr"/>
+      <c r="JQ3" s="1" t="inlineStr"/>
+      <c r="JR3" s="1" t="inlineStr"/>
+      <c r="JS3" s="1" t="inlineStr"/>
+      <c r="JT3" s="1" t="inlineStr"/>
+      <c r="JU3" s="1" t="inlineStr"/>
+      <c r="JV3" s="1" t="inlineStr"/>
+      <c r="JW3" s="1" t="inlineStr"/>
+      <c r="JX3" s="1" t="inlineStr"/>
+      <c r="JY3" s="1" t="inlineStr"/>
+      <c r="JZ3" s="1" t="inlineStr"/>
+      <c r="KA3" s="1" t="inlineStr"/>
+      <c r="KB3" s="1" t="inlineStr"/>
+      <c r="KC3" s="1" t="inlineStr"/>
+      <c r="KD3" s="1" t="inlineStr"/>
+      <c r="KE3" s="1" t="inlineStr"/>
+      <c r="KF3" s="1" t="inlineStr"/>
+      <c r="KG3" s="1" t="inlineStr"/>
+      <c r="KH3" s="1" t="inlineStr"/>
+      <c r="KI3" s="1" t="inlineStr"/>
+      <c r="KJ3" s="1" t="inlineStr"/>
+      <c r="KK3" s="1" t="inlineStr"/>
+      <c r="KL3" s="1" t="inlineStr"/>
+      <c r="KM3" s="1" t="inlineStr"/>
+      <c r="KN3" s="1" t="inlineStr"/>
+      <c r="KO3" s="1" t="inlineStr"/>
+      <c r="KP3" s="1" t="inlineStr"/>
+      <c r="KQ3" s="1" t="inlineStr"/>
+      <c r="KR3" s="1" t="inlineStr"/>
+      <c r="KS3" s="1" t="inlineStr"/>
+      <c r="KT3" s="1" t="inlineStr"/>
+      <c r="KU3" s="1" t="inlineStr"/>
+      <c r="KV3" s="1" t="inlineStr"/>
+      <c r="KW3" s="1" t="inlineStr"/>
+      <c r="KX3" s="1" t="inlineStr"/>
+      <c r="KY3" s="1" t="inlineStr"/>
+      <c r="KZ3" s="1" t="inlineStr"/>
+      <c r="LA3" s="1" t="inlineStr"/>
+      <c r="LB3" s="1" t="inlineStr"/>
+      <c r="LC3" s="1" t="inlineStr"/>
+      <c r="LD3" s="1" t="inlineStr"/>
+      <c r="LE3" s="1" t="inlineStr"/>
+      <c r="LF3" s="1" t="inlineStr"/>
+      <c r="LG3" s="1" t="inlineStr"/>
+      <c r="LH3" s="1" t="inlineStr"/>
+      <c r="LI3" s="1" t="inlineStr"/>
+      <c r="LJ3" s="1" t="inlineStr"/>
+      <c r="LK3" s="1" t="inlineStr"/>
+      <c r="LL3" s="1" t="inlineStr"/>
+      <c r="LM3" s="1" t="inlineStr"/>
+      <c r="LN3" s="1" t="inlineStr"/>
+      <c r="LO3" s="1" t="inlineStr"/>
+      <c r="LP3" s="1" t="inlineStr"/>
+      <c r="LQ3" s="1" t="inlineStr"/>
+      <c r="LR3" s="1" t="inlineStr"/>
+      <c r="LS3" s="1" t="inlineStr"/>
+      <c r="LT3" s="1" t="inlineStr"/>
+      <c r="LU3" s="1" t="inlineStr"/>
+      <c r="LV3" s="1" t="inlineStr"/>
+      <c r="LW3" s="1" t="inlineStr"/>
+      <c r="LX3" s="1" t="inlineStr"/>
+      <c r="LY3" s="1" t="inlineStr"/>
+      <c r="LZ3" s="1" t="inlineStr"/>
+      <c r="MA3" s="1" t="inlineStr"/>
+      <c r="MB3" s="1" t="inlineStr"/>
+      <c r="MC3" s="1" t="inlineStr"/>
+      <c r="MD3" s="1" t="inlineStr"/>
+      <c r="ME3" s="1" t="inlineStr"/>
+      <c r="MF3" s="1" t="inlineStr"/>
+      <c r="MG3" s="1" t="inlineStr"/>
+      <c r="MH3" s="1" t="inlineStr"/>
+      <c r="MI3" s="1" t="inlineStr"/>
+      <c r="MJ3" s="1" t="inlineStr"/>
+      <c r="MK3" s="1" t="inlineStr"/>
+      <c r="ML3" s="1" t="inlineStr"/>
+      <c r="MM3" s="1" t="inlineStr"/>
+      <c r="MN3" s="1" t="inlineStr"/>
+      <c r="MO3" s="1" t="inlineStr"/>
+      <c r="MP3" s="1" t="inlineStr"/>
+      <c r="MQ3" s="1" t="inlineStr"/>
+      <c r="MR3" s="1" t="inlineStr"/>
+      <c r="MS3" s="1" t="inlineStr"/>
+      <c r="MT3" s="1" t="inlineStr"/>
+      <c r="MU3" s="1" t="inlineStr"/>
+      <c r="MV3" s="1" t="inlineStr"/>
+      <c r="MW3" s="1" t="inlineStr"/>
+      <c r="MX3" s="1" t="inlineStr"/>
+      <c r="MY3" s="1" t="inlineStr"/>
+      <c r="MZ3" s="1" t="inlineStr"/>
+      <c r="NA3" s="1" t="inlineStr"/>
+      <c r="NB3" s="1" t="inlineStr"/>
+      <c r="NC3" s="1" t="inlineStr"/>
+      <c r="ND3" s="1" t="inlineStr"/>
+      <c r="NE3" s="1" t="inlineStr"/>
+      <c r="NF3" s="1" t="inlineStr"/>
+      <c r="NG3" s="1" t="inlineStr"/>
+      <c r="NH3" s="1" t="inlineStr"/>
+      <c r="NI3" s="1" t="inlineStr"/>
+      <c r="NJ3" s="1" t="inlineStr"/>
+      <c r="NK3" s="1" t="inlineStr"/>
+      <c r="NL3" s="1" t="inlineStr"/>
+      <c r="NM3" s="1" t="inlineStr"/>
+      <c r="NN3" s="1" t="inlineStr"/>
+      <c r="NO3" s="1" t="inlineStr"/>
+      <c r="NP3" s="1" t="inlineStr"/>
+      <c r="NQ3" s="1" t="inlineStr"/>
+      <c r="NR3" s="1" t="inlineStr"/>
+      <c r="NS3" s="1" t="inlineStr"/>
+      <c r="NT3" s="1" t="inlineStr"/>
+      <c r="NU3" s="1" t="inlineStr"/>
+      <c r="NV3" s="1" t="inlineStr"/>
+      <c r="NW3" s="1" t="inlineStr"/>
+      <c r="NX3" s="1" t="inlineStr"/>
+      <c r="NY3" s="1" t="inlineStr"/>
+      <c r="NZ3" s="1" t="inlineStr"/>
+      <c r="OA3" s="1" t="inlineStr"/>
+      <c r="OB3" s="1" t="inlineStr"/>
+      <c r="OC3" s="1" t="inlineStr"/>
+      <c r="OD3" s="1" t="inlineStr"/>
+      <c r="OE3" s="1" t="inlineStr"/>
+      <c r="OF3" s="1" t="inlineStr"/>
+      <c r="OG3" s="1" t="inlineStr"/>
+      <c r="OH3" s="1" t="inlineStr"/>
+      <c r="OI3" s="1" t="inlineStr"/>
+      <c r="OJ3" s="1" t="inlineStr"/>
+      <c r="OK3" s="1" t="inlineStr"/>
+      <c r="OL3" s="1" t="inlineStr"/>
+      <c r="OM3" s="1" t="inlineStr"/>
+      <c r="ON3" s="1" t="inlineStr"/>
+      <c r="OO3" s="1" t="inlineStr"/>
+      <c r="OP3" s="1" t="inlineStr"/>
+      <c r="OQ3" s="1" t="inlineStr"/>
+      <c r="OR3" s="1" t="inlineStr"/>
+      <c r="OS3" s="1" t="inlineStr"/>
+      <c r="OT3" s="1" t="inlineStr"/>
+      <c r="OU3" s="1" t="inlineStr"/>
+      <c r="OV3" s="1" t="inlineStr"/>
+      <c r="OW3" s="1" t="inlineStr"/>
+      <c r="OX3" s="1" t="inlineStr"/>
+      <c r="OY3" s="1" t="inlineStr"/>
+      <c r="OZ3" s="1" t="inlineStr"/>
+      <c r="PA3" s="1" t="inlineStr"/>
+      <c r="PB3" s="1" t="inlineStr"/>
+      <c r="PC3" s="1" t="inlineStr"/>
+      <c r="PD3" s="1" t="inlineStr"/>
+      <c r="PE3" s="1" t="inlineStr"/>
+      <c r="PF3" s="1" t="inlineStr"/>
+      <c r="PG3" s="1" t="inlineStr"/>
+      <c r="PH3" s="1" t="inlineStr"/>
+      <c r="PI3" s="1" t="inlineStr"/>
+      <c r="PJ3" s="1" t="inlineStr"/>
+      <c r="PK3" s="1" t="inlineStr"/>
+      <c r="PL3" s="1" t="inlineStr"/>
+      <c r="PM3" s="1" t="inlineStr"/>
+      <c r="PN3" s="1" t="inlineStr"/>
+      <c r="PO3" s="1" t="inlineStr"/>
+      <c r="PP3" s="1" t="inlineStr"/>
+      <c r="PQ3" s="1" t="inlineStr"/>
+      <c r="PR3" s="1" t="inlineStr"/>
+      <c r="PS3" s="1" t="inlineStr"/>
+      <c r="PT3" s="1" t="inlineStr"/>
+      <c r="PU3" s="1" t="inlineStr"/>
+      <c r="PV3" s="1" t="inlineStr"/>
+      <c r="PW3" s="1" t="inlineStr"/>
+      <c r="PX3" s="1" t="inlineStr"/>
+      <c r="PY3" s="1" t="inlineStr"/>
+      <c r="PZ3" s="1" t="inlineStr"/>
+      <c r="QA3" s="1" t="inlineStr"/>
+      <c r="QB3" s="1" t="inlineStr"/>
+      <c r="QC3" s="1" t="inlineStr"/>
+      <c r="QD3" s="1" t="inlineStr"/>
+      <c r="QE3" s="1" t="inlineStr"/>
+      <c r="QF3" s="1" t="inlineStr"/>
+      <c r="QG3" s="1" t="inlineStr"/>
+      <c r="QH3" s="1" t="inlineStr"/>
+      <c r="QI3" s="1" t="inlineStr"/>
+      <c r="QJ3" s="1" t="inlineStr"/>
+      <c r="QK3" s="1" t="inlineStr"/>
+      <c r="QL3" s="1" t="inlineStr"/>
+      <c r="QM3" s="1" t="inlineStr"/>
+      <c r="QN3" s="1" t="inlineStr"/>
+      <c r="QO3" s="1" t="inlineStr"/>
+      <c r="QP3" s="1" t="inlineStr"/>
+      <c r="QQ3" s="1" t="inlineStr"/>
+      <c r="QR3" s="1" t="inlineStr"/>
+      <c r="QS3" s="1" t="inlineStr"/>
+      <c r="QT3" s="1" t="inlineStr"/>
+      <c r="QU3" s="1" t="inlineStr"/>
+      <c r="QV3" s="1" t="inlineStr"/>
+      <c r="QW3" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pink_sheet.xlsx
+++ b/data/pink_sheet.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +27,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -50,10 +55,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -890,7 +898,7 @@
     <col width="10" customWidth="1" min="465" max="465"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
@@ -3218,946 +3226,946 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
-      <c r="G2" s="1" t="inlineStr"/>
-      <c r="H2" s="1" t="inlineStr"/>
-      <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
-      <c r="K2" s="1" t="inlineStr"/>
-      <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
-      <c r="N2" s="1" t="inlineStr"/>
-      <c r="O2" s="1" t="inlineStr"/>
-      <c r="P2" s="1" t="inlineStr"/>
-      <c r="Q2" s="1" t="inlineStr"/>
-      <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
-      <c r="T2" s="1" t="inlineStr"/>
-      <c r="U2" s="1" t="inlineStr"/>
-      <c r="V2" s="1" t="inlineStr"/>
-      <c r="W2" s="1" t="inlineStr"/>
-      <c r="X2" s="1" t="inlineStr"/>
-      <c r="Y2" s="1" t="inlineStr"/>
-      <c r="Z2" s="1" t="inlineStr"/>
-      <c r="AA2" s="1" t="inlineStr"/>
-      <c r="AB2" s="1" t="inlineStr"/>
-      <c r="AC2" s="1" t="inlineStr"/>
-      <c r="AD2" s="1" t="inlineStr"/>
-      <c r="AE2" s="1" t="inlineStr"/>
-      <c r="AF2" s="1" t="inlineStr"/>
-      <c r="AG2" s="1" t="inlineStr"/>
-      <c r="AH2" s="1" t="inlineStr"/>
-      <c r="AI2" s="1" t="inlineStr"/>
-      <c r="AJ2" s="1" t="inlineStr"/>
-      <c r="AK2" s="1" t="inlineStr"/>
-      <c r="AL2" s="1" t="inlineStr"/>
-      <c r="AM2" s="1" t="inlineStr"/>
-      <c r="AN2" s="1" t="inlineStr"/>
-      <c r="AO2" s="1" t="inlineStr"/>
-      <c r="AP2" s="1" t="inlineStr"/>
-      <c r="AQ2" s="1" t="inlineStr"/>
-      <c r="AR2" s="1" t="inlineStr"/>
-      <c r="AS2" s="1" t="inlineStr"/>
-      <c r="AT2" s="1" t="inlineStr"/>
-      <c r="AU2" s="1" t="inlineStr"/>
-      <c r="AV2" s="1" t="inlineStr"/>
-      <c r="AW2" s="1" t="inlineStr"/>
-      <c r="AX2" s="1" t="inlineStr"/>
-      <c r="AY2" s="1" t="inlineStr"/>
-      <c r="AZ2" s="1" t="inlineStr"/>
-      <c r="BA2" s="1" t="inlineStr"/>
-      <c r="BB2" s="1" t="inlineStr"/>
-      <c r="BC2" s="1" t="inlineStr"/>
-      <c r="BD2" s="1" t="inlineStr"/>
-      <c r="BE2" s="1" t="inlineStr"/>
-      <c r="BF2" s="1" t="inlineStr"/>
-      <c r="BG2" s="1" t="inlineStr"/>
-      <c r="BH2" s="1" t="inlineStr"/>
-      <c r="BI2" s="1" t="inlineStr"/>
-      <c r="BJ2" s="1" t="inlineStr"/>
-      <c r="BK2" s="1" t="inlineStr"/>
-      <c r="BL2" s="1" t="inlineStr"/>
-      <c r="BM2" s="1" t="inlineStr"/>
-      <c r="BN2" s="1" t="inlineStr"/>
-      <c r="BO2" s="1" t="inlineStr"/>
-      <c r="BP2" s="1" t="inlineStr"/>
-      <c r="BQ2" s="1" t="inlineStr"/>
-      <c r="BR2" s="1" t="inlineStr"/>
-      <c r="BS2" s="1" t="inlineStr"/>
-      <c r="BT2" s="1" t="inlineStr"/>
-      <c r="BU2" s="1" t="inlineStr"/>
-      <c r="BV2" s="1" t="inlineStr"/>
-      <c r="BW2" s="1" t="inlineStr"/>
-      <c r="BX2" s="1" t="inlineStr"/>
-      <c r="BY2" s="1" t="inlineStr"/>
-      <c r="BZ2" s="1" t="inlineStr"/>
-      <c r="CA2" s="1" t="inlineStr"/>
-      <c r="CB2" s="1" t="inlineStr"/>
-      <c r="CC2" s="1" t="inlineStr"/>
-      <c r="CD2" s="1" t="inlineStr"/>
-      <c r="CE2" s="1" t="inlineStr"/>
-      <c r="CF2" s="1" t="inlineStr"/>
-      <c r="CG2" s="1" t="inlineStr"/>
-      <c r="CH2" s="1" t="inlineStr"/>
-      <c r="CI2" s="1" t="inlineStr"/>
-      <c r="CJ2" s="1" t="inlineStr"/>
-      <c r="CK2" s="1" t="inlineStr"/>
-      <c r="CL2" s="1" t="inlineStr"/>
-      <c r="CM2" s="1" t="inlineStr"/>
-      <c r="CN2" s="1" t="inlineStr"/>
-      <c r="CO2" s="1" t="inlineStr"/>
-      <c r="CP2" s="1" t="inlineStr"/>
-      <c r="CQ2" s="1" t="inlineStr"/>
-      <c r="CR2" s="1" t="inlineStr"/>
-      <c r="CS2" s="1" t="inlineStr"/>
-      <c r="CT2" s="1" t="inlineStr"/>
-      <c r="CU2" s="1" t="inlineStr"/>
-      <c r="CV2" s="1" t="inlineStr"/>
-      <c r="CW2" s="1" t="inlineStr"/>
-      <c r="CX2" s="1" t="inlineStr"/>
-      <c r="CY2" s="1" t="inlineStr"/>
-      <c r="CZ2" s="1" t="inlineStr"/>
-      <c r="DA2" s="1" t="inlineStr"/>
-      <c r="DB2" s="1" t="inlineStr"/>
-      <c r="DC2" s="1" t="inlineStr"/>
-      <c r="DD2" s="1" t="inlineStr"/>
-      <c r="DE2" s="1" t="inlineStr"/>
-      <c r="DF2" s="1" t="inlineStr"/>
-      <c r="DG2" s="1" t="inlineStr"/>
-      <c r="DH2" s="1" t="inlineStr"/>
-      <c r="DI2" s="1" t="inlineStr"/>
-      <c r="DJ2" s="1" t="inlineStr"/>
-      <c r="DK2" s="1" t="inlineStr"/>
-      <c r="DL2" s="1" t="inlineStr"/>
-      <c r="DM2" s="1" t="inlineStr"/>
-      <c r="DN2" s="1" t="inlineStr"/>
-      <c r="DO2" s="1" t="inlineStr"/>
-      <c r="DP2" s="1" t="inlineStr"/>
-      <c r="DQ2" s="1" t="inlineStr"/>
-      <c r="DR2" s="1" t="inlineStr"/>
-      <c r="DS2" s="1" t="inlineStr"/>
-      <c r="DT2" s="1" t="inlineStr"/>
-      <c r="DU2" s="1" t="inlineStr"/>
-      <c r="DV2" s="1" t="inlineStr"/>
-      <c r="DW2" s="1" t="inlineStr"/>
-      <c r="DX2" s="1" t="inlineStr"/>
-      <c r="DY2" s="1" t="inlineStr"/>
-      <c r="DZ2" s="1" t="inlineStr"/>
-      <c r="EA2" s="1" t="inlineStr"/>
-      <c r="EB2" s="1" t="inlineStr"/>
-      <c r="EC2" s="1" t="inlineStr"/>
-      <c r="ED2" s="1" t="inlineStr"/>
-      <c r="EE2" s="1" t="inlineStr"/>
-      <c r="EF2" s="1" t="inlineStr"/>
-      <c r="EG2" s="1" t="inlineStr"/>
-      <c r="EH2" s="1" t="inlineStr"/>
-      <c r="EI2" s="1" t="inlineStr"/>
-      <c r="EJ2" s="1" t="inlineStr"/>
-      <c r="EK2" s="1" t="inlineStr"/>
-      <c r="EL2" s="1" t="inlineStr"/>
-      <c r="EM2" s="1" t="inlineStr"/>
-      <c r="EN2" s="1" t="inlineStr"/>
-      <c r="EO2" s="1" t="inlineStr"/>
-      <c r="EP2" s="1" t="inlineStr"/>
-      <c r="EQ2" s="1" t="inlineStr"/>
-      <c r="ER2" s="1" t="inlineStr"/>
-      <c r="ES2" s="1" t="inlineStr"/>
-      <c r="ET2" s="1" t="inlineStr"/>
-      <c r="EU2" s="1" t="inlineStr"/>
-      <c r="EV2" s="1" t="inlineStr"/>
-      <c r="EW2" s="1" t="inlineStr"/>
-      <c r="EX2" s="1" t="inlineStr"/>
-      <c r="EY2" s="1" t="inlineStr"/>
-      <c r="EZ2" s="1" t="inlineStr"/>
-      <c r="FA2" s="1" t="inlineStr"/>
-      <c r="FB2" s="1" t="inlineStr"/>
-      <c r="FC2" s="1" t="inlineStr"/>
-      <c r="FD2" s="1" t="inlineStr"/>
-      <c r="FE2" s="1" t="inlineStr"/>
-      <c r="FF2" s="1" t="inlineStr"/>
-      <c r="FG2" s="1" t="inlineStr"/>
-      <c r="FH2" s="1" t="inlineStr"/>
-      <c r="FI2" s="1" t="inlineStr"/>
-      <c r="FJ2" s="1" t="inlineStr"/>
-      <c r="FK2" s="1" t="inlineStr"/>
-      <c r="FL2" s="1" t="inlineStr"/>
-      <c r="FM2" s="1" t="inlineStr"/>
-      <c r="FN2" s="1" t="inlineStr"/>
-      <c r="FO2" s="1" t="inlineStr"/>
-      <c r="FP2" s="1" t="inlineStr"/>
-      <c r="FQ2" s="1" t="inlineStr"/>
-      <c r="FR2" s="1" t="inlineStr"/>
-      <c r="FS2" s="1" t="inlineStr"/>
-      <c r="FT2" s="1" t="inlineStr"/>
-      <c r="FU2" s="1" t="inlineStr"/>
-      <c r="FV2" s="1" t="inlineStr"/>
-      <c r="FW2" s="1" t="inlineStr"/>
-      <c r="FX2" s="1" t="inlineStr"/>
-      <c r="FY2" s="1" t="inlineStr"/>
-      <c r="FZ2" s="1" t="inlineStr"/>
-      <c r="GA2" s="1" t="inlineStr"/>
-      <c r="GB2" s="1" t="inlineStr"/>
-      <c r="GC2" s="1" t="inlineStr"/>
-      <c r="GD2" s="1" t="inlineStr"/>
-      <c r="GE2" s="1" t="inlineStr"/>
-      <c r="GF2" s="1" t="inlineStr"/>
-      <c r="GG2" s="1" t="inlineStr"/>
-      <c r="GH2" s="1" t="inlineStr"/>
-      <c r="GI2" s="1" t="inlineStr"/>
-      <c r="GJ2" s="1" t="inlineStr"/>
-      <c r="GK2" s="1" t="inlineStr"/>
-      <c r="GL2" s="1" t="inlineStr"/>
-      <c r="GM2" s="1" t="inlineStr"/>
-      <c r="GN2" s="1" t="inlineStr"/>
-      <c r="GO2" s="1" t="inlineStr"/>
-      <c r="GP2" s="1" t="inlineStr"/>
-      <c r="GQ2" s="1" t="inlineStr"/>
-      <c r="GR2" s="1" t="inlineStr"/>
-      <c r="GS2" s="1" t="inlineStr"/>
-      <c r="GT2" s="1" t="inlineStr"/>
-      <c r="GU2" s="1" t="inlineStr"/>
-      <c r="GV2" s="1" t="inlineStr"/>
-      <c r="GW2" s="1" t="inlineStr"/>
-      <c r="GX2" s="1" t="inlineStr"/>
-      <c r="GY2" s="1" t="inlineStr"/>
-      <c r="GZ2" s="1" t="inlineStr"/>
-      <c r="HA2" s="1" t="inlineStr"/>
-      <c r="HB2" s="1" t="inlineStr"/>
-      <c r="HC2" s="1" t="inlineStr"/>
-      <c r="HD2" s="1" t="inlineStr"/>
-      <c r="HE2" s="1" t="inlineStr"/>
-      <c r="HF2" s="1" t="inlineStr"/>
-      <c r="HG2" s="1" t="inlineStr"/>
-      <c r="HH2" s="1" t="inlineStr"/>
-      <c r="HI2" s="1" t="inlineStr"/>
-      <c r="HJ2" s="1" t="inlineStr"/>
-      <c r="HK2" s="1" t="inlineStr"/>
-      <c r="HL2" s="1" t="inlineStr"/>
-      <c r="HM2" s="1" t="inlineStr"/>
-      <c r="HN2" s="1" t="inlineStr"/>
-      <c r="HO2" s="1" t="inlineStr"/>
-      <c r="HP2" s="1" t="inlineStr"/>
-      <c r="HQ2" s="1" t="inlineStr"/>
-      <c r="HR2" s="1" t="inlineStr"/>
-      <c r="HS2" s="1" t="inlineStr"/>
-      <c r="HT2" s="1" t="inlineStr"/>
-      <c r="HU2" s="1" t="inlineStr"/>
-      <c r="HV2" s="1" t="inlineStr"/>
-      <c r="HW2" s="1" t="inlineStr"/>
-      <c r="HX2" s="1" t="inlineStr"/>
-      <c r="HY2" s="1" t="inlineStr"/>
-      <c r="HZ2" s="1" t="inlineStr"/>
-      <c r="IA2" s="1" t="inlineStr"/>
-      <c r="IB2" s="1" t="inlineStr"/>
-      <c r="IC2" s="1" t="inlineStr"/>
-      <c r="ID2" s="1" t="inlineStr"/>
-      <c r="IE2" s="1" t="inlineStr"/>
-      <c r="IF2" s="1" t="inlineStr"/>
-      <c r="IG2" s="1" t="inlineStr"/>
-      <c r="IH2" s="1" t="inlineStr"/>
-      <c r="II2" s="1" t="inlineStr"/>
-      <c r="IJ2" s="1" t="inlineStr"/>
-      <c r="IK2" s="1" t="inlineStr"/>
-      <c r="IL2" s="1" t="inlineStr"/>
-      <c r="IM2" s="1" t="inlineStr"/>
-      <c r="IN2" s="1" t="inlineStr"/>
-      <c r="IO2" s="1" t="inlineStr"/>
-      <c r="IP2" s="1" t="inlineStr"/>
-      <c r="IQ2" s="1" t="inlineStr"/>
-      <c r="IR2" s="1" t="inlineStr"/>
-      <c r="IS2" s="1" t="inlineStr"/>
-      <c r="IT2" s="1" t="inlineStr"/>
-      <c r="IU2" s="1" t="inlineStr"/>
-      <c r="IV2" s="1" t="inlineStr"/>
-      <c r="IW2" s="1" t="inlineStr"/>
-      <c r="IX2" s="1" t="inlineStr"/>
-      <c r="IY2" s="1" t="inlineStr"/>
-      <c r="IZ2" s="1" t="inlineStr"/>
-      <c r="JA2" s="1" t="inlineStr"/>
-      <c r="JB2" s="1" t="inlineStr"/>
-      <c r="JC2" s="1" t="inlineStr"/>
-      <c r="JD2" s="1" t="inlineStr"/>
-      <c r="JE2" s="1" t="inlineStr"/>
-      <c r="JF2" s="1" t="inlineStr"/>
-      <c r="JG2" s="1" t="inlineStr"/>
-      <c r="JH2" s="1" t="inlineStr"/>
-      <c r="JI2" s="1" t="inlineStr"/>
-      <c r="JJ2" s="1" t="inlineStr"/>
-      <c r="JK2" s="1" t="inlineStr"/>
-      <c r="JL2" s="1" t="inlineStr"/>
-      <c r="JM2" s="1" t="inlineStr"/>
-      <c r="JN2" s="1" t="inlineStr"/>
-      <c r="JO2" s="1" t="inlineStr"/>
-      <c r="JP2" s="1" t="inlineStr"/>
-      <c r="JQ2" s="1" t="inlineStr"/>
-      <c r="JR2" s="1" t="inlineStr"/>
-      <c r="JS2" s="1" t="inlineStr"/>
-      <c r="JT2" s="1" t="inlineStr"/>
-      <c r="JU2" s="1" t="inlineStr"/>
-      <c r="JV2" s="1" t="inlineStr"/>
-      <c r="JW2" s="1" t="inlineStr"/>
-      <c r="JX2" s="1" t="inlineStr"/>
-      <c r="JY2" s="1" t="inlineStr"/>
-      <c r="JZ2" s="1" t="inlineStr"/>
-      <c r="KA2" s="1" t="inlineStr"/>
-      <c r="KB2" s="1" t="inlineStr"/>
-      <c r="KC2" s="1" t="inlineStr"/>
-      <c r="KD2" s="1" t="inlineStr"/>
-      <c r="KE2" s="1" t="inlineStr"/>
-      <c r="KF2" s="1" t="inlineStr"/>
-      <c r="KG2" s="1" t="inlineStr"/>
-      <c r="KH2" s="1" t="inlineStr"/>
-      <c r="KI2" s="1" t="inlineStr"/>
-      <c r="KJ2" s="1" t="inlineStr"/>
-      <c r="KK2" s="1" t="inlineStr"/>
-      <c r="KL2" s="1" t="inlineStr"/>
-      <c r="KM2" s="1" t="inlineStr"/>
-      <c r="KN2" s="1" t="inlineStr"/>
-      <c r="KO2" s="1" t="inlineStr"/>
-      <c r="KP2" s="1" t="inlineStr"/>
-      <c r="KQ2" s="1" t="inlineStr"/>
-      <c r="KR2" s="1" t="inlineStr"/>
-      <c r="KS2" s="1" t="inlineStr"/>
-      <c r="KT2" s="1" t="inlineStr"/>
-      <c r="KU2" s="1" t="inlineStr"/>
-      <c r="KV2" s="1" t="inlineStr"/>
-      <c r="KW2" s="1" t="inlineStr"/>
-      <c r="KX2" s="1" t="inlineStr"/>
-      <c r="KY2" s="1" t="inlineStr"/>
-      <c r="KZ2" s="1" t="inlineStr"/>
-      <c r="LA2" s="1" t="inlineStr"/>
-      <c r="LB2" s="1" t="inlineStr"/>
-      <c r="LC2" s="1" t="inlineStr"/>
-      <c r="LD2" s="1" t="inlineStr"/>
-      <c r="LE2" s="1" t="inlineStr"/>
-      <c r="LF2" s="1" t="inlineStr"/>
-      <c r="LG2" s="1" t="inlineStr"/>
-      <c r="LH2" s="1" t="inlineStr"/>
-      <c r="LI2" s="1" t="inlineStr"/>
-      <c r="LJ2" s="1" t="inlineStr"/>
-      <c r="LK2" s="1" t="inlineStr"/>
-      <c r="LL2" s="1" t="inlineStr"/>
-      <c r="LM2" s="1" t="inlineStr"/>
-      <c r="LN2" s="1" t="inlineStr"/>
-      <c r="LO2" s="1" t="inlineStr"/>
-      <c r="LP2" s="1" t="inlineStr"/>
-      <c r="LQ2" s="1" t="inlineStr"/>
-      <c r="LR2" s="1" t="inlineStr"/>
-      <c r="LS2" s="1" t="inlineStr"/>
-      <c r="LT2" s="1" t="inlineStr"/>
-      <c r="LU2" s="1" t="inlineStr"/>
-      <c r="LV2" s="1" t="inlineStr"/>
-      <c r="LW2" s="1" t="inlineStr"/>
-      <c r="LX2" s="1" t="inlineStr"/>
-      <c r="LY2" s="1" t="inlineStr"/>
-      <c r="LZ2" s="1" t="inlineStr"/>
-      <c r="MA2" s="1" t="inlineStr"/>
-      <c r="MB2" s="1" t="inlineStr"/>
-      <c r="MC2" s="1" t="inlineStr"/>
-      <c r="MD2" s="1" t="inlineStr"/>
-      <c r="ME2" s="1" t="inlineStr"/>
-      <c r="MF2" s="1" t="inlineStr"/>
-      <c r="MG2" s="1" t="inlineStr"/>
-      <c r="MH2" s="1" t="inlineStr"/>
-      <c r="MI2" s="1" t="inlineStr"/>
-      <c r="MJ2" s="1" t="inlineStr"/>
-      <c r="MK2" s="1" t="inlineStr"/>
-      <c r="ML2" s="1" t="inlineStr"/>
-      <c r="MM2" s="1" t="inlineStr"/>
-      <c r="MN2" s="1" t="inlineStr"/>
-      <c r="MO2" s="1" t="inlineStr"/>
-      <c r="MP2" s="1" t="inlineStr"/>
-      <c r="MQ2" s="1" t="inlineStr"/>
-      <c r="MR2" s="1" t="inlineStr"/>
-      <c r="MS2" s="1" t="inlineStr"/>
-      <c r="MT2" s="1" t="inlineStr"/>
-      <c r="MU2" s="1" t="inlineStr"/>
-      <c r="MV2" s="1" t="inlineStr"/>
-      <c r="MW2" s="1" t="inlineStr"/>
-      <c r="MX2" s="1" t="inlineStr"/>
-      <c r="MY2" s="1" t="inlineStr"/>
-      <c r="MZ2" s="1" t="inlineStr"/>
-      <c r="NA2" s="1" t="inlineStr"/>
-      <c r="NB2" s="1" t="inlineStr"/>
-      <c r="NC2" s="1" t="inlineStr"/>
-      <c r="ND2" s="1" t="inlineStr"/>
-      <c r="NE2" s="1" t="inlineStr"/>
-      <c r="NF2" s="1" t="inlineStr"/>
-      <c r="NG2" s="1" t="inlineStr"/>
-      <c r="NH2" s="1" t="inlineStr"/>
-      <c r="NI2" s="1" t="inlineStr"/>
-      <c r="NJ2" s="1" t="inlineStr"/>
-      <c r="NK2" s="1" t="inlineStr"/>
-      <c r="NL2" s="1" t="inlineStr"/>
-      <c r="NM2" s="1" t="inlineStr"/>
-      <c r="NN2" s="1" t="inlineStr"/>
-      <c r="NO2" s="1" t="inlineStr"/>
-      <c r="NP2" s="1" t="inlineStr"/>
-      <c r="NQ2" s="1" t="inlineStr"/>
-      <c r="NR2" s="1" t="inlineStr"/>
-      <c r="NS2" s="1" t="inlineStr"/>
-      <c r="NT2" s="1" t="inlineStr"/>
-      <c r="NU2" s="1" t="inlineStr"/>
-      <c r="NV2" s="1" t="inlineStr"/>
-      <c r="NW2" s="1" t="inlineStr"/>
-      <c r="NX2" s="1" t="inlineStr"/>
-      <c r="NY2" s="1" t="inlineStr"/>
-      <c r="NZ2" s="1" t="inlineStr"/>
-      <c r="OA2" s="1" t="inlineStr"/>
-      <c r="OB2" s="1" t="inlineStr"/>
-      <c r="OC2" s="1" t="inlineStr"/>
-      <c r="OD2" s="1" t="inlineStr"/>
-      <c r="OE2" s="1" t="inlineStr"/>
-      <c r="OF2" s="1" t="inlineStr"/>
-      <c r="OG2" s="1" t="inlineStr"/>
-      <c r="OH2" s="1" t="inlineStr"/>
-      <c r="OI2" s="1" t="inlineStr"/>
-      <c r="OJ2" s="1" t="inlineStr"/>
-      <c r="OK2" s="1" t="inlineStr"/>
-      <c r="OL2" s="1" t="inlineStr"/>
-      <c r="OM2" s="1" t="inlineStr"/>
-      <c r="ON2" s="1" t="inlineStr"/>
-      <c r="OO2" s="1" t="inlineStr"/>
-      <c r="OP2" s="1" t="inlineStr"/>
-      <c r="OQ2" s="1" t="inlineStr"/>
-      <c r="OR2" s="1" t="inlineStr"/>
-      <c r="OS2" s="1" t="inlineStr"/>
-      <c r="OT2" s="1" t="inlineStr"/>
-      <c r="OU2" s="1" t="inlineStr"/>
-      <c r="OV2" s="1" t="inlineStr"/>
-      <c r="OW2" s="1" t="inlineStr"/>
-      <c r="OX2" s="1" t="inlineStr"/>
-      <c r="OY2" s="1" t="inlineStr"/>
-      <c r="OZ2" s="1" t="inlineStr"/>
-      <c r="PA2" s="1" t="inlineStr"/>
-      <c r="PB2" s="1" t="inlineStr"/>
-      <c r="PC2" s="1" t="inlineStr"/>
-      <c r="PD2" s="1" t="inlineStr"/>
-      <c r="PE2" s="1" t="inlineStr"/>
-      <c r="PF2" s="1" t="inlineStr"/>
-      <c r="PG2" s="1" t="inlineStr"/>
-      <c r="PH2" s="1" t="inlineStr"/>
-      <c r="PI2" s="1" t="inlineStr"/>
-      <c r="PJ2" s="1" t="inlineStr"/>
-      <c r="PK2" s="1" t="inlineStr"/>
-      <c r="PL2" s="1" t="inlineStr"/>
-      <c r="PM2" s="1" t="inlineStr"/>
-      <c r="PN2" s="1" t="inlineStr"/>
-      <c r="PO2" s="1" t="inlineStr"/>
-      <c r="PP2" s="1" t="inlineStr"/>
-      <c r="PQ2" s="1" t="inlineStr"/>
-      <c r="PR2" s="1" t="inlineStr"/>
-      <c r="PS2" s="1" t="inlineStr"/>
-      <c r="PT2" s="1" t="inlineStr"/>
-      <c r="PU2" s="1" t="inlineStr"/>
-      <c r="PV2" s="1" t="inlineStr"/>
-      <c r="PW2" s="1" t="inlineStr"/>
-      <c r="PX2" s="1" t="inlineStr"/>
-      <c r="PY2" s="1" t="inlineStr"/>
-      <c r="PZ2" s="1" t="inlineStr"/>
-      <c r="QA2" s="1" t="inlineStr"/>
-      <c r="QB2" s="1" t="inlineStr"/>
-      <c r="QC2" s="1" t="inlineStr"/>
-      <c r="QD2" s="1" t="inlineStr"/>
-      <c r="QE2" s="1" t="inlineStr"/>
-      <c r="QF2" s="1" t="inlineStr"/>
-      <c r="QG2" s="1" t="inlineStr"/>
-      <c r="QH2" s="1" t="inlineStr"/>
-      <c r="QI2" s="1" t="inlineStr"/>
-      <c r="QJ2" s="1" t="inlineStr"/>
-      <c r="QK2" s="1" t="inlineStr"/>
-      <c r="QL2" s="1" t="inlineStr"/>
-      <c r="QM2" s="1" t="inlineStr"/>
-      <c r="QN2" s="1" t="inlineStr"/>
-      <c r="QO2" s="1" t="inlineStr"/>
-      <c r="QP2" s="1" t="inlineStr"/>
-      <c r="QQ2" s="1" t="inlineStr"/>
-      <c r="QR2" s="1" t="inlineStr"/>
-      <c r="QS2" s="1" t="inlineStr"/>
-      <c r="QT2" s="1" t="inlineStr"/>
-      <c r="QU2" s="1" t="inlineStr"/>
-      <c r="QV2" s="1" t="inlineStr"/>
-      <c r="QW2" s="1" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AG2" s="2" t="inlineStr"/>
+      <c r="AH2" s="2" t="inlineStr"/>
+      <c r="AI2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AK2" s="2" t="inlineStr"/>
+      <c r="AL2" s="2" t="inlineStr"/>
+      <c r="AM2" s="2" t="inlineStr"/>
+      <c r="AN2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AP2" s="2" t="inlineStr"/>
+      <c r="AQ2" s="2" t="inlineStr"/>
+      <c r="AR2" s="2" t="inlineStr"/>
+      <c r="AS2" s="2" t="inlineStr"/>
+      <c r="AT2" s="2" t="inlineStr"/>
+      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" s="2" t="inlineStr"/>
+      <c r="AX2" s="2" t="inlineStr"/>
+      <c r="AY2" s="2" t="inlineStr"/>
+      <c r="AZ2" s="2" t="inlineStr"/>
+      <c r="BA2" s="2" t="inlineStr"/>
+      <c r="BB2" s="2" t="inlineStr"/>
+      <c r="BC2" s="2" t="inlineStr"/>
+      <c r="BD2" s="2" t="inlineStr"/>
+      <c r="BE2" s="2" t="inlineStr"/>
+      <c r="BF2" s="2" t="inlineStr"/>
+      <c r="BG2" s="2" t="inlineStr"/>
+      <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BM2" s="2" t="inlineStr"/>
+      <c r="BN2" s="2" t="inlineStr"/>
+      <c r="BO2" s="2" t="inlineStr"/>
+      <c r="BP2" s="2" t="inlineStr"/>
+      <c r="BQ2" s="2" t="inlineStr"/>
+      <c r="BR2" s="2" t="inlineStr"/>
+      <c r="BS2" s="2" t="inlineStr"/>
+      <c r="BT2" s="2" t="inlineStr"/>
+      <c r="BU2" s="2" t="inlineStr"/>
+      <c r="BV2" s="2" t="inlineStr"/>
+      <c r="BW2" s="2" t="inlineStr"/>
+      <c r="BX2" s="2" t="inlineStr"/>
+      <c r="BY2" s="2" t="inlineStr"/>
+      <c r="BZ2" s="2" t="inlineStr"/>
+      <c r="CA2" s="2" t="inlineStr"/>
+      <c r="CB2" s="2" t="inlineStr"/>
+      <c r="CC2" s="2" t="inlineStr"/>
+      <c r="CD2" s="2" t="inlineStr"/>
+      <c r="CE2" s="2" t="inlineStr"/>
+      <c r="CF2" s="2" t="inlineStr"/>
+      <c r="CG2" s="2" t="inlineStr"/>
+      <c r="CH2" s="2" t="inlineStr"/>
+      <c r="CI2" s="2" t="inlineStr"/>
+      <c r="CJ2" s="2" t="inlineStr"/>
+      <c r="CK2" s="2" t="inlineStr"/>
+      <c r="CL2" s="2" t="inlineStr"/>
+      <c r="CM2" s="2" t="inlineStr"/>
+      <c r="CN2" s="2" t="inlineStr"/>
+      <c r="CO2" s="2" t="inlineStr"/>
+      <c r="CP2" s="2" t="inlineStr"/>
+      <c r="CQ2" s="2" t="inlineStr"/>
+      <c r="CR2" s="2" t="inlineStr"/>
+      <c r="CS2" s="2" t="inlineStr"/>
+      <c r="CT2" s="2" t="inlineStr"/>
+      <c r="CU2" s="2" t="inlineStr"/>
+      <c r="CV2" s="2" t="inlineStr"/>
+      <c r="CW2" s="2" t="inlineStr"/>
+      <c r="CX2" s="2" t="inlineStr"/>
+      <c r="CY2" s="2" t="inlineStr"/>
+      <c r="CZ2" s="2" t="inlineStr"/>
+      <c r="DA2" s="2" t="inlineStr"/>
+      <c r="DB2" s="2" t="inlineStr"/>
+      <c r="DC2" s="2" t="inlineStr"/>
+      <c r="DD2" s="2" t="inlineStr"/>
+      <c r="DE2" s="2" t="inlineStr"/>
+      <c r="DF2" s="2" t="inlineStr"/>
+      <c r="DG2" s="2" t="inlineStr"/>
+      <c r="DH2" s="2" t="inlineStr"/>
+      <c r="DI2" s="2" t="inlineStr"/>
+      <c r="DJ2" s="2" t="inlineStr"/>
+      <c r="DK2" s="2" t="inlineStr"/>
+      <c r="DL2" s="2" t="inlineStr"/>
+      <c r="DM2" s="2" t="inlineStr"/>
+      <c r="DN2" s="2" t="inlineStr"/>
+      <c r="DO2" s="2" t="inlineStr"/>
+      <c r="DP2" s="2" t="inlineStr"/>
+      <c r="DQ2" s="2" t="inlineStr"/>
+      <c r="DR2" s="2" t="inlineStr"/>
+      <c r="DS2" s="2" t="inlineStr"/>
+      <c r="DT2" s="2" t="inlineStr"/>
+      <c r="DU2" s="2" t="inlineStr"/>
+      <c r="DV2" s="2" t="inlineStr"/>
+      <c r="DW2" s="2" t="inlineStr"/>
+      <c r="DX2" s="2" t="inlineStr"/>
+      <c r="DY2" s="2" t="inlineStr"/>
+      <c r="DZ2" s="2" t="inlineStr"/>
+      <c r="EA2" s="2" t="inlineStr"/>
+      <c r="EB2" s="2" t="inlineStr"/>
+      <c r="EC2" s="2" t="inlineStr"/>
+      <c r="ED2" s="2" t="inlineStr"/>
+      <c r="EE2" s="2" t="inlineStr"/>
+      <c r="EF2" s="2" t="inlineStr"/>
+      <c r="EG2" s="2" t="inlineStr"/>
+      <c r="EH2" s="2" t="inlineStr"/>
+      <c r="EI2" s="2" t="inlineStr"/>
+      <c r="EJ2" s="2" t="inlineStr"/>
+      <c r="EK2" s="2" t="inlineStr"/>
+      <c r="EL2" s="2" t="inlineStr"/>
+      <c r="EM2" s="2" t="inlineStr"/>
+      <c r="EN2" s="2" t="inlineStr"/>
+      <c r="EO2" s="2" t="inlineStr"/>
+      <c r="EP2" s="2" t="inlineStr"/>
+      <c r="EQ2" s="2" t="inlineStr"/>
+      <c r="ER2" s="2" t="inlineStr"/>
+      <c r="ES2" s="2" t="inlineStr"/>
+      <c r="ET2" s="2" t="inlineStr"/>
+      <c r="EU2" s="2" t="inlineStr"/>
+      <c r="EV2" s="2" t="inlineStr"/>
+      <c r="EW2" s="2" t="inlineStr"/>
+      <c r="EX2" s="2" t="inlineStr"/>
+      <c r="EY2" s="2" t="inlineStr"/>
+      <c r="EZ2" s="2" t="inlineStr"/>
+      <c r="FA2" s="2" t="inlineStr"/>
+      <c r="FB2" s="2" t="inlineStr"/>
+      <c r="FC2" s="2" t="inlineStr"/>
+      <c r="FD2" s="2" t="inlineStr"/>
+      <c r="FE2" s="2" t="inlineStr"/>
+      <c r="FF2" s="2" t="inlineStr"/>
+      <c r="FG2" s="2" t="inlineStr"/>
+      <c r="FH2" s="2" t="inlineStr"/>
+      <c r="FI2" s="2" t="inlineStr"/>
+      <c r="FJ2" s="2" t="inlineStr"/>
+      <c r="FK2" s="2" t="inlineStr"/>
+      <c r="FL2" s="2" t="inlineStr"/>
+      <c r="FM2" s="2" t="inlineStr"/>
+      <c r="FN2" s="2" t="inlineStr"/>
+      <c r="FO2" s="2" t="inlineStr"/>
+      <c r="FP2" s="2" t="inlineStr"/>
+      <c r="FQ2" s="2" t="inlineStr"/>
+      <c r="FR2" s="2" t="inlineStr"/>
+      <c r="FS2" s="2" t="inlineStr"/>
+      <c r="FT2" s="2" t="inlineStr"/>
+      <c r="FU2" s="2" t="inlineStr"/>
+      <c r="FV2" s="2" t="inlineStr"/>
+      <c r="FW2" s="2" t="inlineStr"/>
+      <c r="FX2" s="2" t="inlineStr"/>
+      <c r="FY2" s="2" t="inlineStr"/>
+      <c r="FZ2" s="2" t="inlineStr"/>
+      <c r="GA2" s="2" t="inlineStr"/>
+      <c r="GB2" s="2" t="inlineStr"/>
+      <c r="GC2" s="2" t="inlineStr"/>
+      <c r="GD2" s="2" t="inlineStr"/>
+      <c r="GE2" s="2" t="inlineStr"/>
+      <c r="GF2" s="2" t="inlineStr"/>
+      <c r="GG2" s="2" t="inlineStr"/>
+      <c r="GH2" s="2" t="inlineStr"/>
+      <c r="GI2" s="2" t="inlineStr"/>
+      <c r="GJ2" s="2" t="inlineStr"/>
+      <c r="GK2" s="2" t="inlineStr"/>
+      <c r="GL2" s="2" t="inlineStr"/>
+      <c r="GM2" s="2" t="inlineStr"/>
+      <c r="GN2" s="2" t="inlineStr"/>
+      <c r="GO2" s="2" t="inlineStr"/>
+      <c r="GP2" s="2" t="inlineStr"/>
+      <c r="GQ2" s="2" t="inlineStr"/>
+      <c r="GR2" s="2" t="inlineStr"/>
+      <c r="GS2" s="2" t="inlineStr"/>
+      <c r="GT2" s="2" t="inlineStr"/>
+      <c r="GU2" s="2" t="inlineStr"/>
+      <c r="GV2" s="2" t="inlineStr"/>
+      <c r="GW2" s="2" t="inlineStr"/>
+      <c r="GX2" s="2" t="inlineStr"/>
+      <c r="GY2" s="2" t="inlineStr"/>
+      <c r="GZ2" s="2" t="inlineStr"/>
+      <c r="HA2" s="2" t="inlineStr"/>
+      <c r="HB2" s="2" t="inlineStr"/>
+      <c r="HC2" s="2" t="inlineStr"/>
+      <c r="HD2" s="2" t="inlineStr"/>
+      <c r="HE2" s="2" t="inlineStr"/>
+      <c r="HF2" s="2" t="inlineStr"/>
+      <c r="HG2" s="2" t="inlineStr"/>
+      <c r="HH2" s="2" t="inlineStr"/>
+      <c r="HI2" s="2" t="inlineStr"/>
+      <c r="HJ2" s="2" t="inlineStr"/>
+      <c r="HK2" s="2" t="inlineStr"/>
+      <c r="HL2" s="2" t="inlineStr"/>
+      <c r="HM2" s="2" t="inlineStr"/>
+      <c r="HN2" s="2" t="inlineStr"/>
+      <c r="HO2" s="2" t="inlineStr"/>
+      <c r="HP2" s="2" t="inlineStr"/>
+      <c r="HQ2" s="2" t="inlineStr"/>
+      <c r="HR2" s="2" t="inlineStr"/>
+      <c r="HS2" s="2" t="inlineStr"/>
+      <c r="HT2" s="2" t="inlineStr"/>
+      <c r="HU2" s="2" t="inlineStr"/>
+      <c r="HV2" s="2" t="inlineStr"/>
+      <c r="HW2" s="2" t="inlineStr"/>
+      <c r="HX2" s="2" t="inlineStr"/>
+      <c r="HY2" s="2" t="inlineStr"/>
+      <c r="HZ2" s="2" t="inlineStr"/>
+      <c r="IA2" s="2" t="inlineStr"/>
+      <c r="IB2" s="2" t="inlineStr"/>
+      <c r="IC2" s="2" t="inlineStr"/>
+      <c r="ID2" s="2" t="inlineStr"/>
+      <c r="IE2" s="2" t="inlineStr"/>
+      <c r="IF2" s="2" t="inlineStr"/>
+      <c r="IG2" s="2" t="inlineStr"/>
+      <c r="IH2" s="2" t="inlineStr"/>
+      <c r="II2" s="2" t="inlineStr"/>
+      <c r="IJ2" s="2" t="inlineStr"/>
+      <c r="IK2" s="2" t="inlineStr"/>
+      <c r="IL2" s="2" t="inlineStr"/>
+      <c r="IM2" s="2" t="inlineStr"/>
+      <c r="IN2" s="2" t="inlineStr"/>
+      <c r="IO2" s="2" t="inlineStr"/>
+      <c r="IP2" s="2" t="inlineStr"/>
+      <c r="IQ2" s="2" t="inlineStr"/>
+      <c r="IR2" s="2" t="inlineStr"/>
+      <c r="IS2" s="2" t="inlineStr"/>
+      <c r="IT2" s="2" t="inlineStr"/>
+      <c r="IU2" s="2" t="inlineStr"/>
+      <c r="IV2" s="2" t="inlineStr"/>
+      <c r="IW2" s="2" t="inlineStr"/>
+      <c r="IX2" s="2" t="inlineStr"/>
+      <c r="IY2" s="2" t="inlineStr"/>
+      <c r="IZ2" s="2" t="inlineStr"/>
+      <c r="JA2" s="2" t="inlineStr"/>
+      <c r="JB2" s="2" t="inlineStr"/>
+      <c r="JC2" s="2" t="inlineStr"/>
+      <c r="JD2" s="2" t="inlineStr"/>
+      <c r="JE2" s="2" t="inlineStr"/>
+      <c r="JF2" s="2" t="inlineStr"/>
+      <c r="JG2" s="2" t="inlineStr"/>
+      <c r="JH2" s="2" t="inlineStr"/>
+      <c r="JI2" s="2" t="inlineStr"/>
+      <c r="JJ2" s="2" t="inlineStr"/>
+      <c r="JK2" s="2" t="inlineStr"/>
+      <c r="JL2" s="2" t="inlineStr"/>
+      <c r="JM2" s="2" t="inlineStr"/>
+      <c r="JN2" s="2" t="inlineStr"/>
+      <c r="JO2" s="2" t="inlineStr"/>
+      <c r="JP2" s="2" t="inlineStr"/>
+      <c r="JQ2" s="2" t="inlineStr"/>
+      <c r="JR2" s="2" t="inlineStr"/>
+      <c r="JS2" s="2" t="inlineStr"/>
+      <c r="JT2" s="2" t="inlineStr"/>
+      <c r="JU2" s="2" t="inlineStr"/>
+      <c r="JV2" s="2" t="inlineStr"/>
+      <c r="JW2" s="2" t="inlineStr"/>
+      <c r="JX2" s="2" t="inlineStr"/>
+      <c r="JY2" s="2" t="inlineStr"/>
+      <c r="JZ2" s="2" t="inlineStr"/>
+      <c r="KA2" s="2" t="inlineStr"/>
+      <c r="KB2" s="2" t="inlineStr"/>
+      <c r="KC2" s="2" t="inlineStr"/>
+      <c r="KD2" s="2" t="inlineStr"/>
+      <c r="KE2" s="2" t="inlineStr"/>
+      <c r="KF2" s="2" t="inlineStr"/>
+      <c r="KG2" s="2" t="inlineStr"/>
+      <c r="KH2" s="2" t="inlineStr"/>
+      <c r="KI2" s="2" t="inlineStr"/>
+      <c r="KJ2" s="2" t="inlineStr"/>
+      <c r="KK2" s="2" t="inlineStr"/>
+      <c r="KL2" s="2" t="inlineStr"/>
+      <c r="KM2" s="2" t="inlineStr"/>
+      <c r="KN2" s="2" t="inlineStr"/>
+      <c r="KO2" s="2" t="inlineStr"/>
+      <c r="KP2" s="2" t="inlineStr"/>
+      <c r="KQ2" s="2" t="inlineStr"/>
+      <c r="KR2" s="2" t="inlineStr"/>
+      <c r="KS2" s="2" t="inlineStr"/>
+      <c r="KT2" s="2" t="inlineStr"/>
+      <c r="KU2" s="2" t="inlineStr"/>
+      <c r="KV2" s="2" t="inlineStr"/>
+      <c r="KW2" s="2" t="inlineStr"/>
+      <c r="KX2" s="2" t="inlineStr"/>
+      <c r="KY2" s="2" t="inlineStr"/>
+      <c r="KZ2" s="2" t="inlineStr"/>
+      <c r="LA2" s="2" t="inlineStr"/>
+      <c r="LB2" s="2" t="inlineStr"/>
+      <c r="LC2" s="2" t="inlineStr"/>
+      <c r="LD2" s="2" t="inlineStr"/>
+      <c r="LE2" s="2" t="inlineStr"/>
+      <c r="LF2" s="2" t="inlineStr"/>
+      <c r="LG2" s="2" t="inlineStr"/>
+      <c r="LH2" s="2" t="inlineStr"/>
+      <c r="LI2" s="2" t="inlineStr"/>
+      <c r="LJ2" s="2" t="inlineStr"/>
+      <c r="LK2" s="2" t="inlineStr"/>
+      <c r="LL2" s="2" t="inlineStr"/>
+      <c r="LM2" s="2" t="inlineStr"/>
+      <c r="LN2" s="2" t="inlineStr"/>
+      <c r="LO2" s="2" t="inlineStr"/>
+      <c r="LP2" s="2" t="inlineStr"/>
+      <c r="LQ2" s="2" t="inlineStr"/>
+      <c r="LR2" s="2" t="inlineStr"/>
+      <c r="LS2" s="2" t="inlineStr"/>
+      <c r="LT2" s="2" t="inlineStr"/>
+      <c r="LU2" s="2" t="inlineStr"/>
+      <c r="LV2" s="2" t="inlineStr"/>
+      <c r="LW2" s="2" t="inlineStr"/>
+      <c r="LX2" s="2" t="inlineStr"/>
+      <c r="LY2" s="2" t="inlineStr"/>
+      <c r="LZ2" s="2" t="inlineStr"/>
+      <c r="MA2" s="2" t="inlineStr"/>
+      <c r="MB2" s="2" t="inlineStr"/>
+      <c r="MC2" s="2" t="inlineStr"/>
+      <c r="MD2" s="2" t="inlineStr"/>
+      <c r="ME2" s="2" t="inlineStr"/>
+      <c r="MF2" s="2" t="inlineStr"/>
+      <c r="MG2" s="2" t="inlineStr"/>
+      <c r="MH2" s="2" t="inlineStr"/>
+      <c r="MI2" s="2" t="inlineStr"/>
+      <c r="MJ2" s="2" t="inlineStr"/>
+      <c r="MK2" s="2" t="inlineStr"/>
+      <c r="ML2" s="2" t="inlineStr"/>
+      <c r="MM2" s="2" t="inlineStr"/>
+      <c r="MN2" s="2" t="inlineStr"/>
+      <c r="MO2" s="2" t="inlineStr"/>
+      <c r="MP2" s="2" t="inlineStr"/>
+      <c r="MQ2" s="2" t="inlineStr"/>
+      <c r="MR2" s="2" t="inlineStr"/>
+      <c r="MS2" s="2" t="inlineStr"/>
+      <c r="MT2" s="2" t="inlineStr"/>
+      <c r="MU2" s="2" t="inlineStr"/>
+      <c r="MV2" s="2" t="inlineStr"/>
+      <c r="MW2" s="2" t="inlineStr"/>
+      <c r="MX2" s="2" t="inlineStr"/>
+      <c r="MY2" s="2" t="inlineStr"/>
+      <c r="MZ2" s="2" t="inlineStr"/>
+      <c r="NA2" s="2" t="inlineStr"/>
+      <c r="NB2" s="2" t="inlineStr"/>
+      <c r="NC2" s="2" t="inlineStr"/>
+      <c r="ND2" s="2" t="inlineStr"/>
+      <c r="NE2" s="2" t="inlineStr"/>
+      <c r="NF2" s="2" t="inlineStr"/>
+      <c r="NG2" s="2" t="inlineStr"/>
+      <c r="NH2" s="2" t="inlineStr"/>
+      <c r="NI2" s="2" t="inlineStr"/>
+      <c r="NJ2" s="2" t="inlineStr"/>
+      <c r="NK2" s="2" t="inlineStr"/>
+      <c r="NL2" s="2" t="inlineStr"/>
+      <c r="NM2" s="2" t="inlineStr"/>
+      <c r="NN2" s="2" t="inlineStr"/>
+      <c r="NO2" s="2" t="inlineStr"/>
+      <c r="NP2" s="2" t="inlineStr"/>
+      <c r="NQ2" s="2" t="inlineStr"/>
+      <c r="NR2" s="2" t="inlineStr"/>
+      <c r="NS2" s="2" t="inlineStr"/>
+      <c r="NT2" s="2" t="inlineStr"/>
+      <c r="NU2" s="2" t="inlineStr"/>
+      <c r="NV2" s="2" t="inlineStr"/>
+      <c r="NW2" s="2" t="inlineStr"/>
+      <c r="NX2" s="2" t="inlineStr"/>
+      <c r="NY2" s="2" t="inlineStr"/>
+      <c r="NZ2" s="2" t="inlineStr"/>
+      <c r="OA2" s="2" t="inlineStr"/>
+      <c r="OB2" s="2" t="inlineStr"/>
+      <c r="OC2" s="2" t="inlineStr"/>
+      <c r="OD2" s="2" t="inlineStr"/>
+      <c r="OE2" s="2" t="inlineStr"/>
+      <c r="OF2" s="2" t="inlineStr"/>
+      <c r="OG2" s="2" t="inlineStr"/>
+      <c r="OH2" s="2" t="inlineStr"/>
+      <c r="OI2" s="2" t="inlineStr"/>
+      <c r="OJ2" s="2" t="inlineStr"/>
+      <c r="OK2" s="2" t="inlineStr"/>
+      <c r="OL2" s="2" t="inlineStr"/>
+      <c r="OM2" s="2" t="inlineStr"/>
+      <c r="ON2" s="2" t="inlineStr"/>
+      <c r="OO2" s="2" t="inlineStr"/>
+      <c r="OP2" s="2" t="inlineStr"/>
+      <c r="OQ2" s="2" t="inlineStr"/>
+      <c r="OR2" s="2" t="inlineStr"/>
+      <c r="OS2" s="2" t="inlineStr"/>
+      <c r="OT2" s="2" t="inlineStr"/>
+      <c r="OU2" s="2" t="inlineStr"/>
+      <c r="OV2" s="2" t="inlineStr"/>
+      <c r="OW2" s="2" t="inlineStr"/>
+      <c r="OX2" s="2" t="inlineStr"/>
+      <c r="OY2" s="2" t="inlineStr"/>
+      <c r="OZ2" s="2" t="inlineStr"/>
+      <c r="PA2" s="2" t="inlineStr"/>
+      <c r="PB2" s="2" t="inlineStr"/>
+      <c r="PC2" s="2" t="inlineStr"/>
+      <c r="PD2" s="2" t="inlineStr"/>
+      <c r="PE2" s="2" t="inlineStr"/>
+      <c r="PF2" s="2" t="inlineStr"/>
+      <c r="PG2" s="2" t="inlineStr"/>
+      <c r="PH2" s="2" t="inlineStr"/>
+      <c r="PI2" s="2" t="inlineStr"/>
+      <c r="PJ2" s="2" t="inlineStr"/>
+      <c r="PK2" s="2" t="inlineStr"/>
+      <c r="PL2" s="2" t="inlineStr"/>
+      <c r="PM2" s="2" t="inlineStr"/>
+      <c r="PN2" s="2" t="inlineStr"/>
+      <c r="PO2" s="2" t="inlineStr"/>
+      <c r="PP2" s="2" t="inlineStr"/>
+      <c r="PQ2" s="2" t="inlineStr"/>
+      <c r="PR2" s="2" t="inlineStr"/>
+      <c r="PS2" s="2" t="inlineStr"/>
+      <c r="PT2" s="2" t="inlineStr"/>
+      <c r="PU2" s="2" t="inlineStr"/>
+      <c r="PV2" s="2" t="inlineStr"/>
+      <c r="PW2" s="2" t="inlineStr"/>
+      <c r="PX2" s="2" t="inlineStr"/>
+      <c r="PY2" s="2" t="inlineStr"/>
+      <c r="PZ2" s="2" t="inlineStr"/>
+      <c r="QA2" s="2" t="inlineStr"/>
+      <c r="QB2" s="2" t="inlineStr"/>
+      <c r="QC2" s="2" t="inlineStr"/>
+      <c r="QD2" s="2" t="inlineStr"/>
+      <c r="QE2" s="2" t="inlineStr"/>
+      <c r="QF2" s="2" t="inlineStr"/>
+      <c r="QG2" s="2" t="inlineStr"/>
+      <c r="QH2" s="2" t="inlineStr"/>
+      <c r="QI2" s="2" t="inlineStr"/>
+      <c r="QJ2" s="2" t="inlineStr"/>
+      <c r="QK2" s="2" t="inlineStr"/>
+      <c r="QL2" s="2" t="inlineStr"/>
+      <c r="QM2" s="2" t="inlineStr"/>
+      <c r="QN2" s="2" t="inlineStr"/>
+      <c r="QO2" s="2" t="inlineStr"/>
+      <c r="QP2" s="2" t="inlineStr"/>
+      <c r="QQ2" s="2" t="inlineStr"/>
+      <c r="QR2" s="2" t="inlineStr"/>
+      <c r="QS2" s="2" t="inlineStr"/>
+      <c r="QT2" s="2" t="inlineStr"/>
+      <c r="QU2" s="2" t="inlineStr"/>
+      <c r="QV2" s="2" t="inlineStr"/>
+      <c r="QW2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr"/>
-      <c r="D3" s="1" t="inlineStr"/>
-      <c r="E3" s="1" t="inlineStr"/>
-      <c r="F3" s="1" t="inlineStr"/>
-      <c r="G3" s="1" t="inlineStr"/>
-      <c r="H3" s="1" t="inlineStr"/>
-      <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr"/>
-      <c r="L3" s="1" t="inlineStr"/>
-      <c r="M3" s="1" t="inlineStr"/>
-      <c r="N3" s="1" t="inlineStr"/>
-      <c r="O3" s="1" t="inlineStr"/>
-      <c r="P3" s="1" t="inlineStr"/>
-      <c r="Q3" s="1" t="inlineStr"/>
-      <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
-      <c r="T3" s="1" t="inlineStr"/>
-      <c r="U3" s="1" t="inlineStr"/>
-      <c r="V3" s="1" t="inlineStr"/>
-      <c r="W3" s="1" t="inlineStr"/>
-      <c r="X3" s="1" t="inlineStr"/>
-      <c r="Y3" s="1" t="inlineStr"/>
-      <c r="Z3" s="1" t="inlineStr"/>
-      <c r="AA3" s="1" t="inlineStr"/>
-      <c r="AB3" s="1" t="inlineStr"/>
-      <c r="AC3" s="1" t="inlineStr"/>
-      <c r="AD3" s="1" t="inlineStr"/>
-      <c r="AE3" s="1" t="inlineStr"/>
-      <c r="AF3" s="1" t="inlineStr"/>
-      <c r="AG3" s="1" t="inlineStr"/>
-      <c r="AH3" s="1" t="inlineStr"/>
-      <c r="AI3" s="1" t="inlineStr"/>
-      <c r="AJ3" s="1" t="inlineStr"/>
-      <c r="AK3" s="1" t="inlineStr"/>
-      <c r="AL3" s="1" t="inlineStr"/>
-      <c r="AM3" s="1" t="inlineStr"/>
-      <c r="AN3" s="1" t="inlineStr"/>
-      <c r="AO3" s="1" t="inlineStr"/>
-      <c r="AP3" s="1" t="inlineStr"/>
-      <c r="AQ3" s="1" t="inlineStr"/>
-      <c r="AR3" s="1" t="inlineStr"/>
-      <c r="AS3" s="1" t="inlineStr"/>
-      <c r="AT3" s="1" t="inlineStr"/>
-      <c r="AU3" s="1" t="inlineStr"/>
-      <c r="AV3" s="1" t="inlineStr"/>
-      <c r="AW3" s="1" t="inlineStr"/>
-      <c r="AX3" s="1" t="inlineStr"/>
-      <c r="AY3" s="1" t="inlineStr"/>
-      <c r="AZ3" s="1" t="inlineStr"/>
-      <c r="BA3" s="1" t="inlineStr"/>
-      <c r="BB3" s="1" t="inlineStr"/>
-      <c r="BC3" s="1" t="inlineStr"/>
-      <c r="BD3" s="1" t="inlineStr"/>
-      <c r="BE3" s="1" t="inlineStr"/>
-      <c r="BF3" s="1" t="inlineStr"/>
-      <c r="BG3" s="1" t="inlineStr"/>
-      <c r="BH3" s="1" t="inlineStr"/>
-      <c r="BI3" s="1" t="inlineStr"/>
-      <c r="BJ3" s="1" t="inlineStr"/>
-      <c r="BK3" s="1" t="inlineStr"/>
-      <c r="BL3" s="1" t="inlineStr"/>
-      <c r="BM3" s="1" t="inlineStr"/>
-      <c r="BN3" s="1" t="inlineStr"/>
-      <c r="BO3" s="1" t="inlineStr"/>
-      <c r="BP3" s="1" t="inlineStr"/>
-      <c r="BQ3" s="1" t="inlineStr"/>
-      <c r="BR3" s="1" t="inlineStr"/>
-      <c r="BS3" s="1" t="inlineStr"/>
-      <c r="BT3" s="1" t="inlineStr"/>
-      <c r="BU3" s="1" t="inlineStr"/>
-      <c r="BV3" s="1" t="inlineStr"/>
-      <c r="BW3" s="1" t="inlineStr"/>
-      <c r="BX3" s="1" t="inlineStr"/>
-      <c r="BY3" s="1" t="inlineStr"/>
-      <c r="BZ3" s="1" t="inlineStr"/>
-      <c r="CA3" s="1" t="inlineStr"/>
-      <c r="CB3" s="1" t="inlineStr"/>
-      <c r="CC3" s="1" t="inlineStr"/>
-      <c r="CD3" s="1" t="inlineStr"/>
-      <c r="CE3" s="1" t="inlineStr"/>
-      <c r="CF3" s="1" t="inlineStr"/>
-      <c r="CG3" s="1" t="inlineStr"/>
-      <c r="CH3" s="1" t="inlineStr"/>
-      <c r="CI3" s="1" t="inlineStr"/>
-      <c r="CJ3" s="1" t="inlineStr"/>
-      <c r="CK3" s="1" t="inlineStr"/>
-      <c r="CL3" s="1" t="inlineStr"/>
-      <c r="CM3" s="1" t="inlineStr"/>
-      <c r="CN3" s="1" t="inlineStr"/>
-      <c r="CO3" s="1" t="inlineStr"/>
-      <c r="CP3" s="1" t="inlineStr"/>
-      <c r="CQ3" s="1" t="inlineStr"/>
-      <c r="CR3" s="1" t="inlineStr"/>
-      <c r="CS3" s="1" t="inlineStr"/>
-      <c r="CT3" s="1" t="inlineStr"/>
-      <c r="CU3" s="1" t="inlineStr"/>
-      <c r="CV3" s="1" t="inlineStr"/>
-      <c r="CW3" s="1" t="inlineStr"/>
-      <c r="CX3" s="1" t="inlineStr"/>
-      <c r="CY3" s="1" t="inlineStr"/>
-      <c r="CZ3" s="1" t="inlineStr"/>
-      <c r="DA3" s="1" t="inlineStr"/>
-      <c r="DB3" s="1" t="inlineStr"/>
-      <c r="DC3" s="1" t="inlineStr"/>
-      <c r="DD3" s="1" t="inlineStr"/>
-      <c r="DE3" s="1" t="inlineStr"/>
-      <c r="DF3" s="1" t="inlineStr"/>
-      <c r="DG3" s="1" t="inlineStr"/>
-      <c r="DH3" s="1" t="inlineStr"/>
-      <c r="DI3" s="1" t="inlineStr"/>
-      <c r="DJ3" s="1" t="inlineStr"/>
-      <c r="DK3" s="1" t="inlineStr"/>
-      <c r="DL3" s="1" t="inlineStr"/>
-      <c r="DM3" s="1" t="inlineStr"/>
-      <c r="DN3" s="1" t="inlineStr"/>
-      <c r="DO3" s="1" t="inlineStr"/>
-      <c r="DP3" s="1" t="inlineStr"/>
-      <c r="DQ3" s="1" t="inlineStr"/>
-      <c r="DR3" s="1" t="inlineStr"/>
-      <c r="DS3" s="1" t="inlineStr"/>
-      <c r="DT3" s="1" t="inlineStr"/>
-      <c r="DU3" s="1" t="inlineStr"/>
-      <c r="DV3" s="1" t="inlineStr"/>
-      <c r="DW3" s="1" t="inlineStr"/>
-      <c r="DX3" s="1" t="inlineStr"/>
-      <c r="DY3" s="1" t="inlineStr"/>
-      <c r="DZ3" s="1" t="inlineStr"/>
-      <c r="EA3" s="1" t="inlineStr"/>
-      <c r="EB3" s="1" t="inlineStr"/>
-      <c r="EC3" s="1" t="inlineStr"/>
-      <c r="ED3" s="1" t="inlineStr"/>
-      <c r="EE3" s="1" t="inlineStr"/>
-      <c r="EF3" s="1" t="inlineStr"/>
-      <c r="EG3" s="1" t="inlineStr"/>
-      <c r="EH3" s="1" t="inlineStr"/>
-      <c r="EI3" s="1" t="inlineStr"/>
-      <c r="EJ3" s="1" t="inlineStr"/>
-      <c r="EK3" s="1" t="inlineStr"/>
-      <c r="EL3" s="1" t="inlineStr"/>
-      <c r="EM3" s="1" t="inlineStr"/>
-      <c r="EN3" s="1" t="inlineStr"/>
-      <c r="EO3" s="1" t="inlineStr"/>
-      <c r="EP3" s="1" t="inlineStr"/>
-      <c r="EQ3" s="1" t="inlineStr"/>
-      <c r="ER3" s="1" t="inlineStr"/>
-      <c r="ES3" s="1" t="inlineStr"/>
-      <c r="ET3" s="1" t="inlineStr"/>
-      <c r="EU3" s="1" t="inlineStr"/>
-      <c r="EV3" s="1" t="inlineStr"/>
-      <c r="EW3" s="1" t="inlineStr"/>
-      <c r="EX3" s="1" t="inlineStr"/>
-      <c r="EY3" s="1" t="inlineStr"/>
-      <c r="EZ3" s="1" t="inlineStr"/>
-      <c r="FA3" s="1" t="inlineStr"/>
-      <c r="FB3" s="1" t="inlineStr"/>
-      <c r="FC3" s="1" t="inlineStr"/>
-      <c r="FD3" s="1" t="inlineStr"/>
-      <c r="FE3" s="1" t="inlineStr"/>
-      <c r="FF3" s="1" t="inlineStr"/>
-      <c r="FG3" s="1" t="inlineStr"/>
-      <c r="FH3" s="1" t="inlineStr"/>
-      <c r="FI3" s="1" t="inlineStr"/>
-      <c r="FJ3" s="1" t="inlineStr"/>
-      <c r="FK3" s="1" t="inlineStr"/>
-      <c r="FL3" s="1" t="inlineStr"/>
-      <c r="FM3" s="1" t="inlineStr"/>
-      <c r="FN3" s="1" t="inlineStr"/>
-      <c r="FO3" s="1" t="inlineStr"/>
-      <c r="FP3" s="1" t="inlineStr"/>
-      <c r="FQ3" s="1" t="inlineStr"/>
-      <c r="FR3" s="1" t="inlineStr"/>
-      <c r="FS3" s="1" t="inlineStr"/>
-      <c r="FT3" s="1" t="inlineStr"/>
-      <c r="FU3" s="1" t="inlineStr"/>
-      <c r="FV3" s="1" t="inlineStr"/>
-      <c r="FW3" s="1" t="inlineStr"/>
-      <c r="FX3" s="1" t="inlineStr"/>
-      <c r="FY3" s="1" t="inlineStr"/>
-      <c r="FZ3" s="1" t="inlineStr"/>
-      <c r="GA3" s="1" t="inlineStr"/>
-      <c r="GB3" s="1" t="inlineStr"/>
-      <c r="GC3" s="1" t="inlineStr"/>
-      <c r="GD3" s="1" t="inlineStr"/>
-      <c r="GE3" s="1" t="inlineStr"/>
-      <c r="GF3" s="1" t="inlineStr"/>
-      <c r="GG3" s="1" t="inlineStr"/>
-      <c r="GH3" s="1" t="inlineStr"/>
-      <c r="GI3" s="1" t="inlineStr"/>
-      <c r="GJ3" s="1" t="inlineStr"/>
-      <c r="GK3" s="1" t="inlineStr"/>
-      <c r="GL3" s="1" t="inlineStr"/>
-      <c r="GM3" s="1" t="inlineStr"/>
-      <c r="GN3" s="1" t="inlineStr"/>
-      <c r="GO3" s="1" t="inlineStr"/>
-      <c r="GP3" s="1" t="inlineStr"/>
-      <c r="GQ3" s="1" t="inlineStr"/>
-      <c r="GR3" s="1" t="inlineStr"/>
-      <c r="GS3" s="1" t="inlineStr"/>
-      <c r="GT3" s="1" t="inlineStr"/>
-      <c r="GU3" s="1" t="inlineStr"/>
-      <c r="GV3" s="1" t="inlineStr"/>
-      <c r="GW3" s="1" t="inlineStr"/>
-      <c r="GX3" s="1" t="inlineStr"/>
-      <c r="GY3" s="1" t="inlineStr"/>
-      <c r="GZ3" s="1" t="inlineStr"/>
-      <c r="HA3" s="1" t="inlineStr"/>
-      <c r="HB3" s="1" t="inlineStr"/>
-      <c r="HC3" s="1" t="inlineStr"/>
-      <c r="HD3" s="1" t="inlineStr"/>
-      <c r="HE3" s="1" t="inlineStr"/>
-      <c r="HF3" s="1" t="inlineStr"/>
-      <c r="HG3" s="1" t="inlineStr"/>
-      <c r="HH3" s="1" t="inlineStr"/>
-      <c r="HI3" s="1" t="inlineStr"/>
-      <c r="HJ3" s="1" t="inlineStr"/>
-      <c r="HK3" s="1" t="inlineStr"/>
-      <c r="HL3" s="1" t="inlineStr"/>
-      <c r="HM3" s="1" t="inlineStr"/>
-      <c r="HN3" s="1" t="inlineStr"/>
-      <c r="HO3" s="1" t="inlineStr"/>
-      <c r="HP3" s="1" t="inlineStr"/>
-      <c r="HQ3" s="1" t="inlineStr"/>
-      <c r="HR3" s="1" t="inlineStr"/>
-      <c r="HS3" s="1" t="inlineStr"/>
-      <c r="HT3" s="1" t="inlineStr"/>
-      <c r="HU3" s="1" t="inlineStr"/>
-      <c r="HV3" s="1" t="inlineStr"/>
-      <c r="HW3" s="1" t="inlineStr"/>
-      <c r="HX3" s="1" t="inlineStr"/>
-      <c r="HY3" s="1" t="inlineStr"/>
-      <c r="HZ3" s="1" t="inlineStr"/>
-      <c r="IA3" s="1" t="inlineStr"/>
-      <c r="IB3" s="1" t="inlineStr"/>
-      <c r="IC3" s="1" t="inlineStr"/>
-      <c r="ID3" s="1" t="inlineStr"/>
-      <c r="IE3" s="1" t="inlineStr"/>
-      <c r="IF3" s="1" t="inlineStr"/>
-      <c r="IG3" s="1" t="inlineStr"/>
-      <c r="IH3" s="1" t="inlineStr"/>
-      <c r="II3" s="1" t="inlineStr"/>
-      <c r="IJ3" s="1" t="inlineStr"/>
-      <c r="IK3" s="1" t="inlineStr"/>
-      <c r="IL3" s="1" t="inlineStr"/>
-      <c r="IM3" s="1" t="inlineStr"/>
-      <c r="IN3" s="1" t="inlineStr"/>
-      <c r="IO3" s="1" t="inlineStr"/>
-      <c r="IP3" s="1" t="inlineStr"/>
-      <c r="IQ3" s="1" t="inlineStr"/>
-      <c r="IR3" s="1" t="inlineStr"/>
-      <c r="IS3" s="1" t="inlineStr"/>
-      <c r="IT3" s="1" t="inlineStr"/>
-      <c r="IU3" s="1" t="inlineStr"/>
-      <c r="IV3" s="1" t="inlineStr"/>
-      <c r="IW3" s="1" t="inlineStr"/>
-      <c r="IX3" s="1" t="inlineStr"/>
-      <c r="IY3" s="1" t="inlineStr"/>
-      <c r="IZ3" s="1" t="inlineStr"/>
-      <c r="JA3" s="1" t="inlineStr"/>
-      <c r="JB3" s="1" t="inlineStr"/>
-      <c r="JC3" s="1" t="inlineStr"/>
-      <c r="JD3" s="1" t="inlineStr"/>
-      <c r="JE3" s="1" t="inlineStr"/>
-      <c r="JF3" s="1" t="inlineStr"/>
-      <c r="JG3" s="1" t="inlineStr"/>
-      <c r="JH3" s="1" t="inlineStr"/>
-      <c r="JI3" s="1" t="inlineStr"/>
-      <c r="JJ3" s="1" t="inlineStr"/>
-      <c r="JK3" s="1" t="inlineStr"/>
-      <c r="JL3" s="1" t="inlineStr"/>
-      <c r="JM3" s="1" t="inlineStr"/>
-      <c r="JN3" s="1" t="inlineStr"/>
-      <c r="JO3" s="1" t="inlineStr"/>
-      <c r="JP3" s="1" t="inlineStr"/>
-      <c r="JQ3" s="1" t="inlineStr"/>
-      <c r="JR3" s="1" t="inlineStr"/>
-      <c r="JS3" s="1" t="inlineStr"/>
-      <c r="JT3" s="1" t="inlineStr"/>
-      <c r="JU3" s="1" t="inlineStr"/>
-      <c r="JV3" s="1" t="inlineStr"/>
-      <c r="JW3" s="1" t="inlineStr"/>
-      <c r="JX3" s="1" t="inlineStr"/>
-      <c r="JY3" s="1" t="inlineStr"/>
-      <c r="JZ3" s="1" t="inlineStr"/>
-      <c r="KA3" s="1" t="inlineStr"/>
-      <c r="KB3" s="1" t="inlineStr"/>
-      <c r="KC3" s="1" t="inlineStr"/>
-      <c r="KD3" s="1" t="inlineStr"/>
-      <c r="KE3" s="1" t="inlineStr"/>
-      <c r="KF3" s="1" t="inlineStr"/>
-      <c r="KG3" s="1" t="inlineStr"/>
-      <c r="KH3" s="1" t="inlineStr"/>
-      <c r="KI3" s="1" t="inlineStr"/>
-      <c r="KJ3" s="1" t="inlineStr"/>
-      <c r="KK3" s="1" t="inlineStr"/>
-      <c r="KL3" s="1" t="inlineStr"/>
-      <c r="KM3" s="1" t="inlineStr"/>
-      <c r="KN3" s="1" t="inlineStr"/>
-      <c r="KO3" s="1" t="inlineStr"/>
-      <c r="KP3" s="1" t="inlineStr"/>
-      <c r="KQ3" s="1" t="inlineStr"/>
-      <c r="KR3" s="1" t="inlineStr"/>
-      <c r="KS3" s="1" t="inlineStr"/>
-      <c r="KT3" s="1" t="inlineStr"/>
-      <c r="KU3" s="1" t="inlineStr"/>
-      <c r="KV3" s="1" t="inlineStr"/>
-      <c r="KW3" s="1" t="inlineStr"/>
-      <c r="KX3" s="1" t="inlineStr"/>
-      <c r="KY3" s="1" t="inlineStr"/>
-      <c r="KZ3" s="1" t="inlineStr"/>
-      <c r="LA3" s="1" t="inlineStr"/>
-      <c r="LB3" s="1" t="inlineStr"/>
-      <c r="LC3" s="1" t="inlineStr"/>
-      <c r="LD3" s="1" t="inlineStr"/>
-      <c r="LE3" s="1" t="inlineStr"/>
-      <c r="LF3" s="1" t="inlineStr"/>
-      <c r="LG3" s="1" t="inlineStr"/>
-      <c r="LH3" s="1" t="inlineStr"/>
-      <c r="LI3" s="1" t="inlineStr"/>
-      <c r="LJ3" s="1" t="inlineStr"/>
-      <c r="LK3" s="1" t="inlineStr"/>
-      <c r="LL3" s="1" t="inlineStr"/>
-      <c r="LM3" s="1" t="inlineStr"/>
-      <c r="LN3" s="1" t="inlineStr"/>
-      <c r="LO3" s="1" t="inlineStr"/>
-      <c r="LP3" s="1" t="inlineStr"/>
-      <c r="LQ3" s="1" t="inlineStr"/>
-      <c r="LR3" s="1" t="inlineStr"/>
-      <c r="LS3" s="1" t="inlineStr"/>
-      <c r="LT3" s="1" t="inlineStr"/>
-      <c r="LU3" s="1" t="inlineStr"/>
-      <c r="LV3" s="1" t="inlineStr"/>
-      <c r="LW3" s="1" t="inlineStr"/>
-      <c r="LX3" s="1" t="inlineStr"/>
-      <c r="LY3" s="1" t="inlineStr"/>
-      <c r="LZ3" s="1" t="inlineStr"/>
-      <c r="MA3" s="1" t="inlineStr"/>
-      <c r="MB3" s="1" t="inlineStr"/>
-      <c r="MC3" s="1" t="inlineStr"/>
-      <c r="MD3" s="1" t="inlineStr"/>
-      <c r="ME3" s="1" t="inlineStr"/>
-      <c r="MF3" s="1" t="inlineStr"/>
-      <c r="MG3" s="1" t="inlineStr"/>
-      <c r="MH3" s="1" t="inlineStr"/>
-      <c r="MI3" s="1" t="inlineStr"/>
-      <c r="MJ3" s="1" t="inlineStr"/>
-      <c r="MK3" s="1" t="inlineStr"/>
-      <c r="ML3" s="1" t="inlineStr"/>
-      <c r="MM3" s="1" t="inlineStr"/>
-      <c r="MN3" s="1" t="inlineStr"/>
-      <c r="MO3" s="1" t="inlineStr"/>
-      <c r="MP3" s="1" t="inlineStr"/>
-      <c r="MQ3" s="1" t="inlineStr"/>
-      <c r="MR3" s="1" t="inlineStr"/>
-      <c r="MS3" s="1" t="inlineStr"/>
-      <c r="MT3" s="1" t="inlineStr"/>
-      <c r="MU3" s="1" t="inlineStr"/>
-      <c r="MV3" s="1" t="inlineStr"/>
-      <c r="MW3" s="1" t="inlineStr"/>
-      <c r="MX3" s="1" t="inlineStr"/>
-      <c r="MY3" s="1" t="inlineStr"/>
-      <c r="MZ3" s="1" t="inlineStr"/>
-      <c r="NA3" s="1" t="inlineStr"/>
-      <c r="NB3" s="1" t="inlineStr"/>
-      <c r="NC3" s="1" t="inlineStr"/>
-      <c r="ND3" s="1" t="inlineStr"/>
-      <c r="NE3" s="1" t="inlineStr"/>
-      <c r="NF3" s="1" t="inlineStr"/>
-      <c r="NG3" s="1" t="inlineStr"/>
-      <c r="NH3" s="1" t="inlineStr"/>
-      <c r="NI3" s="1" t="inlineStr"/>
-      <c r="NJ3" s="1" t="inlineStr"/>
-      <c r="NK3" s="1" t="inlineStr"/>
-      <c r="NL3" s="1" t="inlineStr"/>
-      <c r="NM3" s="1" t="inlineStr"/>
-      <c r="NN3" s="1" t="inlineStr"/>
-      <c r="NO3" s="1" t="inlineStr"/>
-      <c r="NP3" s="1" t="inlineStr"/>
-      <c r="NQ3" s="1" t="inlineStr"/>
-      <c r="NR3" s="1" t="inlineStr"/>
-      <c r="NS3" s="1" t="inlineStr"/>
-      <c r="NT3" s="1" t="inlineStr"/>
-      <c r="NU3" s="1" t="inlineStr"/>
-      <c r="NV3" s="1" t="inlineStr"/>
-      <c r="NW3" s="1" t="inlineStr"/>
-      <c r="NX3" s="1" t="inlineStr"/>
-      <c r="NY3" s="1" t="inlineStr"/>
-      <c r="NZ3" s="1" t="inlineStr"/>
-      <c r="OA3" s="1" t="inlineStr"/>
-      <c r="OB3" s="1" t="inlineStr"/>
-      <c r="OC3" s="1" t="inlineStr"/>
-      <c r="OD3" s="1" t="inlineStr"/>
-      <c r="OE3" s="1" t="inlineStr"/>
-      <c r="OF3" s="1" t="inlineStr"/>
-      <c r="OG3" s="1" t="inlineStr"/>
-      <c r="OH3" s="1" t="inlineStr"/>
-      <c r="OI3" s="1" t="inlineStr"/>
-      <c r="OJ3" s="1" t="inlineStr"/>
-      <c r="OK3" s="1" t="inlineStr"/>
-      <c r="OL3" s="1" t="inlineStr"/>
-      <c r="OM3" s="1" t="inlineStr"/>
-      <c r="ON3" s="1" t="inlineStr"/>
-      <c r="OO3" s="1" t="inlineStr"/>
-      <c r="OP3" s="1" t="inlineStr"/>
-      <c r="OQ3" s="1" t="inlineStr"/>
-      <c r="OR3" s="1" t="inlineStr"/>
-      <c r="OS3" s="1" t="inlineStr"/>
-      <c r="OT3" s="1" t="inlineStr"/>
-      <c r="OU3" s="1" t="inlineStr"/>
-      <c r="OV3" s="1" t="inlineStr"/>
-      <c r="OW3" s="1" t="inlineStr"/>
-      <c r="OX3" s="1" t="inlineStr"/>
-      <c r="OY3" s="1" t="inlineStr"/>
-      <c r="OZ3" s="1" t="inlineStr"/>
-      <c r="PA3" s="1" t="inlineStr"/>
-      <c r="PB3" s="1" t="inlineStr"/>
-      <c r="PC3" s="1" t="inlineStr"/>
-      <c r="PD3" s="1" t="inlineStr"/>
-      <c r="PE3" s="1" t="inlineStr"/>
-      <c r="PF3" s="1" t="inlineStr"/>
-      <c r="PG3" s="1" t="inlineStr"/>
-      <c r="PH3" s="1" t="inlineStr"/>
-      <c r="PI3" s="1" t="inlineStr"/>
-      <c r="PJ3" s="1" t="inlineStr"/>
-      <c r="PK3" s="1" t="inlineStr"/>
-      <c r="PL3" s="1" t="inlineStr"/>
-      <c r="PM3" s="1" t="inlineStr"/>
-      <c r="PN3" s="1" t="inlineStr"/>
-      <c r="PO3" s="1" t="inlineStr"/>
-      <c r="PP3" s="1" t="inlineStr"/>
-      <c r="PQ3" s="1" t="inlineStr"/>
-      <c r="PR3" s="1" t="inlineStr"/>
-      <c r="PS3" s="1" t="inlineStr"/>
-      <c r="PT3" s="1" t="inlineStr"/>
-      <c r="PU3" s="1" t="inlineStr"/>
-      <c r="PV3" s="1" t="inlineStr"/>
-      <c r="PW3" s="1" t="inlineStr"/>
-      <c r="PX3" s="1" t="inlineStr"/>
-      <c r="PY3" s="1" t="inlineStr"/>
-      <c r="PZ3" s="1" t="inlineStr"/>
-      <c r="QA3" s="1" t="inlineStr"/>
-      <c r="QB3" s="1" t="inlineStr"/>
-      <c r="QC3" s="1" t="inlineStr"/>
-      <c r="QD3" s="1" t="inlineStr"/>
-      <c r="QE3" s="1" t="inlineStr"/>
-      <c r="QF3" s="1" t="inlineStr"/>
-      <c r="QG3" s="1" t="inlineStr"/>
-      <c r="QH3" s="1" t="inlineStr"/>
-      <c r="QI3" s="1" t="inlineStr"/>
-      <c r="QJ3" s="1" t="inlineStr"/>
-      <c r="QK3" s="1" t="inlineStr"/>
-      <c r="QL3" s="1" t="inlineStr"/>
-      <c r="QM3" s="1" t="inlineStr"/>
-      <c r="QN3" s="1" t="inlineStr"/>
-      <c r="QO3" s="1" t="inlineStr"/>
-      <c r="QP3" s="1" t="inlineStr"/>
-      <c r="QQ3" s="1" t="inlineStr"/>
-      <c r="QR3" s="1" t="inlineStr"/>
-      <c r="QS3" s="1" t="inlineStr"/>
-      <c r="QT3" s="1" t="inlineStr"/>
-      <c r="QU3" s="1" t="inlineStr"/>
-      <c r="QV3" s="1" t="inlineStr"/>
-      <c r="QW3" s="1" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr"/>
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" s="2" t="inlineStr"/>
+      <c r="AX3" s="2" t="inlineStr"/>
+      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AZ3" s="2" t="inlineStr"/>
+      <c r="BA3" s="2" t="inlineStr"/>
+      <c r="BB3" s="2" t="inlineStr"/>
+      <c r="BC3" s="2" t="inlineStr"/>
+      <c r="BD3" s="2" t="inlineStr"/>
+      <c r="BE3" s="2" t="inlineStr"/>
+      <c r="BF3" s="2" t="inlineStr"/>
+      <c r="BG3" s="2" t="inlineStr"/>
+      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BM3" s="2" t="inlineStr"/>
+      <c r="BN3" s="2" t="inlineStr"/>
+      <c r="BO3" s="2" t="inlineStr"/>
+      <c r="BP3" s="2" t="inlineStr"/>
+      <c r="BQ3" s="2" t="inlineStr"/>
+      <c r="BR3" s="2" t="inlineStr"/>
+      <c r="BS3" s="2" t="inlineStr"/>
+      <c r="BT3" s="2" t="inlineStr"/>
+      <c r="BU3" s="2" t="inlineStr"/>
+      <c r="BV3" s="2" t="inlineStr"/>
+      <c r="BW3" s="2" t="inlineStr"/>
+      <c r="BX3" s="2" t="inlineStr"/>
+      <c r="BY3" s="2" t="inlineStr"/>
+      <c r="BZ3" s="2" t="inlineStr"/>
+      <c r="CA3" s="2" t="inlineStr"/>
+      <c r="CB3" s="2" t="inlineStr"/>
+      <c r="CC3" s="2" t="inlineStr"/>
+      <c r="CD3" s="2" t="inlineStr"/>
+      <c r="CE3" s="2" t="inlineStr"/>
+      <c r="CF3" s="2" t="inlineStr"/>
+      <c r="CG3" s="2" t="inlineStr"/>
+      <c r="CH3" s="2" t="inlineStr"/>
+      <c r="CI3" s="2" t="inlineStr"/>
+      <c r="CJ3" s="2" t="inlineStr"/>
+      <c r="CK3" s="2" t="inlineStr"/>
+      <c r="CL3" s="2" t="inlineStr"/>
+      <c r="CM3" s="2" t="inlineStr"/>
+      <c r="CN3" s="2" t="inlineStr"/>
+      <c r="CO3" s="2" t="inlineStr"/>
+      <c r="CP3" s="2" t="inlineStr"/>
+      <c r="CQ3" s="2" t="inlineStr"/>
+      <c r="CR3" s="2" t="inlineStr"/>
+      <c r="CS3" s="2" t="inlineStr"/>
+      <c r="CT3" s="2" t="inlineStr"/>
+      <c r="CU3" s="2" t="inlineStr"/>
+      <c r="CV3" s="2" t="inlineStr"/>
+      <c r="CW3" s="2" t="inlineStr"/>
+      <c r="CX3" s="2" t="inlineStr"/>
+      <c r="CY3" s="2" t="inlineStr"/>
+      <c r="CZ3" s="2" t="inlineStr"/>
+      <c r="DA3" s="2" t="inlineStr"/>
+      <c r="DB3" s="2" t="inlineStr"/>
+      <c r="DC3" s="2" t="inlineStr"/>
+      <c r="DD3" s="2" t="inlineStr"/>
+      <c r="DE3" s="2" t="inlineStr"/>
+      <c r="DF3" s="2" t="inlineStr"/>
+      <c r="DG3" s="2" t="inlineStr"/>
+      <c r="DH3" s="2" t="inlineStr"/>
+      <c r="DI3" s="2" t="inlineStr"/>
+      <c r="DJ3" s="2" t="inlineStr"/>
+      <c r="DK3" s="2" t="inlineStr"/>
+      <c r="DL3" s="2" t="inlineStr"/>
+      <c r="DM3" s="2" t="inlineStr"/>
+      <c r="DN3" s="2" t="inlineStr"/>
+      <c r="DO3" s="2" t="inlineStr"/>
+      <c r="DP3" s="2" t="inlineStr"/>
+      <c r="DQ3" s="2" t="inlineStr"/>
+      <c r="DR3" s="2" t="inlineStr"/>
+      <c r="DS3" s="2" t="inlineStr"/>
+      <c r="DT3" s="2" t="inlineStr"/>
+      <c r="DU3" s="2" t="inlineStr"/>
+      <c r="DV3" s="2" t="inlineStr"/>
+      <c r="DW3" s="2" t="inlineStr"/>
+      <c r="DX3" s="2" t="inlineStr"/>
+      <c r="DY3" s="2" t="inlineStr"/>
+      <c r="DZ3" s="2" t="inlineStr"/>
+      <c r="EA3" s="2" t="inlineStr"/>
+      <c r="EB3" s="2" t="inlineStr"/>
+      <c r="EC3" s="2" t="inlineStr"/>
+      <c r="ED3" s="2" t="inlineStr"/>
+      <c r="EE3" s="2" t="inlineStr"/>
+      <c r="EF3" s="2" t="inlineStr"/>
+      <c r="EG3" s="2" t="inlineStr"/>
+      <c r="EH3" s="2" t="inlineStr"/>
+      <c r="EI3" s="2" t="inlineStr"/>
+      <c r="EJ3" s="2" t="inlineStr"/>
+      <c r="EK3" s="2" t="inlineStr"/>
+      <c r="EL3" s="2" t="inlineStr"/>
+      <c r="EM3" s="2" t="inlineStr"/>
+      <c r="EN3" s="2" t="inlineStr"/>
+      <c r="EO3" s="2" t="inlineStr"/>
+      <c r="EP3" s="2" t="inlineStr"/>
+      <c r="EQ3" s="2" t="inlineStr"/>
+      <c r="ER3" s="2" t="inlineStr"/>
+      <c r="ES3" s="2" t="inlineStr"/>
+      <c r="ET3" s="2" t="inlineStr"/>
+      <c r="EU3" s="2" t="inlineStr"/>
+      <c r="EV3" s="2" t="inlineStr"/>
+      <c r="EW3" s="2" t="inlineStr"/>
+      <c r="EX3" s="2" t="inlineStr"/>
+      <c r="EY3" s="2" t="inlineStr"/>
+      <c r="EZ3" s="2" t="inlineStr"/>
+      <c r="FA3" s="2" t="inlineStr"/>
+      <c r="FB3" s="2" t="inlineStr"/>
+      <c r="FC3" s="2" t="inlineStr"/>
+      <c r="FD3" s="2" t="inlineStr"/>
+      <c r="FE3" s="2" t="inlineStr"/>
+      <c r="FF3" s="2" t="inlineStr"/>
+      <c r="FG3" s="2" t="inlineStr"/>
+      <c r="FH3" s="2" t="inlineStr"/>
+      <c r="FI3" s="2" t="inlineStr"/>
+      <c r="FJ3" s="2" t="inlineStr"/>
+      <c r="FK3" s="2" t="inlineStr"/>
+      <c r="FL3" s="2" t="inlineStr"/>
+      <c r="FM3" s="2" t="inlineStr"/>
+      <c r="FN3" s="2" t="inlineStr"/>
+      <c r="FO3" s="2" t="inlineStr"/>
+      <c r="FP3" s="2" t="inlineStr"/>
+      <c r="FQ3" s="2" t="inlineStr"/>
+      <c r="FR3" s="2" t="inlineStr"/>
+      <c r="FS3" s="2" t="inlineStr"/>
+      <c r="FT3" s="2" t="inlineStr"/>
+      <c r="FU3" s="2" t="inlineStr"/>
+      <c r="FV3" s="2" t="inlineStr"/>
+      <c r="FW3" s="2" t="inlineStr"/>
+      <c r="FX3" s="2" t="inlineStr"/>
+      <c r="FY3" s="2" t="inlineStr"/>
+      <c r="FZ3" s="2" t="inlineStr"/>
+      <c r="GA3" s="2" t="inlineStr"/>
+      <c r="GB3" s="2" t="inlineStr"/>
+      <c r="GC3" s="2" t="inlineStr"/>
+      <c r="GD3" s="2" t="inlineStr"/>
+      <c r="GE3" s="2" t="inlineStr"/>
+      <c r="GF3" s="2" t="inlineStr"/>
+      <c r="GG3" s="2" t="inlineStr"/>
+      <c r="GH3" s="2" t="inlineStr"/>
+      <c r="GI3" s="2" t="inlineStr"/>
+      <c r="GJ3" s="2" t="inlineStr"/>
+      <c r="GK3" s="2" t="inlineStr"/>
+      <c r="GL3" s="2" t="inlineStr"/>
+      <c r="GM3" s="2" t="inlineStr"/>
+      <c r="GN3" s="2" t="inlineStr"/>
+      <c r="GO3" s="2" t="inlineStr"/>
+      <c r="GP3" s="2" t="inlineStr"/>
+      <c r="GQ3" s="2" t="inlineStr"/>
+      <c r="GR3" s="2" t="inlineStr"/>
+      <c r="GS3" s="2" t="inlineStr"/>
+      <c r="GT3" s="2" t="inlineStr"/>
+      <c r="GU3" s="2" t="inlineStr"/>
+      <c r="GV3" s="2" t="inlineStr"/>
+      <c r="GW3" s="2" t="inlineStr"/>
+      <c r="GX3" s="2" t="inlineStr"/>
+      <c r="GY3" s="2" t="inlineStr"/>
+      <c r="GZ3" s="2" t="inlineStr"/>
+      <c r="HA3" s="2" t="inlineStr"/>
+      <c r="HB3" s="2" t="inlineStr"/>
+      <c r="HC3" s="2" t="inlineStr"/>
+      <c r="HD3" s="2" t="inlineStr"/>
+      <c r="HE3" s="2" t="inlineStr"/>
+      <c r="HF3" s="2" t="inlineStr"/>
+      <c r="HG3" s="2" t="inlineStr"/>
+      <c r="HH3" s="2" t="inlineStr"/>
+      <c r="HI3" s="2" t="inlineStr"/>
+      <c r="HJ3" s="2" t="inlineStr"/>
+      <c r="HK3" s="2" t="inlineStr"/>
+      <c r="HL3" s="2" t="inlineStr"/>
+      <c r="HM3" s="2" t="inlineStr"/>
+      <c r="HN3" s="2" t="inlineStr"/>
+      <c r="HO3" s="2" t="inlineStr"/>
+      <c r="HP3" s="2" t="inlineStr"/>
+      <c r="HQ3" s="2" t="inlineStr"/>
+      <c r="HR3" s="2" t="inlineStr"/>
+      <c r="HS3" s="2" t="inlineStr"/>
+      <c r="HT3" s="2" t="inlineStr"/>
+      <c r="HU3" s="2" t="inlineStr"/>
+      <c r="HV3" s="2" t="inlineStr"/>
+      <c r="HW3" s="2" t="inlineStr"/>
+      <c r="HX3" s="2" t="inlineStr"/>
+      <c r="HY3" s="2" t="inlineStr"/>
+      <c r="HZ3" s="2" t="inlineStr"/>
+      <c r="IA3" s="2" t="inlineStr"/>
+      <c r="IB3" s="2" t="inlineStr"/>
+      <c r="IC3" s="2" t="inlineStr"/>
+      <c r="ID3" s="2" t="inlineStr"/>
+      <c r="IE3" s="2" t="inlineStr"/>
+      <c r="IF3" s="2" t="inlineStr"/>
+      <c r="IG3" s="2" t="inlineStr"/>
+      <c r="IH3" s="2" t="inlineStr"/>
+      <c r="II3" s="2" t="inlineStr"/>
+      <c r="IJ3" s="2" t="inlineStr"/>
+      <c r="IK3" s="2" t="inlineStr"/>
+      <c r="IL3" s="2" t="inlineStr"/>
+      <c r="IM3" s="2" t="inlineStr"/>
+      <c r="IN3" s="2" t="inlineStr"/>
+      <c r="IO3" s="2" t="inlineStr"/>
+      <c r="IP3" s="2" t="inlineStr"/>
+      <c r="IQ3" s="2" t="inlineStr"/>
+      <c r="IR3" s="2" t="inlineStr"/>
+      <c r="IS3" s="2" t="inlineStr"/>
+      <c r="IT3" s="2" t="inlineStr"/>
+      <c r="IU3" s="2" t="inlineStr"/>
+      <c r="IV3" s="2" t="inlineStr"/>
+      <c r="IW3" s="2" t="inlineStr"/>
+      <c r="IX3" s="2" t="inlineStr"/>
+      <c r="IY3" s="2" t="inlineStr"/>
+      <c r="IZ3" s="2" t="inlineStr"/>
+      <c r="JA3" s="2" t="inlineStr"/>
+      <c r="JB3" s="2" t="inlineStr"/>
+      <c r="JC3" s="2" t="inlineStr"/>
+      <c r="JD3" s="2" t="inlineStr"/>
+      <c r="JE3" s="2" t="inlineStr"/>
+      <c r="JF3" s="2" t="inlineStr"/>
+      <c r="JG3" s="2" t="inlineStr"/>
+      <c r="JH3" s="2" t="inlineStr"/>
+      <c r="JI3" s="2" t="inlineStr"/>
+      <c r="JJ3" s="2" t="inlineStr"/>
+      <c r="JK3" s="2" t="inlineStr"/>
+      <c r="JL3" s="2" t="inlineStr"/>
+      <c r="JM3" s="2" t="inlineStr"/>
+      <c r="JN3" s="2" t="inlineStr"/>
+      <c r="JO3" s="2" t="inlineStr"/>
+      <c r="JP3" s="2" t="inlineStr"/>
+      <c r="JQ3" s="2" t="inlineStr"/>
+      <c r="JR3" s="2" t="inlineStr"/>
+      <c r="JS3" s="2" t="inlineStr"/>
+      <c r="JT3" s="2" t="inlineStr"/>
+      <c r="JU3" s="2" t="inlineStr"/>
+      <c r="JV3" s="2" t="inlineStr"/>
+      <c r="JW3" s="2" t="inlineStr"/>
+      <c r="JX3" s="2" t="inlineStr"/>
+      <c r="JY3" s="2" t="inlineStr"/>
+      <c r="JZ3" s="2" t="inlineStr"/>
+      <c r="KA3" s="2" t="inlineStr"/>
+      <c r="KB3" s="2" t="inlineStr"/>
+      <c r="KC3" s="2" t="inlineStr"/>
+      <c r="KD3" s="2" t="inlineStr"/>
+      <c r="KE3" s="2" t="inlineStr"/>
+      <c r="KF3" s="2" t="inlineStr"/>
+      <c r="KG3" s="2" t="inlineStr"/>
+      <c r="KH3" s="2" t="inlineStr"/>
+      <c r="KI3" s="2" t="inlineStr"/>
+      <c r="KJ3" s="2" t="inlineStr"/>
+      <c r="KK3" s="2" t="inlineStr"/>
+      <c r="KL3" s="2" t="inlineStr"/>
+      <c r="KM3" s="2" t="inlineStr"/>
+      <c r="KN3" s="2" t="inlineStr"/>
+      <c r="KO3" s="2" t="inlineStr"/>
+      <c r="KP3" s="2" t="inlineStr"/>
+      <c r="KQ3" s="2" t="inlineStr"/>
+      <c r="KR3" s="2" t="inlineStr"/>
+      <c r="KS3" s="2" t="inlineStr"/>
+      <c r="KT3" s="2" t="inlineStr"/>
+      <c r="KU3" s="2" t="inlineStr"/>
+      <c r="KV3" s="2" t="inlineStr"/>
+      <c r="KW3" s="2" t="inlineStr"/>
+      <c r="KX3" s="2" t="inlineStr"/>
+      <c r="KY3" s="2" t="inlineStr"/>
+      <c r="KZ3" s="2" t="inlineStr"/>
+      <c r="LA3" s="2" t="inlineStr"/>
+      <c r="LB3" s="2" t="inlineStr"/>
+      <c r="LC3" s="2" t="inlineStr"/>
+      <c r="LD3" s="2" t="inlineStr"/>
+      <c r="LE3" s="2" t="inlineStr"/>
+      <c r="LF3" s="2" t="inlineStr"/>
+      <c r="LG3" s="2" t="inlineStr"/>
+      <c r="LH3" s="2" t="inlineStr"/>
+      <c r="LI3" s="2" t="inlineStr"/>
+      <c r="LJ3" s="2" t="inlineStr"/>
+      <c r="LK3" s="2" t="inlineStr"/>
+      <c r="LL3" s="2" t="inlineStr"/>
+      <c r="LM3" s="2" t="inlineStr"/>
+      <c r="LN3" s="2" t="inlineStr"/>
+      <c r="LO3" s="2" t="inlineStr"/>
+      <c r="LP3" s="2" t="inlineStr"/>
+      <c r="LQ3" s="2" t="inlineStr"/>
+      <c r="LR3" s="2" t="inlineStr"/>
+      <c r="LS3" s="2" t="inlineStr"/>
+      <c r="LT3" s="2" t="inlineStr"/>
+      <c r="LU3" s="2" t="inlineStr"/>
+      <c r="LV3" s="2" t="inlineStr"/>
+      <c r="LW3" s="2" t="inlineStr"/>
+      <c r="LX3" s="2" t="inlineStr"/>
+      <c r="LY3" s="2" t="inlineStr"/>
+      <c r="LZ3" s="2" t="inlineStr"/>
+      <c r="MA3" s="2" t="inlineStr"/>
+      <c r="MB3" s="2" t="inlineStr"/>
+      <c r="MC3" s="2" t="inlineStr"/>
+      <c r="MD3" s="2" t="inlineStr"/>
+      <c r="ME3" s="2" t="inlineStr"/>
+      <c r="MF3" s="2" t="inlineStr"/>
+      <c r="MG3" s="2" t="inlineStr"/>
+      <c r="MH3" s="2" t="inlineStr"/>
+      <c r="MI3" s="2" t="inlineStr"/>
+      <c r="MJ3" s="2" t="inlineStr"/>
+      <c r="MK3" s="2" t="inlineStr"/>
+      <c r="ML3" s="2" t="inlineStr"/>
+      <c r="MM3" s="2" t="inlineStr"/>
+      <c r="MN3" s="2" t="inlineStr"/>
+      <c r="MO3" s="2" t="inlineStr"/>
+      <c r="MP3" s="2" t="inlineStr"/>
+      <c r="MQ3" s="2" t="inlineStr"/>
+      <c r="MR3" s="2" t="inlineStr"/>
+      <c r="MS3" s="2" t="inlineStr"/>
+      <c r="MT3" s="2" t="inlineStr"/>
+      <c r="MU3" s="2" t="inlineStr"/>
+      <c r="MV3" s="2" t="inlineStr"/>
+      <c r="MW3" s="2" t="inlineStr"/>
+      <c r="MX3" s="2" t="inlineStr"/>
+      <c r="MY3" s="2" t="inlineStr"/>
+      <c r="MZ3" s="2" t="inlineStr"/>
+      <c r="NA3" s="2" t="inlineStr"/>
+      <c r="NB3" s="2" t="inlineStr"/>
+      <c r="NC3" s="2" t="inlineStr"/>
+      <c r="ND3" s="2" t="inlineStr"/>
+      <c r="NE3" s="2" t="inlineStr"/>
+      <c r="NF3" s="2" t="inlineStr"/>
+      <c r="NG3" s="2" t="inlineStr"/>
+      <c r="NH3" s="2" t="inlineStr"/>
+      <c r="NI3" s="2" t="inlineStr"/>
+      <c r="NJ3" s="2" t="inlineStr"/>
+      <c r="NK3" s="2" t="inlineStr"/>
+      <c r="NL3" s="2" t="inlineStr"/>
+      <c r="NM3" s="2" t="inlineStr"/>
+      <c r="NN3" s="2" t="inlineStr"/>
+      <c r="NO3" s="2" t="inlineStr"/>
+      <c r="NP3" s="2" t="inlineStr"/>
+      <c r="NQ3" s="2" t="inlineStr"/>
+      <c r="NR3" s="2" t="inlineStr"/>
+      <c r="NS3" s="2" t="inlineStr"/>
+      <c r="NT3" s="2" t="inlineStr"/>
+      <c r="NU3" s="2" t="inlineStr"/>
+      <c r="NV3" s="2" t="inlineStr"/>
+      <c r="NW3" s="2" t="inlineStr"/>
+      <c r="NX3" s="2" t="inlineStr"/>
+      <c r="NY3" s="2" t="inlineStr"/>
+      <c r="NZ3" s="2" t="inlineStr"/>
+      <c r="OA3" s="2" t="inlineStr"/>
+      <c r="OB3" s="2" t="inlineStr"/>
+      <c r="OC3" s="2" t="inlineStr"/>
+      <c r="OD3" s="2" t="inlineStr"/>
+      <c r="OE3" s="2" t="inlineStr"/>
+      <c r="OF3" s="2" t="inlineStr"/>
+      <c r="OG3" s="2" t="inlineStr"/>
+      <c r="OH3" s="2" t="inlineStr"/>
+      <c r="OI3" s="2" t="inlineStr"/>
+      <c r="OJ3" s="2" t="inlineStr"/>
+      <c r="OK3" s="2" t="inlineStr"/>
+      <c r="OL3" s="2" t="inlineStr"/>
+      <c r="OM3" s="2" t="inlineStr"/>
+      <c r="ON3" s="2" t="inlineStr"/>
+      <c r="OO3" s="2" t="inlineStr"/>
+      <c r="OP3" s="2" t="inlineStr"/>
+      <c r="OQ3" s="2" t="inlineStr"/>
+      <c r="OR3" s="2" t="inlineStr"/>
+      <c r="OS3" s="2" t="inlineStr"/>
+      <c r="OT3" s="2" t="inlineStr"/>
+      <c r="OU3" s="2" t="inlineStr"/>
+      <c r="OV3" s="2" t="inlineStr"/>
+      <c r="OW3" s="2" t="inlineStr"/>
+      <c r="OX3" s="2" t="inlineStr"/>
+      <c r="OY3" s="2" t="inlineStr"/>
+      <c r="OZ3" s="2" t="inlineStr"/>
+      <c r="PA3" s="2" t="inlineStr"/>
+      <c r="PB3" s="2" t="inlineStr"/>
+      <c r="PC3" s="2" t="inlineStr"/>
+      <c r="PD3" s="2" t="inlineStr"/>
+      <c r="PE3" s="2" t="inlineStr"/>
+      <c r="PF3" s="2" t="inlineStr"/>
+      <c r="PG3" s="2" t="inlineStr"/>
+      <c r="PH3" s="2" t="inlineStr"/>
+      <c r="PI3" s="2" t="inlineStr"/>
+      <c r="PJ3" s="2" t="inlineStr"/>
+      <c r="PK3" s="2" t="inlineStr"/>
+      <c r="PL3" s="2" t="inlineStr"/>
+      <c r="PM3" s="2" t="inlineStr"/>
+      <c r="PN3" s="2" t="inlineStr"/>
+      <c r="PO3" s="2" t="inlineStr"/>
+      <c r="PP3" s="2" t="inlineStr"/>
+      <c r="PQ3" s="2" t="inlineStr"/>
+      <c r="PR3" s="2" t="inlineStr"/>
+      <c r="PS3" s="2" t="inlineStr"/>
+      <c r="PT3" s="2" t="inlineStr"/>
+      <c r="PU3" s="2" t="inlineStr"/>
+      <c r="PV3" s="2" t="inlineStr"/>
+      <c r="PW3" s="2" t="inlineStr"/>
+      <c r="PX3" s="2" t="inlineStr"/>
+      <c r="PY3" s="2" t="inlineStr"/>
+      <c r="PZ3" s="2" t="inlineStr"/>
+      <c r="QA3" s="2" t="inlineStr"/>
+      <c r="QB3" s="2" t="inlineStr"/>
+      <c r="QC3" s="2" t="inlineStr"/>
+      <c r="QD3" s="2" t="inlineStr"/>
+      <c r="QE3" s="2" t="inlineStr"/>
+      <c r="QF3" s="2" t="inlineStr"/>
+      <c r="QG3" s="2" t="inlineStr"/>
+      <c r="QH3" s="2" t="inlineStr"/>
+      <c r="QI3" s="2" t="inlineStr"/>
+      <c r="QJ3" s="2" t="inlineStr"/>
+      <c r="QK3" s="2" t="inlineStr"/>
+      <c r="QL3" s="2" t="inlineStr"/>
+      <c r="QM3" s="2" t="inlineStr"/>
+      <c r="QN3" s="2" t="inlineStr"/>
+      <c r="QO3" s="2" t="inlineStr"/>
+      <c r="QP3" s="2" t="inlineStr"/>
+      <c r="QQ3" s="2" t="inlineStr"/>
+      <c r="QR3" s="2" t="inlineStr"/>
+      <c r="QS3" s="2" t="inlineStr"/>
+      <c r="QT3" s="2" t="inlineStr"/>
+      <c r="QU3" s="2" t="inlineStr"/>
+      <c r="QV3" s="2" t="inlineStr"/>
+      <c r="QW3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pink_sheet.xlsx
+++ b/data/pink_sheet.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,21 +26,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
+      <name val="Arial Narrow"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,10 +62,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -904,7 +909,7 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>96%Al Secondary Aluminum Ingots CIF Nansha Port China (USD/t)</t>
         </is>
@@ -914,7 +919,7 @@
           <t>96%Al Secondary Aluminum Ingots CIF Ningbo Port China (USD/t)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>96%Al Secondary Aluminum Ingots CIF Qingdao Port China (USD/t)</t>
         </is>
@@ -924,7 +929,7 @@
           <t>96%Al Secondary Aluminum Ingots CIF Qinzhou Port China (USD/t)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>98%Al Secondary Aluminum Ingots CIF Nansha Port China (USD/t)</t>
         </is>
@@ -934,7 +939,7 @@
           <t>98%Al Secondary Aluminum Ingots CIF Ningbo Port China (USD/t)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>98%Al Secondary Aluminum Ingots CIF Qingdao Port China (USD/t)</t>
         </is>
@@ -944,7 +949,7 @@
           <t>98%Al Secondary Aluminum Ingots CIF Qinzhou Port China (USD/t)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Al Secondary Aluminum Ingots CIF Nansha Port China (USD/t)</t>
         </is>
@@ -954,7 +959,7 @@
           <t>Al Secondary Aluminum Ingots CIF Ningbo Port China (USD/t)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Al Secondary Aluminum Ingots CIF Qingdao Port China (USD/t)</t>
         </is>
@@ -964,7 +969,7 @@
           <t>Al Secondary Aluminum Ingots CIF Qinzhou Port China (USD/t)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>SMM A00 Aluminum Ingot (USD/t)</t>
         </is>
@@ -974,7 +979,7 @@
           <t>SMM AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>SMM Chongqing A00 Aluminum Ingot (USD/t)</t>
         </is>
@@ -984,7 +989,7 @@
           <t>SMM Chongqing AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>SMM Foshan A00 Aluminum Ingot (USD/t)</t>
         </is>
@@ -994,7 +999,7 @@
           <t>SMM Foshan AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>SMM Guangyuan A00 Aluminum Ingot (USD/t)</t>
         </is>
@@ -1004,7 +1009,7 @@
           <t>SMM Guangyuan AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>SMM Hangzhou A00 Aluminum Ingot (USD/t)</t>
         </is>
@@ -1014,7 +1019,7 @@
           <t>SMM Hangzhou AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>SMM Henan A00 Aluminum Ingot (USD/t)</t>
         </is>
@@ -1024,7 +1029,7 @@
           <t>SMM Henan AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>SMM Linyi A00 Aluminum Ingot (USD/t)</t>
         </is>
@@ -1034,7 +1039,7 @@
           <t>SMM Linyi AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>SMM Shenyang A00 Aluminum Ingot (USD/t)</t>
         </is>
@@ -1044,7 +1049,7 @@
           <t>SMM Shenyang AAluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>SMM Southern China die-cast Aluminum Ingot (USD/t)</t>
         </is>
@@ -1054,7 +1059,7 @@
           <t>SMM Tianjin A00 Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t>SMM Tianjin AAluminum Ingot (USD/t)</t>
         </is>
@@ -1064,7 +1069,7 @@
           <t>SMM Wuxi A00 Aluminum Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" s="2" t="inlineStr">
         <is>
           <t>SMM Wuxi AAluminum Ingot (USD/t)</t>
         </is>
@@ -1074,7 +1079,7 @@
           <t>UBC Ingot (USD/t)</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot (USD/t)</t>
         </is>
@@ -1084,7 +1089,7 @@
           <t>Aluminum Alloy Ingot A (USD/t)</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot A356 (USD/t)</t>
         </is>
@@ -1094,7 +1099,7 @@
           <t>Aluminum Alloy Ingot A360 (USD/t)</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot A380 (USD/t)</t>
         </is>
@@ -1104,7 +1109,7 @@
           <t>Aluminum Alloy Ingot AC4B (USD/t)</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot ACB (USD/t)</t>
         </is>
@@ -1114,7 +1119,7 @@
           <t>Aluminum Alloy Ingot ADC12 CIF Japan (USD/t)</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot ADC12 CIF Ningbo (USD/t)</t>
         </is>
@@ -1124,7 +1129,7 @@
           <t>Aluminum Alloy Ingot ADCCIF Japan (USD/t)</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot ADCCIF Ningbo (USD/t)</t>
         </is>
@@ -1134,7 +1139,7 @@
           <t>Aluminum Alloy Ingot AlSi(Fe) (USD/t)</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AlSi10Mg(Fe) (USD/t)</t>
         </is>
@@ -1144,7 +1149,7 @@
           <t>Aluminum Alloy Ingot AlSi10MnMg (USD/t)</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AlSi12(Fe) (USD/t)</t>
         </is>
@@ -1154,7 +1159,7 @@
           <t>Aluminum Alloy Ingot AlSi9Cu3 (USD/t)</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AlSiCu (USD/t)</t>
         </is>
@@ -1164,7 +1169,7 @@
           <t>Aluminum Alloy Ingot AlSiMg(Fe) (USD/t)</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot AlSiMnMg (USD/t)</t>
         </is>
@@ -1174,7 +1179,7 @@
           <t>Aluminum Alloy Ingot ZLD (USD/t)</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Alloy Ingot ZLD102 (USD/t)</t>
         </is>
@@ -1184,7 +1189,7 @@
           <t>Aluminum Alloy Ingot ZLD104 (USD/t)</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" s="2" t="inlineStr">
         <is>
           <t>East China Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
@@ -1194,7 +1199,7 @@
           <t>East China Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" s="2" t="inlineStr">
         <is>
           <t>Guizhou Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
@@ -1204,7 +1209,7 @@
           <t>Guizhou Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" s="2" t="inlineStr">
         <is>
           <t>Hunan Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
@@ -1214,7 +1219,7 @@
           <t>Hunan Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" s="2" t="inlineStr">
         <is>
           <t>Low-Carbon Aluminum Alloy Ingot A (USD/t)</t>
         </is>
@@ -1224,7 +1229,7 @@
           <t>Low-Carbon Aluminum Alloy Ingot A356 (USD/t)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" s="2" t="inlineStr">
         <is>
           <t>Low-Carbon Aluminum Alloy Ingot ZLD (USD/t)</t>
         </is>
@@ -1234,7 +1239,7 @@
           <t>Low-Carbon Aluminum Alloy Ingot ZLD102 (USD/t)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" s="2" t="inlineStr">
         <is>
           <t>Low-Carbon Aluminum Alloy Ingot ZLD104 (USD/t)</t>
         </is>
@@ -1244,7 +1249,7 @@
           <t>Malaysia Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" s="2" t="inlineStr">
         <is>
           <t>Malaysia Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
@@ -1254,7 +1259,7 @@
           <t>Malaysia Aluminum Alloy Ingot ADC12 FOB (USD/t)</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" s="2" t="inlineStr">
         <is>
           <t>Malaysia Aluminum Alloy Ingot ADCFOB (USD/t)</t>
         </is>
@@ -1264,7 +1269,7 @@
           <t>Ningbo Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" s="2" t="inlineStr">
         <is>
           <t>Ningbo Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
@@ -1274,7 +1279,7 @@
           <t>Northeast China Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" s="2" t="inlineStr">
         <is>
           <t>Northeast China Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
@@ -1284,7 +1289,7 @@
           <t>Recycled Low-Carbon Aluminum Alloy Ingot A (USD/t)</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" s="2" t="inlineStr">
         <is>
           <t>Recycled Low-Carbon Aluminum Alloy Ingot A356 (USD/t)</t>
         </is>
@@ -1294,7 +1299,7 @@
           <t>SMM Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" s="2" t="inlineStr">
         <is>
           <t>SMM Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
@@ -1304,7 +1309,7 @@
           <t>South China Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" s="2" t="inlineStr">
         <is>
           <t>South China Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
@@ -1314,7 +1319,7 @@
           <t>Southwest China Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" s="2" t="inlineStr">
         <is>
           <t>Southwest China Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
@@ -1324,7 +1329,7 @@
           <t>Thailand Aluminum Alloy Ingot ADC12 FOB (USD/t)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" s="2" t="inlineStr">
         <is>
           <t>Thailand Aluminum Alloy Ingot ADCFOB (USD/t)</t>
         </is>
@@ -1334,7 +1339,7 @@
           <t>Thailand aluminium Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" s="2" t="inlineStr">
         <is>
           <t>Thailand aluminium Alloy Ingot ADC12 (USD/t)</t>
         </is>
@@ -1344,7 +1349,7 @@
           <t>Yunnan Aluminum Alloy Ingot ADC (USD/t)</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" s="2" t="inlineStr">
         <is>
           <t>Yunnan Aluminum Alloy Ingot ADC12 (USD/t)</t>
         </is>
@@ -1354,7 +1359,7 @@
           <t>Aluminum Low-Carbon P1020A Premium Index (USD/t)</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Low-Carbon PA Premium Index (USD/t)</t>
         </is>
@@ -1364,7 +1369,7 @@
           <t>SMM Aluminum Index (USD/t)</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" s="2" t="inlineStr">
         <is>
           <t>-series Low Carbon Double Zero Foil Premium (USD/t)</t>
         </is>
@@ -1374,7 +1379,7 @@
           <t>1-series Low Carbon Double Zero Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" s="2" t="inlineStr">
         <is>
           <t>1070 Aluminum Rod Premium (Inner Mongolia) (USD/t)</t>
         </is>
@@ -1384,7 +1389,7 @@
           <t>1070 Aluminum Rod Premium (Yunan) (USD/t)</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" s="2" t="inlineStr">
         <is>
           <t>12μ C-Coated Li Battery Al Foil Premium (USD/t)</t>
         </is>
@@ -1394,7 +1399,7 @@
           <t>12μ Li Battery Al Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" s="2" t="inlineStr">
         <is>
           <t>13μ C-Coated Li Battery Al Foil Premium (USD/t)</t>
         </is>
@@ -1404,7 +1409,7 @@
           <t>13μ Li Battery Al Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" s="2" t="inlineStr">
         <is>
           <t>15μ Li Battery Al Foil Premium (USD/t)</t>
         </is>
@@ -1414,7 +1419,7 @@
           <t>8-series Low Carbon Double Zero Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" s="2" t="inlineStr">
         <is>
           <t>Aluminium P1020A premium, DDP Midwest US (USD/t)</t>
         </is>
@@ -1424,7 +1429,7 @@
           <t>Aluminium PA premium, DDP Midwest US (USD/t)</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" s="2" t="inlineStr">
         <is>
           <t>Aluminum P0610A Premium FOB Indonesia (USD/t)</t>
         </is>
@@ -1434,7 +1439,7 @@
           <t>Aluminum P1020A Premium FOB Indonesia (USD/t)</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" s="2" t="inlineStr">
         <is>
           <t>Aluminum P1020A Premium in-whs dp Rotterdam (USD/t)</t>
         </is>
@@ -1444,7 +1449,7 @@
           <t>Aluminum P1020A Premium in-whs dup Rotterdam (USD/t)</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" s="2" t="inlineStr">
         <is>
           <t>Aluminum PA Premium FOB Indonesia (USD/t)</t>
         </is>
@@ -1454,7 +1459,7 @@
           <t>Aluminum PA Premium in-whs dp Rotterdam (USD/t)</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" s="2" t="inlineStr">
         <is>
           <t>Aluminum PA Premium in-whs dup Rotterdam (USD/t)</t>
         </is>
@@ -1464,7 +1469,7 @@
           <t>Aluminum Premium CIF Shanghai (USD/t)</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Premium CIF South Korea (USD/t)</t>
         </is>
@@ -1474,7 +1479,7 @@
           <t>Aluminum Premium CIF Thailand (USD/t)</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Premium FCA South Korea (USD/t)</t>
         </is>
@@ -1484,7 +1489,7 @@
           <t>Aluminum Premium In-whs Shanghai (USD/t)</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Quarterly Premium CIF Japan (USD/t)</t>
         </is>
@@ -1494,7 +1499,7 @@
           <t>Aluminum Rod Premium (Inner Mongolia) (USD/t)</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Rod Premium (Yunan) (USD/t)</t>
         </is>
@@ -1504,7 +1509,7 @@
           <t>Aluminum Spot Premium CIF Japan (USD/t)</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" s="2" t="inlineStr">
         <is>
           <t>Baotou φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1514,7 +1519,7 @@
           <t>Baotou φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" s="2" t="inlineStr">
         <is>
           <t>Baotou φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1524,7 +1529,7 @@
           <t>Baotou φAluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" s="2" t="inlineStr">
         <is>
           <t>Foshan 6061 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1534,7 +1539,7 @@
           <t>Foshan 6082 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" s="2" t="inlineStr">
         <is>
           <t>Foshan Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1544,7 +1549,7 @@
           <t>Foshan φ100 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" s="2" t="inlineStr">
         <is>
           <t>Foshan φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1554,7 +1559,7 @@
           <t>Foshan φ150 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" s="2" t="inlineStr">
         <is>
           <t>Foshan φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1564,7 +1569,7 @@
           <t>Foshan φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="ED1" s="2" t="inlineStr">
         <is>
           <t>Foshan φAluminum Billet Premium (USD/t)</t>
         </is>
@@ -1574,7 +1579,7 @@
           <t>Guangdong /Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EF1" s="2" t="inlineStr">
         <is>
           <t>Guangdong 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1584,7 +1589,7 @@
           <t>Guangdong 6101/6201 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EH1" s="2" t="inlineStr">
         <is>
           <t>Guangdong 8030 Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1594,7 +1599,7 @@
           <t>Guangdong 99.70% Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EJ1" s="2" t="inlineStr">
         <is>
           <t>Guangdong AAluminum Rod Premium (USD/t)</t>
         </is>
@@ -1604,7 +1609,7 @@
           <t>Guangdong Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EL1" s="2" t="inlineStr">
         <is>
           <t>Guangdong Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1614,7 +1619,7 @@
           <t>Hebei 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EN1" s="2" t="inlineStr">
         <is>
           <t>Hebei AAluminum Rod Premium (USD/t)</t>
         </is>
@@ -1624,7 +1629,7 @@
           <t>Henan /Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EP1" s="2" t="inlineStr">
         <is>
           <t>Henan 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1634,7 +1639,7 @@
           <t>Henan 6101/6201 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ER1" s="2" t="inlineStr">
         <is>
           <t>Henan 8030 Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1644,7 +1649,7 @@
           <t>Henan 99.70% Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="ET1" s="2" t="inlineStr">
         <is>
           <t>Henan AAluminum Rod Premium (USD/t)</t>
         </is>
@@ -1654,7 +1659,7 @@
           <t>Henan Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EV1" s="2" t="inlineStr">
         <is>
           <t>Henan Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1664,7 +1669,7 @@
           <t>Henan φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EX1" s="2" t="inlineStr">
         <is>
           <t>Henan φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1674,7 +1679,7 @@
           <t>Henan φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="EZ1" s="2" t="inlineStr">
         <is>
           <t>Henan φAluminum Billet Premium (USD/t)</t>
         </is>
@@ -1684,7 +1689,7 @@
           <t>Inner Mongolia 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FB1" s="2" t="inlineStr">
         <is>
           <t>Inner Mongolia 99.70% Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1694,7 +1699,7 @@
           <t>Inner Mongolia AAluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FD1" s="2" t="inlineStr">
         <is>
           <t>Inner Mongolia Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1704,7 +1709,7 @@
           <t>Jiangsu 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FF1" s="2" t="inlineStr">
         <is>
           <t>Jiangsu AAluminum Rod Premium (USD/t)</t>
         </is>
@@ -1714,7 +1719,7 @@
           <t>Linyi φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FH1" s="2" t="inlineStr">
         <is>
           <t>Linyi φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1724,7 +1729,7 @@
           <t>Linyi φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FJ1" s="2" t="inlineStr">
         <is>
           <t>Linyi φAluminum Billet Premium (USD/t)</t>
         </is>
@@ -1734,7 +1739,7 @@
           <t>Nanchang φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FL1" s="2" t="inlineStr">
         <is>
           <t>Nanchang φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1744,7 +1749,7 @@
           <t>Nanchang φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FN1" s="2" t="inlineStr">
         <is>
           <t>Nanchang φAluminum Billet Premium (USD/t)</t>
         </is>
@@ -1754,7 +1759,7 @@
           <t>Photovoltaic Frame Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FP1" s="2" t="inlineStr">
         <is>
           <t>SMM A00 Aluminum Ingot Premium (USD/t)</t>
         </is>
@@ -1764,7 +1769,7 @@
           <t>SMM AAluminum Ingot Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FR1" s="2" t="inlineStr">
         <is>
           <t>SMM Foshan A00 Aluminum Ingot Premium (USD/t)</t>
         </is>
@@ -1774,7 +1779,7 @@
           <t>SMM Foshan AAluminum Ingot Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FT1" s="2" t="inlineStr">
         <is>
           <t>SMM Guangyuan A00 Aluminum Ingot Premium (USD/t)</t>
         </is>
@@ -1784,7 +1789,7 @@
           <t>SMM Guangyuan AAluminum Ingot Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FV1" s="2" t="inlineStr">
         <is>
           <t>SMM Henan A00 Aluminum Ingot Premium (USD/t)</t>
         </is>
@@ -1794,7 +1799,7 @@
           <t>SMM Henan AAluminum Ingot Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FX1" s="2" t="inlineStr">
         <is>
           <t>Shandong /Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1804,7 +1809,7 @@
           <t>Shandong 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="FZ1" s="2" t="inlineStr">
         <is>
           <t>Shandong 61.5% IACS High-conductivity Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1814,7 +1819,7 @@
           <t>Shandong 6101/6201 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GB1" s="2" t="inlineStr">
         <is>
           <t>Shandong 62.5% IACS High-conductivity Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1824,7 +1829,7 @@
           <t>Shandong 8030 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GD1" s="2" t="inlineStr">
         <is>
           <t>Shandong 99.70% Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1834,7 +1839,7 @@
           <t>Shandong AAluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GF1" s="2" t="inlineStr">
         <is>
           <t>Shandong Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1844,7 +1849,7 @@
           <t>Shandong Deoxidized Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GH1" s="2" t="inlineStr">
         <is>
           <t>Shandong IACS High-conductivity Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1854,7 +1859,7 @@
           <t>Wuxi 6061 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GJ1" s="2" t="inlineStr">
         <is>
           <t>Wuxi 6082 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1864,7 +1869,7 @@
           <t>Wuxi Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GL1" s="2" t="inlineStr">
         <is>
           <t>Wuxi φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1874,7 +1879,7 @@
           <t>Wuxi φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GN1" s="2" t="inlineStr">
         <is>
           <t>Wuxi φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1884,7 +1889,7 @@
           <t>Wuxi φAluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GP1" s="2" t="inlineStr">
         <is>
           <t>Xinjiang φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1894,7 +1899,7 @@
           <t>Xinjiang φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GR1" s="2" t="inlineStr">
         <is>
           <t>Xinjiang φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1904,7 +1909,7 @@
           <t>Xinjiang φAluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GT1" s="1" t="inlineStr">
+      <c r="GT1" s="2" t="inlineStr">
         <is>
           <t>Yuannan Low Carbon /Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1914,7 +1919,7 @@
           <t>Yuannan Low Carbon 1A60 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GV1" s="1" t="inlineStr">
+      <c r="GV1" s="2" t="inlineStr">
         <is>
           <t>Yuannan Low Carbon 6101/6201 Aluminum Rod Premium (USD/t)</t>
         </is>
@@ -1924,7 +1929,7 @@
           <t>Yuannan Low Carbon 8030 Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GX1" s="1" t="inlineStr">
+      <c r="GX1" s="2" t="inlineStr">
         <is>
           <t>Yuannan Low Carbon AAluminum Rod Premium (USD/t)</t>
         </is>
@@ -1934,7 +1939,7 @@
           <t>Yuannan Low Carbon Aluminum Rod Premium (USD/t)</t>
         </is>
       </c>
-      <c r="GZ1" s="1" t="inlineStr">
+      <c r="GZ1" s="2" t="inlineStr">
         <is>
           <t>Yunan Low Carbon φ120 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1944,7 +1949,7 @@
           <t>Yunan Low Carbon φ178 Aluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="HB1" s="1" t="inlineStr">
+      <c r="HB1" s="2" t="inlineStr">
         <is>
           <t>Yunan Low Carbon φ90 Aluminum Billet Premium (USD/t)</t>
         </is>
@@ -1954,7 +1959,7 @@
           <t>Yunan Low Carbon φAluminum Billet Premium (USD/t)</t>
         </is>
       </c>
-      <c r="HD1" s="1" t="inlineStr">
+      <c r="HD1" s="2" t="inlineStr">
         <is>
           <t>μ C-Coated Li Battery Al Foil Premium (USD/t)</t>
         </is>
@@ -1964,7 +1969,7 @@
           <t>μ Li Battery Al Foil Premium (USD/t)</t>
         </is>
       </c>
-      <c r="HF1" s="1" t="inlineStr">
+      <c r="HF1" s="2" t="inlineStr">
         <is>
           <t>3N High-Purity Alumina (Al₂O₃≥99.9%, 1um＜D50≤5um) (USD/t)</t>
         </is>
@@ -1974,7 +1979,7 @@
           <t>3N High-Purity Alumina (Al₂O₃≥99.9%, D50=0.4μm) (USD/t)</t>
         </is>
       </c>
-      <c r="HH1" s="1" t="inlineStr">
+      <c r="HH1" s="2" t="inlineStr">
         <is>
           <t>3N High-Purity Alumina (Al₂O₃≥99.9%, D50=0.8um) (USD/t)</t>
         </is>
@@ -1984,7 +1989,7 @@
           <t>3N High-Purity Alumina (Al₂O₃≥99.9%, D50=1um) (USD/t)</t>
         </is>
       </c>
-      <c r="HJ1" s="1" t="inlineStr">
+      <c r="HJ1" s="2" t="inlineStr">
         <is>
           <t>4N High-Purity Alumina (Al₂O₃≥99.99%, 0.5um＜D50≤1um) (USD/t)</t>
         </is>
@@ -1994,7 +1999,7 @@
           <t>4N High-Purity Alumina (Al₂O₃≥99.99%, 1um＜D50≤3um) (USD/t)</t>
         </is>
       </c>
-      <c r="HL1" s="1" t="inlineStr">
+      <c r="HL1" s="2" t="inlineStr">
         <is>
           <t>4N High-Purity Alumina (Al₂O₃≥99.99%, 3um＜D50≤5um) (USD/t)</t>
         </is>
@@ -2004,7 +2009,7 @@
           <t>4N High-Purity Alumina (Al₂O₃≥99.99%, D50=0.1um and D97=0.3um) (USD/t)</t>
         </is>
       </c>
-      <c r="HN1" s="1" t="inlineStr">
+      <c r="HN1" s="2" t="inlineStr">
         <is>
           <t>4N5 High-Purity Alumina (Al₂O₃≥99.995%, 30um＜D50≤40um) (USD/t)</t>
         </is>
@@ -2014,7 +2019,7 @@
           <t>5N High-Purity Alumina (Al₂O₃≥99.999%, 0.2um≤D50≤3um) (USD/t)</t>
         </is>
       </c>
-      <c r="HP1" s="1" t="inlineStr">
+      <c r="HP1" s="2" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥) FOB Brazil (USD/t)</t>
         </is>
@@ -2024,7 +2029,7 @@
           <t>Alumina (Al₂O₃≥) FOB Easten Australia (USD/t)</t>
         </is>
       </c>
-      <c r="HR1" s="1" t="inlineStr">
+      <c r="HR1" s="2" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥) FOB Vietnam (USD/t)</t>
         </is>
@@ -2034,7 +2039,7 @@
           <t>Alumina (Al₂O₃≥) FOB Western Australia (USD/t)</t>
         </is>
       </c>
-      <c r="HT1" s="1" t="inlineStr">
+      <c r="HT1" s="2" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥) Fob Indonesia (USD/t)</t>
         </is>
@@ -2044,7 +2049,7 @@
           <t>Alumina (Al₂O₃≥98.5%) FOB Brazil (USD/t)</t>
         </is>
       </c>
-      <c r="HV1" s="1" t="inlineStr">
+      <c r="HV1" s="2" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥98.5%) FOB Easten Australia (USD/t)</t>
         </is>
@@ -2054,7 +2059,7 @@
           <t>Alumina (Al₂O₃≥98.5%) FOB Vietnam (USD/t)</t>
         </is>
       </c>
-      <c r="HX1" s="1" t="inlineStr">
+      <c r="HX1" s="2" t="inlineStr">
         <is>
           <t>Alumina (Al₂O₃≥98.5%) FOB Western Australia (USD/t)</t>
         </is>
@@ -2064,7 +2069,7 @@
           <t>Alumina (Al₂O₃≥98.5%) Fob Indonesia (USD/t)</t>
         </is>
       </c>
-      <c r="HZ1" s="1" t="inlineStr">
+      <c r="HZ1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Hydroxide (USD/t)</t>
         </is>
@@ -2074,7 +2079,7 @@
           <t>Australia Bauxite (High-Temperature) CIF China (USD/t)</t>
         </is>
       </c>
-      <c r="IB1" s="1" t="inlineStr">
+      <c r="IB1" s="2" t="inlineStr">
         <is>
           <t>Australia Bauxite (Low-Temperature) CIF China (USD/t)</t>
         </is>
@@ -2084,7 +2089,7 @@
           <t>Bauxite CFR Turkey (USD/t)</t>
         </is>
       </c>
-      <c r="ID1" s="1" t="inlineStr">
+      <c r="ID1" s="2" t="inlineStr">
         <is>
           <t>Bauxite FOB Guinea (USD/t)</t>
         </is>
@@ -2094,7 +2099,7 @@
           <t>China Aluminum Hydroxide (USD/t)</t>
         </is>
       </c>
-      <c r="IF1" s="1" t="inlineStr">
+      <c r="IF1" s="2" t="inlineStr">
         <is>
           <t>Guangxi Aluminum Hydroxide (USD/t)</t>
         </is>
@@ -2104,7 +2109,7 @@
           <t>Guangxi Bauxite (A/S ratio , Al₂O₃ ) (USD/t)</t>
         </is>
       </c>
-      <c r="IH1" s="1" t="inlineStr">
+      <c r="IH1" s="2" t="inlineStr">
         <is>
           <t>Guangxi Bauxite (A/S ratio 6, Al₂O₃ 53%) (USD/t)</t>
         </is>
@@ -2114,7 +2119,7 @@
           <t>Guangxi Bauxite (A/S ratio 7, Al₂O₃ 53%) (USD/t)</t>
         </is>
       </c>
-      <c r="IJ1" s="1" t="inlineStr">
+      <c r="IJ1" s="2" t="inlineStr">
         <is>
           <t>Guinean Bauxite CIF China (USD/t)</t>
         </is>
@@ -2124,7 +2129,7 @@
           <t>Guiyang Bauxite (A/S ratio , Al₂O₃ ) (USD/t)</t>
         </is>
       </c>
-      <c r="IL1" s="1" t="inlineStr">
+      <c r="IL1" s="2" t="inlineStr">
         <is>
           <t>Guiyang Bauxite (A/S ratio 6, Al₂O₃ 60%) (USD/t)</t>
         </is>
@@ -2134,7 +2139,7 @@
           <t>Guizhou Aluminum Hydroxide (USD/t)</t>
         </is>
       </c>
-      <c r="IN1" s="1" t="inlineStr">
+      <c r="IN1" s="2" t="inlineStr">
         <is>
           <t>Guizhou Bauxite (USD/t)</t>
         </is>
@@ -2144,7 +2149,7 @@
           <t>Guizhou Bauxite (A/S ratio , Al₂O₃ ) (USD/t)</t>
         </is>
       </c>
-      <c r="IP1" s="1" t="inlineStr">
+      <c r="IP1" s="2" t="inlineStr">
         <is>
           <t>Guizhou Bauxite (A/S ratio 5.5, Al₂O₃ 58%) (USD/t)</t>
         </is>
@@ -2154,7 +2159,7 @@
           <t>Henan Aluminum Hydroxide (USD/t)</t>
         </is>
       </c>
-      <c r="IR1" s="1" t="inlineStr">
+      <c r="IR1" s="2" t="inlineStr">
         <is>
           <t>Henan Bauxite (A/S ratio , Al₂O₃ ) (USD/t)</t>
         </is>
@@ -2164,7 +2169,7 @@
           <t>Henan Bauxite (A/S ratio 5, Al₂O₃ 60%) (USD/t)</t>
         </is>
       </c>
-      <c r="IT1" s="1" t="inlineStr">
+      <c r="IT1" s="2" t="inlineStr">
         <is>
           <t>Henan Bauxite (A/S ratio 6, Al₂O₃ 62%) (USD/t)</t>
         </is>
@@ -2174,7 +2179,7 @@
           <t>High - Purity Alumina (USD/t)</t>
         </is>
       </c>
-      <c r="IV1" s="1" t="inlineStr">
+      <c r="IV1" s="2" t="inlineStr">
         <is>
           <t>Indonesia Bauxite (USD/t)</t>
         </is>
@@ -2184,7 +2189,7 @@
           <t>Malaysia Bauxite CIF China (USD/t)</t>
         </is>
       </c>
-      <c r="IX1" s="1" t="inlineStr">
+      <c r="IX1" s="2" t="inlineStr">
         <is>
           <t>Malaysia Washed Bauxite CIF China (USD/t)</t>
         </is>
@@ -2194,7 +2199,7 @@
           <t>N High-Purity Alumina (Al₂O₃≥, D=um and D=um) (USD/t)</t>
         </is>
       </c>
-      <c r="IZ1" s="1" t="inlineStr">
+      <c r="IZ1" s="2" t="inlineStr">
         <is>
           <t>N High-Purity Alumina (Al₂O₃≥, D=um) (USD/t)</t>
         </is>
@@ -2204,7 +2209,7 @@
           <t>N High-Purity Alumina (Al₂O₃≥, D=μm) (USD/t)</t>
         </is>
       </c>
-      <c r="JB1" s="1" t="inlineStr">
+      <c r="JB1" s="2" t="inlineStr">
         <is>
           <t>N High-Purity Alumina (Al₂O₃≥, um≤D≤um) (USD/t)</t>
         </is>
@@ -2214,7 +2219,7 @@
           <t>N High-Purity Alumina (Al₂O₃≥, um＜D≤um) (USD/t)</t>
         </is>
       </c>
-      <c r="JD1" s="1" t="inlineStr">
+      <c r="JD1" s="2" t="inlineStr">
         <is>
           <t>NHigh-Purity Alumina (Al₂O₃≥, um＜D≤um) (USD/t)</t>
         </is>
@@ -2224,7 +2229,7 @@
           <t>SMM Bayuquan Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JF1" s="1" t="inlineStr">
+      <c r="JF1" s="2" t="inlineStr">
         <is>
           <t>SMM Bayuquan Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
@@ -2234,7 +2239,7 @@
           <t>SMM Guangxi Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JH1" s="1" t="inlineStr">
+      <c r="JH1" s="2" t="inlineStr">
         <is>
           <t>SMM Guangxi Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
@@ -2244,7 +2249,7 @@
           <t>SMM Guizhou Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JJ1" s="1" t="inlineStr">
+      <c r="JJ1" s="2" t="inlineStr">
         <is>
           <t>SMM Guizhou Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
@@ -2254,7 +2259,7 @@
           <t>SMM Henan Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JL1" s="1" t="inlineStr">
+      <c r="JL1" s="2" t="inlineStr">
         <is>
           <t>SMM Henan Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
@@ -2264,7 +2269,7 @@
           <t>SMM Lianyungang Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JN1" s="1" t="inlineStr">
+      <c r="JN1" s="2" t="inlineStr">
         <is>
           <t>SMM Lianyungang Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
@@ -2274,7 +2279,7 @@
           <t>SMM Shandong Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JP1" s="1" t="inlineStr">
+      <c r="JP1" s="2" t="inlineStr">
         <is>
           <t>SMM Shandong Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
@@ -2284,7 +2289,7 @@
           <t>SMM Shanxi Alumina (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JR1" s="1" t="inlineStr">
+      <c r="JR1" s="2" t="inlineStr">
         <is>
           <t>SMM Shanxi Alumina (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
@@ -2294,7 +2299,7 @@
           <t>Shandong Aluminum Hydroxide (USD/t)</t>
         </is>
       </c>
-      <c r="JT1" s="1" t="inlineStr">
+      <c r="JT1" s="2" t="inlineStr">
         <is>
           <t>Shanxi Aluminum Hydroxide (USD/t)</t>
         </is>
@@ -2304,7 +2309,7 @@
           <t>Shanxi Bauxite (USD/t)</t>
         </is>
       </c>
-      <c r="JV1" s="1" t="inlineStr">
+      <c r="JV1" s="2" t="inlineStr">
         <is>
           <t>Shanxi Bauxite (A/S ratio , Al₂O₃ ) (USD/t)</t>
         </is>
@@ -2314,7 +2319,7 @@
           <t>Shanxi Bauxite (A/S ratio 5, Al₂O₃ 60%) (USD/t)</t>
         </is>
       </c>
-      <c r="JX1" s="1" t="inlineStr">
+      <c r="JX1" s="2" t="inlineStr">
         <is>
           <t>The Republic of Ghana Bauxite CIF China (USD/t)</t>
         </is>
@@ -2324,7 +2329,7 @@
           <t>SMM Alumina Index (Al₂O₃≥) (USD/t)</t>
         </is>
       </c>
-      <c r="JZ1" s="1" t="inlineStr">
+      <c r="JZ1" s="2" t="inlineStr">
         <is>
           <t>SMM Alumina Index (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
@@ -2334,7 +2339,7 @@
           <t>SMM Bauxite Index (USD/t)</t>
         </is>
       </c>
-      <c r="KB1" s="1" t="inlineStr">
+      <c r="KB1" s="2" t="inlineStr">
         <is>
           <t>SMM Guangxi Alumina Index (Al₂O₃≥) (USD/t)</t>
         </is>
@@ -2344,7 +2349,7 @@
           <t>SMM Guangxi Alumina Index (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="KD1" s="1" t="inlineStr">
+      <c r="KD1" s="2" t="inlineStr">
         <is>
           <t>SMM Guizhou Alumina Index (Al₂O₃≥) (USD/t)</t>
         </is>
@@ -2354,7 +2359,7 @@
           <t>SMM Guizhou Alumina Index (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="KF1" s="1" t="inlineStr">
+      <c r="KF1" s="2" t="inlineStr">
         <is>
           <t>SMM Henan Alumina Index (Al₂O₃≥) (USD/t)</t>
         </is>
@@ -2364,7 +2369,7 @@
           <t>SMM Henan Alumina Index (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="KH1" s="1" t="inlineStr">
+      <c r="KH1" s="2" t="inlineStr">
         <is>
           <t>SMM Shandong Alumina Index (Al₂O₃≥) (USD/t)</t>
         </is>
@@ -2374,7 +2379,7 @@
           <t>SMM Shandong Alumina Index (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="KJ1" s="1" t="inlineStr">
+      <c r="KJ1" s="2" t="inlineStr">
         <is>
           <t>SMM Shanxi Alumina Index (Al₂O₃≥) (USD/t)</t>
         </is>
@@ -2384,7 +2389,7 @@
           <t>SMM Shanxi Alumina Index (Al₂O₃≥98.5%) (USD/t)</t>
         </is>
       </c>
-      <c r="KL1" s="1" t="inlineStr">
+      <c r="KL1" s="2" t="inlineStr">
         <is>
           <t>East China High Sulfur Ordinary Calcined Petroleum Coke (USD/t)</t>
         </is>
@@ -2394,7 +2399,7 @@
           <t>East China Medium-High Sulfur Low Vanadium Calcined Petroleum Coke (USD/t)</t>
         </is>
       </c>
-      <c r="KN1" s="1" t="inlineStr">
+      <c r="KN1" s="2" t="inlineStr">
         <is>
           <t>East China Medium-High Sulfur Ordinary Calcined Petroleum Coke (USD/t)</t>
         </is>
@@ -2404,7 +2409,7 @@
           <t>East China Medium-Sulfur Low Vanadium Calcined Petroleum Coke (USD/t)</t>
         </is>
       </c>
-      <c r="KP1" s="1" t="inlineStr">
+      <c r="KP1" s="2" t="inlineStr">
         <is>
           <t>East China Medium-Sulfur Ordinary Calcined Petroleum Coke (USD/t)</t>
         </is>
@@ -2414,7 +2419,7 @@
           <t>Northeast China Low-Sulfur Calcined Petroleum Coke (USD/t)</t>
         </is>
       </c>
-      <c r="KR1" s="1" t="inlineStr">
+      <c r="KR1" s="2" t="inlineStr">
         <is>
           <t>Northeast China SMM # Petroleum Coke Spot price Index (USD/t)</t>
         </is>
@@ -2424,7 +2429,7 @@
           <t>Northeast China SMM 1# Petroleum Coke Spot price Index (USD/t)</t>
         </is>
       </c>
-      <c r="KT1" s="1" t="inlineStr">
+      <c r="KT1" s="2" t="inlineStr">
         <is>
           <t>Northwest China SMM # Petroleum Coke Spot Price Index (USD/t)</t>
         </is>
@@ -2434,7 +2439,7 @@
           <t>Northwest China SMM 3# Petroleum Coke Spot Price Index (USD/t)</t>
         </is>
       </c>
-      <c r="KV1" s="1" t="inlineStr">
+      <c r="KV1" s="2" t="inlineStr">
         <is>
           <t>Petroleum Coke Index (USD/t)</t>
         </is>
@@ -2444,7 +2449,7 @@
           <t>Shandong SMM # Petroleum Coke Spot price Index (USD/t)</t>
         </is>
       </c>
-      <c r="KX1" s="1" t="inlineStr">
+      <c r="KX1" s="2" t="inlineStr">
         <is>
           <t>Shandong SMM 2# Petroleum Coke Spot price Index (USD/t)</t>
         </is>
@@ -2454,7 +2459,7 @@
           <t>Shandong SMM 3# Petroleum Coke Spot price Index (USD/t)</t>
         </is>
       </c>
-      <c r="KZ1" s="1" t="inlineStr">
+      <c r="KZ1" s="2" t="inlineStr">
         <is>
           <t>Shandong SMM 4# Petroleum Coke Spot price Index (USD/t)</t>
         </is>
@@ -2464,7 +2469,7 @@
           <t>Coal Tar Pitch (USD/t)</t>
         </is>
       </c>
-      <c r="LB1" s="1" t="inlineStr">
+      <c r="LB1" s="2" t="inlineStr">
         <is>
           <t>Coal tar pitch (Hebei) (USD/t)</t>
         </is>
@@ -2474,7 +2479,7 @@
           <t>Coal tar pitch (Shandong) (USD/t)</t>
         </is>
       </c>
-      <c r="LD1" s="1" t="inlineStr">
+      <c r="LD1" s="2" t="inlineStr">
         <is>
           <t>Coal tar pitch (Shanxi) (USD/t)</t>
         </is>
@@ -2484,7 +2489,7 @@
           <t>Central China Prebaked Anode (USD/t)</t>
         </is>
       </c>
-      <c r="LF1" s="1" t="inlineStr">
+      <c r="LF1" s="2" t="inlineStr">
         <is>
           <t>East China Prebaked Anode (USD/t)</t>
         </is>
@@ -2494,7 +2499,7 @@
           <t>Northwest China Prebaked Anode (USD/t)</t>
         </is>
       </c>
-      <c r="LH1" s="1" t="inlineStr">
+      <c r="LH1" s="2" t="inlineStr">
         <is>
           <t>Prebaked Anode (USD/t)</t>
         </is>
@@ -2504,7 +2509,7 @@
           <t>Prebaked Anode for High-Purity Aluminum FOB China (USD/t)</t>
         </is>
       </c>
-      <c r="LJ1" s="1" t="inlineStr">
+      <c r="LJ1" s="2" t="inlineStr">
         <is>
           <t>Prebaked Anode for High-end Aluminum FOB China (USD/t)</t>
         </is>
@@ -2514,7 +2519,7 @@
           <t>Southwest China Prebaked Anode (USD/t)</t>
         </is>
       </c>
-      <c r="LL1" s="1" t="inlineStr">
+      <c r="LL1" s="2" t="inlineStr">
         <is>
           <t>5182 Aluminum Alloy Sheets and Strips Used for Motor (USD/t)</t>
         </is>
@@ -2524,7 +2529,7 @@
           <t>5754 Aluminum Alloy Sheets and Strips Used for Motor (USD/t)</t>
         </is>
       </c>
-      <c r="LN1" s="1" t="inlineStr">
+      <c r="LN1" s="2" t="inlineStr">
         <is>
           <t>6061 Aluminum Alloy Sheets and Strips Used for Motor (USD/t)</t>
         </is>
@@ -2534,7 +2539,7 @@
           <t>Al-Ti-B Wires A, Aluminum Based Master Alloy (USD/t)</t>
         </is>
       </c>
-      <c r="LP1" s="1" t="inlineStr">
+      <c r="LP1" s="2" t="inlineStr">
         <is>
           <t>Al-Ti-B Wires B, Aluminum Based Master Alloy (USD/t)</t>
         </is>
@@ -2544,7 +2549,7 @@
           <t>Al-Ti-B Wires C, Aluminum Based Master Alloy (USD/t)</t>
         </is>
       </c>
-      <c r="LR1" s="1" t="inlineStr">
+      <c r="LR1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Alloy Sheets and Strips Used for Motor (USD/t)</t>
         </is>
@@ -2554,7 +2559,7 @@
           <t>Aluminum Based Master Alloy (USD/t)</t>
         </is>
       </c>
-      <c r="LT1" s="1" t="inlineStr">
+      <c r="LT1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Based Master Alloy AlSi (USD/t)</t>
         </is>
@@ -2564,7 +2569,7 @@
           <t>Aluminum Based Master Alloy AlSi12 (USD/t)</t>
         </is>
       </c>
-      <c r="LV1" s="1" t="inlineStr">
+      <c r="LV1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Based Master Alloy AlSi20 (USD/t)</t>
         </is>
@@ -2574,7 +2579,7 @@
           <t>Aluminum Based Master Alloy AlSi50 (USD/t)</t>
         </is>
       </c>
-      <c r="LX1" s="1" t="inlineStr">
+      <c r="LX1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Strontium Alloy AlSr (USD/t)</t>
         </is>
@@ -2584,7 +2589,7 @@
           <t>Aluminum Strontium Alloy AlSr10 (USD/t)</t>
         </is>
       </c>
-      <c r="LZ1" s="1" t="inlineStr">
+      <c r="LZ1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Billet (USD/t)</t>
         </is>
@@ -2594,7 +2599,7 @@
           <t>Fe 0.2-0.25% Foshan Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MB1" s="1" t="inlineStr">
+      <c r="MB1" s="2" t="inlineStr">
         <is>
           <t>Fe 0.2-0.25% Hubei Remelting Al Billet (USD/t)</t>
         </is>
@@ -2604,7 +2609,7 @@
           <t>Fe 0.2-0.25% Linyi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MD1" s="1" t="inlineStr">
+      <c r="MD1" s="2" t="inlineStr">
         <is>
           <t>Fe 0.2-0.25% Nanchang Remelting Al Billet (USD/t)</t>
         </is>
@@ -2614,7 +2619,7 @@
           <t>Fe 0.2-0.25% Wuxi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MF1" s="1" t="inlineStr">
+      <c r="MF1" s="2" t="inlineStr">
         <is>
           <t>Fe 0.2-0.25% Xuchang Remelting Al Billet (USD/t)</t>
         </is>
@@ -2624,7 +2629,7 @@
           <t>Fe 0.25-0.35% Foshan Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MH1" s="1" t="inlineStr">
+      <c r="MH1" s="2" t="inlineStr">
         <is>
           <t>Fe 0.25-0.35% Hubei Remelting Al Billet (USD/t)</t>
         </is>
@@ -2634,7 +2639,7 @@
           <t>Fe 0.25-0.35% Linyi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MJ1" s="1" t="inlineStr">
+      <c r="MJ1" s="2" t="inlineStr">
         <is>
           <t>Fe 0.25-0.35% Nanchang Remelting Al Billet (USD/t)</t>
         </is>
@@ -2644,7 +2649,7 @@
           <t>Fe 0.25-0.35% Wuxi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="ML1" s="1" t="inlineStr">
+      <c r="ML1" s="2" t="inlineStr">
         <is>
           <t>Fe 0.25-0.35% Xuchang Remelting Al Billet (USD/t)</t>
         </is>
@@ -2654,7 +2659,7 @@
           <t>Fe 0.35-0.5% Foshan Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MN1" s="1" t="inlineStr">
+      <c r="MN1" s="2" t="inlineStr">
         <is>
           <t>Fe 0.35-0.5% Hubei Remelting Al Billet (USD/t)</t>
         </is>
@@ -2664,7 +2669,7 @@
           <t>Fe 0.35-0.5% Linyi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MP1" s="1" t="inlineStr">
+      <c r="MP1" s="2" t="inlineStr">
         <is>
           <t>Fe 0.35-0.5% Nanchang Remelting Al Billet (USD/t)</t>
         </is>
@@ -2674,7 +2679,7 @@
           <t>Fe 0.35-0.5% Wuxi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MR1" s="1" t="inlineStr">
+      <c r="MR1" s="2" t="inlineStr">
         <is>
           <t>Fe 0.35-0.5% Xuchang Remelting Al Billet (USD/t)</t>
         </is>
@@ -2684,7 +2689,7 @@
           <t>Fe Foshan Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MT1" s="1" t="inlineStr">
+      <c r="MT1" s="2" t="inlineStr">
         <is>
           <t>Fe Hubei Remelting Al Billet (USD/t)</t>
         </is>
@@ -2694,7 +2699,7 @@
           <t>Fe Linyi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MV1" s="1" t="inlineStr">
+      <c r="MV1" s="2" t="inlineStr">
         <is>
           <t>Fe Nanchang Remelting Al Billet (USD/t)</t>
         </is>
@@ -2704,7 +2709,7 @@
           <t>Fe Wuxi Remelting Al Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MX1" s="1" t="inlineStr">
+      <c r="MX1" s="2" t="inlineStr">
         <is>
           <t>Fe Xuchang Remelting Al Billet (USD/t)</t>
         </is>
@@ -2714,7 +2719,7 @@
           <t>Foshan Aluminum Extrusions Billet (USD/t)</t>
         </is>
       </c>
-      <c r="MZ1" s="1" t="inlineStr">
+      <c r="MZ1" s="2" t="inlineStr">
         <is>
           <t>Low Carbon φ120 Aluminum Billet (USD/t)</t>
         </is>
@@ -2724,7 +2729,7 @@
           <t>Low Carbon φ178 Aluminum Billet (USD/t)</t>
         </is>
       </c>
-      <c r="NB1" s="1" t="inlineStr">
+      <c r="NB1" s="2" t="inlineStr">
         <is>
           <t>Low Carbon φ90 Aluminum Billet (USD/t)</t>
         </is>
@@ -2734,7 +2739,7 @@
           <t>Low Carbon φAluminum Billet (USD/t)</t>
         </is>
       </c>
-      <c r="ND1" s="1" t="inlineStr">
+      <c r="ND1" s="2" t="inlineStr">
         <is>
           <t>Nanchang Aluminum Extrusions Billet (USD/t)</t>
         </is>
@@ -2744,7 +2749,7 @@
           <t>Remelting Billet (USD/t)</t>
         </is>
       </c>
-      <c r="NF1" s="1" t="inlineStr">
+      <c r="NF1" s="2" t="inlineStr">
         <is>
           <t>Shandong Aluminum Extrusions Billet (USD/t)</t>
         </is>
@@ -2754,7 +2759,7 @@
           <t>Aluminum Cast - rolled Coil (USD/t)</t>
         </is>
       </c>
-      <c r="NH1" s="1" t="inlineStr">
+      <c r="NH1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Extrusions (USD/t)</t>
         </is>
@@ -2764,7 +2769,7 @@
           <t>Aluminum Extrusions formwork (USD/t)</t>
         </is>
       </c>
-      <c r="NJ1" s="1" t="inlineStr">
+      <c r="NJ1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Extrusions formwork (Lease) (USD/t)</t>
         </is>
@@ -2774,7 +2779,7 @@
           <t>Foshan Anodized Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NL1" s="1" t="inlineStr">
+      <c r="NL1" s="2" t="inlineStr">
         <is>
           <t>Foshan Surface Electrophoresis Aluminum Extrusions (USD/t)</t>
         </is>
@@ -2784,7 +2789,7 @@
           <t>Foshan Surface Sprayed Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NN1" s="1" t="inlineStr">
+      <c r="NN1" s="2" t="inlineStr">
         <is>
           <t>Foshan Thermal Break Aluminum Extrusions (USD/t)</t>
         </is>
@@ -2794,7 +2799,7 @@
           <t>Jiangxi Anodized Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NP1" s="1" t="inlineStr">
+      <c r="NP1" s="2" t="inlineStr">
         <is>
           <t>Nanchang Surface Electrophoresis Aluminum Extrusions (USD/t)</t>
         </is>
@@ -2804,7 +2809,7 @@
           <t>Nanchang Surface Sprayed Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NR1" s="1" t="inlineStr">
+      <c r="NR1" s="2" t="inlineStr">
         <is>
           <t>Nanchang Thermal Break Aluminum Extrusions (USD/t)</t>
         </is>
@@ -2814,7 +2819,7 @@
           <t>Shandong Anodized Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NT1" s="1" t="inlineStr">
+      <c r="NT1" s="2" t="inlineStr">
         <is>
           <t>Shandong Surface Electrophoresis Aluminum Extrusions (USD/t)</t>
         </is>
@@ -2824,7 +2829,7 @@
           <t>Shandong Surface Sprayed Aluminum Extrusions (USD/t)</t>
         </is>
       </c>
-      <c r="NV1" s="1" t="inlineStr">
+      <c r="NV1" s="2" t="inlineStr">
         <is>
           <t>Shandong Thermal Break Aluminum Extrusions (USD/t)</t>
         </is>
@@ -2834,7 +2839,7 @@
           <t>-series Secondary Aluminum Plate/Sheet and Strip (USD/t)</t>
         </is>
       </c>
-      <c r="NX1" s="1" t="inlineStr">
+      <c r="NX1" s="2" t="inlineStr">
         <is>
           <t>1-series Secondary Aluminum Plate/Sheet and Strip (USD/t)</t>
         </is>
@@ -2844,7 +2849,7 @@
           <t>3-series Secondary Aluminum Plate/Sheet and Strip (USD/t)</t>
         </is>
       </c>
-      <c r="NZ1" s="1" t="inlineStr">
+      <c r="NZ1" s="2" t="inlineStr">
         <is>
           <t>3003 Aluminum Plate/Sheet and Strip for Battery Case (USD/t)</t>
         </is>
@@ -2854,7 +2859,7 @@
           <t>5-series Secondary Aluminum Plate/Sheet and Strip (USD/t)</t>
         </is>
       </c>
-      <c r="OB1" s="1" t="inlineStr">
+      <c r="OB1" s="2" t="inlineStr">
         <is>
           <t>6-series Secondary Aluminum Plate/Sheet and Strip (USD/t)</t>
         </is>
@@ -2864,7 +2869,7 @@
           <t>Aluminum Plate / Sheet and Strip (USD/t)</t>
         </is>
       </c>
-      <c r="OD1" s="1" t="inlineStr">
+      <c r="OD1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Plate/Sheet and Strip for Battery Case (USD/t)</t>
         </is>
@@ -2874,7 +2879,7 @@
           <t>Henan /Presensitized Plate Substrate (USD/t)</t>
         </is>
       </c>
-      <c r="OF1" s="1" t="inlineStr">
+      <c r="OF1" s="2" t="inlineStr">
         <is>
           <t>Henan 1050/1060 Presensitized Plate Substrate (USD/t)</t>
         </is>
@@ -2884,7 +2889,7 @@
           <t>Henan 1100 Decorative Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OH1" s="1" t="inlineStr">
+      <c r="OH1" s="2" t="inlineStr">
         <is>
           <t>Henan 3003 Oil Tank Plate (USD/t)</t>
         </is>
@@ -2894,7 +2899,7 @@
           <t>Henan Decorative Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OJ1" s="1" t="inlineStr">
+      <c r="OJ1" s="2" t="inlineStr">
         <is>
           <t>Henan Oil Tank Plate (USD/t)</t>
         </is>
@@ -2904,7 +2909,7 @@
           <t>Neimenggu /Presensitized Plate Substrate (USD/t)</t>
         </is>
       </c>
-      <c r="OL1" s="1" t="inlineStr">
+      <c r="OL1" s="2" t="inlineStr">
         <is>
           <t>Neimenggu 1050/1060 Presensitized Plate Substrate (USD/t)</t>
         </is>
@@ -2914,7 +2919,7 @@
           <t>Neimenggu 1100 Decorative Plate (USD/t)</t>
         </is>
       </c>
-      <c r="ON1" s="1" t="inlineStr">
+      <c r="ON1" s="2" t="inlineStr">
         <is>
           <t>Neimenggu 3003 Oil Tank Plate (USD/t)</t>
         </is>
@@ -2924,7 +2929,7 @@
           <t>Neimenggu Decorative Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OP1" s="1" t="inlineStr">
+      <c r="OP1" s="2" t="inlineStr">
         <is>
           <t>Neimenggu Oil Tank Plate (USD/t)</t>
         </is>
@@ -2934,7 +2939,7 @@
           <t>Shandong /Presensitized Plate Substrate (USD/t)</t>
         </is>
       </c>
-      <c r="OR1" s="1" t="inlineStr">
+      <c r="OR1" s="2" t="inlineStr">
         <is>
           <t>Shandong 1050/1060 Presensitized Plate Substrate (USD/t)</t>
         </is>
@@ -2944,7 +2949,7 @@
           <t>Shandong 1100 Decorative Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OT1" s="1" t="inlineStr">
+      <c r="OT1" s="2" t="inlineStr">
         <is>
           <t>Shandong 3003 Oil Tank Plate (USD/t)</t>
         </is>
@@ -2954,7 +2959,7 @@
           <t>Shandong Decorative Plate (USD/t)</t>
         </is>
       </c>
-      <c r="OV1" s="1" t="inlineStr">
+      <c r="OV1" s="2" t="inlineStr">
         <is>
           <t>Shandong Oil Tank Plate (USD/t)</t>
         </is>
@@ -2964,7 +2969,7 @@
           <t>Aluminum Foil (USD/t)</t>
         </is>
       </c>
-      <c r="OX1" s="1" t="inlineStr">
+      <c r="OX1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Foil Processing Fee (USD/t)</t>
         </is>
@@ -2974,7 +2979,7 @@
           <t>Carbon-Coated Lithium Battery Aluminum Foil (12μ) (USD/t)</t>
         </is>
       </c>
-      <c r="OZ1" s="1" t="inlineStr">
+      <c r="OZ1" s="2" t="inlineStr">
         <is>
           <t>Carbon-Coated Lithium Battery Aluminum Foil (13μ) (USD/t)</t>
         </is>
@@ -2984,7 +2989,7 @@
           <t>Carbon-Coated Lithium Battery Aluminum Foil (μ) (USD/t)</t>
         </is>
       </c>
-      <c r="PB1" s="1" t="inlineStr">
+      <c r="PB1" s="2" t="inlineStr">
         <is>
           <t>Lithium Battery Aluminum Foil (12μ) (USD/t)</t>
         </is>
@@ -2994,7 +2999,7 @@
           <t>Lithium Battery Aluminum Foil (13μ) (USD/t)</t>
         </is>
       </c>
-      <c r="PD1" s="1" t="inlineStr">
+      <c r="PD1" s="2" t="inlineStr">
         <is>
           <t>Lithium Battery Aluminum Foil (15μ) (USD/t)</t>
         </is>
@@ -3004,7 +3009,7 @@
           <t>Lithium Battery Aluminum Foil (μ) (USD/t)</t>
         </is>
       </c>
-      <c r="PF1" s="1" t="inlineStr">
+      <c r="PF1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Rod (USD/t)</t>
         </is>
@@ -3014,7 +3019,7 @@
           <t>Low Carbon /Aluminum Rod (Guangdong) (USD/t)</t>
         </is>
       </c>
-      <c r="PH1" s="1" t="inlineStr">
+      <c r="PH1" s="2" t="inlineStr">
         <is>
           <t>Low Carbon 1A60 Aluminum Rod (Guangdong) (USD/t)</t>
         </is>
@@ -3024,7 +3029,7 @@
           <t>Low Carbon 6101/6201 Aluminum Rod (Guangdong) (USD/t)</t>
         </is>
       </c>
-      <c r="PJ1" s="1" t="inlineStr">
+      <c r="PJ1" s="2" t="inlineStr">
         <is>
           <t>Low Carbon 8030 Aluminum Rod (Guangdong) (USD/t)</t>
         </is>
@@ -3034,7 +3039,7 @@
           <t>Low Carbon AAluminum Rod (Guangdong) (USD/t)</t>
         </is>
       </c>
-      <c r="PL1" s="1" t="inlineStr">
+      <c r="PL1" s="2" t="inlineStr">
         <is>
           <t>Low Carbon Aluminum Rod (Guangdong) (USD/t)</t>
         </is>
@@ -3044,7 +3049,7 @@
           <t>Aluminum Scrap quotations outside China (USD/t)</t>
         </is>
       </c>
-      <c r="PN1" s="1" t="inlineStr">
+      <c r="PN1" s="2" t="inlineStr">
         <is>
           <t>Malaysia Scrap Mixed Aluminium Castings (Tense) (USD/t)</t>
         </is>
@@ -3054,7 +3059,7 @@
           <t>Ningbo Port Imported Twitch Scrap (USD/t)</t>
         </is>
       </c>
-      <c r="PP1" s="1" t="inlineStr">
+      <c r="PP1" s="2" t="inlineStr">
         <is>
           <t>Scrap Mixed Aluminium Castings (Tense) FOB Malaysia (USD/t)</t>
         </is>
@@ -3064,7 +3069,7 @@
           <t>Tianjin Port Imported Twitch Scrap (USD/t)</t>
         </is>
       </c>
-      <c r="PR1" s="1" t="inlineStr">
+      <c r="PR1" s="2" t="inlineStr">
         <is>
           <t>99.70% Deoxidized Aluminum Granules (Guangdong) (USD/t)</t>
         </is>
@@ -3074,7 +3079,7 @@
           <t>Aluminum Low-Carbon P1020A (USD/t)</t>
         </is>
       </c>
-      <c r="PT1" s="1" t="inlineStr">
+      <c r="PT1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Low-Carbon PA (USD/t)</t>
         </is>
@@ -3084,7 +3089,7 @@
           <t>Aluminum Powder (USD/t)</t>
         </is>
       </c>
-      <c r="PV1" s="1" t="inlineStr">
+      <c r="PV1" s="2" t="inlineStr">
         <is>
           <t>Aluminum Slab (USD/t)</t>
         </is>
@@ -3094,7 +3099,7 @@
           <t>Aluminum fluoride (USD/t)</t>
         </is>
       </c>
-      <c r="PX1" s="1" t="inlineStr">
+      <c r="PX1" s="2" t="inlineStr">
         <is>
           <t>Aluminum import arbitrage(AL) (USD/t)</t>
         </is>
@@ -3104,7 +3109,7 @@
           <t>Aluminum import arbitrage(AL) CNY/mt (USD/t)</t>
         </is>
       </c>
-      <c r="PZ1" s="1" t="inlineStr">
+      <c r="PZ1" s="2" t="inlineStr">
         <is>
           <t>Aluminum import arbitrage(Spot) (USD/t)</t>
         </is>
@@ -3114,7 +3119,7 @@
           <t>Aluminum import arbitrage(Spot) CNY/mt (USD/t)</t>
         </is>
       </c>
-      <c r="QB1" s="1" t="inlineStr">
+      <c r="QB1" s="2" t="inlineStr">
         <is>
           <t>Deoxidized Aluminum Granules (Guangdong) (USD/t)</t>
         </is>
@@ -3124,7 +3129,7 @@
           <t>LME Name Unit Open High Low Latest Change Vol. LMEselect Aluminum Month USD/mt (USD/t)</t>
         </is>
       </c>
-      <c r="QD1" s="1" t="inlineStr">
+      <c r="QD1" s="2" t="inlineStr">
         <is>
           <t>LMEselect Aluminum Month (USD/t)</t>
         </is>
@@ -3134,7 +3139,7 @@
           <t>LMEselect Aluminum Month USD/mt (USD/t)</t>
         </is>
       </c>
-      <c r="QF1" s="1" t="inlineStr">
+      <c r="QF1" s="2" t="inlineStr">
         <is>
           <t>Name Unit Open High Low Latest Change Vol. LMEselect Aluminum Month USD/mt (USD/t)</t>
         </is>
@@ -3144,7 +3149,7 @@
           <t>SMM Aluminum Spot/LME M (USD/t)</t>
         </is>
       </c>
-      <c r="QH1" s="1" t="inlineStr">
+      <c r="QH1" s="2" t="inlineStr">
         <is>
           <t>SMM Low - Carbon Aluminum (USD/t)</t>
         </is>
@@ -3154,7 +3159,7 @@
           <t>Shanghai -series Brazing Aluminum Semis (USD/t)</t>
         </is>
       </c>
-      <c r="QJ1" s="1" t="inlineStr">
+      <c r="QJ1" s="2" t="inlineStr">
         <is>
           <t>Shanghai 1-series Brazing Aluminum Semis (USD/t)</t>
         </is>
@@ -3164,7 +3169,7 @@
           <t>Shanghai 3-series Brazing Aluminum Semis (USD/t)</t>
         </is>
       </c>
-      <c r="QL1" s="1" t="inlineStr">
+      <c r="QL1" s="2" t="inlineStr">
         <is>
           <t>Shanghai 7-series Brazing Aluminum Semis (USD/t)</t>
         </is>
@@ -3174,7 +3179,7 @@
           <t>Shanghai Atomized Aluminum Powder (USD/t)</t>
         </is>
       </c>
-      <c r="QN1" s="1" t="inlineStr">
+      <c r="QN1" s="2" t="inlineStr">
         <is>
           <t>Xinjiang 99.99% High Purity Aluminum (USD/t)</t>
         </is>
@@ -3184,7 +3189,7 @@
           <t>Xinjiang 99.996% High Purity Aluminum (USD/t)</t>
         </is>
       </c>
-      <c r="QP1" s="1" t="inlineStr">
+      <c r="QP1" s="2" t="inlineStr">
         <is>
           <t>Xinjiang High Purity Aluminum (USD/t)</t>
         </is>
@@ -3194,7 +3199,7 @@
           <t>Yunnan -series Aluminum Slab (USD/t)</t>
         </is>
       </c>
-      <c r="QR1" s="1" t="inlineStr">
+      <c r="QR1" s="2" t="inlineStr">
         <is>
           <t>Yunnan 1-series Aluminum Slab (USD/t)</t>
         </is>
@@ -3204,7 +3209,7 @@
           <t>Yunnan 3-series Aluminum Slab (USD/t)</t>
         </is>
       </c>
-      <c r="QT1" s="1" t="inlineStr">
+      <c r="QT1" s="2" t="inlineStr">
         <is>
           <t>Yunnan 5-series Aluminum Slab (USD/t)</t>
         </is>
@@ -3214,7 +3219,7 @@
           <t>Yunnan 6-series Aluminum Slab (USD/t)</t>
         </is>
       </c>
-      <c r="QV1" s="1" t="inlineStr">
+      <c r="QV1" s="2" t="inlineStr">
         <is>
           <t>Index (USD/t)</t>
         </is>
@@ -3226,946 +3231,946 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="K2" s="1" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr"/>
       <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="W2" s="1" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Y2" s="1" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
-      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AA2" s="1" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="1" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr"/>
-      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AE2" s="1" t="inlineStr"/>
       <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
+      <c r="AG2" s="1" t="inlineStr"/>
       <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
+      <c r="AI2" s="1" t="inlineStr"/>
       <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
+      <c r="AK2" s="1" t="inlineStr"/>
       <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
+      <c r="AM2" s="1" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="1" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
+      <c r="AQ2" s="1" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
+      <c r="AS2" s="1" t="inlineStr"/>
       <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AU2" s="1" t="inlineStr"/>
       <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
+      <c r="AW2" s="1" t="inlineStr"/>
       <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
+      <c r="AY2" s="1" t="inlineStr"/>
       <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
+      <c r="BA2" s="1" t="inlineStr"/>
       <c r="BB2" s="2" t="inlineStr"/>
-      <c r="BC2" s="2" t="inlineStr"/>
+      <c r="BC2" s="1" t="inlineStr"/>
       <c r="BD2" s="2" t="inlineStr"/>
-      <c r="BE2" s="2" t="inlineStr"/>
+      <c r="BE2" s="1" t="inlineStr"/>
       <c r="BF2" s="2" t="inlineStr"/>
-      <c r="BG2" s="2" t="inlineStr"/>
+      <c r="BG2" s="1" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="1" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BK2" s="1" t="inlineStr"/>
       <c r="BL2" s="2" t="inlineStr"/>
-      <c r="BM2" s="2" t="inlineStr"/>
+      <c r="BM2" s="1" t="inlineStr"/>
       <c r="BN2" s="2" t="inlineStr"/>
-      <c r="BO2" s="2" t="inlineStr"/>
+      <c r="BO2" s="1" t="inlineStr"/>
       <c r="BP2" s="2" t="inlineStr"/>
-      <c r="BQ2" s="2" t="inlineStr"/>
+      <c r="BQ2" s="1" t="inlineStr"/>
       <c r="BR2" s="2" t="inlineStr"/>
-      <c r="BS2" s="2" t="inlineStr"/>
+      <c r="BS2" s="1" t="inlineStr"/>
       <c r="BT2" s="2" t="inlineStr"/>
-      <c r="BU2" s="2" t="inlineStr"/>
+      <c r="BU2" s="1" t="inlineStr"/>
       <c r="BV2" s="2" t="inlineStr"/>
-      <c r="BW2" s="2" t="inlineStr"/>
+      <c r="BW2" s="1" t="inlineStr"/>
       <c r="BX2" s="2" t="inlineStr"/>
-      <c r="BY2" s="2" t="inlineStr"/>
+      <c r="BY2" s="1" t="inlineStr"/>
       <c r="BZ2" s="2" t="inlineStr"/>
-      <c r="CA2" s="2" t="inlineStr"/>
+      <c r="CA2" s="1" t="inlineStr"/>
       <c r="CB2" s="2" t="inlineStr"/>
-      <c r="CC2" s="2" t="inlineStr"/>
+      <c r="CC2" s="1" t="inlineStr"/>
       <c r="CD2" s="2" t="inlineStr"/>
-      <c r="CE2" s="2" t="inlineStr"/>
+      <c r="CE2" s="1" t="inlineStr"/>
       <c r="CF2" s="2" t="inlineStr"/>
-      <c r="CG2" s="2" t="inlineStr"/>
+      <c r="CG2" s="1" t="inlineStr"/>
       <c r="CH2" s="2" t="inlineStr"/>
-      <c r="CI2" s="2" t="inlineStr"/>
+      <c r="CI2" s="1" t="inlineStr"/>
       <c r="CJ2" s="2" t="inlineStr"/>
-      <c r="CK2" s="2" t="inlineStr"/>
+      <c r="CK2" s="1" t="inlineStr"/>
       <c r="CL2" s="2" t="inlineStr"/>
-      <c r="CM2" s="2" t="inlineStr"/>
+      <c r="CM2" s="1" t="inlineStr"/>
       <c r="CN2" s="2" t="inlineStr"/>
-      <c r="CO2" s="2" t="inlineStr"/>
+      <c r="CO2" s="1" t="inlineStr"/>
       <c r="CP2" s="2" t="inlineStr"/>
-      <c r="CQ2" s="2" t="inlineStr"/>
+      <c r="CQ2" s="1" t="inlineStr"/>
       <c r="CR2" s="2" t="inlineStr"/>
-      <c r="CS2" s="2" t="inlineStr"/>
+      <c r="CS2" s="1" t="inlineStr"/>
       <c r="CT2" s="2" t="inlineStr"/>
-      <c r="CU2" s="2" t="inlineStr"/>
+      <c r="CU2" s="1" t="inlineStr"/>
       <c r="CV2" s="2" t="inlineStr"/>
-      <c r="CW2" s="2" t="inlineStr"/>
+      <c r="CW2" s="1" t="inlineStr"/>
       <c r="CX2" s="2" t="inlineStr"/>
-      <c r="CY2" s="2" t="inlineStr"/>
+      <c r="CY2" s="1" t="inlineStr"/>
       <c r="CZ2" s="2" t="inlineStr"/>
-      <c r="DA2" s="2" t="inlineStr"/>
+      <c r="DA2" s="1" t="inlineStr"/>
       <c r="DB2" s="2" t="inlineStr"/>
-      <c r="DC2" s="2" t="inlineStr"/>
+      <c r="DC2" s="1" t="inlineStr"/>
       <c r="DD2" s="2" t="inlineStr"/>
-      <c r="DE2" s="2" t="inlineStr"/>
+      <c r="DE2" s="1" t="inlineStr"/>
       <c r="DF2" s="2" t="inlineStr"/>
-      <c r="DG2" s="2" t="inlineStr"/>
+      <c r="DG2" s="1" t="inlineStr"/>
       <c r="DH2" s="2" t="inlineStr"/>
-      <c r="DI2" s="2" t="inlineStr"/>
+      <c r="DI2" s="1" t="inlineStr"/>
       <c r="DJ2" s="2" t="inlineStr"/>
-      <c r="DK2" s="2" t="inlineStr"/>
+      <c r="DK2" s="1" t="inlineStr"/>
       <c r="DL2" s="2" t="inlineStr"/>
-      <c r="DM2" s="2" t="inlineStr"/>
+      <c r="DM2" s="1" t="inlineStr"/>
       <c r="DN2" s="2" t="inlineStr"/>
-      <c r="DO2" s="2" t="inlineStr"/>
+      <c r="DO2" s="1" t="inlineStr"/>
       <c r="DP2" s="2" t="inlineStr"/>
-      <c r="DQ2" s="2" t="inlineStr"/>
+      <c r="DQ2" s="1" t="inlineStr"/>
       <c r="DR2" s="2" t="inlineStr"/>
-      <c r="DS2" s="2" t="inlineStr"/>
+      <c r="DS2" s="1" t="inlineStr"/>
       <c r="DT2" s="2" t="inlineStr"/>
-      <c r="DU2" s="2" t="inlineStr"/>
+      <c r="DU2" s="1" t="inlineStr"/>
       <c r="DV2" s="2" t="inlineStr"/>
-      <c r="DW2" s="2" t="inlineStr"/>
+      <c r="DW2" s="1" t="inlineStr"/>
       <c r="DX2" s="2" t="inlineStr"/>
-      <c r="DY2" s="2" t="inlineStr"/>
+      <c r="DY2" s="1" t="inlineStr"/>
       <c r="DZ2" s="2" t="inlineStr"/>
-      <c r="EA2" s="2" t="inlineStr"/>
+      <c r="EA2" s="1" t="inlineStr"/>
       <c r="EB2" s="2" t="inlineStr"/>
-      <c r="EC2" s="2" t="inlineStr"/>
+      <c r="EC2" s="1" t="inlineStr"/>
       <c r="ED2" s="2" t="inlineStr"/>
-      <c r="EE2" s="2" t="inlineStr"/>
+      <c r="EE2" s="1" t="inlineStr"/>
       <c r="EF2" s="2" t="inlineStr"/>
-      <c r="EG2" s="2" t="inlineStr"/>
+      <c r="EG2" s="1" t="inlineStr"/>
       <c r="EH2" s="2" t="inlineStr"/>
-      <c r="EI2" s="2" t="inlineStr"/>
+      <c r="EI2" s="1" t="inlineStr"/>
       <c r="EJ2" s="2" t="inlineStr"/>
-      <c r="EK2" s="2" t="inlineStr"/>
+      <c r="EK2" s="1" t="inlineStr"/>
       <c r="EL2" s="2" t="inlineStr"/>
-      <c r="EM2" s="2" t="inlineStr"/>
+      <c r="EM2" s="1" t="inlineStr"/>
       <c r="EN2" s="2" t="inlineStr"/>
-      <c r="EO2" s="2" t="inlineStr"/>
+      <c r="EO2" s="1" t="inlineStr"/>
       <c r="EP2" s="2" t="inlineStr"/>
-      <c r="EQ2" s="2" t="inlineStr"/>
+      <c r="EQ2" s="1" t="inlineStr"/>
       <c r="ER2" s="2" t="inlineStr"/>
-      <c r="ES2" s="2" t="inlineStr"/>
+      <c r="ES2" s="1" t="inlineStr"/>
       <c r="ET2" s="2" t="inlineStr"/>
-      <c r="EU2" s="2" t="inlineStr"/>
+      <c r="EU2" s="1" t="inlineStr"/>
       <c r="EV2" s="2" t="inlineStr"/>
-      <c r="EW2" s="2" t="inlineStr"/>
+      <c r="EW2" s="1" t="inlineStr"/>
       <c r="EX2" s="2" t="inlineStr"/>
-      <c r="EY2" s="2" t="inlineStr"/>
+      <c r="EY2" s="1" t="inlineStr"/>
       <c r="EZ2" s="2" t="inlineStr"/>
-      <c r="FA2" s="2" t="inlineStr"/>
+      <c r="FA2" s="1" t="inlineStr"/>
       <c r="FB2" s="2" t="inlineStr"/>
-      <c r="FC2" s="2" t="inlineStr"/>
+      <c r="FC2" s="1" t="inlineStr"/>
       <c r="FD2" s="2" t="inlineStr"/>
-      <c r="FE2" s="2" t="inlineStr"/>
+      <c r="FE2" s="1" t="inlineStr"/>
       <c r="FF2" s="2" t="inlineStr"/>
-      <c r="FG2" s="2" t="inlineStr"/>
+      <c r="FG2" s="1" t="inlineStr"/>
       <c r="FH2" s="2" t="inlineStr"/>
-      <c r="FI2" s="2" t="inlineStr"/>
+      <c r="FI2" s="1" t="inlineStr"/>
       <c r="FJ2" s="2" t="inlineStr"/>
-      <c r="FK2" s="2" t="inlineStr"/>
+      <c r="FK2" s="1" t="inlineStr"/>
       <c r="FL2" s="2" t="inlineStr"/>
-      <c r="FM2" s="2" t="inlineStr"/>
+      <c r="FM2" s="1" t="inlineStr"/>
       <c r="FN2" s="2" t="inlineStr"/>
-      <c r="FO2" s="2" t="inlineStr"/>
+      <c r="FO2" s="1" t="inlineStr"/>
       <c r="FP2" s="2" t="inlineStr"/>
-      <c r="FQ2" s="2" t="inlineStr"/>
+      <c r="FQ2" s="1" t="inlineStr"/>
       <c r="FR2" s="2" t="inlineStr"/>
-      <c r="FS2" s="2" t="inlineStr"/>
+      <c r="FS2" s="1" t="inlineStr"/>
       <c r="FT2" s="2" t="inlineStr"/>
-      <c r="FU2" s="2" t="inlineStr"/>
+      <c r="FU2" s="1" t="inlineStr"/>
       <c r="FV2" s="2" t="inlineStr"/>
-      <c r="FW2" s="2" t="inlineStr"/>
+      <c r="FW2" s="1" t="inlineStr"/>
       <c r="FX2" s="2" t="inlineStr"/>
-      <c r="FY2" s="2" t="inlineStr"/>
+      <c r="FY2" s="1" t="inlineStr"/>
       <c r="FZ2" s="2" t="inlineStr"/>
-      <c r="GA2" s="2" t="inlineStr"/>
+      <c r="GA2" s="1" t="inlineStr"/>
       <c r="GB2" s="2" t="inlineStr"/>
-      <c r="GC2" s="2" t="inlineStr"/>
+      <c r="GC2" s="1" t="inlineStr"/>
       <c r="GD2" s="2" t="inlineStr"/>
-      <c r="GE2" s="2" t="inlineStr"/>
+      <c r="GE2" s="1" t="inlineStr"/>
       <c r="GF2" s="2" t="inlineStr"/>
-      <c r="GG2" s="2" t="inlineStr"/>
+      <c r="GG2" s="1" t="inlineStr"/>
       <c r="GH2" s="2" t="inlineStr"/>
-      <c r="GI2" s="2" t="inlineStr"/>
+      <c r="GI2" s="1" t="inlineStr"/>
       <c r="GJ2" s="2" t="inlineStr"/>
-      <c r="GK2" s="2" t="inlineStr"/>
+      <c r="GK2" s="1" t="inlineStr"/>
       <c r="GL2" s="2" t="inlineStr"/>
-      <c r="GM2" s="2" t="inlineStr"/>
+      <c r="GM2" s="1" t="inlineStr"/>
       <c r="GN2" s="2" t="inlineStr"/>
-      <c r="GO2" s="2" t="inlineStr"/>
+      <c r="GO2" s="1" t="inlineStr"/>
       <c r="GP2" s="2" t="inlineStr"/>
-      <c r="GQ2" s="2" t="inlineStr"/>
+      <c r="GQ2" s="1" t="inlineStr"/>
       <c r="GR2" s="2" t="inlineStr"/>
-      <c r="GS2" s="2" t="inlineStr"/>
+      <c r="GS2" s="1" t="inlineStr"/>
       <c r="GT2" s="2" t="inlineStr"/>
-      <c r="GU2" s="2" t="inlineStr"/>
+      <c r="GU2" s="1" t="inlineStr"/>
       <c r="GV2" s="2" t="inlineStr"/>
-      <c r="GW2" s="2" t="inlineStr"/>
+      <c r="GW2" s="1" t="inlineStr"/>
       <c r="GX2" s="2" t="inlineStr"/>
-      <c r="GY2" s="2" t="inlineStr"/>
+      <c r="GY2" s="1" t="inlineStr"/>
       <c r="GZ2" s="2" t="inlineStr"/>
-      <c r="HA2" s="2" t="inlineStr"/>
+      <c r="HA2" s="1" t="inlineStr"/>
       <c r="HB2" s="2" t="inlineStr"/>
-      <c r="HC2" s="2" t="inlineStr"/>
+      <c r="HC2" s="1" t="inlineStr"/>
       <c r="HD2" s="2" t="inlineStr"/>
-      <c r="HE2" s="2" t="inlineStr"/>
+      <c r="HE2" s="1" t="inlineStr"/>
       <c r="HF2" s="2" t="inlineStr"/>
-      <c r="HG2" s="2" t="inlineStr"/>
+      <c r="HG2" s="1" t="inlineStr"/>
       <c r="HH2" s="2" t="inlineStr"/>
-      <c r="HI2" s="2" t="inlineStr"/>
+      <c r="HI2" s="1" t="inlineStr"/>
       <c r="HJ2" s="2" t="inlineStr"/>
-      <c r="HK2" s="2" t="inlineStr"/>
+      <c r="HK2" s="1" t="inlineStr"/>
       <c r="HL2" s="2" t="inlineStr"/>
-      <c r="HM2" s="2" t="inlineStr"/>
+      <c r="HM2" s="1" t="inlineStr"/>
       <c r="HN2" s="2" t="inlineStr"/>
-      <c r="HO2" s="2" t="inlineStr"/>
+      <c r="HO2" s="1" t="inlineStr"/>
       <c r="HP2" s="2" t="inlineStr"/>
-      <c r="HQ2" s="2" t="inlineStr"/>
+      <c r="HQ2" s="1" t="inlineStr"/>
       <c r="HR2" s="2" t="inlineStr"/>
-      <c r="HS2" s="2" t="inlineStr"/>
+      <c r="HS2" s="1" t="inlineStr"/>
       <c r="HT2" s="2" t="inlineStr"/>
-      <c r="HU2" s="2" t="inlineStr"/>
+      <c r="HU2" s="1" t="inlineStr"/>
       <c r="HV2" s="2" t="inlineStr"/>
-      <c r="HW2" s="2" t="inlineStr"/>
+      <c r="HW2" s="1" t="inlineStr"/>
       <c r="HX2" s="2" t="inlineStr"/>
-      <c r="HY2" s="2" t="inlineStr"/>
+      <c r="HY2" s="1" t="inlineStr"/>
       <c r="HZ2" s="2" t="inlineStr"/>
-      <c r="IA2" s="2" t="inlineStr"/>
+      <c r="IA2" s="1" t="inlineStr"/>
       <c r="IB2" s="2" t="inlineStr"/>
-      <c r="IC2" s="2" t="inlineStr"/>
+      <c r="IC2" s="1" t="inlineStr"/>
       <c r="ID2" s="2" t="inlineStr"/>
-      <c r="IE2" s="2" t="inlineStr"/>
+      <c r="IE2" s="1" t="inlineStr"/>
       <c r="IF2" s="2" t="inlineStr"/>
-      <c r="IG2" s="2" t="inlineStr"/>
+      <c r="IG2" s="1" t="inlineStr"/>
       <c r="IH2" s="2" t="inlineStr"/>
-      <c r="II2" s="2" t="inlineStr"/>
+      <c r="II2" s="1" t="inlineStr"/>
       <c r="IJ2" s="2" t="inlineStr"/>
-      <c r="IK2" s="2" t="inlineStr"/>
+      <c r="IK2" s="1" t="inlineStr"/>
       <c r="IL2" s="2" t="inlineStr"/>
-      <c r="IM2" s="2" t="inlineStr"/>
+      <c r="IM2" s="1" t="inlineStr"/>
       <c r="IN2" s="2" t="inlineStr"/>
-      <c r="IO2" s="2" t="inlineStr"/>
+      <c r="IO2" s="1" t="inlineStr"/>
       <c r="IP2" s="2" t="inlineStr"/>
-      <c r="IQ2" s="2" t="inlineStr"/>
+      <c r="IQ2" s="1" t="inlineStr"/>
       <c r="IR2" s="2" t="inlineStr"/>
-      <c r="IS2" s="2" t="inlineStr"/>
+      <c r="IS2" s="1" t="inlineStr"/>
       <c r="IT2" s="2" t="inlineStr"/>
-      <c r="IU2" s="2" t="inlineStr"/>
+      <c r="IU2" s="1" t="inlineStr"/>
       <c r="IV2" s="2" t="inlineStr"/>
-      <c r="IW2" s="2" t="inlineStr"/>
+      <c r="IW2" s="1" t="inlineStr"/>
       <c r="IX2" s="2" t="inlineStr"/>
-      <c r="IY2" s="2" t="inlineStr"/>
+      <c r="IY2" s="1" t="inlineStr"/>
       <c r="IZ2" s="2" t="inlineStr"/>
-      <c r="JA2" s="2" t="inlineStr"/>
+      <c r="JA2" s="1" t="inlineStr"/>
       <c r="JB2" s="2" t="inlineStr"/>
-      <c r="JC2" s="2" t="inlineStr"/>
+      <c r="JC2" s="1" t="inlineStr"/>
       <c r="JD2" s="2" t="inlineStr"/>
-      <c r="JE2" s="2" t="inlineStr"/>
+      <c r="JE2" s="1" t="inlineStr"/>
       <c r="JF2" s="2" t="inlineStr"/>
-      <c r="JG2" s="2" t="inlineStr"/>
+      <c r="JG2" s="1" t="inlineStr"/>
       <c r="JH2" s="2" t="inlineStr"/>
-      <c r="JI2" s="2" t="inlineStr"/>
+      <c r="JI2" s="1" t="inlineStr"/>
       <c r="JJ2" s="2" t="inlineStr"/>
-      <c r="JK2" s="2" t="inlineStr"/>
+      <c r="JK2" s="1" t="inlineStr"/>
       <c r="JL2" s="2" t="inlineStr"/>
-      <c r="JM2" s="2" t="inlineStr"/>
+      <c r="JM2" s="1" t="inlineStr"/>
       <c r="JN2" s="2" t="inlineStr"/>
-      <c r="JO2" s="2" t="inlineStr"/>
+      <c r="JO2" s="1" t="inlineStr"/>
       <c r="JP2" s="2" t="inlineStr"/>
-      <c r="JQ2" s="2" t="inlineStr"/>
+      <c r="JQ2" s="1" t="inlineStr"/>
       <c r="JR2" s="2" t="inlineStr"/>
-      <c r="JS2" s="2" t="inlineStr"/>
+      <c r="JS2" s="1" t="inlineStr"/>
       <c r="JT2" s="2" t="inlineStr"/>
-      <c r="JU2" s="2" t="inlineStr"/>
+      <c r="JU2" s="1" t="inlineStr"/>
       <c r="JV2" s="2" t="inlineStr"/>
-      <c r="JW2" s="2" t="inlineStr"/>
+      <c r="JW2" s="1" t="inlineStr"/>
       <c r="JX2" s="2" t="inlineStr"/>
-      <c r="JY2" s="2" t="inlineStr"/>
+      <c r="JY2" s="1" t="inlineStr"/>
       <c r="JZ2" s="2" t="inlineStr"/>
-      <c r="KA2" s="2" t="inlineStr"/>
+      <c r="KA2" s="1" t="inlineStr"/>
       <c r="KB2" s="2" t="inlineStr"/>
-      <c r="KC2" s="2" t="inlineStr"/>
+      <c r="KC2" s="1" t="inlineStr"/>
       <c r="KD2" s="2" t="inlineStr"/>
-      <c r="KE2" s="2" t="inlineStr"/>
+      <c r="KE2" s="1" t="inlineStr"/>
       <c r="KF2" s="2" t="inlineStr"/>
-      <c r="KG2" s="2" t="inlineStr"/>
+      <c r="KG2" s="1" t="inlineStr"/>
       <c r="KH2" s="2" t="inlineStr"/>
-      <c r="KI2" s="2" t="inlineStr"/>
+      <c r="KI2" s="1" t="inlineStr"/>
       <c r="KJ2" s="2" t="inlineStr"/>
-      <c r="KK2" s="2" t="inlineStr"/>
+      <c r="KK2" s="1" t="inlineStr"/>
       <c r="KL2" s="2" t="inlineStr"/>
-      <c r="KM2" s="2" t="inlineStr"/>
+      <c r="KM2" s="1" t="inlineStr"/>
       <c r="KN2" s="2" t="inlineStr"/>
-      <c r="KO2" s="2" t="inlineStr"/>
+      <c r="KO2" s="1" t="inlineStr"/>
       <c r="KP2" s="2" t="inlineStr"/>
-      <c r="KQ2" s="2" t="inlineStr"/>
+      <c r="KQ2" s="1" t="inlineStr"/>
       <c r="KR2" s="2" t="inlineStr"/>
-      <c r="KS2" s="2" t="inlineStr"/>
+      <c r="KS2" s="1" t="inlineStr"/>
       <c r="KT2" s="2" t="inlineStr"/>
-      <c r="KU2" s="2" t="inlineStr"/>
+      <c r="KU2" s="1" t="inlineStr"/>
       <c r="KV2" s="2" t="inlineStr"/>
-      <c r="KW2" s="2" t="inlineStr"/>
+      <c r="KW2" s="1" t="inlineStr"/>
       <c r="KX2" s="2" t="inlineStr"/>
-      <c r="KY2" s="2" t="inlineStr"/>
+      <c r="KY2" s="1" t="inlineStr"/>
       <c r="KZ2" s="2" t="inlineStr"/>
-      <c r="LA2" s="2" t="inlineStr"/>
+      <c r="LA2" s="1" t="inlineStr"/>
       <c r="LB2" s="2" t="inlineStr"/>
-      <c r="LC2" s="2" t="inlineStr"/>
+      <c r="LC2" s="1" t="inlineStr"/>
       <c r="LD2" s="2" t="inlineStr"/>
-      <c r="LE2" s="2" t="inlineStr"/>
+      <c r="LE2" s="1" t="inlineStr"/>
       <c r="LF2" s="2" t="inlineStr"/>
-      <c r="LG2" s="2" t="inlineStr"/>
+      <c r="LG2" s="1" t="inlineStr"/>
       <c r="LH2" s="2" t="inlineStr"/>
-      <c r="LI2" s="2" t="inlineStr"/>
+      <c r="LI2" s="1" t="inlineStr"/>
       <c r="LJ2" s="2" t="inlineStr"/>
-      <c r="LK2" s="2" t="inlineStr"/>
+      <c r="LK2" s="1" t="inlineStr"/>
       <c r="LL2" s="2" t="inlineStr"/>
-      <c r="LM2" s="2" t="inlineStr"/>
+      <c r="LM2" s="1" t="inlineStr"/>
       <c r="LN2" s="2" t="inlineStr"/>
-      <c r="LO2" s="2" t="inlineStr"/>
+      <c r="LO2" s="1" t="inlineStr"/>
       <c r="LP2" s="2" t="inlineStr"/>
-      <c r="LQ2" s="2" t="inlineStr"/>
+      <c r="LQ2" s="1" t="inlineStr"/>
       <c r="LR2" s="2" t="inlineStr"/>
-      <c r="LS2" s="2" t="inlineStr"/>
+      <c r="LS2" s="1" t="inlineStr"/>
       <c r="LT2" s="2" t="inlineStr"/>
-      <c r="LU2" s="2" t="inlineStr"/>
+      <c r="LU2" s="1" t="inlineStr"/>
       <c r="LV2" s="2" t="inlineStr"/>
-      <c r="LW2" s="2" t="inlineStr"/>
+      <c r="LW2" s="1" t="inlineStr"/>
       <c r="LX2" s="2" t="inlineStr"/>
-      <c r="LY2" s="2" t="inlineStr"/>
+      <c r="LY2" s="1" t="inlineStr"/>
       <c r="LZ2" s="2" t="inlineStr"/>
-      <c r="MA2" s="2" t="inlineStr"/>
+      <c r="MA2" s="1" t="inlineStr"/>
       <c r="MB2" s="2" t="inlineStr"/>
-      <c r="MC2" s="2" t="inlineStr"/>
+      <c r="MC2" s="1" t="inlineStr"/>
       <c r="MD2" s="2" t="inlineStr"/>
-      <c r="ME2" s="2" t="inlineStr"/>
+      <c r="ME2" s="1" t="inlineStr"/>
       <c r="MF2" s="2" t="inlineStr"/>
-      <c r="MG2" s="2" t="inlineStr"/>
+      <c r="MG2" s="1" t="inlineStr"/>
       <c r="MH2" s="2" t="inlineStr"/>
-      <c r="MI2" s="2" t="inlineStr"/>
+      <c r="MI2" s="1" t="inlineStr"/>
       <c r="MJ2" s="2" t="inlineStr"/>
-      <c r="MK2" s="2" t="inlineStr"/>
+      <c r="MK2" s="1" t="inlineStr"/>
       <c r="ML2" s="2" t="inlineStr"/>
-      <c r="MM2" s="2" t="inlineStr"/>
+      <c r="MM2" s="1" t="inlineStr"/>
       <c r="MN2" s="2" t="inlineStr"/>
-      <c r="MO2" s="2" t="inlineStr"/>
+      <c r="MO2" s="1" t="inlineStr"/>
       <c r="MP2" s="2" t="inlineStr"/>
-      <c r="MQ2" s="2" t="inlineStr"/>
+      <c r="MQ2" s="1" t="inlineStr"/>
       <c r="MR2" s="2" t="inlineStr"/>
-      <c r="MS2" s="2" t="inlineStr"/>
+      <c r="MS2" s="1" t="inlineStr"/>
       <c r="MT2" s="2" t="inlineStr"/>
-      <c r="MU2" s="2" t="inlineStr"/>
+      <c r="MU2" s="1" t="inlineStr"/>
       <c r="MV2" s="2" t="inlineStr"/>
-      <c r="MW2" s="2" t="inlineStr"/>
+      <c r="MW2" s="1" t="inlineStr"/>
       <c r="MX2" s="2" t="inlineStr"/>
-      <c r="MY2" s="2" t="inlineStr"/>
+      <c r="MY2" s="1" t="inlineStr"/>
       <c r="MZ2" s="2" t="inlineStr"/>
-      <c r="NA2" s="2" t="inlineStr"/>
+      <c r="NA2" s="1" t="inlineStr"/>
       <c r="NB2" s="2" t="inlineStr"/>
-      <c r="NC2" s="2" t="inlineStr"/>
+      <c r="NC2" s="1" t="inlineStr"/>
       <c r="ND2" s="2" t="inlineStr"/>
-      <c r="NE2" s="2" t="inlineStr"/>
+      <c r="NE2" s="1" t="inlineStr"/>
       <c r="NF2" s="2" t="inlineStr"/>
-      <c r="NG2" s="2" t="inlineStr"/>
+      <c r="NG2" s="1" t="inlineStr"/>
       <c r="NH2" s="2" t="inlineStr"/>
-      <c r="NI2" s="2" t="inlineStr"/>
+      <c r="NI2" s="1" t="inlineStr"/>
       <c r="NJ2" s="2" t="inlineStr"/>
-      <c r="NK2" s="2" t="inlineStr"/>
+      <c r="NK2" s="1" t="inlineStr"/>
       <c r="NL2" s="2" t="inlineStr"/>
-      <c r="NM2" s="2" t="inlineStr"/>
+      <c r="NM2" s="1" t="inlineStr"/>
       <c r="NN2" s="2" t="inlineStr"/>
-      <c r="NO2" s="2" t="inlineStr"/>
+      <c r="NO2" s="1" t="inlineStr"/>
       <c r="NP2" s="2" t="inlineStr"/>
-      <c r="NQ2" s="2" t="inlineStr"/>
+      <c r="NQ2" s="1" t="inlineStr"/>
       <c r="NR2" s="2" t="inlineStr"/>
-      <c r="NS2" s="2" t="inlineStr"/>
+      <c r="NS2" s="1" t="inlineStr"/>
       <c r="NT2" s="2" t="inlineStr"/>
-      <c r="NU2" s="2" t="inlineStr"/>
+      <c r="NU2" s="1" t="inlineStr"/>
       <c r="NV2" s="2" t="inlineStr"/>
-      <c r="NW2" s="2" t="inlineStr"/>
+      <c r="NW2" s="1" t="inlineStr"/>
       <c r="NX2" s="2" t="inlineStr"/>
-      <c r="NY2" s="2" t="inlineStr"/>
+      <c r="NY2" s="1" t="inlineStr"/>
       <c r="NZ2" s="2" t="inlineStr"/>
-      <c r="OA2" s="2" t="inlineStr"/>
+      <c r="OA2" s="1" t="inlineStr"/>
       <c r="OB2" s="2" t="inlineStr"/>
-      <c r="OC2" s="2" t="inlineStr"/>
+      <c r="OC2" s="1" t="inlineStr"/>
       <c r="OD2" s="2" t="inlineStr"/>
-      <c r="OE2" s="2" t="inlineStr"/>
+      <c r="OE2" s="1" t="inlineStr"/>
       <c r="OF2" s="2" t="inlineStr"/>
-      <c r="OG2" s="2" t="inlineStr"/>
+      <c r="OG2" s="1" t="inlineStr"/>
       <c r="OH2" s="2" t="inlineStr"/>
-      <c r="OI2" s="2" t="inlineStr"/>
+      <c r="OI2" s="1" t="inlineStr"/>
       <c r="OJ2" s="2" t="inlineStr"/>
-      <c r="OK2" s="2" t="inlineStr"/>
+      <c r="OK2" s="1" t="inlineStr"/>
       <c r="OL2" s="2" t="inlineStr"/>
-      <c r="OM2" s="2" t="inlineStr"/>
+      <c r="OM2" s="1" t="inlineStr"/>
       <c r="ON2" s="2" t="inlineStr"/>
-      <c r="OO2" s="2" t="inlineStr"/>
+      <c r="OO2" s="1" t="inlineStr"/>
       <c r="OP2" s="2" t="inlineStr"/>
-      <c r="OQ2" s="2" t="inlineStr"/>
+      <c r="OQ2" s="1" t="inlineStr"/>
       <c r="OR2" s="2" t="inlineStr"/>
-      <c r="OS2" s="2" t="inlineStr"/>
+      <c r="OS2" s="1" t="inlineStr"/>
       <c r="OT2" s="2" t="inlineStr"/>
-      <c r="OU2" s="2" t="inlineStr"/>
+      <c r="OU2" s="1" t="inlineStr"/>
       <c r="OV2" s="2" t="inlineStr"/>
-      <c r="OW2" s="2" t="inlineStr"/>
+      <c r="OW2" s="1" t="inlineStr"/>
       <c r="OX2" s="2" t="inlineStr"/>
-      <c r="OY2" s="2" t="inlineStr"/>
+      <c r="OY2" s="1" t="inlineStr"/>
       <c r="OZ2" s="2" t="inlineStr"/>
-      <c r="PA2" s="2" t="inlineStr"/>
+      <c r="PA2" s="1" t="inlineStr"/>
       <c r="PB2" s="2" t="inlineStr"/>
-      <c r="PC2" s="2" t="inlineStr"/>
+      <c r="PC2" s="1" t="inlineStr"/>
       <c r="PD2" s="2" t="inlineStr"/>
-      <c r="PE2" s="2" t="inlineStr"/>
+      <c r="PE2" s="1" t="inlineStr"/>
       <c r="PF2" s="2" t="inlineStr"/>
-      <c r="PG2" s="2" t="inlineStr"/>
+      <c r="PG2" s="1" t="inlineStr"/>
       <c r="PH2" s="2" t="inlineStr"/>
-      <c r="PI2" s="2" t="inlineStr"/>
+      <c r="PI2" s="1" t="inlineStr"/>
       <c r="PJ2" s="2" t="inlineStr"/>
-      <c r="PK2" s="2" t="inlineStr"/>
+      <c r="PK2" s="1" t="inlineStr"/>
       <c r="PL2" s="2" t="inlineStr"/>
-      <c r="PM2" s="2" t="inlineStr"/>
+      <c r="PM2" s="1" t="inlineStr"/>
       <c r="PN2" s="2" t="inlineStr"/>
-      <c r="PO2" s="2" t="inlineStr"/>
+      <c r="PO2" s="1" t="inlineStr"/>
       <c r="PP2" s="2" t="inlineStr"/>
-      <c r="PQ2" s="2" t="inlineStr"/>
+      <c r="PQ2" s="1" t="inlineStr"/>
       <c r="PR2" s="2" t="inlineStr"/>
-      <c r="PS2" s="2" t="inlineStr"/>
+      <c r="PS2" s="1" t="inlineStr"/>
       <c r="PT2" s="2" t="inlineStr"/>
-      <c r="PU2" s="2" t="inlineStr"/>
+      <c r="PU2" s="1" t="inlineStr"/>
       <c r="PV2" s="2" t="inlineStr"/>
-      <c r="PW2" s="2" t="inlineStr"/>
+      <c r="PW2" s="1" t="inlineStr"/>
       <c r="PX2" s="2" t="inlineStr"/>
-      <c r="PY2" s="2" t="inlineStr"/>
+      <c r="PY2" s="1" t="inlineStr"/>
       <c r="PZ2" s="2" t="inlineStr"/>
-      <c r="QA2" s="2" t="inlineStr"/>
+      <c r="QA2" s="1" t="inlineStr"/>
       <c r="QB2" s="2" t="inlineStr"/>
-      <c r="QC2" s="2" t="inlineStr"/>
+      <c r="QC2" s="1" t="inlineStr"/>
       <c r="QD2" s="2" t="inlineStr"/>
-      <c r="QE2" s="2" t="inlineStr"/>
+      <c r="QE2" s="1" t="inlineStr"/>
       <c r="QF2" s="2" t="inlineStr"/>
-      <c r="QG2" s="2" t="inlineStr"/>
+      <c r="QG2" s="1" t="inlineStr"/>
       <c r="QH2" s="2" t="inlineStr"/>
-      <c r="QI2" s="2" t="inlineStr"/>
+      <c r="QI2" s="1" t="inlineStr"/>
       <c r="QJ2" s="2" t="inlineStr"/>
-      <c r="QK2" s="2" t="inlineStr"/>
+      <c r="QK2" s="1" t="inlineStr"/>
       <c r="QL2" s="2" t="inlineStr"/>
-      <c r="QM2" s="2" t="inlineStr"/>
+      <c r="QM2" s="1" t="inlineStr"/>
       <c r="QN2" s="2" t="inlineStr"/>
-      <c r="QO2" s="2" t="inlineStr"/>
+      <c r="QO2" s="1" t="inlineStr"/>
       <c r="QP2" s="2" t="inlineStr"/>
-      <c r="QQ2" s="2" t="inlineStr"/>
+      <c r="QQ2" s="1" t="inlineStr"/>
       <c r="QR2" s="2" t="inlineStr"/>
-      <c r="QS2" s="2" t="inlineStr"/>
+      <c r="QS2" s="1" t="inlineStr"/>
       <c r="QT2" s="2" t="inlineStr"/>
-      <c r="QU2" s="2" t="inlineStr"/>
+      <c r="QU2" s="1" t="inlineStr"/>
       <c r="QV2" s="2" t="inlineStr"/>
-      <c r="QW2" s="2" t="inlineStr"/>
+      <c r="QW2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr"/>
+      <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
+      <c r="W3" s="1" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr"/>
-      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Y3" s="1" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
-      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AA3" s="1" t="inlineStr"/>
       <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="1" t="inlineStr"/>
       <c r="AD3" s="2" t="inlineStr"/>
-      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AE3" s="1" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AG3" s="1" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AI3" s="1" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AK3" s="1" t="inlineStr"/>
       <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AM3" s="1" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="1" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="1" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
+      <c r="AS3" s="1" t="inlineStr"/>
       <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AU3" s="1" t="inlineStr"/>
       <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
+      <c r="AW3" s="1" t="inlineStr"/>
       <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AY3" s="1" t="inlineStr"/>
       <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
+      <c r="BA3" s="1" t="inlineStr"/>
       <c r="BB3" s="2" t="inlineStr"/>
-      <c r="BC3" s="2" t="inlineStr"/>
+      <c r="BC3" s="1" t="inlineStr"/>
       <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr"/>
+      <c r="BE3" s="1" t="inlineStr"/>
       <c r="BF3" s="2" t="inlineStr"/>
-      <c r="BG3" s="2" t="inlineStr"/>
+      <c r="BG3" s="1" t="inlineStr"/>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="1" t="inlineStr"/>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BK3" s="1" t="inlineStr"/>
       <c r="BL3" s="2" t="inlineStr"/>
-      <c r="BM3" s="2" t="inlineStr"/>
+      <c r="BM3" s="1" t="inlineStr"/>
       <c r="BN3" s="2" t="inlineStr"/>
-      <c r="BO3" s="2" t="inlineStr"/>
+      <c r="BO3" s="1" t="inlineStr"/>
       <c r="BP3" s="2" t="inlineStr"/>
-      <c r="BQ3" s="2" t="inlineStr"/>
+      <c r="BQ3" s="1" t="inlineStr"/>
       <c r="BR3" s="2" t="inlineStr"/>
-      <c r="BS3" s="2" t="inlineStr"/>
+      <c r="BS3" s="1" t="inlineStr"/>
       <c r="BT3" s="2" t="inlineStr"/>
-      <c r="BU3" s="2" t="inlineStr"/>
+      <c r="BU3" s="1" t="inlineStr"/>
       <c r="BV3" s="2" t="inlineStr"/>
-      <c r="BW3" s="2" t="inlineStr"/>
+      <c r="BW3" s="1" t="inlineStr"/>
       <c r="BX3" s="2" t="inlineStr"/>
-      <c r="BY3" s="2" t="inlineStr"/>
+      <c r="BY3" s="1" t="inlineStr"/>
       <c r="BZ3" s="2" t="inlineStr"/>
-      <c r="CA3" s="2" t="inlineStr"/>
+      <c r="CA3" s="1" t="inlineStr"/>
       <c r="CB3" s="2" t="inlineStr"/>
-      <c r="CC3" s="2" t="inlineStr"/>
+      <c r="CC3" s="1" t="inlineStr"/>
       <c r="CD3" s="2" t="inlineStr"/>
-      <c r="CE3" s="2" t="inlineStr"/>
+      <c r="CE3" s="1" t="inlineStr"/>
       <c r="CF3" s="2" t="inlineStr"/>
-      <c r="CG3" s="2" t="inlineStr"/>
+      <c r="CG3" s="1" t="inlineStr"/>
       <c r="CH3" s="2" t="inlineStr"/>
-      <c r="CI3" s="2" t="inlineStr"/>
+      <c r="CI3" s="1" t="inlineStr"/>
       <c r="CJ3" s="2" t="inlineStr"/>
-      <c r="CK3" s="2" t="inlineStr"/>
+      <c r="CK3" s="1" t="inlineStr"/>
       <c r="CL3" s="2" t="inlineStr"/>
-      <c r="CM3" s="2" t="inlineStr"/>
+      <c r="CM3" s="1" t="inlineStr"/>
       <c r="CN3" s="2" t="inlineStr"/>
-      <c r="CO3" s="2" t="inlineStr"/>
+      <c r="CO3" s="1" t="inlineStr"/>
       <c r="CP3" s="2" t="inlineStr"/>
-      <c r="CQ3" s="2" t="inlineStr"/>
+      <c r="CQ3" s="1" t="inlineStr"/>
       <c r="CR3" s="2" t="inlineStr"/>
-      <c r="CS3" s="2" t="inlineStr"/>
+      <c r="CS3" s="1" t="inlineStr"/>
       <c r="CT3" s="2" t="inlineStr"/>
-      <c r="CU3" s="2" t="inlineStr"/>
+      <c r="CU3" s="1" t="inlineStr"/>
       <c r="CV3" s="2" t="inlineStr"/>
-      <c r="CW3" s="2" t="inlineStr"/>
+      <c r="CW3" s="1" t="inlineStr"/>
       <c r="CX3" s="2" t="inlineStr"/>
-      <c r="CY3" s="2" t="inlineStr"/>
+      <c r="CY3" s="1" t="inlineStr"/>
       <c r="CZ3" s="2" t="inlineStr"/>
-      <c r="DA3" s="2" t="inlineStr"/>
+      <c r="DA3" s="1" t="inlineStr"/>
       <c r="DB3" s="2" t="inlineStr"/>
-      <c r="DC3" s="2" t="inlineStr"/>
+      <c r="DC3" s="1" t="inlineStr"/>
       <c r="DD3" s="2" t="inlineStr"/>
-      <c r="DE3" s="2" t="inlineStr"/>
+      <c r="DE3" s="1" t="inlineStr"/>
       <c r="DF3" s="2" t="inlineStr"/>
-      <c r="DG3" s="2" t="inlineStr"/>
+      <c r="DG3" s="1" t="inlineStr"/>
       <c r="DH3" s="2" t="inlineStr"/>
-      <c r="DI3" s="2" t="inlineStr"/>
+      <c r="DI3" s="1" t="inlineStr"/>
       <c r="DJ3" s="2" t="inlineStr"/>
-      <c r="DK3" s="2" t="inlineStr"/>
+      <c r="DK3" s="1" t="inlineStr"/>
       <c r="DL3" s="2" t="inlineStr"/>
-      <c r="DM3" s="2" t="inlineStr"/>
+      <c r="DM3" s="1" t="inlineStr"/>
       <c r="DN3" s="2" t="inlineStr"/>
-      <c r="DO3" s="2" t="inlineStr"/>
+      <c r="DO3" s="1" t="inlineStr"/>
       <c r="DP3" s="2" t="inlineStr"/>
-      <c r="DQ3" s="2" t="inlineStr"/>
+      <c r="DQ3" s="1" t="inlineStr"/>
       <c r="DR3" s="2" t="inlineStr"/>
-      <c r="DS3" s="2" t="inlineStr"/>
+      <c r="DS3" s="1" t="inlineStr"/>
       <c r="DT3" s="2" t="inlineStr"/>
-      <c r="DU3" s="2" t="inlineStr"/>
+      <c r="DU3" s="1" t="inlineStr"/>
       <c r="DV3" s="2" t="inlineStr"/>
-      <c r="DW3" s="2" t="inlineStr"/>
+      <c r="DW3" s="1" t="inlineStr"/>
       <c r="DX3" s="2" t="inlineStr"/>
-      <c r="DY3" s="2" t="inlineStr"/>
+      <c r="DY3" s="1" t="inlineStr"/>
       <c r="DZ3" s="2" t="inlineStr"/>
-      <c r="EA3" s="2" t="inlineStr"/>
+      <c r="EA3" s="1" t="inlineStr"/>
       <c r="EB3" s="2" t="inlineStr"/>
-      <c r="EC3" s="2" t="inlineStr"/>
+      <c r="EC3" s="1" t="inlineStr"/>
       <c r="ED3" s="2" t="inlineStr"/>
-      <c r="EE3" s="2" t="inlineStr"/>
+      <c r="EE3" s="1" t="inlineStr"/>
       <c r="EF3" s="2" t="inlineStr"/>
-      <c r="EG3" s="2" t="inlineStr"/>
+      <c r="EG3" s="1" t="inlineStr"/>
       <c r="EH3" s="2" t="inlineStr"/>
-      <c r="EI3" s="2" t="inlineStr"/>
+      <c r="EI3" s="1" t="inlineStr"/>
       <c r="EJ3" s="2" t="inlineStr"/>
-      <c r="EK3" s="2" t="inlineStr"/>
+      <c r="EK3" s="1" t="inlineStr"/>
       <c r="EL3" s="2" t="inlineStr"/>
-      <c r="EM3" s="2" t="inlineStr"/>
+      <c r="EM3" s="1" t="inlineStr"/>
       <c r="EN3" s="2" t="inlineStr"/>
-      <c r="EO3" s="2" t="inlineStr"/>
+      <c r="EO3" s="1" t="inlineStr"/>
       <c r="EP3" s="2" t="inlineStr"/>
-      <c r="EQ3" s="2" t="inlineStr"/>
+      <c r="EQ3" s="1" t="inlineStr"/>
       <c r="ER3" s="2" t="inlineStr"/>
-      <c r="ES3" s="2" t="inlineStr"/>
+      <c r="ES3" s="1" t="inlineStr"/>
       <c r="ET3" s="2" t="inlineStr"/>
-      <c r="EU3" s="2" t="inlineStr"/>
+      <c r="EU3" s="1" t="inlineStr"/>
       <c r="EV3" s="2" t="inlineStr"/>
-      <c r="EW3" s="2" t="inlineStr"/>
+      <c r="EW3" s="1" t="inlineStr"/>
       <c r="EX3" s="2" t="inlineStr"/>
-      <c r="EY3" s="2" t="inlineStr"/>
+      <c r="EY3" s="1" t="inlineStr"/>
       <c r="EZ3" s="2" t="inlineStr"/>
-      <c r="FA3" s="2" t="inlineStr"/>
+      <c r="FA3" s="1" t="inlineStr"/>
       <c r="FB3" s="2" t="inlineStr"/>
-      <c r="FC3" s="2" t="inlineStr"/>
+      <c r="FC3" s="1" t="inlineStr"/>
       <c r="FD3" s="2" t="inlineStr"/>
-      <c r="FE3" s="2" t="inlineStr"/>
+      <c r="FE3" s="1" t="inlineStr"/>
       <c r="FF3" s="2" t="inlineStr"/>
-      <c r="FG3" s="2" t="inlineStr"/>
+      <c r="FG3" s="1" t="inlineStr"/>
       <c r="FH3" s="2" t="inlineStr"/>
-      <c r="FI3" s="2" t="inlineStr"/>
+      <c r="FI3" s="1" t="inlineStr"/>
       <c r="FJ3" s="2" t="inlineStr"/>
-      <c r="FK3" s="2" t="inlineStr"/>
+      <c r="FK3" s="1" t="inlineStr"/>
       <c r="FL3" s="2" t="inlineStr"/>
-      <c r="FM3" s="2" t="inlineStr"/>
+      <c r="FM3" s="1" t="inlineStr"/>
       <c r="FN3" s="2" t="inlineStr"/>
-      <c r="FO3" s="2" t="inlineStr"/>
+      <c r="FO3" s="1" t="inlineStr"/>
       <c r="FP3" s="2" t="inlineStr"/>
-      <c r="FQ3" s="2" t="inlineStr"/>
+      <c r="FQ3" s="1" t="inlineStr"/>
       <c r="FR3" s="2" t="inlineStr"/>
-      <c r="FS3" s="2" t="inlineStr"/>
+      <c r="FS3" s="1" t="inlineStr"/>
       <c r="FT3" s="2" t="inlineStr"/>
-      <c r="FU3" s="2" t="inlineStr"/>
+      <c r="FU3" s="1" t="inlineStr"/>
       <c r="FV3" s="2" t="inlineStr"/>
-      <c r="FW3" s="2" t="inlineStr"/>
+      <c r="FW3" s="1" t="inlineStr"/>
       <c r="FX3" s="2" t="inlineStr"/>
-      <c r="FY3" s="2" t="inlineStr"/>
+      <c r="FY3" s="1" t="inlineStr"/>
       <c r="FZ3" s="2" t="inlineStr"/>
-      <c r="GA3" s="2" t="inlineStr"/>
+      <c r="GA3" s="1" t="inlineStr"/>
       <c r="GB3" s="2" t="inlineStr"/>
-      <c r="GC3" s="2" t="inlineStr"/>
+      <c r="GC3" s="1" t="inlineStr"/>
       <c r="GD3" s="2" t="inlineStr"/>
-      <c r="GE3" s="2" t="inlineStr"/>
+      <c r="GE3" s="1" t="inlineStr"/>
       <c r="GF3" s="2" t="inlineStr"/>
-      <c r="GG3" s="2" t="inlineStr"/>
+      <c r="GG3" s="1" t="inlineStr"/>
       <c r="GH3" s="2" t="inlineStr"/>
-      <c r="GI3" s="2" t="inlineStr"/>
+      <c r="GI3" s="1" t="inlineStr"/>
       <c r="GJ3" s="2" t="inlineStr"/>
-      <c r="GK3" s="2" t="inlineStr"/>
+      <c r="GK3" s="1" t="inlineStr"/>
       <c r="GL3" s="2" t="inlineStr"/>
-      <c r="GM3" s="2" t="inlineStr"/>
+      <c r="GM3" s="1" t="inlineStr"/>
       <c r="GN3" s="2" t="inlineStr"/>
-      <c r="GO3" s="2" t="inlineStr"/>
+      <c r="GO3" s="1" t="inlineStr"/>
       <c r="GP3" s="2" t="inlineStr"/>
-      <c r="GQ3" s="2" t="inlineStr"/>
+      <c r="GQ3" s="1" t="inlineStr"/>
       <c r="GR3" s="2" t="inlineStr"/>
-      <c r="GS3" s="2" t="inlineStr"/>
+      <c r="GS3" s="1" t="inlineStr"/>
       <c r="GT3" s="2" t="inlineStr"/>
-      <c r="GU3" s="2" t="inlineStr"/>
+      <c r="GU3" s="1" t="inlineStr"/>
       <c r="GV3" s="2" t="inlineStr"/>
-      <c r="GW3" s="2" t="inlineStr"/>
+      <c r="GW3" s="1" t="inlineStr"/>
       <c r="GX3" s="2" t="inlineStr"/>
-      <c r="GY3" s="2" t="inlineStr"/>
+      <c r="GY3" s="1" t="inlineStr"/>
       <c r="GZ3" s="2" t="inlineStr"/>
-      <c r="HA3" s="2" t="inlineStr"/>
+      <c r="HA3" s="1" t="inlineStr"/>
       <c r="HB3" s="2" t="inlineStr"/>
-      <c r="HC3" s="2" t="inlineStr"/>
+      <c r="HC3" s="1" t="inlineStr"/>
       <c r="HD3" s="2" t="inlineStr"/>
-      <c r="HE3" s="2" t="inlineStr"/>
+      <c r="HE3" s="1" t="inlineStr"/>
       <c r="HF3" s="2" t="inlineStr"/>
-      <c r="HG3" s="2" t="inlineStr"/>
+      <c r="HG3" s="1" t="inlineStr"/>
       <c r="HH3" s="2" t="inlineStr"/>
-      <c r="HI3" s="2" t="inlineStr"/>
+      <c r="HI3" s="1" t="inlineStr"/>
       <c r="HJ3" s="2" t="inlineStr"/>
-      <c r="HK3" s="2" t="inlineStr"/>
+      <c r="HK3" s="1" t="inlineStr"/>
       <c r="HL3" s="2" t="inlineStr"/>
-      <c r="HM3" s="2" t="inlineStr"/>
+      <c r="HM3" s="1" t="inlineStr"/>
       <c r="HN3" s="2" t="inlineStr"/>
-      <c r="HO3" s="2" t="inlineStr"/>
+      <c r="HO3" s="1" t="inlineStr"/>
       <c r="HP3" s="2" t="inlineStr"/>
-      <c r="HQ3" s="2" t="inlineStr"/>
+      <c r="HQ3" s="1" t="inlineStr"/>
       <c r="HR3" s="2" t="inlineStr"/>
-      <c r="HS3" s="2" t="inlineStr"/>
+      <c r="HS3" s="1" t="inlineStr"/>
       <c r="HT3" s="2" t="inlineStr"/>
-      <c r="HU3" s="2" t="inlineStr"/>
+      <c r="HU3" s="1" t="inlineStr"/>
       <c r="HV3" s="2" t="inlineStr"/>
-      <c r="HW3" s="2" t="inlineStr"/>
+      <c r="HW3" s="1" t="inlineStr"/>
       <c r="HX3" s="2" t="inlineStr"/>
-      <c r="HY3" s="2" t="inlineStr"/>
+      <c r="HY3" s="1" t="inlineStr"/>
       <c r="HZ3" s="2" t="inlineStr"/>
-      <c r="IA3" s="2" t="inlineStr"/>
+      <c r="IA3" s="1" t="inlineStr"/>
       <c r="IB3" s="2" t="inlineStr"/>
-      <c r="IC3" s="2" t="inlineStr"/>
+      <c r="IC3" s="1" t="inlineStr"/>
       <c r="ID3" s="2" t="inlineStr"/>
-      <c r="IE3" s="2" t="inlineStr"/>
+      <c r="IE3" s="1" t="inlineStr"/>
       <c r="IF3" s="2" t="inlineStr"/>
-      <c r="IG3" s="2" t="inlineStr"/>
+      <c r="IG3" s="1" t="inlineStr"/>
       <c r="IH3" s="2" t="inlineStr"/>
-      <c r="II3" s="2" t="inlineStr"/>
+      <c r="II3" s="1" t="inlineStr"/>
       <c r="IJ3" s="2" t="inlineStr"/>
-      <c r="IK3" s="2" t="inlineStr"/>
+      <c r="IK3" s="1" t="inlineStr"/>
       <c r="IL3" s="2" t="inlineStr"/>
-      <c r="IM3" s="2" t="inlineStr"/>
+      <c r="IM3" s="1" t="inlineStr"/>
       <c r="IN3" s="2" t="inlineStr"/>
-      <c r="IO3" s="2" t="inlineStr"/>
+      <c r="IO3" s="1" t="inlineStr"/>
       <c r="IP3" s="2" t="inlineStr"/>
-      <c r="IQ3" s="2" t="inlineStr"/>
+      <c r="IQ3" s="1" t="inlineStr"/>
       <c r="IR3" s="2" t="inlineStr"/>
-      <c r="IS3" s="2" t="inlineStr"/>
+      <c r="IS3" s="1" t="inlineStr"/>
       <c r="IT3" s="2" t="inlineStr"/>
-      <c r="IU3" s="2" t="inlineStr"/>
+      <c r="IU3" s="1" t="inlineStr"/>
       <c r="IV3" s="2" t="inlineStr"/>
-      <c r="IW3" s="2" t="inlineStr"/>
+      <c r="IW3" s="1" t="inlineStr"/>
       <c r="IX3" s="2" t="inlineStr"/>
-      <c r="IY3" s="2" t="inlineStr"/>
+      <c r="IY3" s="1" t="inlineStr"/>
       <c r="IZ3" s="2" t="inlineStr"/>
-      <c r="JA3" s="2" t="inlineStr"/>
+      <c r="JA3" s="1" t="inlineStr"/>
       <c r="JB3" s="2" t="inlineStr"/>
-      <c r="JC3" s="2" t="inlineStr"/>
+      <c r="JC3" s="1" t="inlineStr"/>
       <c r="JD3" s="2" t="inlineStr"/>
-      <c r="JE3" s="2" t="inlineStr"/>
+      <c r="JE3" s="1" t="inlineStr"/>
       <c r="JF3" s="2" t="inlineStr"/>
-      <c r="JG3" s="2" t="inlineStr"/>
+      <c r="JG3" s="1" t="inlineStr"/>
       <c r="JH3" s="2" t="inlineStr"/>
-      <c r="JI3" s="2" t="inlineStr"/>
+      <c r="JI3" s="1" t="inlineStr"/>
       <c r="JJ3" s="2" t="inlineStr"/>
-      <c r="JK3" s="2" t="inlineStr"/>
+      <c r="JK3" s="1" t="inlineStr"/>
       <c r="JL3" s="2" t="inlineStr"/>
-      <c r="JM3" s="2" t="inlineStr"/>
+      <c r="JM3" s="1" t="inlineStr"/>
       <c r="JN3" s="2" t="inlineStr"/>
-      <c r="JO3" s="2" t="inlineStr"/>
+      <c r="JO3" s="1" t="inlineStr"/>
       <c r="JP3" s="2" t="inlineStr"/>
-      <c r="JQ3" s="2" t="inlineStr"/>
+      <c r="JQ3" s="1" t="inlineStr"/>
       <c r="JR3" s="2" t="inlineStr"/>
-      <c r="JS3" s="2" t="inlineStr"/>
+      <c r="JS3" s="1" t="inlineStr"/>
       <c r="JT3" s="2" t="inlineStr"/>
-      <c r="JU3" s="2" t="inlineStr"/>
+      <c r="JU3" s="1" t="inlineStr"/>
       <c r="JV3" s="2" t="inlineStr"/>
-      <c r="JW3" s="2" t="inlineStr"/>
+      <c r="JW3" s="1" t="inlineStr"/>
       <c r="JX3" s="2" t="inlineStr"/>
-      <c r="JY3" s="2" t="inlineStr"/>
+      <c r="JY3" s="1" t="inlineStr"/>
       <c r="JZ3" s="2" t="inlineStr"/>
-      <c r="KA3" s="2" t="inlineStr"/>
+      <c r="KA3" s="1" t="inlineStr"/>
       <c r="KB3" s="2" t="inlineStr"/>
-      <c r="KC3" s="2" t="inlineStr"/>
+      <c r="KC3" s="1" t="inlineStr"/>
       <c r="KD3" s="2" t="inlineStr"/>
-      <c r="KE3" s="2" t="inlineStr"/>
+      <c r="KE3" s="1" t="inlineStr"/>
       <c r="KF3" s="2" t="inlineStr"/>
-      <c r="KG3" s="2" t="inlineStr"/>
+      <c r="KG3" s="1" t="inlineStr"/>
       <c r="KH3" s="2" t="inlineStr"/>
-      <c r="KI3" s="2" t="inlineStr"/>
+      <c r="KI3" s="1" t="inlineStr"/>
       <c r="KJ3" s="2" t="inlineStr"/>
-      <c r="KK3" s="2" t="inlineStr"/>
+      <c r="KK3" s="1" t="inlineStr"/>
       <c r="KL3" s="2" t="inlineStr"/>
-      <c r="KM3" s="2" t="inlineStr"/>
+      <c r="KM3" s="1" t="inlineStr"/>
       <c r="KN3" s="2" t="inlineStr"/>
-      <c r="KO3" s="2" t="inlineStr"/>
+      <c r="KO3" s="1" t="inlineStr"/>
       <c r="KP3" s="2" t="inlineStr"/>
-      <c r="KQ3" s="2" t="inlineStr"/>
+      <c r="KQ3" s="1" t="inlineStr"/>
       <c r="KR3" s="2" t="inlineStr"/>
-      <c r="KS3" s="2" t="inlineStr"/>
+      <c r="KS3" s="1" t="inlineStr"/>
       <c r="KT3" s="2" t="inlineStr"/>
-      <c r="KU3" s="2" t="inlineStr"/>
+      <c r="KU3" s="1" t="inlineStr"/>
       <c r="KV3" s="2" t="inlineStr"/>
-      <c r="KW3" s="2" t="inlineStr"/>
+      <c r="KW3" s="1" t="inlineStr"/>
       <c r="KX3" s="2" t="inlineStr"/>
-      <c r="KY3" s="2" t="inlineStr"/>
+      <c r="KY3" s="1" t="inlineStr"/>
       <c r="KZ3" s="2" t="inlineStr"/>
-      <c r="LA3" s="2" t="inlineStr"/>
+      <c r="LA3" s="1" t="inlineStr"/>
       <c r="LB3" s="2" t="inlineStr"/>
-      <c r="LC3" s="2" t="inlineStr"/>
+      <c r="LC3" s="1" t="inlineStr"/>
       <c r="LD3" s="2" t="inlineStr"/>
-      <c r="LE3" s="2" t="inlineStr"/>
+      <c r="LE3" s="1" t="inlineStr"/>
       <c r="LF3" s="2" t="inlineStr"/>
-      <c r="LG3" s="2" t="inlineStr"/>
+      <c r="LG3" s="1" t="inlineStr"/>
       <c r="LH3" s="2" t="inlineStr"/>
-      <c r="LI3" s="2" t="inlineStr"/>
+      <c r="LI3" s="1" t="inlineStr"/>
       <c r="LJ3" s="2" t="inlineStr"/>
-      <c r="LK3" s="2" t="inlineStr"/>
+      <c r="LK3" s="1" t="inlineStr"/>
       <c r="LL3" s="2" t="inlineStr"/>
-      <c r="LM3" s="2" t="inlineStr"/>
+      <c r="LM3" s="1" t="inlineStr"/>
       <c r="LN3" s="2" t="inlineStr"/>
-      <c r="LO3" s="2" t="inlineStr"/>
+      <c r="LO3" s="1" t="inlineStr"/>
       <c r="LP3" s="2" t="inlineStr"/>
-      <c r="LQ3" s="2" t="inlineStr"/>
+      <c r="LQ3" s="1" t="inlineStr"/>
       <c r="LR3" s="2" t="inlineStr"/>
-      <c r="LS3" s="2" t="inlineStr"/>
+      <c r="LS3" s="1" t="inlineStr"/>
       <c r="LT3" s="2" t="inlineStr"/>
-      <c r="LU3" s="2" t="inlineStr"/>
+      <c r="LU3" s="1" t="inlineStr"/>
       <c r="LV3" s="2" t="inlineStr"/>
-      <c r="LW3" s="2" t="inlineStr"/>
+      <c r="LW3" s="1" t="inlineStr"/>
       <c r="LX3" s="2" t="inlineStr"/>
-      <c r="LY3" s="2" t="inlineStr"/>
+      <c r="LY3" s="1" t="inlineStr"/>
       <c r="LZ3" s="2" t="inlineStr"/>
-      <c r="MA3" s="2" t="inlineStr"/>
+      <c r="MA3" s="1" t="inlineStr"/>
       <c r="MB3" s="2" t="inlineStr"/>
-      <c r="MC3" s="2" t="inlineStr"/>
+      <c r="MC3" s="1" t="inlineStr"/>
       <c r="MD3" s="2" t="inlineStr"/>
-      <c r="ME3" s="2" t="inlineStr"/>
+      <c r="ME3" s="1" t="inlineStr"/>
       <c r="MF3" s="2" t="inlineStr"/>
-      <c r="MG3" s="2" t="inlineStr"/>
+      <c r="MG3" s="1" t="inlineStr"/>
       <c r="MH3" s="2" t="inlineStr"/>
-      <c r="MI3" s="2" t="inlineStr"/>
+      <c r="MI3" s="1" t="inlineStr"/>
       <c r="MJ3" s="2" t="inlineStr"/>
-      <c r="MK3" s="2" t="inlineStr"/>
+      <c r="MK3" s="1" t="inlineStr"/>
       <c r="ML3" s="2" t="inlineStr"/>
-      <c r="MM3" s="2" t="inlineStr"/>
+      <c r="MM3" s="1" t="inlineStr"/>
       <c r="MN3" s="2" t="inlineStr"/>
-      <c r="MO3" s="2" t="inlineStr"/>
+      <c r="MO3" s="1" t="inlineStr"/>
       <c r="MP3" s="2" t="inlineStr"/>
-      <c r="MQ3" s="2" t="inlineStr"/>
+      <c r="MQ3" s="1" t="inlineStr"/>
       <c r="MR3" s="2" t="inlineStr"/>
-      <c r="MS3" s="2" t="inlineStr"/>
+      <c r="MS3" s="1" t="inlineStr"/>
       <c r="MT3" s="2" t="inlineStr"/>
-      <c r="MU3" s="2" t="inlineStr"/>
+      <c r="MU3" s="1" t="inlineStr"/>
       <c r="MV3" s="2" t="inlineStr"/>
-      <c r="MW3" s="2" t="inlineStr"/>
+      <c r="MW3" s="1" t="inlineStr"/>
       <c r="MX3" s="2" t="inlineStr"/>
-      <c r="MY3" s="2" t="inlineStr"/>
+      <c r="MY3" s="1" t="inlineStr"/>
       <c r="MZ3" s="2" t="inlineStr"/>
-      <c r="NA3" s="2" t="inlineStr"/>
+      <c r="NA3" s="1" t="inlineStr"/>
       <c r="NB3" s="2" t="inlineStr"/>
-      <c r="NC3" s="2" t="inlineStr"/>
+      <c r="NC3" s="1" t="inlineStr"/>
       <c r="ND3" s="2" t="inlineStr"/>
-      <c r="NE3" s="2" t="inlineStr"/>
+      <c r="NE3" s="1" t="inlineStr"/>
       <c r="NF3" s="2" t="inlineStr"/>
-      <c r="NG3" s="2" t="inlineStr"/>
+      <c r="NG3" s="1" t="inlineStr"/>
       <c r="NH3" s="2" t="inlineStr"/>
-      <c r="NI3" s="2" t="inlineStr"/>
+      <c r="NI3" s="1" t="inlineStr"/>
       <c r="NJ3" s="2" t="inlineStr"/>
-      <c r="NK3" s="2" t="inlineStr"/>
+      <c r="NK3" s="1" t="inlineStr"/>
       <c r="NL3" s="2" t="inlineStr"/>
-      <c r="NM3" s="2" t="inlineStr"/>
+      <c r="NM3" s="1" t="inlineStr"/>
       <c r="NN3" s="2" t="inlineStr"/>
-      <c r="NO3" s="2" t="inlineStr"/>
+      <c r="NO3" s="1" t="inlineStr"/>
       <c r="NP3" s="2" t="inlineStr"/>
-      <c r="NQ3" s="2" t="inlineStr"/>
+      <c r="NQ3" s="1" t="inlineStr"/>
       <c r="NR3" s="2" t="inlineStr"/>
-      <c r="NS3" s="2" t="inlineStr"/>
+      <c r="NS3" s="1" t="inlineStr"/>
       <c r="NT3" s="2" t="inlineStr"/>
-      <c r="NU3" s="2" t="inlineStr"/>
+      <c r="NU3" s="1" t="inlineStr"/>
       <c r="NV3" s="2" t="inlineStr"/>
-      <c r="NW3" s="2" t="inlineStr"/>
+      <c r="NW3" s="1" t="inlineStr"/>
       <c r="NX3" s="2" t="inlineStr"/>
-      <c r="NY3" s="2" t="inlineStr"/>
+      <c r="NY3" s="1" t="inlineStr"/>
       <c r="NZ3" s="2" t="inlineStr"/>
-      <c r="OA3" s="2" t="inlineStr"/>
+      <c r="OA3" s="1" t="inlineStr"/>
       <c r="OB3" s="2" t="inlineStr"/>
-      <c r="OC3" s="2" t="inlineStr"/>
+      <c r="OC3" s="1" t="inlineStr"/>
       <c r="OD3" s="2" t="inlineStr"/>
-      <c r="OE3" s="2" t="inlineStr"/>
+      <c r="OE3" s="1" t="inlineStr"/>
       <c r="OF3" s="2" t="inlineStr"/>
-      <c r="OG3" s="2" t="inlineStr"/>
+      <c r="OG3" s="1" t="inlineStr"/>
       <c r="OH3" s="2" t="inlineStr"/>
-      <c r="OI3" s="2" t="inlineStr"/>
+      <c r="OI3" s="1" t="inlineStr"/>
       <c r="OJ3" s="2" t="inlineStr"/>
-      <c r="OK3" s="2" t="inlineStr"/>
+      <c r="OK3" s="1" t="inlineStr"/>
       <c r="OL3" s="2" t="inlineStr"/>
-      <c r="OM3" s="2" t="inlineStr"/>
+      <c r="OM3" s="1" t="inlineStr"/>
       <c r="ON3" s="2" t="inlineStr"/>
-      <c r="OO3" s="2" t="inlineStr"/>
+      <c r="OO3" s="1" t="inlineStr"/>
       <c r="OP3" s="2" t="inlineStr"/>
-      <c r="OQ3" s="2" t="inlineStr"/>
+      <c r="OQ3" s="1" t="inlineStr"/>
       <c r="OR3" s="2" t="inlineStr"/>
-      <c r="OS3" s="2" t="inlineStr"/>
+      <c r="OS3" s="1" t="inlineStr"/>
       <c r="OT3" s="2" t="inlineStr"/>
-      <c r="OU3" s="2" t="inlineStr"/>
+      <c r="OU3" s="1" t="inlineStr"/>
       <c r="OV3" s="2" t="inlineStr"/>
-      <c r="OW3" s="2" t="inlineStr"/>
+      <c r="OW3" s="1" t="inlineStr"/>
       <c r="OX3" s="2" t="inlineStr"/>
-      <c r="OY3" s="2" t="inlineStr"/>
+      <c r="OY3" s="1" t="inlineStr"/>
       <c r="OZ3" s="2" t="inlineStr"/>
-      <c r="PA3" s="2" t="inlineStr"/>
+      <c r="PA3" s="1" t="inlineStr"/>
       <c r="PB3" s="2" t="inlineStr"/>
-      <c r="PC3" s="2" t="inlineStr"/>
+      <c r="PC3" s="1" t="inlineStr"/>
       <c r="PD3" s="2" t="inlineStr"/>
-      <c r="PE3" s="2" t="inlineStr"/>
+      <c r="PE3" s="1" t="inlineStr"/>
       <c r="PF3" s="2" t="inlineStr"/>
-      <c r="PG3" s="2" t="inlineStr"/>
+      <c r="PG3" s="1" t="inlineStr"/>
       <c r="PH3" s="2" t="inlineStr"/>
-      <c r="PI3" s="2" t="inlineStr"/>
+      <c r="PI3" s="1" t="inlineStr"/>
       <c r="PJ3" s="2" t="inlineStr"/>
-      <c r="PK3" s="2" t="inlineStr"/>
+      <c r="PK3" s="1" t="inlineStr"/>
       <c r="PL3" s="2" t="inlineStr"/>
-      <c r="PM3" s="2" t="inlineStr"/>
+      <c r="PM3" s="1" t="inlineStr"/>
       <c r="PN3" s="2" t="inlineStr"/>
-      <c r="PO3" s="2" t="inlineStr"/>
+      <c r="PO3" s="1" t="inlineStr"/>
       <c r="PP3" s="2" t="inlineStr"/>
-      <c r="PQ3" s="2" t="inlineStr"/>
+      <c r="PQ3" s="1" t="inlineStr"/>
       <c r="PR3" s="2" t="inlineStr"/>
-      <c r="PS3" s="2" t="inlineStr"/>
+      <c r="PS3" s="1" t="inlineStr"/>
       <c r="PT3" s="2" t="inlineStr"/>
-      <c r="PU3" s="2" t="inlineStr"/>
+      <c r="PU3" s="1" t="inlineStr"/>
       <c r="PV3" s="2" t="inlineStr"/>
-      <c r="PW3" s="2" t="inlineStr"/>
+      <c r="PW3" s="1" t="inlineStr"/>
       <c r="PX3" s="2" t="inlineStr"/>
-      <c r="PY3" s="2" t="inlineStr"/>
+      <c r="PY3" s="1" t="inlineStr"/>
       <c r="PZ3" s="2" t="inlineStr"/>
-      <c r="QA3" s="2" t="inlineStr"/>
+      <c r="QA3" s="1" t="inlineStr"/>
       <c r="QB3" s="2" t="inlineStr"/>
-      <c r="QC3" s="2" t="inlineStr"/>
+      <c r="QC3" s="1" t="inlineStr"/>
       <c r="QD3" s="2" t="inlineStr"/>
-      <c r="QE3" s="2" t="inlineStr"/>
+      <c r="QE3" s="1" t="inlineStr"/>
       <c r="QF3" s="2" t="inlineStr"/>
-      <c r="QG3" s="2" t="inlineStr"/>
+      <c r="QG3" s="1" t="inlineStr"/>
       <c r="QH3" s="2" t="inlineStr"/>
-      <c r="QI3" s="2" t="inlineStr"/>
+      <c r="QI3" s="1" t="inlineStr"/>
       <c r="QJ3" s="2" t="inlineStr"/>
-      <c r="QK3" s="2" t="inlineStr"/>
+      <c r="QK3" s="1" t="inlineStr"/>
       <c r="QL3" s="2" t="inlineStr"/>
-      <c r="QM3" s="2" t="inlineStr"/>
+      <c r="QM3" s="1" t="inlineStr"/>
       <c r="QN3" s="2" t="inlineStr"/>
-      <c r="QO3" s="2" t="inlineStr"/>
+      <c r="QO3" s="1" t="inlineStr"/>
       <c r="QP3" s="2" t="inlineStr"/>
-      <c r="QQ3" s="2" t="inlineStr"/>
+      <c r="QQ3" s="1" t="inlineStr"/>
       <c r="QR3" s="2" t="inlineStr"/>
-      <c r="QS3" s="2" t="inlineStr"/>
+      <c r="QS3" s="1" t="inlineStr"/>
       <c r="QT3" s="2" t="inlineStr"/>
-      <c r="QU3" s="2" t="inlineStr"/>
+      <c r="QU3" s="1" t="inlineStr"/>
       <c r="QV3" s="2" t="inlineStr"/>
-      <c r="QW3" s="2" t="inlineStr"/>
+      <c r="QW3" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pink_sheet.xlsx
+++ b/data/pink_sheet.xlsx
@@ -48,7 +48,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -56,16 +56,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
